--- a/p/ds_25/apache-spark/topic-list_ap-spk.xlsx
+++ b/p/ds_25/apache-spark/topic-list_ap-spk.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="16910" windowHeight="16880" tabRatio="698" activeTab="3"/>
+    <workbookView windowWidth="14020" windowHeight="16300" tabRatio="698" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="what" sheetId="21" r:id="rId1"/>
@@ -12,7 +12,7 @@
     <sheet name="features" sheetId="23" r:id="rId3"/>
     <sheet name="features2" sheetId="25" r:id="rId4"/>
     <sheet name="core" sheetId="2" r:id="rId5"/>
-    <sheet name="intermed" sheetId="5" r:id="rId6"/>
+    <sheet name="architect" sheetId="5" r:id="rId6"/>
     <sheet name="ques" sheetId="6" r:id="rId7"/>
     <sheet name="-" sheetId="8" r:id="rId8"/>
   </sheets>
@@ -34,12 +34,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="291">
-  <si>
-    <t>Apache Spark ?</t>
-  </si>
-  <si>
-    <r>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="343">
+  <si>
+    <t>Apache Spark ? vs Hadoop not pandas</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF4183C4"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>Apache Spark</t>
     </r>
     <r>
@@ -119,6 +125,57 @@
     <t>https://www.tutorialspoint.com/apache_spark/apache_spark_rdd.htm</t>
   </si>
   <si>
+    <t>What does it mean that DataFrames are immutable?</t>
+  </si>
+  <si>
+    <r>
+      <t>DataFrames are a collection of transformations and actions that are defined against one or more data sources, but ultimately Apache Spark resolves queries back to the original data sources, so the data itself is not changed, and no DataFrames are changed. In other words, DataFrames are </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF161616"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>immutable</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF161616"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>. Because of this, after performing transformations, a new DataFrame is returned that has to be saved to a variable in order to access it in subsequent operations. If you want to evaluate an intermediate step of your transformation, call an action.</t>
+    </r>
+  </si>
+  <si>
+    <t>Key steps in job's creation and execution, including:</t>
+  </si>
+  <si>
+    <t>Logical plan generation</t>
+  </si>
+  <si>
+    <t>Physical plan generation</t>
+  </si>
+  <si>
+    <t>Job submission and scheduling</t>
+  </si>
+  <si>
+    <t>Task's creation, execution and result handling</t>
+  </si>
+  <si>
+    <t>How shuffle is done in Spark</t>
+  </si>
+  <si>
+    <t>Cache mechanism</t>
+  </si>
+  <si>
+    <t>Broadcast mechanism</t>
+  </si>
+  <si>
     <t>Data Sources in Spark</t>
   </si>
   <si>
@@ -126,25 +183,31 @@
   </si>
   <si>
     <r>
-      <t>At a high level, any Spark application creates </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
+      <rPr>
         <sz val="12"/>
         <color rgb="FF333333"/>
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t>RDDs</t>
-    </r>
-    <r>
-      <rPr>
+      <t>At a high level, any Spark application creates </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
         <sz val="12"/>
         <color rgb="FF333333"/>
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
+      <t>RDDs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t> out of some input, run </t>
     </r>
     <r>
@@ -192,6 +255,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">The execution of the Spark program is performed using an Interactive Client (e.g. Scala Shell or PySpark), or by submitting a job via the </t>
     </r>
     <r>
@@ -362,367 +431,818 @@
     <t>It provides an abstracted layer of ‘DataSet API,’ with smarter big data computation efficiency, which is superior to that of Resilient Distributed Datasets or PySpark RDDs, and eases the structured data manipulation process.</t>
   </si>
   <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/pyspark/#dataframes</t>
+  </si>
+  <si>
+    <t>DataFrames are the primary objects in Apache Spark. A DataFrame is a dataset organized into named columns. You can think of a DataFrame like a spreadsheet or a SQL table, a two-dimensional labeled data structure of a series of records (similar to rows in a table) and columns of different types. DataFrames provide a rich set of functions (for example, select columns, filter, join, and aggregate) that allow you to perform common data manipulation and analysis tasks efficiently.</t>
+  </si>
+  <si>
+    <t>Some important DataFrame elements include:</t>
+  </si>
+  <si>
+    <t>Schema: A schema defines the column names and types of a DataFrame. Data formats have different semantics for schema definition and enforcement. Some data sources provide schema information, while others either rely on manual schema definition or allow schema inference. Users can define schemas manually or schemas can be read from a data source.</t>
+  </si>
+  <si>
+    <r>
+      <t>Rows</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF161616"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t>: Spark represents records in a DataFrame as</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF161616"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.2"/>
+        <color rgb="FF161616"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Row</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF161616"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF161616"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t>objects. While underlying data formats such as Delta Lake use columns to store data, for optimization Spark caches and shuffles data using rows.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Columns</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF161616"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t>: Columns in Spark are similar to columns in a spreadsheet and can represent a simple type such as a string or integer, but also complex types like array, map, or null. You can write queries that select, manipulate, or remove columns from a data source. Possible data sources include tables, views, files, or other DataFrames. Columns are never removed from a dataset or a DataFrame, they are just omitted from results through</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF161616"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.2"/>
+        <color rgb="FF161616"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>.drop</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF161616"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF161616"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t>transformations or omission in</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF161616"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.2"/>
+        <color rgb="FF161616"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>select</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF161616"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF161616"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t>statements.</t>
+    </r>
+  </si>
+  <si>
     <t>Spark Catalyst</t>
   </si>
   <si>
     <t>Optimizes and executes Spark SQL queries efficiently, enhancing performance and scalability.</t>
   </si>
   <si>
-    <t>Apache Spark</t>
+    <t>Data Processing and ETL</t>
+  </si>
+  <si>
+    <t>Data processing and ETL (extract, transform, load) are critical components in data engineering workflows. Organizations need to extract data from various sources, transform it into a suitable format, and load it into a data warehouse or data lake for analysis.</t>
+  </si>
+  <si>
+    <t>How Spark can help:</t>
+  </si>
+  <si>
+    <t>Spark’s ability to handle large-scale data processing makes it ideal for ETL tasks. Its in-memory computation significantly speeds up the transformation processes, while its integration with various data sources simplifies data extraction and loading.</t>
+  </si>
+  <si>
+    <t>from pyspark.sql import SparkSession</t>
+  </si>
+  <si>
+    <t>spark = SparkSession.builder \</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    .appName('demo_app') \</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    .config("spark.hadoop.fs.s3.access.key", "XXXXXXXX") \</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    .config("spark.hadoop.fs.s3.secret.key", "XXXXXXXX") \</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    .config("spark.hadoop.com.amazonaws.services.s3.enableV4", "true") \</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    .config('spark.hadoop.fs.s3a.aws.credentials.provider', 'org.apache.hadoop.fs.s3a.SimpleAWSCredentialsProvider') \</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    .config("spark.hadoop.fs.s3.endpoint", "XXXXXXXXXXXXXXX") \</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    .config("spark.hadoop.fs.s3a.connection.establish.timeout","45000") \</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    .getOrCreate()</t>
+  </si>
+  <si>
+    <t># Extract data from a CSV file</t>
+  </si>
+  <si>
+    <t>df = spark.read.csv("s3://bucket-name/data.csv", header=True, inferSchema=True)</t>
+  </si>
+  <si>
+    <t># Transform data by filtering and selecting relevant columns</t>
+  </si>
+  <si>
+    <t>df_transformed = df.filter(df['age'] &gt; 18).select("name", "age", "email")</t>
+  </si>
+  <si>
+    <t># Load data into a database</t>
+  </si>
+  <si>
+    <t>df_transformed.write.format("jdbc").option("url", "jdbc:postgresql://&lt;HOST&gt;:&lt;PORT&gt;/&lt;DB_NAME&gt;?user=&lt;DB_USER&gt;&amp;password=&lt;DB_PASSWORD&gt;"").option("dbtable", "adult_users").save()</t>
+  </si>
+  <si>
+    <t>Stream Processing</t>
+  </si>
+  <si>
+    <t>Real-time data streams need to be processed on-the-fly for applications like live analytics, monitoring, and alerting systems.</t>
+  </si>
+  <si>
+    <t>Spark Streaming allows you to process live data streams, dividing the data into batches and processing them using Spark’s APIs.</t>
+  </si>
+  <si>
+    <t>from pyspark.streaming import StreamingContext</t>
+  </si>
+  <si>
+    <t># Create a Spark session</t>
+  </si>
+  <si>
+    <t>.appName("SocketTextStream") \</t>
+  </si>
+  <si>
+    <t>.getOrCreate()</t>
+  </si>
+  <si>
+    <t># Create a StreamingContext with a batch interval of 10 seconds</t>
+  </si>
+  <si>
+    <t>ssc = StreamingContext(spark.sparkContext, 10)</t>
+  </si>
+  <si>
+    <t># Create a DStream that will connect to hostname:port, e.g., localhost:9999</t>
+  </si>
+  <si>
+    <t>lines = ssc.socketTextStream("localhost", 9999)</t>
+  </si>
+  <si>
+    <t># Process the lines DStream by splitting the lines into words</t>
+  </si>
+  <si>
+    <t>words = lines.flatMap(lambda line: line.split(" "))</t>
+  </si>
+  <si>
+    <t># Map each word to a tuple (word, 1)</t>
+  </si>
+  <si>
+    <t>pairs = words.map(lambda word: (word, 1))</t>
+  </si>
+  <si>
+    <t># Reduce by key (word) to count the number of occurrences</t>
+  </si>
+  <si>
+    <t>word_counts = pairs.reduceByKey(lambda x, y: x + y)</t>
+  </si>
+  <si>
+    <t># Print the resulting word counts</t>
+  </si>
+  <si>
+    <t>word_counts.pprint()</t>
+  </si>
+  <si>
+    <t># Start the streaming computation</t>
+  </si>
+  <si>
+    <t>ssc.start()</t>
+  </si>
+  <si>
+    <t># Wait for the streaming to finish</t>
+  </si>
+  <si>
+    <t>ssc.awaitTermination()</t>
+  </si>
+  <si>
+    <t>Machine Learning and AI</t>
+  </si>
+  <si>
+    <t>Machine learning and AI applications often require processing large datasets to train and evaluate models.</t>
+  </si>
+  <si>
+    <t>Spark’s MLlib library provides scalable machine learning algorithms that can be easily integrated into your data pipeline. It supports various algorithms for classification, regression, clustering, and collaborative filtering.</t>
+  </si>
+  <si>
+    <t>from pyspark.ml.classification import LogisticRegression</t>
+  </si>
+  <si>
+    <t>from pyspark.ml.feature import VectorAssembler</t>
+  </si>
+  <si>
+    <t># Load data</t>
+  </si>
+  <si>
+    <t>data = spark.read.csv("s3://bucket-name/data.csv", header=True, inferSchema=True)</t>
+  </si>
+  <si>
+    <t># Feature engineering</t>
+  </si>
+  <si>
+    <t>assembler = VectorAssembler(inputCols=["feature1", "feature2"], outputCol="features")</t>
+  </si>
+  <si>
+    <t>data = assembler.transform(data)</t>
+  </si>
+  <si>
+    <t># Train a logistic regression model</t>
+  </si>
+  <si>
+    <t>lr = LogisticRegression(featuresCol='features', labelCol='label')</t>
+  </si>
+  <si>
+    <t>model = lr.fit(data)</t>
+  </si>
+  <si>
+    <t># Predict</t>
+  </si>
+  <si>
+    <t>predictions = model.transform(data)</t>
+  </si>
+  <si>
+    <t>predictions.select("features", "label", "prediction").show()</t>
+  </si>
+  <si>
+    <t>Data Analytics</t>
+  </si>
+  <si>
+    <t>Enterprises need to analyze large datasets to derive business insights and make data-driven decisions.</t>
+  </si>
+  <si>
+    <t>Spark SQL provides an interface for structured data processing using SQL queries, making it easy to perform data analytics.</t>
+  </si>
+  <si>
+    <t># Load data into a DataFrame</t>
+  </si>
+  <si>
+    <t>df = spark.read.json("s3://bucket-name/data.json")</t>
+  </si>
+  <si>
+    <t># Register the DataFrame as a SQL temporary view</t>
+  </si>
+  <si>
+    <t>df.createOrReplaceTempView("data_table")</t>
+  </si>
+  <si>
+    <t># Perform SQL query</t>
+  </si>
+  <si>
+    <t>result = spark.sql("SELECT category, COUNT(*) as count FROM data_table GROUP BY category")</t>
+  </si>
+  <si>
+    <t># Show results</t>
+  </si>
+  <si>
+    <t>result.show()</t>
+  </si>
+  <si>
+    <t>Log Processing</t>
+  </si>
+  <si>
+    <t>Analyzing logs is essential for monitoring, troubleshooting, and improving system performance.</t>
+  </si>
+  <si>
+    <t>Spark’s ability to process large volumes of data quickly makes it suitable for log processing tasks.</t>
+  </si>
+  <si>
+    <t># Load log data</t>
+  </si>
+  <si>
+    <t>logs = spark.read.text("s3://bucket-name/logs/*.log")</t>
+  </si>
+  <si>
+    <t># Process logs to extract useful information</t>
+  </si>
+  <si>
+    <t>error_logs = logs.filter(logs.value.contains("ERROR"))</t>
+  </si>
+  <si>
+    <t># Show the results</t>
+  </si>
+  <si>
+    <t>error_counts = error_logs.count()</t>
+  </si>
+  <si>
+    <t>print( f"Count Errors: {error_counts}")</t>
+  </si>
+  <si>
+    <t>Fog Computing</t>
+  </si>
+  <si>
+    <t>Fog computing involves processing data closer to where it is generated, reducing latency and bandwidth usage.</t>
+  </si>
+  <si>
+    <t>Spark’s architecture allows it to be deployed in a fog computing environment, processing data locally before sending aggregated results to a central server.</t>
+  </si>
+  <si>
+    <t># Simulate local data processing on edge devices</t>
+  </si>
+  <si>
+    <t>local_data = spark.read.json("file:///path/to/local/data.json")</t>
+  </si>
+  <si>
+    <t># Perform local aggregations</t>
+  </si>
+  <si>
+    <t>local_aggregates = local_data.groupBy("sensor_id").agg({"value": "avg"})</t>
+  </si>
+  <si>
+    <t># Send aggregated results to the central server</t>
+  </si>
+  <si>
+    <t>local_aggregates.write.format("jdbc").option("url", "jdbc:mysql://central-server/db").option("dbtable", "aggregates").save()</t>
+  </si>
+  <si>
+    <t>Recommendation Systems</t>
+  </si>
+  <si>
+    <t>Recommendation systems are widely used in e-commerce and content platforms to provide personalized recommendations to users.</t>
+  </si>
+  <si>
+    <t>Spark’s MLlib includes collaborative filtering algorithms, such as ALS (alternating least squares), which can be used to build recommendation systems.</t>
+  </si>
+  <si>
+    <t>from pyspark.ml.recommendation import ALS</t>
+  </si>
+  <si>
+    <t># Load user-item ratings data</t>
+  </si>
+  <si>
+    <t>ratings = spark.read.csv("s3://bucket-name/ratings.csv", header=True, inferSchema=True)</t>
+  </si>
+  <si>
+    <t># Build the recommendation model using ALS</t>
+  </si>
+  <si>
+    <t>als = ALS(userCol="userId", itemCol="movieId", ratingCol="rating")</t>
+  </si>
+  <si>
+    <t>model = als.fit(ratings)</t>
+  </si>
+  <si>
+    <t># Generate top 10 movie recommendations for each user</t>
+  </si>
+  <si>
+    <t>user_recommendations = model.recommendForAllUsers(10)</t>
+  </si>
+  <si>
+    <t># Show recommendations</t>
+  </si>
+  <si>
+    <t>user_recommendations.show()</t>
+  </si>
+  <si>
+    <t>Real-time Advertising</t>
+  </si>
+  <si>
+    <t>Real-time advertising requires processing user interactions in real-time to serve personalized ads.</t>
+  </si>
+  <si>
+    <t>Spark Streaming can process user interaction data in real-time, enabling dynamic ad placement based on user behavior.</t>
+  </si>
+  <si>
+    <t># Function to simulate getting ads based on user profiles</t>
+  </si>
+  <si>
+    <t>def get_ad_for_user(user_profile):</t>
+  </si>
+  <si>
+    <t># Placeholder logic for selecting an ad based on the user profile</t>
+  </si>
+  <si>
+    <t>return f"Ad_for_user_{user_profile['user_id']}"</t>
+  </si>
+  <si>
+    <t># Simulate real-time data stream for user interactions</t>
+  </si>
+  <si>
+    <t>interactions = ssc.socketTextStream("localhost", 9999)</t>
+  </si>
+  <si>
+    <t># Process interactions to update user profiles</t>
+  </si>
+  <si>
+    <t>user_profiles = interactions.map(lambda interaction: (interaction.user_id, interaction))</t>
+  </si>
+  <si>
+    <t># Serve ads based on updated profiles</t>
+  </si>
+  <si>
+    <t>ads = user_profiles.map(lambda profile: (profile[0], get_ad_for_user(profile[1])))</t>
+  </si>
+  <si>
+    <t># Print the ads served</t>
+  </si>
+  <si>
+    <t>ads.pprint()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apache Spark
+</t>
   </si>
   <si>
     <t>Top used features</t>
   </si>
   <si>
-    <t>Data Processing and ETL</t>
-  </si>
-  <si>
-    <t>Data processing and ETL (extract, transform, load) are critical components in data engineering workflows. Organizations need to extract data from various sources, transform it into a suitable format, and load it into a data warehouse or data lake for analysis.</t>
-  </si>
-  <si>
-    <t>How Spark can help:</t>
-  </si>
-  <si>
-    <t>Spark’s ability to handle large-scale data processing makes it ideal for ETL tasks. Its in-memory computation significantly speeds up the transformation processes, while its integration with various data sources simplifies data extraction and loading.</t>
-  </si>
-  <si>
-    <t>from pyspark.sql import SparkSession</t>
-  </si>
-  <si>
-    <t>spark = SparkSession.builder \</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    .appName('demo_app') \</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    .config("spark.hadoop.fs.s3.access.key", "XXXXXXXX") \</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    .config("spark.hadoop.fs.s3.secret.key", "XXXXXXXX") \</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    .config("spark.hadoop.com.amazonaws.services.s3.enableV4", "true") \</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    .config('spark.hadoop.fs.s3a.aws.credentials.provider', 'org.apache.hadoop.fs.s3a.SimpleAWSCredentialsProvider') \</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    .config("spark.hadoop.fs.s3.endpoint", "XXXXXXXXXXXXXXX") \</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    .config("spark.hadoop.fs.s3a.connection.establish.timeout","45000") \</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    .getOrCreate()</t>
-  </si>
-  <si>
-    <t># Extract data from a CSV file</t>
-  </si>
-  <si>
-    <t>df = spark.read.csv("s3://bucket-name/data.csv", header=True, inferSchema=True)</t>
-  </si>
-  <si>
-    <t># Transform data by filtering and selecting relevant columns</t>
-  </si>
-  <si>
-    <t>df_transformed = df.filter(df['age'] &gt; 18).select("name", "age", "email")</t>
-  </si>
-  <si>
-    <t># Load data into a database</t>
-  </si>
-  <si>
-    <t>df_transformed.write.format("jdbc").option("url", "jdbc:postgresql://&lt;HOST&gt;:&lt;PORT&gt;/&lt;DB_NAME&gt;?user=&lt;DB_USER&gt;&amp;password=&lt;DB_PASSWORD&gt;"").option("dbtable", "adult_users").save()</t>
-  </si>
-  <si>
-    <t>Stream Processing</t>
-  </si>
-  <si>
-    <t>Real-time data streams need to be processed on-the-fly for applications like live analytics, monitoring, and alerting systems.</t>
-  </si>
-  <si>
-    <t>Spark Streaming allows you to process live data streams, dividing the data into batches and processing them using Spark’s APIs.</t>
-  </si>
-  <si>
-    <t>from pyspark.streaming import StreamingContext</t>
-  </si>
-  <si>
-    <t># Create a Spark session</t>
-  </si>
-  <si>
-    <t>.appName("SocketTextStream") \</t>
-  </si>
-  <si>
-    <t>.getOrCreate()</t>
-  </si>
-  <si>
-    <t># Create a StreamingContext with a batch interval of 10 seconds</t>
-  </si>
-  <si>
-    <t>ssc = StreamingContext(spark.sparkContext, 10)</t>
-  </si>
-  <si>
-    <t># Create a DStream that will connect to hostname:port, e.g., localhost:9999</t>
-  </si>
-  <si>
-    <t>lines = ssc.socketTextStream("localhost", 9999)</t>
-  </si>
-  <si>
-    <t># Process the lines DStream by splitting the lines into words</t>
-  </si>
-  <si>
-    <t>words = lines.flatMap(lambda line: line.split(" "))</t>
-  </si>
-  <si>
-    <t># Map each word to a tuple (word, 1)</t>
-  </si>
-  <si>
-    <t>pairs = words.map(lambda word: (word, 1))</t>
-  </si>
-  <si>
-    <t># Reduce by key (word) to count the number of occurrences</t>
-  </si>
-  <si>
-    <t>word_counts = pairs.reduceByKey(lambda x, y: x + y)</t>
-  </si>
-  <si>
-    <t># Print the resulting word counts</t>
-  </si>
-  <si>
-    <t>word_counts.pprint()</t>
-  </si>
-  <si>
-    <t># Start the streaming computation</t>
-  </si>
-  <si>
-    <t>ssc.start()</t>
-  </si>
-  <si>
-    <t># Wait for the streaming to finish</t>
-  </si>
-  <si>
-    <t>ssc.awaitTermination()</t>
-  </si>
-  <si>
-    <t>Machine Learning and AI</t>
-  </si>
-  <si>
-    <t>Machine learning and AI applications often require processing large datasets to train and evaluate models.</t>
-  </si>
-  <si>
-    <t>Spark’s MLlib library provides scalable machine learning algorithms that can be easily integrated into your data pipeline. It supports various algorithms for classification, regression, clustering, and collaborative filtering.</t>
-  </si>
-  <si>
-    <t>from pyspark.ml.classification import LogisticRegression</t>
-  </si>
-  <si>
-    <t>from pyspark.ml.feature import VectorAssembler</t>
-  </si>
-  <si>
-    <t># Load data</t>
-  </si>
-  <si>
-    <t>data = spark.read.csv("s3://bucket-name/data.csv", header=True, inferSchema=True)</t>
-  </si>
-  <si>
-    <t># Feature engineering</t>
-  </si>
-  <si>
-    <t>assembler = VectorAssembler(inputCols=["feature1", "feature2"], outputCol="features")</t>
-  </si>
-  <si>
-    <t>data = assembler.transform(data)</t>
-  </si>
-  <si>
-    <t># Train a logistic regression model</t>
-  </si>
-  <si>
-    <t>lr = LogisticRegression(featuresCol='features', labelCol='label')</t>
-  </si>
-  <si>
-    <t>model = lr.fit(data)</t>
-  </si>
-  <si>
-    <t># Predict</t>
-  </si>
-  <si>
-    <t>predictions = model.transform(data)</t>
-  </si>
-  <si>
-    <t>predictions.select("features", "label", "prediction").show()</t>
-  </si>
-  <si>
-    <t>Data Analytics</t>
-  </si>
-  <si>
-    <t>Enterprises need to analyze large datasets to derive business insights and make data-driven decisions.</t>
-  </si>
-  <si>
-    <t>Spark SQL provides an interface for structured data processing using SQL queries, making it easy to perform data analytics.</t>
-  </si>
-  <si>
-    <t># Load data into a DataFrame</t>
-  </si>
-  <si>
-    <t>df = spark.read.json("s3://bucket-name/data.json")</t>
-  </si>
-  <si>
-    <t># Register the DataFrame as a SQL temporary view</t>
-  </si>
-  <si>
-    <t>df.createOrReplaceTempView("data_table")</t>
-  </si>
-  <si>
-    <t># Perform SQL query</t>
-  </si>
-  <si>
-    <t>result = spark.sql("SELECT category, COUNT(*) as count FROM data_table GROUP BY category")</t>
-  </si>
-  <si>
-    <t># Show results</t>
-  </si>
-  <si>
-    <t>result.show()</t>
-  </si>
-  <si>
-    <t>Log Processing</t>
-  </si>
-  <si>
-    <t>Analyzing logs is essential for monitoring, troubleshooting, and improving system performance.</t>
-  </si>
-  <si>
-    <t>Spark’s ability to process large volumes of data quickly makes it suitable for log processing tasks.</t>
-  </si>
-  <si>
-    <t># Load log data</t>
-  </si>
-  <si>
-    <t>logs = spark.read.text("s3://bucket-name/logs/*.log")</t>
-  </si>
-  <si>
-    <t># Process logs to extract useful information</t>
-  </si>
-  <si>
-    <t>error_logs = logs.filter(logs.value.contains("ERROR"))</t>
-  </si>
-  <si>
-    <t># Show the results</t>
-  </si>
-  <si>
-    <t>error_counts = error_logs.count()</t>
-  </si>
-  <si>
-    <t>print( f"Count Errors: {error_counts}")</t>
-  </si>
-  <si>
-    <t>Fog Computing</t>
-  </si>
-  <si>
-    <t>Fog computing involves processing data closer to where it is generated, reducing latency and bandwidth usage.</t>
-  </si>
-  <si>
-    <t>Spark’s architecture allows it to be deployed in a fog computing environment, processing data locally before sending aggregated results to a central server.</t>
-  </si>
-  <si>
-    <t># Simulate local data processing on edge devices</t>
-  </si>
-  <si>
-    <t>local_data = spark.read.json("file:///path/to/local/data.json")</t>
-  </si>
-  <si>
-    <t># Perform local aggregations</t>
-  </si>
-  <si>
-    <t>local_aggregates = local_data.groupBy("sensor_id").agg({"value": "avg"})</t>
-  </si>
-  <si>
-    <t># Send aggregated results to the central server</t>
-  </si>
-  <si>
-    <t>local_aggregates.write.format("jdbc").option("url", "jdbc:mysql://central-server/db").option("dbtable", "aggregates").save()</t>
-  </si>
-  <si>
-    <t>Recommendation Systems</t>
-  </si>
-  <si>
-    <t>Recommendation systems are widely used in e-commerce and content platforms to provide personalized recommendations to users.</t>
-  </si>
-  <si>
-    <t>Spark’s MLlib includes collaborative filtering algorithms, such as ALS (alternating least squares), which can be used to build recommendation systems.</t>
-  </si>
-  <si>
-    <t>from pyspark.ml.recommendation import ALS</t>
-  </si>
-  <si>
-    <t># Load user-item ratings data</t>
-  </si>
-  <si>
-    <t>ratings = spark.read.csv("s3://bucket-name/ratings.csv", header=True, inferSchema=True)</t>
-  </si>
-  <si>
-    <t># Build the recommendation model using ALS</t>
-  </si>
-  <si>
-    <t>als = ALS(userCol="userId", itemCol="movieId", ratingCol="rating")</t>
-  </si>
-  <si>
-    <t>model = als.fit(ratings)</t>
-  </si>
-  <si>
-    <t># Generate top 10 movie recommendations for each user</t>
-  </si>
-  <si>
-    <t>user_recommendations = model.recommendForAllUsers(10)</t>
-  </si>
-  <si>
-    <t># Show recommendations</t>
-  </si>
-  <si>
-    <t>user_recommendations.show()</t>
-  </si>
-  <si>
-    <t>Real-time Advertising</t>
-  </si>
-  <si>
-    <t>Real-time advertising requires processing user interactions in real-time to serve personalized ads.</t>
-  </si>
-  <si>
-    <t>Spark Streaming can process user interaction data in real-time, enabling dynamic ad placement based on user behavior.</t>
-  </si>
-  <si>
-    <t># Function to simulate getting ads based on user profiles</t>
-  </si>
-  <si>
-    <t>def get_ad_for_user(user_profile):</t>
-  </si>
-  <si>
-    <t># Placeholder logic for selecting an ad based on the user profile</t>
-  </si>
-  <si>
-    <t>return f"Ad_for_user_{user_profile['user_id']}"</t>
-  </si>
-  <si>
-    <t># Simulate real-time data stream for user interactions</t>
-  </si>
-  <si>
-    <t>interactions = ssc.socketTextStream("localhost", 9999)</t>
-  </si>
-  <si>
-    <t># Process interactions to update user profiles</t>
-  </si>
-  <si>
-    <t>user_profiles = interactions.map(lambda interaction: (interaction.user_id, interaction))</t>
-  </si>
-  <si>
-    <t># Serve ads based on updated profiles</t>
-  </si>
-  <si>
-    <t>ads = user_profiles.map(lambda profile: (profile[0], get_ad_for_user(profile[1])))</t>
-  </si>
-  <si>
-    <t># Print the ads served</t>
-  </si>
-  <si>
-    <t>ads.pprint()</t>
+    <t>A</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/databricks/pyspark/#data-processing</t>
+  </si>
+  <si>
+    <t>Transformations</t>
+  </si>
+  <si>
+    <t>In Spark you express processing logic as transformations, which are instructions for loading and manipulating data using DataFrames</t>
+  </si>
+  <si>
+    <t>Reading data</t>
+  </si>
+  <si>
+    <t>Joins</t>
+  </si>
+  <si>
+    <t>Aggregations</t>
+  </si>
+  <si>
+    <t>Type casting</t>
+  </si>
+  <si>
+    <t>Lazy Evaluation</t>
+  </si>
+  <si>
+    <r>
+      <t>Spark optimizes data processing by identifying the most efficient physical plan to evaluate logic specified by transformations. However, Spark does not act on transformations until actions are called. Rather than evaluating each transformation in the exact order specified, Spark waits until an action triggers computation on all transformations. This is known as lazy evaluation, or lazy loading, which allows you to</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF161616"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF161616"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t>chain</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF161616"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF161616"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t>multiple operations because Spark handles their execution in a deferred manner, rather than immediately executing them when they are defined.</t>
+    </r>
+  </si>
+  <si>
+    <t>Actions</t>
+  </si>
+  <si>
+    <t>Actions instruct Spark to compute a result from a series of transformations on one or more DataFrames. Action operations return a value, and can be any of the following:</t>
+  </si>
+  <si>
+    <r>
+      <t>Actions to output data in the console or your editor, such as</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF161616"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.2"/>
+        <color rgb="FF161616"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>display</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF161616"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF161616"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t>or</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF161616"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.2"/>
+        <color rgb="FF161616"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>show</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Actions to collect data (returns</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF161616"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.2"/>
+        <color rgb="FF161616"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Row</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF161616"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF161616"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t>objects), such as</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF161616"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.2"/>
+        <color rgb="FF161616"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>take(n)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF161616"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t>, and</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF161616"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.2"/>
+        <color rgb="FF161616"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>first</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF161616"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF161616"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t>or</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF161616"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.2"/>
+        <color rgb="FF161616"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>head</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Actions to write to data sources, such as</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF161616"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.2"/>
+        <color rgb="FF161616"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>saveAsTable</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Aggregations that trigger a computation, such as</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF161616"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.2"/>
+        <color rgb="FF161616"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>count</t>
+    </r>
   </si>
   <si>
     <t>Spark Commands</t>
@@ -943,6 +1463,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">df </t>
     </r>
     <r>
@@ -984,6 +1510,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>df.where(</t>
     </r>
     <r>
@@ -1112,6 +1644,128 @@
   </si>
   <si>
     <t>https://docs.databricks.com/aws/en/getting-started/dataframes</t>
+  </si>
+  <si>
+    <t>Spark Internals</t>
+  </si>
+  <si>
+    <t>https://github.com/JerryLead/SparkInternals/blob/master/markdown/english/0-Introduction.md</t>
+  </si>
+  <si>
+    <t>Overview Overview of Apache Spark</t>
+  </si>
+  <si>
+    <t>There may have one or multiple ExecutorBackend processes in each Worker node, each one possesses an Executor instance. Each Executor object maintains a thread pool. Each task runs on a thread.</t>
+  </si>
+  <si>
+    <t>Each application has one driver and multiple executors. All tasks within the same executor belongs to the same application</t>
+  </si>
+  <si>
+    <t>In Standalone deployment mode, ExecutorBackend is instantiated as CoarseGrainedExecutorBackend</t>
+  </si>
+  <si>
+    <t>Worker controls the CoarseGrainedExecutorBackend by using a ExecutorRunner</t>
+  </si>
+  <si>
+    <t>Example job code:</t>
+  </si>
+  <si>
+    <t>def main(args: Array[String]) {
+    val sparkConf = new SparkConf().setAppName("GroupBy Test")
+    var numMappers = 100
+    var numKVPairs = 10000
+    var valSize = 1000
+    var numReducers = 36
+    val sc = new SparkContext(sparkConf)
+    val pairs1 = sc.parallelize(0 until numMappers, numMappers).flatMap { p =&gt;
+      val ranGen = new Random
+      var arr1 = new Array[(Int, Array[Byte])](numKVPairs)
+      for (i &lt;- 0 until numKVPairs) {
+        val byteArr = new Array[Byte](valSize)
+        ranGen.nextBytes(byteArr)
+        arr1(i) = (ranGen.nextInt(Int.MaxValue), byteArr)
+      }
+      arr1
+    }.cache
+    // Enforce that everything has been calculated and in cache
+    pairs1.count
+    println(pairs1.groupByKey(numReducers).count)
+    sc.stop()
+  }</t>
+  </si>
+  <si>
+    <t>Job logical plan Logical plan of a job (data dependency graph)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a logical plan (or data dependency graph) will be created, then a physical plan (in the form of a DAG) will be generated. After that, concrete tasks will be generated and executed. </t>
+  </si>
+  <si>
+    <r>
+      <t>A call of function</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.2"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="var(--fontStack-monospace"/>
+        <charset val="134"/>
+      </rPr>
+      <t>RDD.toDebugString</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t>will return the logical plan:</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">  MapPartitionsRDD[3] at groupByKey at GroupByTest.scala:51 (36 partitions)
+    ShuffledRDD[2] at groupByKey at GroupByTest.scala:51 (36 partitions)
+      FlatMappedRDD[1] at flatMap at GroupByTest.scala:38 (100 partitions)
+        ParallelCollectionRDD[0] at parallelize at GroupByTest.scala:38 (100 partitions)</t>
+  </si>
+  <si>
+    <t>Job physical plan Physical plan</t>
+  </si>
+  <si>
+    <t>Shuffle details Shuffle process</t>
+  </si>
+  <si>
+    <t>Architecture Coordination of system modules in job execution</t>
+  </si>
+  <si>
+    <t>Cache and Checkpoint Cache and Checkpoint</t>
+  </si>
+  <si>
+    <t>Broadcast Broadcast feature</t>
+  </si>
+  <si>
+    <t>Job Scheduling TODO</t>
+  </si>
+  <si>
+    <t>Fault-tolerance TODO</t>
   </si>
 </sst>
 </file>
@@ -1124,7 +1778,7 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
   </numFmts>
-  <fonts count="41">
+  <fonts count="48">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1151,6 +1805,25 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF1F2328"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="11"/>
       <name val="Bahnschrift"/>
       <charset val="134"/>
@@ -1170,13 +1843,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color rgb="FF333333"/>
       <name val="Calibri"/>
@@ -1184,13 +1850,43 @@
     </font>
     <font>
       <sz val="12"/>
-      <color theme="1"/>
+      <color rgb="FF161616"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FF000000"/>
+      <color rgb="FF4183C4"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF161616"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF161616"/>
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
@@ -1202,34 +1898,8 @@
       <charset val="134"/>
     </font>
     <font>
-      <i/>
       <sz val="12"/>
-      <color rgb="FF4C4C4C"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF51565E"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF4183C4"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
@@ -1385,9 +2055,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10.2"/>
+      <color rgb="FF161616"/>
+      <name val="Consolas"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
+      <i/>
       <sz val="12"/>
-      <color rgb="FF333333"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF4070A0"/>
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
@@ -1398,15 +2080,29 @@
       <charset val="134"/>
     </font>
     <font>
+      <i/>
       <sz val="12"/>
-      <color rgb="FF4070A0"/>
+      <color rgb="FF161616"/>
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
+      <sz val="10.2"/>
+      <color rgb="FF1F2328"/>
+      <name val="var(--fontStack-monospace"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <i/>
       <sz val="12"/>
+      <color rgb="FF161616"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF333333"/>
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
@@ -1744,31 +2440,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1777,119 +2461,131 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="39" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="39" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="39" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="39" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="39" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="39" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="39" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="39" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="39" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="39" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="38" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1897,108 +2593,125 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
@@ -2134,8 +2847,97 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="21062950"/>
+          <a:off x="0" y="21850350"/>
           <a:ext cx="4203700" cy="2032000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>102235</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>6551295</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>27940</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1" descr="deploy"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1" r:link="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1041400" y="1480185"/>
+          <a:ext cx="6894195" cy="5437505"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>107315</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>66040</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>6770370</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>56515</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2" descr="deploy"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId3" r:link="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="107315" y="16633190"/>
+          <a:ext cx="8047355" cy="5699125"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2432,153 +3234,200 @@
   <dimension ref="A1:A93"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="15.5"/>
   <cols>
-    <col min="1" max="1" width="93.1307692307692" style="41" customWidth="1"/>
-    <col min="2" max="2" width="4.53846153846154" style="26" customWidth="1"/>
-    <col min="3" max="3" width="4.46153846153846" style="26" customWidth="1"/>
-    <col min="4" max="4" width="30.6153846153846" style="26" customWidth="1"/>
-    <col min="5" max="16384" width="9.23076923076923" style="26"/>
+    <col min="1" max="1" width="93.1307692307692" style="48" customWidth="1"/>
+    <col min="2" max="2" width="4.53846153846154" style="8" customWidth="1"/>
+    <col min="3" max="3" width="4.46153846153846" style="8" customWidth="1"/>
+    <col min="4" max="4" width="30.6153846153846" style="8" customWidth="1"/>
+    <col min="5" max="16384" width="9.23076923076923" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="49" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="42"/>
+      <c r="A2" s="49"/>
     </row>
     <row r="3" ht="62" spans="1:1">
-      <c r="A3" s="43" t="s">
+      <c r="A3" s="50" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
-      <c r="A4" s="44"/>
-    </row>
     <row r="16" ht="31" spans="1:1">
-      <c r="A16" s="45" t="s">
+      <c r="A16" s="51" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="18" ht="62" spans="1:1">
-      <c r="A18" s="41" t="s">
+      <c r="A18" s="48" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="41" t="s">
+      <c r="A19" s="48" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="41" t="s">
+      <c r="A20" s="48" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="21" ht="46.5" spans="1:1">
-      <c r="A21" s="41" t="s">
+      <c r="A21" s="48" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="23" ht="31" spans="1:1">
-      <c r="A23" s="41" t="s">
+      <c r="A23" s="48" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="46" t="s">
+      <c r="A25" s="49" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="41" t="s">
+      <c r="A26" s="48" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="41" t="s">
+      <c r="A27" s="48" t="s">
         <v>10</v>
       </c>
     </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="52" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" ht="77.5" spans="1:1">
+      <c r="A30" s="53" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="49" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="48" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="48" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="48" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="48" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="48" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="48" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="48" t="s">
+        <v>20</v>
+      </c>
+    </row>
     <row r="72" spans="1:1">
-      <c r="A72" s="46" t="s">
-        <v>11</v>
+      <c r="A72" s="49" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="73" spans="1:1">
-      <c r="A73" s="41" t="s">
-        <v>12</v>
+      <c r="A73" s="48" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="75" ht="31" spans="1:1">
-      <c r="A75" s="47" t="s">
-        <v>13</v>
+      <c r="A75" s="54" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="78" spans="1:1">
-      <c r="A78" s="48" t="s">
-        <v>14</v>
+      <c r="A78" s="55" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="79" spans="1:1">
-      <c r="A79" s="41" t="s">
-        <v>15</v>
+      <c r="A79" s="48" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="80" ht="31" spans="1:1">
-      <c r="A80" s="49" t="s">
-        <v>16</v>
+      <c r="A80" s="56" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="81" spans="1:1">
-      <c r="A81" s="25"/>
+      <c r="A81" s="8"/>
     </row>
     <row r="82" ht="31" spans="1:1">
-      <c r="A82" s="49" t="s">
-        <v>17</v>
+      <c r="A82" s="56" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="83" spans="1:1">
-      <c r="A83" s="25"/>
+      <c r="A83" s="8"/>
     </row>
     <row r="84" spans="1:1">
-      <c r="A84" s="49" t="s">
-        <v>18</v>
+      <c r="A84" s="56" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="85" spans="1:1">
-      <c r="A85" s="50" t="s">
-        <v>19</v>
+      <c r="A85" s="57" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="86" spans="1:1">
-      <c r="A86" s="50" t="s">
-        <v>20</v>
+      <c r="A86" s="57" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="87" spans="1:1">
-      <c r="A87" s="50" t="s">
-        <v>21</v>
+      <c r="A87" s="57" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="88" ht="31" spans="1:1">
-      <c r="A88" s="50" t="s">
-        <v>22</v>
+      <c r="A88" s="57" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="89" spans="1:1">
-      <c r="A89" s="50" t="s">
-        <v>23</v>
+      <c r="A89" s="57" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="90" spans="1:1">
-      <c r="A90" s="50" t="s">
-        <v>24</v>
+      <c r="A90" s="57" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="91" ht="31" spans="1:1">
-      <c r="A91" s="50" t="s">
-        <v>25</v>
+      <c r="A91" s="57" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="93" spans="1:1">
@@ -2594,338 +3443,1344 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D59"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="14.5" outlineLevelCol="3"/>
+  <dimension ref="A1:D249"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="15.5" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="3.61538461538462" style="31" customWidth="1"/>
-    <col min="2" max="2" width="3.38461538461538" style="31" customWidth="1"/>
-    <col min="3" max="3" width="87.1538461538462" style="31" customWidth="1"/>
-    <col min="4" max="4" width="1.53846153846154" style="31" customWidth="1"/>
-    <col min="5" max="16384" width="9.23076923076923" style="31"/>
+    <col min="1" max="1" width="3.43076923076923" style="34" customWidth="1"/>
+    <col min="2" max="2" width="3.01538461538462" style="34" customWidth="1"/>
+    <col min="3" max="3" width="87.1538461538462" style="34" customWidth="1"/>
+    <col min="4" max="4" width="1.53846153846154" style="34" customWidth="1"/>
+    <col min="5" max="16384" width="9.23076923076923" style="34"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:2">
-      <c r="B1" s="32" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" ht="64" customHeight="1" spans="1:4">
-      <c r="A3" s="33">
+      <c r="B1" s="35" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" ht="64" customHeight="1" spans="1:4">
+      <c r="A2" s="36">
         <v>1</v>
       </c>
-      <c r="B3" s="34" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-    </row>
-    <row r="4" ht="73" customHeight="1" spans="1:4">
-      <c r="A4" s="33">
+      <c r="B2" s="37" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+    </row>
+    <row r="3" ht="79" customHeight="1" spans="1:4">
+      <c r="A3" s="36">
         <v>2</v>
       </c>
-      <c r="B4" s="34" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-    </row>
-    <row r="5" ht="31" customHeight="1" spans="1:4">
-      <c r="A5" s="33">
+      <c r="B3" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+    </row>
+    <row r="4" ht="31" customHeight="1" spans="1:4">
+      <c r="A4" s="36">
         <v>3</v>
       </c>
-      <c r="B5" s="34" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
-    </row>
-    <row r="6" ht="32" customHeight="1" spans="1:4">
-      <c r="A6" s="33">
+      <c r="B4" s="37" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="37"/>
+      <c r="D4" s="37"/>
+    </row>
+    <row r="5" ht="32" customHeight="1" spans="1:4">
+      <c r="A5" s="36">
         <v>4</v>
       </c>
-      <c r="B6" s="34" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" s="34"/>
-      <c r="D6" s="34"/>
-    </row>
-    <row r="7" ht="33" customHeight="1" spans="1:4">
-      <c r="A7" s="33">
+      <c r="B5" s="37" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" s="37"/>
+      <c r="D5" s="37"/>
+    </row>
+    <row r="6" ht="33" customHeight="1" spans="1:4">
+      <c r="A6" s="36">
         <v>5</v>
       </c>
-      <c r="B7" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="C7" s="34"/>
-      <c r="D7" s="34"/>
-    </row>
-    <row r="8" ht="33" customHeight="1" spans="1:4">
-      <c r="A8" s="33">
+      <c r="B6" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="37"/>
+      <c r="D6" s="37"/>
+    </row>
+    <row r="7" ht="35" customHeight="1" spans="1:4">
+      <c r="A7" s="36">
         <v>6</v>
       </c>
-      <c r="B8" s="34" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" s="34"/>
-      <c r="D8" s="34"/>
-    </row>
-    <row r="9" ht="15" customHeight="1" spans="1:4">
-      <c r="A9" s="33"/>
-      <c r="B9" s="34"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
-    </row>
-    <row r="10" ht="15" customHeight="1" spans="1:4">
-      <c r="A10" s="33"/>
-      <c r="B10" s="34"/>
-      <c r="C10" s="34"/>
-      <c r="D10" s="34"/>
-    </row>
-    <row r="11" ht="16" customHeight="1" spans="1:4">
-      <c r="A11" s="33"/>
-      <c r="B11" s="35" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" s="34"/>
-      <c r="D11" s="34"/>
+      <c r="B7" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="37"/>
+      <c r="D7" s="37"/>
+    </row>
+    <row r="8" ht="15" customHeight="1" spans="1:4">
+      <c r="A8" s="36"/>
+      <c r="B8" s="37"/>
+      <c r="C8" s="37"/>
+      <c r="D8" s="37"/>
+    </row>
+    <row r="9" ht="16" customHeight="1" spans="1:4">
+      <c r="A9" s="36"/>
+      <c r="B9" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="37"/>
+      <c r="D9" s="37"/>
+    </row>
+    <row r="10" spans="2:2">
+      <c r="B10" s="34" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2">
+      <c r="B11" s="34" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="12" spans="2:2">
-      <c r="B12" s="31" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="13" spans="2:2">
-      <c r="B13" s="36" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="14" spans="2:2">
-      <c r="B14" s="31" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" ht="29" spans="3:3">
-      <c r="C15" s="37" t="s">
-        <v>37</v>
-      </c>
+      <c r="B12" s="34" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" ht="31" spans="3:3">
+      <c r="C13" s="39" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="2:2">
+      <c r="B15" s="34" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" spans="3:3">
+      <c r="C16" s="39" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17" spans="3:3">
+      <c r="C17" s="39"/>
     </row>
     <row r="18" spans="2:2">
-      <c r="B18" s="36" t="s">
-        <v>38</v>
+      <c r="B18" s="34" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="3:3">
-      <c r="C19" s="38" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="20" spans="3:3">
-      <c r="C20" s="38"/>
+      <c r="C19" s="39" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="21" spans="2:2">
-      <c r="B21" s="36" t="s">
-        <v>40</v>
+      <c r="B21" s="34" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="22" spans="3:3">
-      <c r="C22" s="38" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="23" spans="2:2">
-      <c r="B23" s="36"/>
-    </row>
-    <row r="24" spans="2:2">
-      <c r="B24" s="36" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="25" spans="3:3">
-      <c r="C25" s="38" t="s">
+      <c r="C22" s="39" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="23" ht="27" customHeight="1" spans="3:3">
+      <c r="C23" s="39" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="24" ht="27" customHeight="1" spans="3:3">
+      <c r="C24" s="39" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1" spans="3:3">
+      <c r="C25" s="39"/>
+    </row>
+    <row r="26" spans="2:2">
+      <c r="B26" s="34" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="27" ht="31" spans="3:3">
+      <c r="C27" s="39" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="28" ht="46.5" spans="3:3">
+      <c r="C28" s="39" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="29" ht="31" spans="3:3">
+      <c r="C29" s="39" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="30" spans="3:3">
+      <c r="C30" s="39"/>
+    </row>
+    <row r="31" spans="2:2">
+      <c r="B31" s="34" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="32" spans="3:3">
+      <c r="C32" s="39" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="33" ht="31" spans="3:3">
+      <c r="C33" s="39" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="34" ht="62" spans="3:3">
+      <c r="C34" s="39" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="35" spans="3:3">
+      <c r="C35" s="39"/>
+    </row>
+    <row r="36" spans="2:2">
+      <c r="B36" s="34" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="37" spans="3:3">
+      <c r="C37" s="39" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="38" ht="31" spans="3:3">
+      <c r="C38" s="39" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="39" ht="46.5" spans="3:3">
+      <c r="C39" s="39" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="40" spans="3:3">
+      <c r="C40" s="39"/>
+    </row>
+    <row r="41" spans="2:2">
+      <c r="B41" s="34" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="42" spans="3:3">
+      <c r="C42" s="39" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="43" ht="31" spans="3:3">
+      <c r="C43" s="39" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="44" spans="3:3">
+      <c r="C44" s="39"/>
+    </row>
+    <row r="45" spans="2:2">
+      <c r="B45" s="34" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="46" spans="3:3">
+      <c r="C46" s="39" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="47" spans="3:3">
+      <c r="C47" s="39"/>
+    </row>
+    <row r="48" spans="2:2">
+      <c r="B48" s="34" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="49" spans="3:3">
+      <c r="C49" s="39" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="50" ht="31" spans="3:3">
+      <c r="C50" s="40" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="51" spans="3:3">
+      <c r="C51" s="40" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="52" ht="87.5" spans="3:3">
+      <c r="C52" s="32" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="53" spans="3:3">
+      <c r="C53"/>
+    </row>
+    <row r="54" ht="17.5" spans="3:3">
+      <c r="C54" s="32" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="55" ht="70" spans="3:3">
+      <c r="C55" s="33" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="56" ht="35" spans="3:3">
+      <c r="C56" s="33" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="57" ht="87.5" spans="3:3">
+      <c r="C57" s="33" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="58" ht="17.5" spans="3:3">
+      <c r="C58" s="32"/>
+    </row>
+    <row r="59" spans="2:2">
+      <c r="B59" s="34" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="60" spans="3:3">
+      <c r="C60" s="39" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" s="41" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="26" ht="27" customHeight="1" spans="2:3">
-      <c r="B26" s="36"/>
-      <c r="C26" s="37" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="27" ht="27" customHeight="1" spans="2:3">
-      <c r="B27" s="36"/>
-      <c r="C27" s="37" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="28" ht="16" customHeight="1" spans="2:3">
-      <c r="B28" s="36"/>
-      <c r="C28" s="37"/>
-    </row>
-    <row r="29" spans="2:2">
-      <c r="B29" s="36" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="30" ht="29" spans="3:3">
-      <c r="C30" s="38" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="31" ht="46.5" spans="2:3">
-      <c r="B31" s="36"/>
-      <c r="C31" s="39" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="32" ht="46.5" spans="2:3">
-      <c r="B32" s="36"/>
-      <c r="C32" s="39" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="33" ht="15.5" spans="2:3">
-      <c r="B33" s="36"/>
-      <c r="C33" s="39"/>
-    </row>
-    <row r="34" spans="2:2">
-      <c r="B34" s="36" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="35" spans="3:3">
-      <c r="C35" s="38" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="36" ht="31" spans="2:3">
-      <c r="B36" s="36"/>
-      <c r="C36" s="39" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="37" ht="62" spans="2:3">
-      <c r="B37" s="36"/>
-      <c r="C37" s="39" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="38" ht="15.5" spans="2:3">
-      <c r="B38" s="36"/>
-      <c r="C38" s="39"/>
-    </row>
-    <row r="39" spans="2:2">
-      <c r="B39" s="36" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="40" spans="3:3">
-      <c r="C40" s="38" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="41" ht="31" spans="2:3">
-      <c r="B41" s="36"/>
-      <c r="C41" s="39" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="42" ht="46.5" spans="2:3">
-      <c r="B42" s="36"/>
-      <c r="C42" s="39" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="43" ht="15.5" spans="2:3">
-      <c r="B43" s="36"/>
-      <c r="C43" s="39"/>
-    </row>
-    <row r="44" spans="2:2">
-      <c r="B44" s="36" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="45" spans="3:3">
-      <c r="C45" s="38" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="46" ht="31" spans="2:3">
-      <c r="B46" s="36"/>
-      <c r="C46" s="39" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="47" ht="15.5" spans="2:3">
-      <c r="B47" s="36"/>
-      <c r="C47" s="39"/>
-    </row>
-    <row r="48" ht="15.5" spans="2:3">
-      <c r="B48" s="36"/>
-      <c r="C48" s="39"/>
-    </row>
-    <row r="49" spans="2:2">
-      <c r="B49" s="36" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="50" spans="3:3">
-      <c r="C50" s="38" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="51" spans="2:3">
-      <c r="B51" s="36"/>
-      <c r="C51" s="38"/>
-    </row>
-    <row r="52" spans="2:3">
-      <c r="B52" s="36"/>
-      <c r="C52" s="38"/>
-    </row>
-    <row r="53" spans="2:2">
-      <c r="B53" s="36" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="54" spans="3:3">
-      <c r="C54" s="38" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="55" ht="46.5" spans="2:3">
-      <c r="B55" s="36"/>
-      <c r="C55" s="40" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="56" ht="15.5" spans="2:3">
-      <c r="B56" s="36"/>
-      <c r="C56" s="40"/>
-    </row>
-    <row r="57" ht="15.5" spans="2:3">
-      <c r="B57" s="36"/>
-      <c r="C57" s="40"/>
-    </row>
-    <row r="58" spans="2:2">
-      <c r="B58" s="36" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="59" spans="3:3">
-      <c r="C59" s="38" t="s">
-        <v>67</v>
-      </c>
+    <row r="64" spans="1:2">
+      <c r="A64" s="34">
+        <v>1</v>
+      </c>
+      <c r="B64" s="34" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="65" ht="46.5" spans="3:3">
+      <c r="C65" s="42" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="66" spans="3:3">
+      <c r="C66" s="43" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="67" ht="46.5" spans="3:3">
+      <c r="C67" s="42" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="68" spans="2:3">
+      <c r="B68" s="44"/>
+      <c r="C68" s="40"/>
+    </row>
+    <row r="69" spans="2:3">
+      <c r="B69" s="44"/>
+      <c r="C69" s="40" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="70" spans="2:3">
+      <c r="B70" s="44"/>
+      <c r="C70" s="40"/>
+    </row>
+    <row r="71" hidden="1" spans="2:3">
+      <c r="B71" s="44"/>
+      <c r="C71" s="40" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="72" hidden="1" spans="2:3">
+      <c r="B72" s="44"/>
+      <c r="C72" s="40" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="73" hidden="1" spans="2:3">
+      <c r="B73" s="44"/>
+      <c r="C73" s="40" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="74" hidden="1" spans="2:3">
+      <c r="B74" s="44"/>
+      <c r="C74" s="40" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="75" hidden="1" spans="2:3">
+      <c r="B75" s="44"/>
+      <c r="C75" s="40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="76" ht="31" hidden="1" spans="2:3">
+      <c r="B76" s="44"/>
+      <c r="C76" s="40" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="77" hidden="1" spans="2:3">
+      <c r="B77" s="44"/>
+      <c r="C77" s="40" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="78" hidden="1" spans="2:3">
+      <c r="B78" s="44"/>
+      <c r="C78" s="40" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="79" hidden="1" spans="2:3">
+      <c r="B79" s="44"/>
+      <c r="C79" s="40" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="80" hidden="1" spans="2:3">
+      <c r="B80" s="44"/>
+      <c r="C80" s="40"/>
+    </row>
+    <row r="81" hidden="1" spans="2:3">
+      <c r="B81" s="44"/>
+      <c r="C81" s="40" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="82" hidden="1" spans="2:3">
+      <c r="B82" s="44"/>
+      <c r="C82" s="40" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="83" hidden="1" spans="2:3">
+      <c r="B83" s="44"/>
+      <c r="C83" s="40"/>
+    </row>
+    <row r="84" hidden="1" spans="2:3">
+      <c r="B84" s="44"/>
+      <c r="C84" s="40" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="85" hidden="1" spans="2:3">
+      <c r="B85" s="44"/>
+      <c r="C85" s="40" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="86" hidden="1" spans="2:3">
+      <c r="B86" s="44"/>
+      <c r="C86" s="40"/>
+    </row>
+    <row r="87" hidden="1" spans="2:3">
+      <c r="B87" s="44"/>
+      <c r="C87" s="40" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="88" ht="46.5" hidden="1" spans="2:3">
+      <c r="B88" s="44"/>
+      <c r="C88" s="40" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="89" spans="2:3">
+      <c r="B89" s="44"/>
+      <c r="C89" s="40"/>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90" s="44">
+        <v>2</v>
+      </c>
+      <c r="B90" s="45" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="91" ht="31" spans="2:3">
+      <c r="B91" s="44"/>
+      <c r="C91" s="42" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="92" spans="2:2">
+      <c r="B92" s="44"/>
+    </row>
+    <row r="93" spans="2:3">
+      <c r="B93" s="44"/>
+      <c r="C93" s="43" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="94" ht="31" spans="2:3">
+      <c r="B94" s="44"/>
+      <c r="C94" s="42" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="95" spans="2:3">
+      <c r="B95" s="44"/>
+      <c r="C95" s="40"/>
+    </row>
+    <row r="96" spans="2:3">
+      <c r="B96" s="44"/>
+      <c r="C96" s="40" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="97" spans="2:3">
+      <c r="B97" s="44"/>
+      <c r="C97" s="40" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="98" spans="2:3">
+      <c r="B98" s="44"/>
+      <c r="C98" s="40"/>
+    </row>
+    <row r="99" spans="2:3">
+      <c r="B99" s="44"/>
+      <c r="C99" s="40" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="100" hidden="1" spans="2:3">
+      <c r="B100" s="44"/>
+      <c r="C100" s="40" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="101" hidden="1" spans="2:3">
+      <c r="B101" s="44"/>
+      <c r="C101" s="40" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="102" hidden="1" spans="2:3">
+      <c r="B102" s="44"/>
+      <c r="C102" s="40" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="103" hidden="1" spans="2:3">
+      <c r="B103" s="44"/>
+      <c r="C103" s="40"/>
+    </row>
+    <row r="104" hidden="1" spans="2:3">
+      <c r="B104" s="44"/>
+      <c r="C104" s="40" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="105" hidden="1" spans="2:3">
+      <c r="B105" s="44"/>
+      <c r="C105" s="40" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="106" hidden="1" spans="2:3">
+      <c r="B106" s="44"/>
+      <c r="C106" s="40"/>
+    </row>
+    <row r="107" hidden="1" spans="2:3">
+      <c r="B107" s="44"/>
+      <c r="C107" s="40" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="108" hidden="1" spans="2:3">
+      <c r="B108" s="44"/>
+      <c r="C108" s="40" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="109" hidden="1" spans="2:3">
+      <c r="B109" s="44"/>
+      <c r="C109" s="40"/>
+    </row>
+    <row r="110" hidden="1" spans="2:3">
+      <c r="B110" s="44"/>
+      <c r="C110" s="40" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="111" hidden="1" spans="2:3">
+      <c r="B111" s="44"/>
+      <c r="C111" s="40" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="112" hidden="1" spans="2:3">
+      <c r="B112" s="44"/>
+      <c r="C112" s="40"/>
+    </row>
+    <row r="113" hidden="1" spans="2:3">
+      <c r="B113" s="44"/>
+      <c r="C113" s="40" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="114" hidden="1" spans="2:3">
+      <c r="B114" s="44"/>
+      <c r="C114" s="40" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="115" hidden="1" spans="2:3">
+      <c r="B115" s="44"/>
+      <c r="C115" s="40"/>
+    </row>
+    <row r="116" hidden="1" spans="2:3">
+      <c r="B116" s="44"/>
+      <c r="C116" s="40" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="117" hidden="1" spans="2:3">
+      <c r="B117" s="44"/>
+      <c r="C117" s="40" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="118" hidden="1" spans="2:3">
+      <c r="B118" s="44"/>
+      <c r="C118" s="40"/>
+    </row>
+    <row r="119" hidden="1" spans="2:3">
+      <c r="B119" s="44"/>
+      <c r="C119" s="40" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="120" hidden="1" spans="2:3">
+      <c r="B120" s="44"/>
+      <c r="C120" s="40" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="121" hidden="1" spans="2:3">
+      <c r="B121" s="44"/>
+      <c r="C121" s="40"/>
+    </row>
+    <row r="122" hidden="1" spans="2:3">
+      <c r="B122" s="44"/>
+      <c r="C122" s="40" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="123" hidden="1" spans="2:3">
+      <c r="B123" s="44"/>
+      <c r="C123" s="40" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="124" hidden="1" spans="2:3">
+      <c r="B124" s="44"/>
+      <c r="C124" s="40"/>
+    </row>
+    <row r="125" hidden="1" spans="2:3">
+      <c r="B125" s="44"/>
+      <c r="C125" s="40" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="126" hidden="1" spans="2:3">
+      <c r="B126" s="44"/>
+      <c r="C126" s="40" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="127" spans="2:3">
+      <c r="B127" s="44"/>
+      <c r="C127" s="40"/>
+    </row>
+    <row r="128" spans="1:2">
+      <c r="A128" s="46">
+        <v>3</v>
+      </c>
+      <c r="B128" s="45" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="129" spans="2:3">
+      <c r="B129" s="44"/>
+      <c r="C129" s="42" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="130" spans="2:3">
+      <c r="B130" s="44"/>
+      <c r="C130" s="43" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="131" ht="31" spans="2:3">
+      <c r="B131" s="44"/>
+      <c r="C131" s="42" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="132" spans="2:3">
+      <c r="B132" s="44"/>
+      <c r="C132" s="40"/>
+    </row>
+    <row r="133" spans="2:3">
+      <c r="B133" s="44"/>
+      <c r="C133" s="40" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="134" spans="2:3">
+      <c r="B134" s="44"/>
+      <c r="C134" s="40" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="135" spans="2:3">
+      <c r="B135" s="44"/>
+      <c r="C135" s="40"/>
+    </row>
+    <row r="136" spans="2:3">
+      <c r="B136" s="44"/>
+      <c r="C136" s="40" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="137" hidden="1" spans="2:3">
+      <c r="B137" s="44"/>
+      <c r="C137" s="40" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="138" hidden="1" spans="2:3">
+      <c r="B138" s="44"/>
+      <c r="C138" s="40"/>
+    </row>
+    <row r="139" hidden="1" spans="2:3">
+      <c r="B139" s="44"/>
+      <c r="C139" s="40" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="140" hidden="1" spans="2:3">
+      <c r="B140" s="44"/>
+      <c r="C140" s="40" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="141" hidden="1" spans="2:3">
+      <c r="B141" s="44"/>
+      <c r="C141" s="40" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="142" hidden="1" spans="2:3">
+      <c r="B142" s="44"/>
+      <c r="C142" s="40"/>
+    </row>
+    <row r="143" hidden="1" spans="2:3">
+      <c r="B143" s="44"/>
+      <c r="C143" s="40" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="144" hidden="1" spans="2:3">
+      <c r="B144" s="44"/>
+      <c r="C144" s="40" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="145" hidden="1" spans="2:3">
+      <c r="B145" s="44"/>
+      <c r="C145" s="40" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="146" hidden="1" spans="2:3">
+      <c r="B146" s="44"/>
+      <c r="C146" s="40"/>
+    </row>
+    <row r="147" hidden="1" spans="2:3">
+      <c r="B147" s="44"/>
+      <c r="C147" s="40" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="148" hidden="1" spans="2:3">
+      <c r="B148" s="44"/>
+      <c r="C148" s="40" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="149" hidden="1" spans="2:3">
+      <c r="B149" s="44"/>
+      <c r="C149" s="40" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="150" spans="3:3">
+      <c r="C150" s="40"/>
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151" s="44">
+        <v>4</v>
+      </c>
+      <c r="B151" s="45" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="152" spans="2:3">
+      <c r="B152" s="44"/>
+      <c r="C152" s="42" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="153" spans="2:2">
+      <c r="B153" s="44"/>
+    </row>
+    <row r="154" spans="2:3">
+      <c r="B154" s="44"/>
+      <c r="C154" s="43" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="155" ht="31" spans="2:3">
+      <c r="B155" s="44"/>
+      <c r="C155" s="42" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="156" spans="2:3">
+      <c r="B156" s="44"/>
+      <c r="C156" s="40"/>
+    </row>
+    <row r="157" spans="2:3">
+      <c r="B157" s="44"/>
+      <c r="C157" s="40" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="158" hidden="1" spans="2:3">
+      <c r="B158" s="44"/>
+      <c r="C158" s="40" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="159" hidden="1" spans="2:3">
+      <c r="B159" s="44"/>
+      <c r="C159" s="40"/>
+    </row>
+    <row r="160" hidden="1" spans="2:3">
+      <c r="B160" s="44"/>
+      <c r="C160" s="40" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="161" hidden="1" spans="2:3">
+      <c r="B161" s="44"/>
+      <c r="C161" s="40" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="162" hidden="1" spans="2:3">
+      <c r="B162" s="44"/>
+      <c r="C162" s="40"/>
+    </row>
+    <row r="163" hidden="1" spans="2:3">
+      <c r="B163" s="44"/>
+      <c r="C163" s="40" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="164" hidden="1" spans="2:3">
+      <c r="B164" s="44"/>
+      <c r="C164" s="40" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="165" hidden="1" spans="2:3">
+      <c r="B165" s="44"/>
+      <c r="C165" s="40"/>
+    </row>
+    <row r="166" hidden="1" spans="2:3">
+      <c r="B166" s="44"/>
+      <c r="C166" s="40" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="167" hidden="1" spans="2:3">
+      <c r="B167" s="44"/>
+      <c r="C167" s="40" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="168" spans="2:3">
+      <c r="B168" s="44"/>
+      <c r="C168" s="40"/>
+    </row>
+    <row r="169" spans="1:2">
+      <c r="A169" s="44">
+        <v>5</v>
+      </c>
+      <c r="B169" s="45" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="170" spans="2:3">
+      <c r="B170" s="44"/>
+      <c r="C170" s="42" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="171" spans="2:2">
+      <c r="B171" s="44"/>
+    </row>
+    <row r="172" spans="2:3">
+      <c r="B172" s="44"/>
+      <c r="C172" s="43" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="173" spans="2:3">
+      <c r="B173" s="44"/>
+      <c r="C173" s="42" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="174" spans="2:3">
+      <c r="B174" s="44"/>
+      <c r="C174" s="40"/>
+    </row>
+    <row r="175" spans="2:3">
+      <c r="B175" s="44"/>
+      <c r="C175" s="40" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="176" hidden="1" spans="2:3">
+      <c r="B176" s="44"/>
+      <c r="C176" s="40" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="177" hidden="1" spans="2:3">
+      <c r="B177" s="44"/>
+      <c r="C177" s="40" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="178" hidden="1" spans="2:3">
+      <c r="B178" s="44"/>
+      <c r="C178" s="40" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="179" hidden="1" spans="2:3">
+      <c r="B179" s="44"/>
+      <c r="C179" s="40"/>
+    </row>
+    <row r="180" hidden="1" spans="2:3">
+      <c r="B180" s="44"/>
+      <c r="C180" s="40" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="181" hidden="1" spans="2:3">
+      <c r="B181" s="44"/>
+      <c r="C181" s="40"/>
+    </row>
+    <row r="182" hidden="1" spans="2:3">
+      <c r="B182" s="44"/>
+      <c r="C182" s="40" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="183" hidden="1" spans="2:3">
+      <c r="B183" s="44"/>
+      <c r="C183" s="40"/>
+    </row>
+    <row r="184" hidden="1" spans="2:3">
+      <c r="B184" s="44"/>
+      <c r="C184" s="40" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="185" spans="2:3">
+      <c r="B185" s="44"/>
+      <c r="C185" s="40"/>
+    </row>
+    <row r="186" spans="1:2">
+      <c r="A186" s="44">
+        <v>6</v>
+      </c>
+      <c r="B186" s="45" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="187" spans="2:3">
+      <c r="B187" s="44"/>
+      <c r="C187" s="42" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="188" spans="2:2">
+      <c r="B188" s="44"/>
+    </row>
+    <row r="189" spans="2:3">
+      <c r="B189" s="44"/>
+      <c r="C189" s="43" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="190" ht="31" spans="2:3">
+      <c r="B190" s="44"/>
+      <c r="C190" s="42" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="191" spans="2:3">
+      <c r="B191" s="44"/>
+      <c r="C191" s="40"/>
+    </row>
+    <row r="192" spans="2:3">
+      <c r="B192" s="44"/>
+      <c r="C192" s="40" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="193" hidden="1" spans="2:3">
+      <c r="B193" s="44"/>
+      <c r="C193" s="40" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="194" hidden="1" spans="2:3">
+      <c r="B194" s="44"/>
+      <c r="C194" s="40"/>
+    </row>
+    <row r="195" hidden="1" spans="2:3">
+      <c r="B195" s="44"/>
+      <c r="C195" s="40" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="196" hidden="1" spans="2:3">
+      <c r="B196" s="44"/>
+      <c r="C196" s="40" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="197" hidden="1" spans="2:3">
+      <c r="B197" s="44"/>
+      <c r="C197" s="40"/>
+    </row>
+    <row r="198" hidden="1" spans="2:3">
+      <c r="B198" s="44"/>
+      <c r="C198" s="40" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="199" ht="31" hidden="1" spans="2:3">
+      <c r="B199" s="44"/>
+      <c r="C199" s="40" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="200" spans="2:3">
+      <c r="B200" s="44"/>
+      <c r="C200" s="40"/>
+    </row>
+    <row r="201" spans="1:2">
+      <c r="A201" s="44">
+        <v>7</v>
+      </c>
+      <c r="B201" s="45" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="202" ht="31" spans="2:3">
+      <c r="B202" s="44"/>
+      <c r="C202" s="42" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="203" spans="2:2">
+      <c r="B203" s="44"/>
+    </row>
+    <row r="204" spans="2:3">
+      <c r="B204" s="44"/>
+      <c r="C204" s="43" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="205" ht="31" spans="2:3">
+      <c r="B205" s="44"/>
+      <c r="C205" s="42" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="206" spans="2:3">
+      <c r="B206" s="44"/>
+      <c r="C206" s="40"/>
+    </row>
+    <row r="207" spans="2:3">
+      <c r="B207" s="44"/>
+      <c r="C207" s="40" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="208" spans="2:3">
+      <c r="B208" s="44"/>
+      <c r="C208" s="40"/>
+    </row>
+    <row r="209" hidden="1" spans="2:3">
+      <c r="B209" s="44"/>
+      <c r="C209" s="40" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="210" hidden="1" spans="2:3">
+      <c r="B210" s="44"/>
+      <c r="C210" s="40" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="211" hidden="1" spans="2:3">
+      <c r="B211" s="44"/>
+      <c r="C211" s="40"/>
+    </row>
+    <row r="212" hidden="1" spans="2:3">
+      <c r="B212" s="44"/>
+      <c r="C212" s="40" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="213" hidden="1" spans="2:3">
+      <c r="B213" s="44"/>
+      <c r="C213" s="40" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="214" hidden="1" spans="2:3">
+      <c r="B214" s="44"/>
+      <c r="C214" s="40" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="215" hidden="1" spans="2:3">
+      <c r="B215" s="44"/>
+      <c r="C215" s="40"/>
+    </row>
+    <row r="216" hidden="1" spans="2:3">
+      <c r="B216" s="44"/>
+      <c r="C216" s="40" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="217" hidden="1" spans="2:3">
+      <c r="B217" s="44"/>
+      <c r="C217" s="40" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="218" hidden="1" spans="2:3">
+      <c r="B218" s="44"/>
+      <c r="C218" s="40"/>
+    </row>
+    <row r="219" hidden="1" spans="2:3">
+      <c r="B219" s="44"/>
+      <c r="C219" s="40" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="220" hidden="1" spans="2:3">
+      <c r="B220" s="44"/>
+      <c r="C220" s="40" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="221" spans="2:3">
+      <c r="B221" s="44"/>
+      <c r="C221" s="40"/>
+    </row>
+    <row r="222" spans="1:2">
+      <c r="A222" s="44">
+        <v>8</v>
+      </c>
+      <c r="B222" s="45" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="223" spans="2:3">
+      <c r="B223" s="44"/>
+      <c r="C223" s="42" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="224" spans="2:2">
+      <c r="B224" s="44"/>
+    </row>
+    <row r="225" spans="2:3">
+      <c r="B225" s="44"/>
+      <c r="C225" s="43" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="226" ht="31" spans="2:3">
+      <c r="B226" s="44"/>
+      <c r="C226" s="47" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="227" spans="2:3">
+      <c r="B227" s="44"/>
+      <c r="C227" s="40"/>
+    </row>
+    <row r="228" spans="2:3">
+      <c r="B228" s="44"/>
+      <c r="C228" s="40" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="229" hidden="1" spans="2:3">
+      <c r="B229" s="44"/>
+      <c r="C229" s="40" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="230" hidden="1" spans="2:3">
+      <c r="B230" s="44"/>
+      <c r="C230" s="40"/>
+    </row>
+    <row r="231" hidden="1" spans="2:3">
+      <c r="B231" s="44"/>
+      <c r="C231" s="40" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="232" hidden="1" spans="2:3">
+      <c r="B232" s="44"/>
+      <c r="C232" s="40" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="233" hidden="1" spans="2:3">
+      <c r="B233" s="44"/>
+      <c r="C233" s="40"/>
+    </row>
+    <row r="234" hidden="1" spans="2:3">
+      <c r="B234" s="44"/>
+      <c r="C234" s="40" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="235" hidden="1" spans="2:3">
+      <c r="B235" s="44"/>
+      <c r="C235" s="40" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="236" hidden="1" spans="2:3">
+      <c r="B236" s="44"/>
+      <c r="C236" s="40"/>
+    </row>
+    <row r="237" hidden="1" spans="2:3">
+      <c r="B237" s="44"/>
+      <c r="C237" s="40" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="238" hidden="1" spans="2:3">
+      <c r="B238" s="44"/>
+      <c r="C238" s="40" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="239" hidden="1" spans="2:3">
+      <c r="B239" s="44"/>
+      <c r="C239" s="40"/>
+    </row>
+    <row r="240" hidden="1" spans="2:3">
+      <c r="B240" s="44"/>
+      <c r="C240" s="40" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="241" hidden="1" spans="2:3">
+      <c r="B241" s="44"/>
+      <c r="C241" s="40" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="242" hidden="1" spans="2:3">
+      <c r="B242" s="44"/>
+      <c r="C242" s="40"/>
+    </row>
+    <row r="243" hidden="1" spans="2:3">
+      <c r="B243" s="44"/>
+      <c r="C243" s="40" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="244" hidden="1" spans="2:3">
+      <c r="B244" s="44"/>
+      <c r="C244" s="40" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="245" hidden="1" spans="2:3">
+      <c r="B245" s="44"/>
+      <c r="C245" s="40"/>
+    </row>
+    <row r="246" hidden="1" spans="2:3">
+      <c r="B246" s="44"/>
+      <c r="C246" s="40" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="247" hidden="1" spans="2:3">
+      <c r="B247" s="44"/>
+      <c r="C247" s="40" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="248" spans="2:3">
+      <c r="B248" s="44"/>
+      <c r="C248" s="40"/>
+    </row>
+    <row r="249" spans="2:3">
+      <c r="B249" s="44"/>
+      <c r="C249" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="B2:D2"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B8:D8"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="C55" r:id="rId1" display="It provides an abstracted layer of ‘DataSet API,’ with smarter big data computation efficiency, which is superior to that of Resilient Distributed Datasets or PySpark RDDs, and eases the structured data manipulation process." tooltip="https://www.simplilearn.com/tutorials/pyspark-tutorial/pyspark-rdd"/>
+    <hyperlink ref="C50" r:id="rId1" display="It provides an abstracted layer of ‘DataSet API,’ with smarter big data computation efficiency, which is superior to that of Resilient Distributed Datasets or PySpark RDDs, and eases the structured data manipulation process." tooltip="https://www.simplilearn.com/tutorials/pyspark-tutorial/pyspark-rdd"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -2935,753 +4790,115 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B194"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="15.5" outlineLevelCol="1"/>
+  <dimension ref="A1:D24"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="15.5" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="4.46153846153846" style="20" customWidth="1"/>
-    <col min="2" max="2" width="88.8692307692308" style="21" customWidth="1"/>
-    <col min="3" max="3" width="4.46153846153846" style="22" customWidth="1"/>
-    <col min="4" max="4" width="30.6153846153846" style="22" customWidth="1"/>
-    <col min="5" max="16384" width="9.23076923076923" style="22"/>
+    <col min="1" max="1" width="4.46153846153846" style="27" customWidth="1"/>
+    <col min="2" max="2" width="4.49230769230769" style="28" customWidth="1"/>
+    <col min="3" max="3" width="9.23076923076923" style="28"/>
+    <col min="4" max="4" width="73.7846153846154" style="28" customWidth="1"/>
+    <col min="5" max="16384" width="9.23076923076923" style="28"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:2">
-      <c r="B1" s="23" t="s">
-        <v>68</v>
+      <c r="B1" s="29" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="2" spans="2:2">
-      <c r="B2" s="23" t="s">
-        <v>69</v>
+      <c r="B2" s="29" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="3" spans="2:2">
-      <c r="B3" s="24" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="2:2">
-      <c r="B4" s="24"/>
+      <c r="B3" s="30"/>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="27" t="s">
+        <v>203</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="5" spans="2:2">
-      <c r="B5" s="24"/>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="25">
-        <v>1</v>
-      </c>
-      <c r="B6" s="26" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="7" ht="46.5" spans="1:2">
-      <c r="A7" s="25"/>
-      <c r="B7" s="27" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="25"/>
-      <c r="B8" s="28" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="9" ht="46.5" spans="1:2">
-      <c r="A9" s="25"/>
-      <c r="B9" s="27" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="11" spans="2:2">
-      <c r="B11" s="21" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="13" spans="2:2">
-      <c r="B13" s="21" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="14" spans="2:2">
-      <c r="B14" s="21" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="15" hidden="1" spans="2:2">
-      <c r="B15" s="21" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="16" hidden="1" spans="2:2">
-      <c r="B16" s="21" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="17" hidden="1" spans="2:2">
-      <c r="B17" s="21" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="18" ht="31" hidden="1" spans="2:2">
-      <c r="B18" s="21" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="19" hidden="1" spans="2:2">
-      <c r="B19" s="21" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="20" hidden="1" spans="2:2">
-      <c r="B20" s="21" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="21" hidden="1" spans="2:2">
-      <c r="B21" s="21" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="22" hidden="1"/>
-    <row r="23" hidden="1" spans="2:2">
-      <c r="B23" s="21" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="24" hidden="1" spans="2:2">
-      <c r="B24" s="21" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="25" hidden="1"/>
-    <row r="26" hidden="1" spans="2:2">
-      <c r="B26" s="21" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="27" hidden="1" spans="2:2">
-      <c r="B27" s="21" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="28" hidden="1"/>
-    <row r="29" hidden="1" spans="2:2">
-      <c r="B29" s="21" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="30" ht="46.5" hidden="1" spans="2:2">
-      <c r="B30" s="21" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33" s="20">
-        <v>2</v>
-      </c>
-      <c r="B33" s="29" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="34" spans="2:2">
-      <c r="B34" s="25"/>
-    </row>
-    <row r="35" ht="31" spans="2:2">
-      <c r="B35" s="27" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="36" spans="2:2">
-      <c r="B36" s="25"/>
-    </row>
-    <row r="37" spans="2:2">
-      <c r="B37" s="28" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="38" ht="31" spans="2:2">
-      <c r="B38" s="27" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="40" spans="2:2">
-      <c r="B40" s="21" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="41" spans="2:2">
-      <c r="B41" s="21" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="43" spans="2:2">
-      <c r="B43" s="21" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="44" spans="2:2">
-      <c r="B44" s="21" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="45" hidden="1" spans="2:2">
-      <c r="B45" s="21" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="46" hidden="1" spans="2:2">
-      <c r="B46" s="21" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="47" hidden="1"/>
-    <row r="48" hidden="1" spans="2:2">
-      <c r="B48" s="21" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="49" hidden="1" spans="2:2">
-      <c r="B49" s="21" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="50" hidden="1"/>
-    <row r="51" hidden="1" spans="2:2">
-      <c r="B51" s="21" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="52" hidden="1" spans="2:2">
-      <c r="B52" s="21" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="53" hidden="1"/>
-    <row r="54" hidden="1" spans="2:2">
-      <c r="B54" s="21" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="55" hidden="1" spans="2:2">
-      <c r="B55" s="21" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="56" hidden="1"/>
-    <row r="57" hidden="1" spans="2:2">
-      <c r="B57" s="21" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="58" hidden="1" spans="2:2">
-      <c r="B58" s="21" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="59" hidden="1"/>
-    <row r="60" hidden="1" spans="2:2">
-      <c r="B60" s="21" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="61" hidden="1" spans="2:2">
-      <c r="B61" s="21" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="62" hidden="1"/>
-    <row r="63" hidden="1" spans="2:2">
-      <c r="B63" s="21" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="64" hidden="1" spans="2:2">
-      <c r="B64" s="21" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="65" hidden="1"/>
-    <row r="66" hidden="1" spans="2:2">
-      <c r="B66" s="21" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="67" hidden="1" spans="2:2">
-      <c r="B67" s="21" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="68" hidden="1"/>
-    <row r="69" hidden="1" spans="2:2">
-      <c r="B69" s="21" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="70" hidden="1" spans="2:2">
-      <c r="B70" s="21" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2">
-      <c r="A72" s="20">
-        <v>3</v>
-      </c>
-      <c r="B72" s="29" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="73" spans="2:2">
-      <c r="B73" s="27" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="74" spans="2:2">
-      <c r="B74" s="28" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="75" ht="32" customHeight="1" spans="2:2">
-      <c r="B75" s="27" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="77" spans="2:2">
-      <c r="B77" s="21" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="78" spans="2:2">
-      <c r="B78" s="21" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="80" spans="2:2">
-      <c r="B80" s="21" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="81" spans="2:2">
-      <c r="B81" s="21" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="82" hidden="1"/>
-    <row r="83" hidden="1" spans="2:2">
-      <c r="B83" s="21" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="84" hidden="1" spans="2:2">
-      <c r="B84" s="21" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="85" hidden="1" spans="2:2">
-      <c r="B85" s="21" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="86" hidden="1"/>
-    <row r="87" hidden="1" spans="2:2">
-      <c r="B87" s="21" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="88" hidden="1" spans="2:2">
-      <c r="B88" s="21" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="89" hidden="1" spans="2:2">
-      <c r="B89" s="21" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="90" hidden="1"/>
-    <row r="91" hidden="1" spans="2:2">
-      <c r="B91" s="21" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="92" hidden="1" spans="2:2">
-      <c r="B92" s="21" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="93" hidden="1" spans="2:2">
-      <c r="B93" s="21" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2">
-      <c r="A95" s="20">
-        <v>4</v>
-      </c>
-      <c r="B95" s="29" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="96" spans="2:2">
-      <c r="B96" s="27" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="97" spans="2:2">
-      <c r="B97" s="25"/>
-    </row>
-    <row r="98" spans="2:2">
-      <c r="B98" s="28" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="99" ht="31" spans="2:2">
-      <c r="B99" s="27" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="101" spans="2:2">
-      <c r="B101" s="21" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="102" spans="2:2">
-      <c r="B102" s="21" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="103" hidden="1"/>
-    <row r="104" hidden="1" spans="2:2">
-      <c r="B104" s="21" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="105" hidden="1" spans="2:2">
-      <c r="B105" s="21" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="106" hidden="1"/>
-    <row r="107" hidden="1" spans="2:2">
-      <c r="B107" s="21" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="108" hidden="1" spans="2:2">
-      <c r="B108" s="21" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="109" hidden="1"/>
-    <row r="110" hidden="1" spans="2:2">
-      <c r="B110" s="21" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="111" hidden="1" spans="2:2">
-      <c r="B111" s="21" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2">
-      <c r="A114" s="20">
-        <v>5</v>
-      </c>
-      <c r="B114" s="29" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="115" spans="2:2">
-      <c r="B115" s="27" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="116" spans="2:2">
-      <c r="B116" s="25"/>
-    </row>
-    <row r="117" spans="2:2">
-      <c r="B117" s="28" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="118" spans="2:2">
-      <c r="B118" s="27" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="120" spans="2:2">
-      <c r="B120" s="21" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="121" spans="2:2">
-      <c r="B121" s="21" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="122" hidden="1" spans="2:2">
-      <c r="B122" s="21" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="123" hidden="1" spans="2:2">
-      <c r="B123" s="21" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="124" hidden="1"/>
-    <row r="125" hidden="1" spans="2:2">
-      <c r="B125" s="21" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="126" hidden="1"/>
-    <row r="127" hidden="1" spans="2:2">
-      <c r="B127" s="21" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="128" hidden="1"/>
-    <row r="129" hidden="1" spans="2:2">
-      <c r="B129" s="21" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2">
-      <c r="A132" s="20">
-        <v>6</v>
-      </c>
-      <c r="B132" s="29" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="133" spans="2:2">
-      <c r="B133" s="27" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="134" spans="2:2">
-      <c r="B134" s="25"/>
-    </row>
-    <row r="135" spans="2:2">
-      <c r="B135" s="28" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="136" ht="31" spans="2:2">
-      <c r="B136" s="27" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="138" spans="2:2">
-      <c r="B138" s="21" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="139" hidden="1" spans="2:2">
-      <c r="B139" s="21" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="140" hidden="1"/>
-    <row r="141" hidden="1" spans="2:2">
-      <c r="B141" s="21" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="142" hidden="1" spans="2:2">
-      <c r="B142" s="21" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="143" hidden="1"/>
-    <row r="144" hidden="1" spans="2:2">
-      <c r="B144" s="21" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="145" ht="31" hidden="1" spans="2:2">
-      <c r="B145" s="21" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2">
-      <c r="A148" s="20">
-        <v>7</v>
-      </c>
-      <c r="B148" s="29" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="149" ht="31" spans="2:2">
-      <c r="B149" s="27" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="150" spans="2:2">
-      <c r="B150" s="25"/>
-    </row>
-    <row r="151" spans="2:2">
-      <c r="B151" s="28" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="152" ht="31" spans="2:2">
-      <c r="B152" s="27" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="154" spans="2:2">
-      <c r="B154" s="21" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="156" hidden="1" spans="2:2">
-      <c r="B156" s="21" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="157" hidden="1" spans="2:2">
-      <c r="B157" s="21" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="158" hidden="1"/>
-    <row r="159" hidden="1" spans="2:2">
-      <c r="B159" s="21" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="160" hidden="1" spans="2:2">
-      <c r="B160" s="21" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="161" hidden="1" spans="2:2">
-      <c r="B161" s="21" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="162" hidden="1"/>
-    <row r="163" hidden="1" spans="2:2">
-      <c r="B163" s="21" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="164" hidden="1" spans="2:2">
-      <c r="B164" s="21" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="165" hidden="1"/>
-    <row r="166" hidden="1" spans="2:2">
-      <c r="B166" s="21" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="167" hidden="1" spans="2:2">
-      <c r="B167" s="21" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="169" spans="1:2">
-      <c r="A169" s="20">
-        <v>8</v>
-      </c>
-      <c r="B169" s="29" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="170" spans="2:2">
-      <c r="B170" s="27" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="171" spans="2:2">
-      <c r="B171" s="25"/>
-    </row>
-    <row r="172" spans="2:2">
-      <c r="B172" s="28" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="173" ht="23" customHeight="1" spans="2:2">
-      <c r="B173" s="30" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="175" spans="2:2">
-      <c r="B175" s="21" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="176" spans="2:2">
-      <c r="B176" s="21" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="178" hidden="1" spans="2:2">
-      <c r="B178" s="21" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="179" hidden="1" spans="2:2">
-      <c r="B179" s="21" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="180" hidden="1"/>
-    <row r="181" hidden="1" spans="2:2">
-      <c r="B181" s="21" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="182" hidden="1" spans="2:2">
-      <c r="B182" s="21" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="183" hidden="1"/>
-    <row r="184" hidden="1" spans="2:2">
-      <c r="B184" s="21" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="185" hidden="1" spans="2:2">
-      <c r="B185" s="21" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="186" hidden="1"/>
-    <row r="187" hidden="1" spans="2:2">
-      <c r="B187" s="21" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="188" hidden="1" spans="2:2">
-      <c r="B188" s="21" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="189" hidden="1"/>
-    <row r="190" hidden="1" spans="2:2">
-      <c r="B190" s="21" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="191" hidden="1" spans="2:2">
-      <c r="B191" s="21" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="192" hidden="1"/>
-    <row r="193" hidden="1" spans="2:2">
-      <c r="B193" s="21" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="194" hidden="1" spans="2:2">
-      <c r="B194" s="21" t="s">
-        <v>112</v>
+      <c r="B5" s="28" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="6" ht="17.5" spans="2:2">
+      <c r="B6" s="31" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="7" ht="35" spans="2:4">
+      <c r="B7" s="31"/>
+      <c r="D7" s="32" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="8" ht="17.5" spans="3:3">
+      <c r="C8" s="31" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="9" ht="17.5" spans="3:3">
+      <c r="C9" s="31"/>
+    </row>
+    <row r="10" ht="17.5" spans="3:3">
+      <c r="C10" s="31"/>
+    </row>
+    <row r="11" spans="3:3">
+      <c r="C11" s="28" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="12" spans="3:3">
+      <c r="C12" s="28" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="13" spans="3:3">
+      <c r="C13" s="28" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="16" ht="17.5" spans="2:2">
+      <c r="B16" s="31" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="17" ht="122.5" spans="4:4">
+      <c r="D17" s="32" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="20" ht="35" spans="2:4">
+      <c r="B20" s="28" t="s">
+        <v>213</v>
+      </c>
+      <c r="D20" s="32" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="21" ht="17.5" spans="4:4">
+      <c r="D21" s="33" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="22" ht="17.5" spans="4:4">
+      <c r="D22" s="33" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="23" ht="17.5" spans="4:4">
+      <c r="D23" s="33" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="24" ht="17.5" spans="4:4">
+      <c r="D24" s="33" t="s">
+        <v>218</v>
       </c>
     </row>
   </sheetData>
@@ -3701,428 +4918,428 @@
   <sheetData>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="14" t="s">
-        <v>187</v>
+      <c r="A4" s="21" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>188</v>
+        <v>220</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>189</v>
+        <v>221</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="14" t="s">
-        <v>190</v>
+      <c r="A8" s="21" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>191</v>
+        <v>223</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>192</v>
+        <v>224</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="14" t="s">
-        <v>193</v>
+      <c r="A12" s="21" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>194</v>
+        <v>226</v>
       </c>
     </row>
     <row r="14" spans="2:2">
       <c r="B14" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>192</v>
+        <v>224</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="14" t="s">
-        <v>196</v>
+      <c r="A17" s="21" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>197</v>
+        <v>229</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>198</v>
+        <v>230</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>199</v>
+        <v>231</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>200</v>
+        <v>232</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>201</v>
+        <v>233</v>
       </c>
     </row>
     <row r="23" spans="2:2">
       <c r="B23" t="s">
-        <v>202</v>
+        <v>234</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>203</v>
+        <v>235</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="14" t="s">
-        <v>204</v>
+      <c r="A26" s="21" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>205</v>
+        <v>237</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>206</v>
+        <v>238</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>207</v>
+        <v>239</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
     </row>
     <row r="31" hidden="1" spans="1:1">
       <c r="A31" t="s">
-        <v>209</v>
+        <v>241</v>
       </c>
     </row>
     <row r="32" hidden="1" spans="1:1">
       <c r="A32" t="s">
-        <v>210</v>
+        <v>242</v>
       </c>
     </row>
     <row r="33" hidden="1" spans="1:1">
       <c r="A33" t="s">
-        <v>211</v>
+        <v>243</v>
       </c>
     </row>
     <row r="34" hidden="1" spans="1:1">
       <c r="A34" t="s">
-        <v>212</v>
+        <v>244</v>
       </c>
     </row>
     <row r="35" hidden="1" spans="1:1">
       <c r="A35" t="s">
-        <v>213</v>
+        <v>245</v>
       </c>
     </row>
     <row r="36" hidden="1" spans="1:1">
       <c r="A36" t="s">
-        <v>214</v>
+        <v>246</v>
       </c>
     </row>
     <row r="37" hidden="1" spans="1:1">
       <c r="A37" t="s">
-        <v>215</v>
+        <v>247</v>
       </c>
     </row>
     <row r="38" hidden="1" spans="1:1">
       <c r="A38" t="s">
-        <v>216</v>
+        <v>248</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>217</v>
+        <v>249</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>218</v>
+        <v>250</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>219</v>
+        <v>251</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>220</v>
+        <v>252</v>
       </c>
     </row>
     <row r="43" spans="1:1">
-      <c r="A43" s="15" t="s">
-        <v>221</v>
+      <c r="A43" s="22" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>222</v>
+        <v>254</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>223</v>
+        <v>255</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>225</v>
+        <v>257</v>
       </c>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="14" t="s">
-        <v>226</v>
+      <c r="A49" s="21" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>197</v>
+        <v>229</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>198</v>
+        <v>230</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>227</v>
+        <v>259</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>228</v>
+        <v>260</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>229</v>
+        <v>261</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>230</v>
+        <v>262</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>231</v>
+        <v>263</v>
       </c>
     </row>
     <row r="59" spans="1:1">
-      <c r="A59" s="14" t="s">
-        <v>232</v>
+      <c r="A59" s="21" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>233</v>
+        <v>265</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>234</v>
+        <v>266</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" t="s">
-        <v>235</v>
+        <v>267</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="s">
-        <v>236</v>
+        <v>268</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>237</v>
+        <v>269</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" t="s">
-        <v>238</v>
+        <v>270</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" t="s">
-        <v>239</v>
+        <v>271</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" t="s">
-        <v>198</v>
+        <v>230</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" t="s">
-        <v>240</v>
+        <v>272</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" t="s">
-        <v>241</v>
+        <v>273</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" t="s">
-        <v>192</v>
+        <v>224</v>
       </c>
     </row>
     <row r="72" spans="1:1">
-      <c r="A72" s="14" t="s">
-        <v>242</v>
+      <c r="A72" s="21" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" t="s">
-        <v>233</v>
+        <v>265</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" t="s">
-        <v>243</v>
+        <v>275</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" t="s">
-        <v>244</v>
+        <v>276</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" t="s">
-        <v>245</v>
+        <v>277</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" t="s">
-        <v>246</v>
+        <v>278</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" t="s">
-        <v>247</v>
+        <v>279</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" t="s">
-        <v>248</v>
+        <v>280</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" t="s">
-        <v>249</v>
+        <v>281</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" t="s">
-        <v>250</v>
+        <v>282</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" t="s">
-        <v>251</v>
+        <v>283</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" t="s">
-        <v>252</v>
+        <v>284</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" t="s">
-        <v>239</v>
+        <v>271</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" t="s">
-        <v>253</v>
+        <v>285</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86" t="s">
-        <v>254</v>
+        <v>286</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87" t="s">
-        <v>255</v>
+        <v>287</v>
       </c>
     </row>
     <row r="89" spans="1:1">
       <c r="A89" t="s">
-        <v>256</v>
+        <v>288</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" t="s">
-        <v>257</v>
+        <v>289</v>
       </c>
     </row>
     <row r="91" spans="1:2">
-      <c r="A91" s="16"/>
-      <c r="B91" s="16"/>
+      <c r="A91" s="23"/>
+      <c r="B91" s="23"/>
     </row>
     <row r="92" spans="1:2">
-      <c r="A92" s="17" t="s">
-        <v>258</v>
-      </c>
-      <c r="B92" s="16"/>
+      <c r="A92" s="24" t="s">
+        <v>290</v>
+      </c>
+      <c r="B92" s="23"/>
     </row>
     <row r="93" spans="1:2">
-      <c r="A93" s="18" t="s">
-        <v>259</v>
-      </c>
-      <c r="B93" s="16"/>
+      <c r="A93" s="25" t="s">
+        <v>291</v>
+      </c>
+      <c r="B93" s="23"/>
     </row>
     <row r="94" spans="1:2">
-      <c r="A94" s="18" t="s">
-        <v>260</v>
-      </c>
-      <c r="B94" s="16"/>
+      <c r="A94" s="25" t="s">
+        <v>292</v>
+      </c>
+      <c r="B94" s="23"/>
     </row>
     <row r="95" spans="1:2">
-      <c r="A95" s="19"/>
-      <c r="B95" s="16"/>
+      <c r="A95" s="26"/>
+      <c r="B95" s="23"/>
     </row>
     <row r="96" spans="1:2">
-      <c r="A96" s="16"/>
-      <c r="B96" s="16"/>
+      <c r="A96" s="23"/>
+      <c r="B96" s="23"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4136,260 +5353,245 @@
   <dimension ref="A1:H88"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="27.3307692307692" style="5" customWidth="1"/>
-    <col min="2" max="2" width="19.8307692307692" style="6" customWidth="1"/>
-    <col min="3" max="3" width="2.41538461538462" style="5" customWidth="1"/>
-    <col min="4" max="4" width="3.33076923076923" style="5" customWidth="1"/>
-    <col min="5" max="5" width="12.6692307692308" style="5" customWidth="1"/>
-    <col min="6" max="6" width="12.1692307692308" style="5" customWidth="1"/>
-    <col min="7" max="8" width="4.5" style="5" customWidth="1"/>
-    <col min="9" max="16384" width="11" style="5"/>
+    <col min="1" max="1" width="27.3307692307692" style="13" customWidth="1"/>
+    <col min="2" max="2" width="19.8307692307692" style="14" customWidth="1"/>
+    <col min="3" max="3" width="2.41538461538462" style="13" customWidth="1"/>
+    <col min="4" max="4" width="3.33076923076923" style="13" customWidth="1"/>
+    <col min="5" max="5" width="12.6692307692308" style="13" customWidth="1"/>
+    <col min="6" max="6" width="12.1692307692308" style="13" customWidth="1"/>
+    <col min="7" max="8" width="4.5" style="13" customWidth="1"/>
+    <col min="9" max="16384" width="11" style="13"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:2">
-      <c r="B1" s="6" t="s">
-        <v>261</v>
+      <c r="B1" s="14" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>266</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>267</v>
+      <c r="A2" s="13" t="s">
+        <v>294</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>295</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>297</v>
+      </c>
+      <c r="G2" s="15" t="s">
+        <v>298</v>
+      </c>
+      <c r="H2" s="13" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="4" spans="2:2">
-      <c r="B4" s="6" t="s">
-        <v>268</v>
+      <c r="B4" s="14" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="5" ht="15.5" spans="3:3">
       <c r="C5" t="s">
-        <v>269</v>
+        <v>301</v>
       </c>
     </row>
     <row r="6" ht="15.5" spans="3:4">
-      <c r="C6" s="6"/>
+      <c r="C6" s="14"/>
       <c r="D6" t="s">
-        <v>270</v>
+        <v>302</v>
       </c>
     </row>
     <row r="7" ht="15.5" spans="3:3">
       <c r="C7" t="s">
-        <v>271</v>
+        <v>303</v>
       </c>
     </row>
     <row r="8" ht="15.5" spans="3:3">
       <c r="C8" t="s">
-        <v>272</v>
+        <v>304</v>
       </c>
     </row>
     <row r="9" ht="15.5" spans="1:4">
-      <c r="A9" s="8"/>
-      <c r="C9" s="6"/>
+      <c r="A9" s="16"/>
+      <c r="C9" s="14"/>
       <c r="D9" t="s">
-        <v>273</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10" ht="15.5" spans="3:4">
-      <c r="C10" s="6"/>
+      <c r="C10" s="14"/>
       <c r="D10" t="s">
-        <v>274</v>
+        <v>306</v>
       </c>
     </row>
     <row r="11" ht="15.5" spans="3:4">
-      <c r="C11" s="6"/>
+      <c r="C11" s="14"/>
       <c r="D11" t="s">
-        <v>275</v>
+        <v>307</v>
       </c>
     </row>
     <row r="12" ht="15.5" spans="3:4">
-      <c r="C12" s="6"/>
+      <c r="C12" s="14"/>
       <c r="D12" t="s">
-        <v>276</v>
+        <v>308</v>
       </c>
     </row>
     <row r="13" ht="15.5" spans="3:4">
-      <c r="C13" s="6"/>
+      <c r="C13" s="14"/>
       <c r="D13" t="s">
-        <v>277</v>
+        <v>309</v>
       </c>
     </row>
     <row r="14" ht="15.5" spans="3:3">
       <c r="C14" t="s">
-        <v>278</v>
+        <v>310</v>
       </c>
     </row>
     <row r="15" ht="15.5" spans="3:4">
-      <c r="C15" s="6"/>
+      <c r="C15" s="14"/>
       <c r="D15" t="s">
-        <v>279</v>
+        <v>311</v>
       </c>
     </row>
     <row r="16" ht="15.5" spans="3:4">
-      <c r="C16" s="6"/>
+      <c r="C16" s="14"/>
       <c r="D16" t="s">
-        <v>280</v>
+        <v>312</v>
       </c>
     </row>
     <row r="17" ht="15.5" spans="3:4">
-      <c r="C17" s="6"/>
+      <c r="C17" s="14"/>
       <c r="D17" t="s">
-        <v>281</v>
+        <v>313</v>
       </c>
     </row>
     <row r="18" ht="15.5" spans="3:4">
-      <c r="C18" s="6"/>
+      <c r="C18" s="14"/>
       <c r="D18" t="s">
-        <v>282</v>
+        <v>314</v>
       </c>
     </row>
     <row r="19" ht="15.5" spans="3:4">
-      <c r="C19" s="6"/>
+      <c r="C19" s="14"/>
       <c r="D19" t="s">
-        <v>283</v>
+        <v>315</v>
       </c>
     </row>
     <row r="20" ht="15.5" spans="3:3">
       <c r="C20" t="s">
-        <v>284</v>
+        <v>316</v>
       </c>
     </row>
     <row r="21" ht="15.5" spans="3:3">
       <c r="C21" t="s">
-        <v>285</v>
+        <v>317</v>
       </c>
     </row>
     <row r="22" ht="15.5" spans="3:4">
-      <c r="C22" s="6"/>
+      <c r="C22" s="14"/>
       <c r="D22" t="s">
-        <v>286</v>
+        <v>318</v>
       </c>
     </row>
     <row r="23" ht="15.5" spans="3:4">
-      <c r="C23" s="6"/>
+      <c r="C23" s="14"/>
       <c r="D23" t="s">
-        <v>287</v>
+        <v>319</v>
       </c>
     </row>
     <row r="24" ht="15.5" spans="3:3">
       <c r="C24" t="s">
-        <v>288</v>
+        <v>320</v>
       </c>
     </row>
     <row r="29" spans="3:3">
-      <c r="C29" s="5" t="s">
-        <v>289</v>
+      <c r="C29" s="13" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="9"/>
-      <c r="B30" s="10"/>
-      <c r="D30" s="5" t="s">
-        <v>290</v>
+      <c r="A30" s="17"/>
+      <c r="B30" s="18"/>
+      <c r="D30" s="13" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="9"/>
-      <c r="B31" s="10"/>
+      <c r="A31" s="17"/>
+      <c r="B31" s="18"/>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="9"/>
-      <c r="B32" s="10"/>
+      <c r="A32" s="17"/>
+      <c r="B32" s="18"/>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="9"/>
+      <c r="A33" s="17"/>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="9"/>
-      <c r="B34" s="10"/>
+      <c r="A34" s="17"/>
+      <c r="B34" s="18"/>
     </row>
     <row r="39" spans="1:1">
-      <c r="A39" s="9"/>
+      <c r="A39" s="17"/>
     </row>
     <row r="40" spans="1:1">
-      <c r="A40" s="9"/>
+      <c r="A40" s="17"/>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="9"/>
+      <c r="A41" s="17"/>
     </row>
     <row r="43" spans="1:1">
-      <c r="A43" s="9"/>
+      <c r="A43" s="17"/>
     </row>
     <row r="56" spans="4:4">
-      <c r="D56" s="11"/>
+      <c r="D56" s="19"/>
     </row>
     <row r="57" spans="4:4">
-      <c r="D57" s="11"/>
+      <c r="D57" s="19"/>
     </row>
     <row r="58" spans="4:4">
-      <c r="D58" s="12"/>
+      <c r="D58" s="20"/>
     </row>
     <row r="61" spans="3:6">
-      <c r="C61" s="9"/>
-      <c r="D61" s="9"/>
-      <c r="E61" s="9"/>
-      <c r="F61" s="9"/>
+      <c r="C61" s="17"/>
+      <c r="D61" s="17"/>
+      <c r="E61" s="17"/>
+      <c r="F61" s="17"/>
     </row>
     <row r="62" spans="3:6">
-      <c r="C62" s="9"/>
-      <c r="D62" s="9"/>
-      <c r="E62" s="9"/>
-      <c r="F62" s="9"/>
+      <c r="C62" s="17"/>
+      <c r="D62" s="17"/>
+      <c r="E62" s="17"/>
+      <c r="F62" s="17"/>
     </row>
     <row r="63" spans="3:6">
-      <c r="C63" s="9"/>
-      <c r="D63" s="9"/>
-      <c r="E63" s="9"/>
-      <c r="F63" s="9"/>
+      <c r="C63" s="17"/>
+      <c r="D63" s="17"/>
+      <c r="E63" s="17"/>
+      <c r="F63" s="17"/>
     </row>
     <row r="64" spans="3:6">
-      <c r="C64" s="9"/>
-      <c r="D64" s="9"/>
-      <c r="F64" s="9"/>
+      <c r="C64" s="17"/>
+      <c r="D64" s="17"/>
+      <c r="F64" s="17"/>
     </row>
     <row r="65" spans="3:6">
-      <c r="C65" s="9"/>
-      <c r="D65" s="9"/>
-      <c r="E65" s="9"/>
-      <c r="F65" s="9"/>
+      <c r="C65" s="17"/>
+      <c r="D65" s="17"/>
+      <c r="E65" s="17"/>
+      <c r="F65" s="17"/>
     </row>
     <row r="66" spans="3:6">
-      <c r="C66" s="9"/>
-      <c r="D66" s="9"/>
-      <c r="E66" s="9"/>
-      <c r="F66" s="9"/>
-    </row>
-    <row r="80" spans="2:2">
-      <c r="B80" s="13"/>
-    </row>
-    <row r="81" spans="2:2">
-      <c r="B81" s="13"/>
-    </row>
-    <row r="82" spans="2:2">
-      <c r="B82" s="13"/>
-    </row>
-    <row r="83" spans="2:2">
-      <c r="B83" s="13"/>
-    </row>
-    <row r="84" spans="2:2">
-      <c r="B84" s="13"/>
+      <c r="C66" s="17"/>
+      <c r="D66" s="17"/>
+      <c r="E66" s="17"/>
+      <c r="F66" s="17"/>
     </row>
     <row r="88" spans="4:4">
-      <c r="D88" s="11"/>
+      <c r="D88" s="19"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4401,46 +5603,159 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultColWidth="8.66923076923077" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="7"/>
+  <dimension ref="A1:G149"/>
+  <sheetFormatPr defaultColWidth="8.66923076923077" defaultRowHeight="15.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="25.2538461538462" style="2" customWidth="1"/>
-    <col min="2" max="2" width="19.8307692307692" style="2" customWidth="1"/>
-    <col min="3" max="3" width="5.66923076923077" style="2" customWidth="1"/>
-    <col min="4" max="4" width="7.08461538461538" style="2" customWidth="1"/>
-    <col min="5" max="5" width="7.75384615384615" style="2" customWidth="1"/>
-    <col min="6" max="6" width="12.1692307692308" style="2" customWidth="1"/>
-    <col min="7" max="8" width="4.5" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="8.66923076923077" style="2"/>
+    <col min="1" max="1" width="4.30769230769231" style="5" customWidth="1"/>
+    <col min="2" max="4" width="4.15384615384615" style="6" customWidth="1"/>
+    <col min="5" max="5" width="82.6538461538462" style="7" customWidth="1"/>
+    <col min="6" max="6" width="12.1692307692308" style="8" customWidth="1"/>
+    <col min="7" max="8" width="4.5" style="8" customWidth="1"/>
+    <col min="9" max="16384" width="8.66923076923077" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="7:7">
-      <c r="G1" s="3"/>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>267</v>
+    <row r="1" spans="2:7">
+      <c r="B1" s="9" t="s">
+        <v>323</v>
+      </c>
+      <c r="G1" s="10"/>
+    </row>
+    <row r="2" spans="7:7">
+      <c r="G2" s="10"/>
+    </row>
+    <row r="4" spans="2:2">
+      <c r="B4" s="6" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="5">
+        <v>1</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2">
+      <c r="B11"/>
+    </row>
+    <row r="37" ht="52.5" spans="5:5">
+      <c r="E37" s="11" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="38" ht="35" spans="5:5">
+      <c r="E38" s="11" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="39" ht="35" spans="5:5">
+      <c r="E39" s="11" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="40" ht="17.5" spans="5:5">
+      <c r="E40" s="11" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="42" spans="2:2">
+      <c r="B42" s="6" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="43" ht="403" spans="5:5">
+      <c r="E43" s="7" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" s="5">
+        <v>2</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="47" ht="31" spans="5:5">
+      <c r="E47" s="7" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="48" ht="17.5" spans="3:3">
+      <c r="C48" s="12" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="49" ht="62" spans="5:5">
+      <c r="E49" s="7" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2">
+      <c r="B51"/>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" s="5">
+        <v>3</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94" s="5">
+        <v>4</v>
+      </c>
+      <c r="B94" s="6" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" s="5">
+        <v>5</v>
+      </c>
+      <c r="B105" s="6" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" s="5">
+        <v>6</v>
+      </c>
+      <c r="B116" s="6" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127" s="5">
+        <v>7</v>
+      </c>
+      <c r="B127" s="6" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
+      <c r="A138" s="5">
+        <v>8</v>
+      </c>
+      <c r="B138" s="6" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149" s="5">
+        <v>9</v>
+      </c>
+      <c r="B149" s="6" t="s">
+        <v>342</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="142" orientation="portrait"/>
   <headerFooter/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4462,22 +5777,22 @@
   <sheetData>
     <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
-        <v>262</v>
+        <v>294</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>263</v>
+        <v>295</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>264</v>
+        <v>296</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>265</v>
+        <v>297</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>266</v>
+        <v>298</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>267</v>
+        <v>299</v>
       </c>
     </row>
     <row r="3" ht="14.75"/>

--- a/p/ds_25/apache-spark/topic-list_ap-spk.xlsx
+++ b/p/ds_25/apache-spark/topic-list_ap-spk.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="15650" windowHeight="17600" tabRatio="698" activeTab="5"/>
+    <workbookView windowWidth="29000" windowHeight="13120" tabRatio="698" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="what" sheetId="21" r:id="rId1"/>
@@ -79,25 +79,31 @@
   </si>
   <si>
     <r>
-      <t>You could also describe Spark as a distributed, data processing engine for </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
+      <rPr>
         <sz val="12"/>
         <color rgb="FF333333"/>
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t>batch and streaming modes</t>
-    </r>
-    <r>
-      <rPr>
+      <t>You could also describe Spark as a distributed, data processing engine for </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
         <sz val="12"/>
         <color rgb="FF333333"/>
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
+      <t>batch and streaming modes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t> featuring SQL queries, graph processing, and Machine Learning. + Spark R</t>
     </r>
   </si>
@@ -424,6 +430,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">Datasets and DataFrames
 </t>
     </r>
@@ -452,6 +464,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>A DataFrame is a Dataset organized into named columns. It is conceptually equivalent to a table in a relational database or a data frame in R/Python,</t>
     </r>
     <r>
@@ -3197,24 +3216,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10.2"/>
+      <color rgb="FF161616"/>
+      <name val="Consolas"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.2"/>
+      <color rgb="FF1F2328"/>
+      <name val="var(--fontStack-monospace"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <i/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF333333"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10.2"/>
-      <color rgb="FF161616"/>
-      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
@@ -3227,7 +3245,14 @@
       <i/>
       <sz val="12"/>
       <color rgb="FF161616"/>
-      <name val="Segoe UI"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF333333"/>
+      <name val="Calibri"/>
       <charset val="134"/>
     </font>
     <font>
@@ -3238,9 +3263,10 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10.2"/>
-      <color rgb="FF1F2328"/>
-      <name val="var(--fontStack-monospace"/>
+      <b/>
+      <i/>
+      <sz val="12"/>
+      <name val="Calibri"/>
       <charset val="134"/>
     </font>
     <font>
@@ -3253,14 +3279,7 @@
       <i/>
       <sz val="12"/>
       <color rgb="FF161616"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <sz val="12"/>
-      <name val="Calibri"/>
+      <name val="Segoe UI"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -3742,7 +3761,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3778,9 +3797,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -3845,9 +3861,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -3858,7 +3871,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -4403,335 +4415,334 @@
   <dimension ref="A1:B127"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="15.5" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="1.08461538461538" style="53" customWidth="1"/>
-    <col min="2" max="2" width="93.1307692307692" style="49" customWidth="1"/>
-    <col min="3" max="3" width="4.53846153846154" style="38" customWidth="1"/>
-    <col min="4" max="4" width="4.46153846153846" style="38" customWidth="1"/>
-    <col min="5" max="5" width="30.6153846153846" style="38" customWidth="1"/>
-    <col min="6" max="16384" width="9.23076923076923" style="38"/>
+    <col min="1" max="1" width="1.08461538461538" style="38" customWidth="1"/>
+    <col min="2" max="2" width="93.1307692307692" style="47" customWidth="1"/>
+    <col min="3" max="4" width="3.52307692307692" style="37" customWidth="1"/>
+    <col min="5" max="5" width="30.6153846153846" style="37" customWidth="1"/>
+    <col min="6" max="16384" width="9.23076923076923" style="37"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:2">
-      <c r="B1" s="51" t="s">
+      <c r="B1" s="49" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="2:2">
-      <c r="B2" s="51"/>
+      <c r="B2" s="49"/>
     </row>
     <row r="3" ht="62" spans="2:2">
-      <c r="B3" s="54" t="s">
+      <c r="B3" s="51" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="16" ht="31" spans="2:2">
-      <c r="B16" s="55" t="s">
+      <c r="B16" s="52" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="18" ht="62" spans="2:2">
-      <c r="B18" s="49" t="s">
+      <c r="B18" s="47" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="19" spans="2:2">
-      <c r="B19" s="49" t="s">
+      <c r="B19" s="47" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="20" spans="2:2">
-      <c r="B20" s="49" t="s">
+      <c r="B20" s="47" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="21" ht="46.5" spans="2:2">
-      <c r="B21" s="49" t="s">
+      <c r="B21" s="47" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="47" t="s">
+      <c r="A23" s="46" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="24" spans="2:2">
-      <c r="B24" s="49" t="s">
+      <c r="B24" s="47" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="25" ht="46.5" spans="2:2">
-      <c r="B25" s="49" t="s">
+      <c r="B25" s="47" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="26" spans="2:2">
-      <c r="B26" s="49" t="s">
+      <c r="B26" s="47" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="27" ht="31" spans="2:2">
-      <c r="B27" s="49" t="s">
+      <c r="B27" s="47" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="29" ht="31" spans="2:2">
-      <c r="B29" s="49" t="s">
+      <c r="B29" s="47" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="53" t="s">
+      <c r="A31" s="38" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="32" ht="31" spans="2:2">
-      <c r="B32" s="49" t="s">
+      <c r="B32" s="47" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="33" ht="31" spans="2:2">
-      <c r="B33" s="49" t="s">
+      <c r="B33" s="47" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="36" spans="2:2">
-      <c r="B36" s="51" t="s">
+      <c r="B36" s="49" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="37" spans="2:2">
-      <c r="B37" s="49" t="s">
+      <c r="B37" s="47" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="38" spans="2:2">
-      <c r="B38" s="49" t="s">
+      <c r="B38" s="47" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="40" spans="2:2">
-      <c r="B40" s="56" t="s">
+      <c r="B40" s="53" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="41" ht="77.5" spans="2:2">
-      <c r="B41" s="57" t="s">
+      <c r="B41" s="54" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="43" spans="1:1">
-      <c r="A43" s="53" t="s">
+      <c r="A43" s="38" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="44" spans="2:2">
-      <c r="B44" s="49" t="s">
+      <c r="B44" s="47" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="45" spans="2:2">
-      <c r="B45" s="49" t="s">
+      <c r="B45" s="47" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="46" spans="2:2">
-      <c r="B46" s="49" t="s">
+      <c r="B46" s="47" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="48" spans="1:1">
-      <c r="A48" s="53" t="s">
+      <c r="A48" s="38" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="49" spans="2:2">
-      <c r="B49" s="49" t="s">
+      <c r="B49" s="47" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="50" spans="2:2">
-      <c r="B50" s="49" t="s">
+      <c r="B50" s="47" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="51" spans="2:2">
-      <c r="B51" s="49" t="s">
+      <c r="B51" s="47" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="53" spans="1:1">
-      <c r="A53" s="53" t="s">
+      <c r="A53" s="38" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="54" spans="2:2">
-      <c r="B54" s="49" t="s">
+      <c r="B54" s="47" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="55" spans="2:2">
-      <c r="B55" s="49" t="s">
+      <c r="B55" s="47" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="56" spans="2:2">
-      <c r="B56" s="49" t="s">
+      <c r="B56" s="47" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="57" spans="2:2">
-      <c r="B57" s="49" t="s">
+      <c r="B57" s="47" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="59" spans="1:1">
-      <c r="A59" s="53" t="s">
+      <c r="A59" s="38" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="60" spans="2:2">
-      <c r="B60" s="49" t="s">
+      <c r="B60" s="47" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="61" spans="2:2">
-      <c r="B61" s="49" t="s">
+      <c r="B61" s="47" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="62" spans="2:2">
-      <c r="B62" s="49" t="s">
+      <c r="B62" s="47" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="65" spans="1:1">
-      <c r="A65" s="53" t="s">
+      <c r="A65" s="38" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="66" spans="2:2">
-      <c r="B66" s="49" t="s">
+      <c r="B66" s="47" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="68" spans="1:1">
-      <c r="A68" s="47" t="s">
+      <c r="A68" s="46" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="69" spans="2:2">
-      <c r="B69" s="49" t="s">
+      <c r="B69" s="47" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="70" spans="2:2">
-      <c r="B70" s="49" t="s">
+      <c r="B70" s="47" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="71" spans="2:2">
-      <c r="B71" s="49" t="s">
+      <c r="B71" s="47" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="72" spans="2:2">
-      <c r="B72" s="49" t="s">
+      <c r="B72" s="47" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="73" spans="2:2">
-      <c r="B73" s="49" t="s">
+      <c r="B73" s="47" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="74" spans="2:2">
-      <c r="B74" s="49" t="s">
+      <c r="B74" s="47" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="75" spans="2:2">
-      <c r="B75" s="49" t="s">
+      <c r="B75" s="47" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="106" spans="2:2">
-      <c r="B106" s="51" t="s">
+      <c r="B106" s="49" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="107" spans="2:2">
-      <c r="B107" s="49" t="s">
+      <c r="B107" s="47" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="109" ht="31" spans="2:2">
-      <c r="B109" s="58" t="s">
+      <c r="B109" s="55" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="112" spans="2:2">
-      <c r="B112" s="59" t="s">
+      <c r="B112" s="56" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="113" spans="2:2">
-      <c r="B113" s="49" t="s">
+      <c r="B113" s="47" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="114" ht="31" spans="2:2">
-      <c r="B114" s="60" t="s">
+      <c r="B114" s="57" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="115" spans="2:2">
-      <c r="B115" s="38"/>
+      <c r="B115" s="37"/>
     </row>
     <row r="116" ht="31" spans="2:2">
-      <c r="B116" s="60" t="s">
+      <c r="B116" s="57" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="117" spans="2:2">
-      <c r="B117" s="38"/>
+      <c r="B117" s="37"/>
     </row>
     <row r="118" spans="2:2">
-      <c r="B118" s="60" t="s">
+      <c r="B118" s="57" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="119" spans="2:2">
-      <c r="B119" s="61" t="s">
+      <c r="B119" s="58" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="120" spans="2:2">
-      <c r="B120" s="61" t="s">
+      <c r="B120" s="58" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="121" spans="2:2">
-      <c r="B121" s="61" t="s">
+      <c r="B121" s="58" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="122" ht="31" spans="2:2">
-      <c r="B122" s="61" t="s">
+      <c r="B122" s="58" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="123" spans="2:2">
-      <c r="B123" s="61" t="s">
+      <c r="B123" s="58" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="124" spans="2:2">
-      <c r="B124" s="61" t="s">
+      <c r="B124" s="58" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="125" ht="31" spans="2:2">
-      <c r="B125" s="61" t="s">
+      <c r="B125" s="58" t="s">
         <v>62</v>
       </c>
     </row>
@@ -4752,108 +4763,108 @@
   <dimension ref="A1:D34"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="15.5" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="3.39230769230769" style="45" customWidth="1"/>
-    <col min="2" max="2" width="2.94615384615385" style="46" customWidth="1"/>
-    <col min="3" max="3" width="2.88461538461538" style="46" customWidth="1"/>
-    <col min="4" max="4" width="83.9692307692308" style="46" customWidth="1"/>
-    <col min="5" max="16384" width="9.23076923076923" style="46"/>
+    <col min="1" max="1" width="3.39230769230769" style="44" customWidth="1"/>
+    <col min="2" max="2" width="2.94615384615385" style="45" customWidth="1"/>
+    <col min="3" max="3" width="2.88461538461538" style="45" customWidth="1"/>
+    <col min="4" max="4" width="83.9692307692308" style="45" customWidth="1"/>
+    <col min="5" max="16384" width="9.23076923076923" style="45"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:2">
-      <c r="B1" s="47" t="s">
+      <c r="B1" s="46" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="2" spans="2:2">
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="46" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="3" spans="2:2">
-      <c r="B3" s="30"/>
+      <c r="B3" s="29"/>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="46" t="s">
+      <c r="A4" s="45" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="46" t="s">
+      <c r="A5" s="45" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="46" t="s">
+      <c r="A6" s="45" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="7" ht="46.5" spans="4:4">
-      <c r="D7" s="48" t="s">
+      <c r="D7" s="11" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="8" ht="80" customHeight="1" spans="4:4">
-      <c r="D8" s="49" t="s">
+      <c r="D8" s="47" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="9" ht="46.5" spans="4:4">
-      <c r="D9" s="50" t="s">
+      <c r="D9" s="48" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="10" ht="108.5" spans="4:4">
-      <c r="D10" s="51" t="s">
+    <row r="10" ht="93" spans="4:4">
+      <c r="D10" s="49" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="11" spans="4:4">
-      <c r="D11" s="49" t="s">
+      <c r="D11" s="47" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="13" spans="4:4">
-      <c r="D13" s="46" t="s">
+      <c r="D13" s="45" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="17" ht="17.5" spans="2:2">
-      <c r="B17" s="52" t="s">
+      <c r="B17" s="50" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="18" ht="35" spans="2:4">
-      <c r="B18" s="52"/>
+      <c r="B18" s="50"/>
       <c r="D18" s="9" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="19" ht="17.5" spans="3:3">
-      <c r="C19" s="52" t="s">
+      <c r="C19" s="50" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="20" ht="17.5" spans="3:4">
-      <c r="C20" s="52"/>
-      <c r="D20" s="49"/>
+      <c r="C20" s="50"/>
+      <c r="D20" s="47"/>
     </row>
     <row r="21" spans="3:3">
-      <c r="C21" s="46" t="s">
+      <c r="C21" s="45" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="22" spans="3:3">
-      <c r="C22" s="46" t="s">
+      <c r="C22" s="45" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="23" spans="3:3">
-      <c r="C23" s="46" t="s">
+      <c r="C23" s="45" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="26" ht="17.5" spans="2:2">
-      <c r="B26" s="52" t="s">
+      <c r="B26" s="50" t="s">
         <v>80</v>
       </c>
     </row>
@@ -4863,7 +4874,7 @@
       </c>
     </row>
     <row r="30" ht="35" spans="2:4">
-      <c r="B30" s="46" t="s">
+      <c r="B30" s="45" t="s">
         <v>82</v>
       </c>
       <c r="D30" s="9" t="s">
@@ -4903,30 +4914,30 @@
   <dimension ref="A1:G200"/>
   <sheetFormatPr defaultColWidth="8.66923076923077" defaultRowHeight="15.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="3.07692307692308" style="35" customWidth="1"/>
-    <col min="2" max="4" width="4.15384615384615" style="36" customWidth="1"/>
-    <col min="5" max="5" width="82.6538461538462" style="37" customWidth="1"/>
-    <col min="6" max="6" width="12.1692307692308" style="38" customWidth="1"/>
-    <col min="7" max="8" width="4.5" style="38" customWidth="1"/>
-    <col min="9" max="16384" width="8.66923076923077" style="38"/>
+    <col min="1" max="1" width="3.07692307692308" style="34" customWidth="1"/>
+    <col min="2" max="4" width="4.15384615384615" style="35" customWidth="1"/>
+    <col min="5" max="5" width="82.6538461538462" style="36" customWidth="1"/>
+    <col min="6" max="6" width="12.1692307692308" style="37" customWidth="1"/>
+    <col min="7" max="8" width="4.5" style="37" customWidth="1"/>
+    <col min="9" max="16384" width="8.66923076923077" style="37"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:7">
-      <c r="B1" s="39" t="s">
+      <c r="B1" s="38" t="s">
         <v>88</v>
       </c>
-      <c r="G1" s="40"/>
+      <c r="G1" s="39"/>
     </row>
     <row r="2" spans="2:2">
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="35" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="35">
+      <c r="A5" s="34">
         <v>1</v>
       </c>
-      <c r="B5" s="36" t="s">
+      <c r="B5" s="35" t="s">
         <v>90</v>
       </c>
     </row>
@@ -4934,75 +4945,75 @@
       <c r="B6"/>
     </row>
     <row r="32" ht="52.5" spans="5:5">
-      <c r="E32" s="41" t="s">
+      <c r="E32" s="40" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="33" ht="35" spans="5:5">
-      <c r="E33" s="41" t="s">
+      <c r="E33" s="40" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="34" ht="35" spans="5:5">
-      <c r="E34" s="41" t="s">
+      <c r="E34" s="40" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="35" ht="17.5" spans="5:5">
-      <c r="E35" s="41" t="s">
+      <c r="E35" s="40" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="37" spans="2:2">
-      <c r="B37" s="36" t="s">
+      <c r="B37" s="35" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="38" ht="403" spans="5:5">
-      <c r="E38" s="37" t="s">
+      <c r="E38" s="36" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="40" ht="232.5" spans="5:5">
-      <c r="E40" s="42" t="s">
+      <c r="E40" s="41" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="42" spans="3:3">
-      <c r="C42" s="36" t="s">
+      <c r="C42" s="35" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="43" spans="3:3">
-      <c r="C43" s="36" t="s">
+      <c r="C43" s="35" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="44" spans="3:3">
-      <c r="C44" s="36" t="s">
+      <c r="C44" s="35" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="35">
+      <c r="A46" s="34">
         <v>2</v>
       </c>
-      <c r="B46" s="36" t="s">
+      <c r="B46" s="35" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="47" ht="31" spans="5:5">
-      <c r="E47" s="37" t="s">
+      <c r="E47" s="36" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="48" ht="17.5" spans="3:3">
-      <c r="C48" s="43" t="s">
+      <c r="C48" s="42" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="49" ht="62" spans="5:5">
-      <c r="E49" s="37" t="s">
+      <c r="E49" s="36" t="s">
         <v>104</v>
       </c>
     </row>
@@ -5010,12 +5021,12 @@
       <c r="B51"/>
     </row>
     <row r="83" spans="2:2">
-      <c r="B83" s="36" t="s">
+      <c r="B83" s="35" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="84" ht="35" spans="5:5">
-      <c r="E84" s="44" t="s">
+      <c r="E84" s="43" t="s">
         <v>106</v>
       </c>
     </row>
@@ -5023,22 +5034,22 @@
       <c r="E85"/>
     </row>
     <row r="86" ht="17.5" spans="5:5">
-      <c r="E86" s="44" t="s">
+      <c r="E86" s="43" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="87" ht="17.5" spans="5:5">
-      <c r="E87" s="41" t="s">
+      <c r="E87" s="40" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="88" ht="17.5" spans="5:5">
-      <c r="E88" s="41" t="s">
+      <c r="E88" s="40" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="90" ht="52.5" spans="5:5">
-      <c r="E90" s="44" t="s">
+      <c r="E90" s="43" t="s">
         <v>110</v>
       </c>
     </row>
@@ -5046,635 +5057,635 @@
       <c r="E91"/>
     </row>
     <row r="92" ht="52.5" spans="5:5">
-      <c r="E92" s="44" t="s">
+      <c r="E92" s="43" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="94" spans="2:2">
-      <c r="B94" s="36" t="s">
+      <c r="B94" s="35" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="95" spans="2:6">
-      <c r="B95" s="39" t="s">
+      <c r="B95" s="38" t="s">
         <v>113</v>
       </c>
-      <c r="C95" s="39"/>
-      <c r="D95" s="39" t="s">
+      <c r="C95" s="38"/>
+      <c r="D95" s="38" t="s">
         <v>114</v>
       </c>
-      <c r="E95" s="39" t="s">
+      <c r="E95" s="38" t="s">
         <v>115</v>
       </c>
-      <c r="F95" s="37"/>
+      <c r="F95" s="36"/>
     </row>
     <row r="96" spans="2:6">
-      <c r="B96" s="36" t="s">
+      <c r="B96" s="35" t="s">
         <v>116</v>
       </c>
-      <c r="D96" s="36" t="s">
+      <c r="D96" s="35" t="s">
         <v>117</v>
       </c>
-      <c r="E96" s="36" t="s">
+      <c r="E96" s="35" t="s">
         <v>118</v>
       </c>
-      <c r="F96" s="37"/>
+      <c r="F96" s="36"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="36" t="s">
+      <c r="B97" s="35" t="s">
         <v>119</v>
       </c>
-      <c r="D97" s="36" t="s">
+      <c r="D97" s="35" t="s">
         <v>120</v>
       </c>
-      <c r="E97" s="36" t="s">
+      <c r="E97" s="35" t="s">
         <v>121</v>
       </c>
-      <c r="F97" s="37"/>
+      <c r="F97" s="36"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="36" t="s">
+      <c r="B98" s="35" t="s">
         <v>122</v>
       </c>
-      <c r="D98" s="36" t="s">
+      <c r="D98" s="35" t="s">
         <v>123</v>
       </c>
-      <c r="E98" s="36" t="s">
+      <c r="E98" s="35" t="s">
         <v>124</v>
       </c>
-      <c r="F98" s="37"/>
+      <c r="F98" s="36"/>
     </row>
     <row r="99" spans="2:6">
-      <c r="B99" s="36" t="s">
+      <c r="B99" s="35" t="s">
         <v>125</v>
       </c>
-      <c r="D99" s="36" t="s">
+      <c r="D99" s="35" t="s">
         <v>126</v>
       </c>
-      <c r="E99" s="36" t="s">
+      <c r="E99" s="35" t="s">
         <v>127</v>
       </c>
-      <c r="F99" s="37"/>
+      <c r="F99" s="36"/>
     </row>
     <row r="100" spans="2:6">
-      <c r="B100" s="36" t="s">
+      <c r="B100" s="35" t="s">
         <v>128</v>
       </c>
-      <c r="D100" s="36" t="s">
+      <c r="D100" s="35" t="s">
         <v>126</v>
       </c>
-      <c r="E100" s="36" t="s">
+      <c r="E100" s="35" t="s">
         <v>129</v>
       </c>
-      <c r="F100" s="37"/>
+      <c r="F100" s="36"/>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="36" t="s">
+      <c r="B101" s="35" t="s">
         <v>130</v>
       </c>
-      <c r="D101" s="36" t="s">
+      <c r="D101" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="E101" s="36" t="s">
+      <c r="E101" s="35" t="s">
         <v>132</v>
       </c>
-      <c r="F101" s="37"/>
+      <c r="F101" s="36"/>
     </row>
     <row r="102" spans="2:6">
-      <c r="B102" s="36" t="s">
+      <c r="B102" s="35" t="s">
         <v>133</v>
       </c>
-      <c r="D102" s="36" t="s">
+      <c r="D102" s="35" t="s">
         <v>134</v>
       </c>
-      <c r="E102" s="36"/>
-      <c r="F102" s="37"/>
+      <c r="E102" s="35"/>
+      <c r="F102" s="36"/>
     </row>
     <row r="103" spans="2:6">
-      <c r="B103" s="36" t="s">
+      <c r="B103" s="35" t="s">
         <v>135</v>
       </c>
-      <c r="E103" s="36"/>
-      <c r="F103" s="37"/>
+      <c r="E103" s="35"/>
+      <c r="F103" s="36"/>
     </row>
     <row r="104" spans="2:6">
-      <c r="B104" s="36" t="s">
+      <c r="B104" s="35" t="s">
         <v>136</v>
       </c>
-      <c r="E104" s="36"/>
-      <c r="F104" s="37"/>
+      <c r="E104" s="35"/>
+      <c r="F104" s="36"/>
     </row>
     <row r="105" spans="2:6">
-      <c r="B105" s="36" t="s">
+      <c r="B105" s="35" t="s">
         <v>137</v>
       </c>
-      <c r="E105" s="36"/>
-      <c r="F105" s="37"/>
+      <c r="E105" s="35"/>
+      <c r="F105" s="36"/>
     </row>
     <row r="106" spans="2:6">
-      <c r="B106" s="36" t="s">
+      <c r="B106" s="35" t="s">
         <v>138</v>
       </c>
-      <c r="E106" s="36"/>
-      <c r="F106" s="37"/>
+      <c r="E106" s="35"/>
+      <c r="F106" s="36"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="36" t="s">
+      <c r="B107" s="35" t="s">
         <v>139</v>
       </c>
-      <c r="E107" s="36"/>
-      <c r="F107" s="37"/>
+      <c r="E107" s="35"/>
+      <c r="F107" s="36"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="36" t="s">
+      <c r="B108" s="35" t="s">
         <v>140</v>
       </c>
-      <c r="E108" s="36"/>
-      <c r="F108" s="37"/>
+      <c r="E108" s="35"/>
+      <c r="F108" s="36"/>
     </row>
     <row r="109" spans="2:6">
-      <c r="B109" s="36" t="s">
+      <c r="B109" s="35" t="s">
         <v>141</v>
       </c>
-      <c r="E109" s="36"/>
-      <c r="F109" s="37"/>
+      <c r="E109" s="35"/>
+      <c r="F109" s="36"/>
     </row>
     <row r="110" spans="2:6">
-      <c r="B110" s="36" t="s">
+      <c r="B110" s="35" t="s">
         <v>142</v>
       </c>
-      <c r="E110" s="36"/>
-      <c r="F110" s="37"/>
+      <c r="E110" s="35"/>
+      <c r="F110" s="36"/>
     </row>
     <row r="111" spans="2:6">
-      <c r="B111" s="36" t="s">
+      <c r="B111" s="35" t="s">
         <v>143</v>
       </c>
-      <c r="E111" s="36"/>
-      <c r="F111" s="37"/>
+      <c r="E111" s="35"/>
+      <c r="F111" s="36"/>
     </row>
     <row r="112" spans="2:6">
-      <c r="B112" s="36" t="s">
+      <c r="B112" s="35" t="s">
         <v>144</v>
       </c>
-      <c r="E112" s="36"/>
-      <c r="F112" s="37"/>
+      <c r="E112" s="35"/>
+      <c r="F112" s="36"/>
     </row>
     <row r="113" spans="2:6">
-      <c r="B113" s="36" t="s">
+      <c r="B113" s="35" t="s">
         <v>145</v>
       </c>
-      <c r="E113" s="36"/>
-      <c r="F113" s="37"/>
+      <c r="E113" s="35"/>
+      <c r="F113" s="36"/>
     </row>
     <row r="115" spans="2:2">
-      <c r="B115" s="39" t="s">
+      <c r="B115" s="38" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="116" ht="263.5" spans="5:5">
-      <c r="E116" s="37" t="s">
+      <c r="E116" s="36" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="117" spans="2:2">
-      <c r="B117" s="36" t="s">
+      <c r="B117" s="35" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="119" spans="1:2">
-      <c r="A119" s="35">
+      <c r="A119" s="34">
         <v>3</v>
       </c>
-      <c r="B119" s="36" t="s">
+      <c r="B119" s="35" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="120" ht="62" spans="5:5">
-      <c r="E120" s="37" t="s">
+      <c r="E120" s="36" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="122" ht="108.5" spans="5:5">
-      <c r="E122" s="37" t="s">
+      <c r="E122" s="36" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="124" spans="3:3">
-      <c r="C124" s="39" t="s">
+      <c r="C124" s="38" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="125" spans="3:3">
-      <c r="C125" s="36" t="s">
+      <c r="C125" s="35" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="126" spans="3:3">
-      <c r="C126" s="39" t="s">
+      <c r="C126" s="38" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="127" spans="2:5">
-      <c r="B127" s="39" t="s">
+      <c r="B127" s="38" t="s">
         <v>153</v>
       </c>
-      <c r="C127" s="39"/>
-      <c r="D127" s="39" t="s">
+      <c r="C127" s="38"/>
+      <c r="D127" s="38" t="s">
         <v>154</v>
       </c>
-      <c r="E127" s="39" t="s">
+      <c r="E127" s="38" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="128" spans="2:5">
-      <c r="B128" s="36" t="s">
+      <c r="B128" s="35" t="s">
         <v>156</v>
       </c>
-      <c r="D128" s="36" t="s">
+      <c r="D128" s="35" t="s">
         <v>157</v>
       </c>
-      <c r="E128" s="36" t="s">
+      <c r="E128" s="35" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="129" spans="2:5">
-      <c r="B129" s="36" t="s">
+      <c r="B129" s="35" t="s">
         <v>159</v>
       </c>
-      <c r="D129" s="36" t="s">
+      <c r="D129" s="35" t="s">
         <v>160</v>
       </c>
-      <c r="E129" s="36" t="s">
+      <c r="E129" s="35" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="130" spans="2:5">
-      <c r="B130" s="36" t="s">
+      <c r="B130" s="35" t="s">
         <v>162</v>
       </c>
-      <c r="D130" s="36" t="s">
+      <c r="D130" s="35" t="s">
         <v>163</v>
       </c>
-      <c r="E130" s="36" t="s">
+      <c r="E130" s="35" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="131" spans="2:5">
-      <c r="B131" s="36" t="s">
+      <c r="B131" s="35" t="s">
         <v>165</v>
       </c>
-      <c r="D131" s="36" t="s">
+      <c r="D131" s="35" t="s">
         <v>166</v>
       </c>
-      <c r="E131" s="36" t="s">
+      <c r="E131" s="35" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="132" spans="2:5">
-      <c r="B132" s="36" t="s">
+      <c r="B132" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="D132" s="36" t="s">
+      <c r="D132" s="35" t="s">
         <v>168</v>
       </c>
-      <c r="E132" s="36" t="s">
+      <c r="E132" s="35" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="133" spans="2:5">
-      <c r="B133" s="36" t="s">
+      <c r="B133" s="35" t="s">
         <v>169</v>
       </c>
-      <c r="D133" s="36" t="s">
+      <c r="D133" s="35" t="s">
         <v>170</v>
       </c>
-      <c r="E133" s="36" t="s">
+      <c r="E133" s="35" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="134" spans="2:5">
-      <c r="B134" s="36" t="s">
+      <c r="B134" s="35" t="s">
         <v>171</v>
       </c>
-      <c r="D134" s="36" t="s">
+      <c r="D134" s="35" t="s">
         <v>172</v>
       </c>
-      <c r="E134" s="36" t="s">
+      <c r="E134" s="35" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="135" spans="2:5">
-      <c r="B135" s="36" t="s">
+      <c r="B135" s="35" t="s">
         <v>173</v>
       </c>
-      <c r="D135" s="36" t="s">
+      <c r="D135" s="35" t="s">
         <v>174</v>
       </c>
-      <c r="E135" s="36" t="s">
+      <c r="E135" s="35" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="136" spans="2:5">
-      <c r="B136" s="36" t="s">
+      <c r="B136" s="35" t="s">
         <v>176</v>
       </c>
-      <c r="D136" s="36" t="s">
+      <c r="D136" s="35" t="s">
         <v>177</v>
       </c>
-      <c r="E136" s="36" t="s">
+      <c r="E136" s="35" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="137" spans="2:5">
-      <c r="B137" s="36" t="s">
+      <c r="B137" s="35" t="s">
         <v>179</v>
       </c>
-      <c r="D137" s="36" t="s">
+      <c r="D137" s="35" t="s">
         <v>180</v>
       </c>
-      <c r="E137" s="36" t="s">
+      <c r="E137" s="35" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="138" ht="46.5" spans="5:5">
-      <c r="E138" s="37" t="s">
+      <c r="E138" s="36" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="140" spans="1:2">
-      <c r="A140" s="35">
+      <c r="A140" s="34">
         <v>4</v>
       </c>
-      <c r="B140" s="36" t="s">
+      <c r="B140" s="35" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="141" spans="2:2">
-      <c r="B141" s="36" t="s">
+      <c r="B141" s="35" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="142" spans="2:2">
-      <c r="B142" s="36" t="s">
+      <c r="B142" s="35" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="143" spans="2:2">
-      <c r="B143" s="36" t="s">
+      <c r="B143" s="35" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="144" ht="46.5" spans="5:5">
-      <c r="E144" s="37" t="s">
+      <c r="E144" s="36" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="145" ht="62" spans="5:5">
-      <c r="E145" s="37" t="s">
+      <c r="E145" s="36" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="146" ht="31" spans="5:5">
-      <c r="E146" s="37" t="s">
+      <c r="E146" s="36" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="147" spans="5:5">
-      <c r="E147" s="37" t="s">
+      <c r="E147" s="36" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="149" spans="1:2">
-      <c r="A149" s="35">
+      <c r="A149" s="34">
         <v>6</v>
       </c>
-      <c r="B149" s="36" t="s">
+      <c r="B149" s="35" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="150" ht="31" spans="5:5">
-      <c r="E150" s="37" t="s">
+      <c r="E150" s="36" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="151" ht="17.5" spans="5:5">
-      <c r="E151" s="43" t="s">
+      <c r="E151" s="42" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="152" spans="3:3">
-      <c r="C152" s="36" t="s">
+      <c r="C152" s="35" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="153" spans="3:3">
-      <c r="C153" s="36" t="s">
+      <c r="C153" s="35" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="155" ht="139.5" spans="5:5">
-      <c r="E155" s="37" t="s">
+      <c r="E155" s="36" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="156" ht="31" spans="5:5">
-      <c r="E156" s="37" t="s">
+      <c r="E156" s="36" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="158" spans="2:5">
-      <c r="B158" s="39" t="s">
+      <c r="B158" s="38" t="s">
         <v>198</v>
       </c>
-      <c r="C158" s="39"/>
-      <c r="D158" s="39"/>
-      <c r="E158" s="42" t="s">
+      <c r="C158" s="38"/>
+      <c r="D158" s="38"/>
+      <c r="E158" s="41" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="159" ht="31" spans="2:5">
-      <c r="B159" s="36" t="s">
+      <c r="B159" s="35" t="s">
         <v>200</v>
       </c>
-      <c r="E159" s="37" t="s">
+      <c r="E159" s="36" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="160" ht="31" spans="2:5">
-      <c r="B160" s="36" t="s">
+      <c r="B160" s="35" t="s">
         <v>202</v>
       </c>
-      <c r="E160" s="37" t="s">
+      <c r="E160" s="36" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="161" ht="31" spans="2:5">
-      <c r="B161" s="36" t="s">
+      <c r="B161" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="E161" s="37" t="s">
+      <c r="E161" s="36" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="162" spans="2:2">
-      <c r="B162" s="36" t="s">
+      <c r="B162" s="35" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="163" ht="31" spans="2:5">
-      <c r="B163" s="36" t="s">
+      <c r="B163" s="35" t="s">
         <v>207</v>
       </c>
-      <c r="E163" s="37" t="s">
+      <c r="E163" s="36" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="164" spans="2:2">
-      <c r="B164" s="36" t="s">
+      <c r="B164" s="35" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="165" spans="2:5">
-      <c r="B165" s="36" t="s">
+      <c r="B165" s="35" t="s">
         <v>209</v>
       </c>
-      <c r="E165" s="37" t="s">
+      <c r="E165" s="36" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="166" spans="2:5">
-      <c r="B166" s="36" t="s">
+      <c r="B166" s="35" t="s">
         <v>211</v>
       </c>
-      <c r="E166" s="37" t="s">
+      <c r="E166" s="36" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="167" ht="31" spans="2:5">
-      <c r="B167" s="36" t="s">
+      <c r="B167" s="35" t="s">
         <v>213</v>
       </c>
-      <c r="E167" s="37" t="s">
+      <c r="E167" s="36" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="169" ht="124" spans="5:5">
-      <c r="E169" s="37" t="s">
+      <c r="E169" s="36" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="171" spans="4:4">
-      <c r="D171" s="39" t="s">
+      <c r="D171" s="38" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="172" ht="232.5" spans="5:5">
-      <c r="E172" s="37" t="s">
+      <c r="E172" s="36" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="174" spans="4:4">
-      <c r="D174" s="39" t="s">
+      <c r="D174" s="38" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="175" ht="62" spans="5:5">
-      <c r="E175" s="37" t="s">
+      <c r="E175" s="36" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="177" spans="2:2">
-      <c r="B177" s="36" t="s">
+      <c r="B177" s="35" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="178" spans="1:2">
-      <c r="A178" s="35">
+      <c r="A178" s="34">
         <v>7</v>
       </c>
-      <c r="B178" s="39" t="s">
+      <c r="B178" s="38" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="179" spans="2:2">
-      <c r="B179" s="36" t="s">
+      <c r="B179" s="35" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="180" ht="93" spans="5:5">
-      <c r="E180" s="37" t="s">
+      <c r="E180" s="36" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="181" spans="3:3">
-      <c r="C181" s="36" t="s">
+      <c r="C181" s="35" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="182" ht="310" spans="5:5">
-      <c r="E182" s="37" t="s">
+      <c r="E182" s="36" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="184" ht="139.5" spans="5:5">
-      <c r="E184" s="37" t="s">
+      <c r="E184" s="36" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="186" spans="3:3">
-      <c r="C186" s="36" t="s">
+      <c r="C186" s="35" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="187" ht="62" spans="5:5">
-      <c r="E187" s="37" t="s">
+      <c r="E187" s="36" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="189" ht="46.5" spans="5:5">
-      <c r="E189" s="37" t="s">
+      <c r="E189" s="36" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="191" ht="155" spans="5:5">
-      <c r="E191" s="37" t="s">
+      <c r="E191" s="36" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="193" spans="4:4">
-      <c r="D193" s="36" t="s">
+      <c r="D193" s="35" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="194" ht="31" spans="5:5">
-      <c r="E194" s="37" t="s">
+      <c r="E194" s="36" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="195" spans="5:5">
-      <c r="E195" s="37" t="s">
+      <c r="E195" s="36" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="196" spans="5:5">
-      <c r="E196" s="37" t="s">
+      <c r="E196" s="36" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="198" spans="1:2">
-      <c r="A198" s="35">
+      <c r="A198" s="34">
         <v>8</v>
       </c>
-      <c r="B198" s="36" t="s">
+      <c r="B198" s="35" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="200" spans="1:2">
-      <c r="A200" s="35">
+      <c r="A200" s="34">
         <v>9</v>
       </c>
-      <c r="B200" s="36" t="s">
+      <c r="B200" s="35" t="s">
         <v>236</v>
       </c>
     </row>
@@ -5701,7 +5712,7 @@
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="28" t="s">
         <v>238</v>
       </c>
     </row>
@@ -5716,7 +5727,7 @@
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="29" t="s">
+      <c r="A8" s="28" t="s">
         <v>241</v>
       </c>
     </row>
@@ -5741,7 +5752,7 @@
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="29" t="s">
+      <c r="A14" s="28" t="s">
         <v>246</v>
       </c>
     </row>
@@ -5756,7 +5767,7 @@
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="29" t="s">
+      <c r="A18" s="28" t="s">
         <v>249</v>
       </c>
     </row>
@@ -5776,7 +5787,7 @@
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="29" t="s">
+      <c r="A23" s="28" t="s">
         <v>252</v>
       </c>
     </row>
@@ -5816,7 +5827,7 @@
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="29" t="s">
+      <c r="A32" s="28" t="s">
         <v>260</v>
       </c>
     </row>
@@ -5901,7 +5912,7 @@
       </c>
     </row>
     <row r="49" hidden="1" spans="1:1">
-      <c r="A49" s="30" t="s">
+      <c r="A49" s="29" t="s">
         <v>277</v>
       </c>
     </row>
@@ -5926,7 +5937,7 @@
       </c>
     </row>
     <row r="55" spans="1:1">
-      <c r="A55" s="29" t="s">
+      <c r="A55" s="28" t="s">
         <v>282</v>
       </c>
     </row>
@@ -5967,7 +5978,7 @@
       </c>
     </row>
     <row r="65" spans="1:1">
-      <c r="A65" s="29" t="s">
+      <c r="A65" s="28" t="s">
         <v>288</v>
       </c>
     </row>
@@ -6027,7 +6038,7 @@
       </c>
     </row>
     <row r="78" spans="1:1">
-      <c r="A78" s="29" t="s">
+      <c r="A78" s="28" t="s">
         <v>298</v>
       </c>
     </row>
@@ -6118,36 +6129,36 @@
       </c>
     </row>
     <row r="97" spans="1:2">
-      <c r="A97" s="31"/>
-      <c r="B97" s="31"/>
+      <c r="A97" s="30"/>
+      <c r="B97" s="30"/>
     </row>
     <row r="98" spans="1:2">
-      <c r="A98" s="32" t="s">
+      <c r="A98" s="31" t="s">
         <v>314</v>
       </c>
-      <c r="B98" s="31"/>
+      <c r="B98" s="30"/>
     </row>
     <row r="99" spans="1:2">
-      <c r="A99" s="33" t="s">
+      <c r="A99" s="32" t="s">
         <v>315</v>
       </c>
-      <c r="B99" s="31"/>
+      <c r="B99" s="30"/>
     </row>
     <row r="100" spans="1:2">
-      <c r="A100" s="33" t="s">
+      <c r="A100" s="32" t="s">
         <v>316</v>
       </c>
-      <c r="B100" s="31"/>
+      <c r="B100" s="30"/>
     </row>
     <row r="101" spans="1:2">
-      <c r="A101" s="34"/>
-      <c r="B101" s="31"/>
+      <c r="A101" s="33"/>
+      <c r="B101" s="30"/>
     </row>
     <row r="102" spans="2:2">
-      <c r="B102" s="31"/>
+      <c r="B102" s="30"/>
     </row>
     <row r="104" spans="1:1">
-      <c r="A104" s="31" t="s">
+      <c r="A104" s="30" t="s">
         <v>317</v>
       </c>
     </row>
@@ -6169,43 +6180,43 @@
   <dimension ref="A1:H88"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="27.3307692307692" style="21" customWidth="1"/>
-    <col min="2" max="2" width="19.8307692307692" style="22" customWidth="1"/>
-    <col min="3" max="3" width="2.41538461538462" style="21" customWidth="1"/>
-    <col min="4" max="4" width="3.33076923076923" style="21" customWidth="1"/>
-    <col min="5" max="5" width="12.6692307692308" style="21" customWidth="1"/>
-    <col min="6" max="6" width="12.1692307692308" style="21" customWidth="1"/>
-    <col min="7" max="8" width="4.5" style="21" customWidth="1"/>
-    <col min="9" max="16384" width="11" style="21"/>
+    <col min="1" max="1" width="27.3307692307692" style="20" customWidth="1"/>
+    <col min="2" max="2" width="19.8307692307692" style="21" customWidth="1"/>
+    <col min="3" max="3" width="2.41538461538462" style="20" customWidth="1"/>
+    <col min="4" max="4" width="3.33076923076923" style="20" customWidth="1"/>
+    <col min="5" max="5" width="12.6692307692308" style="20" customWidth="1"/>
+    <col min="6" max="6" width="12.1692307692308" style="20" customWidth="1"/>
+    <col min="7" max="8" width="4.5" style="20" customWidth="1"/>
+    <col min="9" max="16384" width="11" style="20"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:2">
-      <c r="B1" s="22" t="s">
+      <c r="B1" s="21" t="s">
         <v>319</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="20" t="s">
         <v>320</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="21" t="s">
         <v>321</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="20" t="s">
         <v>322</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="20" t="s">
         <v>323</v>
       </c>
-      <c r="G2" s="23" t="s">
+      <c r="G2" s="22" t="s">
         <v>324</v>
       </c>
-      <c r="H2" s="21" t="s">
+      <c r="H2" s="20" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="4" spans="2:2">
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="21" t="s">
         <v>326</v>
       </c>
     </row>
@@ -6215,7 +6226,7 @@
       </c>
     </row>
     <row r="6" ht="15.5" spans="3:4">
-      <c r="C6" s="22"/>
+      <c r="C6" s="21"/>
       <c r="D6" t="s">
         <v>328</v>
       </c>
@@ -6231,32 +6242,32 @@
       </c>
     </row>
     <row r="9" ht="15.5" spans="1:4">
-      <c r="A9" s="24"/>
-      <c r="C9" s="22"/>
+      <c r="A9" s="23"/>
+      <c r="C9" s="21"/>
       <c r="D9" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="10" ht="15.5" spans="3:4">
-      <c r="C10" s="22"/>
+      <c r="C10" s="21"/>
       <c r="D10" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="11" ht="15.5" spans="3:4">
-      <c r="C11" s="22"/>
+      <c r="C11" s="21"/>
       <c r="D11" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="12" ht="15.5" spans="3:4">
-      <c r="C12" s="22"/>
+      <c r="C12" s="21"/>
       <c r="D12" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="13" ht="15.5" spans="3:4">
-      <c r="C13" s="22"/>
+      <c r="C13" s="21"/>
       <c r="D13" t="s">
         <v>335</v>
       </c>
@@ -6267,31 +6278,31 @@
       </c>
     </row>
     <row r="15" ht="15.5" spans="3:4">
-      <c r="C15" s="22"/>
+      <c r="C15" s="21"/>
       <c r="D15" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="16" ht="15.5" spans="3:4">
-      <c r="C16" s="22"/>
+      <c r="C16" s="21"/>
       <c r="D16" t="s">
         <v>338</v>
       </c>
     </row>
     <row r="17" ht="15.5" spans="3:4">
-      <c r="C17" s="22"/>
+      <c r="C17" s="21"/>
       <c r="D17" t="s">
         <v>339</v>
       </c>
     </row>
     <row r="18" ht="15.5" spans="3:4">
-      <c r="C18" s="22"/>
+      <c r="C18" s="21"/>
       <c r="D18" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="19" ht="15.5" spans="3:4">
-      <c r="C19" s="22"/>
+      <c r="C19" s="21"/>
       <c r="D19" t="s">
         <v>341</v>
       </c>
@@ -6307,13 +6318,13 @@
       </c>
     </row>
     <row r="22" ht="15.5" spans="3:4">
-      <c r="C22" s="22"/>
+      <c r="C22" s="21"/>
       <c r="D22" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="23" ht="15.5" spans="3:4">
-      <c r="C23" s="22"/>
+      <c r="C23" s="21"/>
       <c r="D23" t="s">
         <v>345</v>
       </c>
@@ -6324,90 +6335,90 @@
       </c>
     </row>
     <row r="29" spans="3:3">
-      <c r="C29" s="21" t="s">
+      <c r="C29" s="20" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="25"/>
-      <c r="B30" s="26"/>
-      <c r="D30" s="21" t="s">
+      <c r="A30" s="24"/>
+      <c r="B30" s="25"/>
+      <c r="D30" s="20" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="25"/>
-      <c r="B31" s="26"/>
+      <c r="A31" s="24"/>
+      <c r="B31" s="25"/>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="25"/>
-      <c r="B32" s="26"/>
+      <c r="A32" s="24"/>
+      <c r="B32" s="25"/>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="25"/>
+      <c r="A33" s="24"/>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="25"/>
-      <c r="B34" s="26"/>
+      <c r="A34" s="24"/>
+      <c r="B34" s="25"/>
     </row>
     <row r="39" spans="1:1">
-      <c r="A39" s="25"/>
+      <c r="A39" s="24"/>
     </row>
     <row r="40" spans="1:1">
-      <c r="A40" s="25"/>
+      <c r="A40" s="24"/>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="25"/>
+      <c r="A41" s="24"/>
     </row>
     <row r="43" spans="1:1">
-      <c r="A43" s="25"/>
+      <c r="A43" s="24"/>
     </row>
     <row r="56" spans="4:4">
-      <c r="D56" s="27"/>
+      <c r="D56" s="26"/>
     </row>
     <row r="57" spans="4:4">
-      <c r="D57" s="27"/>
+      <c r="D57" s="26"/>
     </row>
     <row r="58" spans="4:4">
-      <c r="D58" s="28"/>
+      <c r="D58" s="27"/>
     </row>
     <row r="61" spans="3:6">
-      <c r="C61" s="25"/>
-      <c r="D61" s="25"/>
-      <c r="E61" s="25"/>
-      <c r="F61" s="25"/>
+      <c r="C61" s="24"/>
+      <c r="D61" s="24"/>
+      <c r="E61" s="24"/>
+      <c r="F61" s="24"/>
     </row>
     <row r="62" spans="3:6">
-      <c r="C62" s="25"/>
-      <c r="D62" s="25"/>
-      <c r="E62" s="25"/>
-      <c r="F62" s="25"/>
+      <c r="C62" s="24"/>
+      <c r="D62" s="24"/>
+      <c r="E62" s="24"/>
+      <c r="F62" s="24"/>
     </row>
     <row r="63" spans="3:6">
-      <c r="C63" s="25"/>
-      <c r="D63" s="25"/>
-      <c r="E63" s="25"/>
-      <c r="F63" s="25"/>
+      <c r="C63" s="24"/>
+      <c r="D63" s="24"/>
+      <c r="E63" s="24"/>
+      <c r="F63" s="24"/>
     </row>
     <row r="64" spans="3:6">
-      <c r="C64" s="25"/>
-      <c r="D64" s="25"/>
-      <c r="F64" s="25"/>
+      <c r="C64" s="24"/>
+      <c r="D64" s="24"/>
+      <c r="F64" s="24"/>
     </row>
     <row r="65" spans="3:6">
-      <c r="C65" s="25"/>
-      <c r="D65" s="25"/>
-      <c r="E65" s="25"/>
-      <c r="F65" s="25"/>
+      <c r="C65" s="24"/>
+      <c r="D65" s="24"/>
+      <c r="E65" s="24"/>
+      <c r="F65" s="24"/>
     </row>
     <row r="66" spans="3:6">
-      <c r="C66" s="25"/>
-      <c r="D66" s="25"/>
-      <c r="E66" s="25"/>
-      <c r="F66" s="25"/>
+      <c r="C66" s="24"/>
+      <c r="D66" s="24"/>
+      <c r="E66" s="24"/>
+      <c r="F66" s="24"/>
     </row>
     <row r="88" spans="4:4">
-      <c r="D88" s="27"/>
+      <c r="D88" s="26"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6422,11 +6433,11 @@
   <dimension ref="A3"/>
   <sheetFormatPr defaultColWidth="8.66923076923077" defaultRowHeight="12.5" outlineLevelRow="2"/>
   <cols>
-    <col min="1" max="16384" width="8.66923076923077" style="20"/>
+    <col min="1" max="16384" width="8.66923076923077" style="19"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:1">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="19" t="s">
         <v>349</v>
       </c>
     </row>
@@ -6453,42 +6464,42 @@
   <dimension ref="A2:H5"/>
   <sheetFormatPr defaultColWidth="8.66923076923077" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="17.2538461538462" style="17" customWidth="1"/>
-    <col min="2" max="2" width="8.66923076923077" style="17"/>
-    <col min="3" max="3" width="5.66923076923077" style="17" customWidth="1"/>
-    <col min="4" max="4" width="7.08461538461538" style="17" customWidth="1"/>
-    <col min="5" max="5" width="7.75384615384615" style="17" customWidth="1"/>
-    <col min="6" max="6" width="23.4692307692308" style="17" customWidth="1"/>
-    <col min="7" max="8" width="4.5" style="17" customWidth="1"/>
-    <col min="9" max="16384" width="8.66923076923077" style="17"/>
+    <col min="1" max="1" width="17.2538461538462" style="16" customWidth="1"/>
+    <col min="2" max="2" width="8.66923076923077" style="16"/>
+    <col min="3" max="3" width="5.66923076923077" style="16" customWidth="1"/>
+    <col min="4" max="4" width="7.08461538461538" style="16" customWidth="1"/>
+    <col min="5" max="5" width="7.75384615384615" style="16" customWidth="1"/>
+    <col min="6" max="6" width="23.4692307692308" style="16" customWidth="1"/>
+    <col min="7" max="8" width="4.5" style="16" customWidth="1"/>
+    <col min="9" max="16384" width="8.66923076923077" style="16"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:8">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="16" t="s">
         <v>320</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="16" t="s">
         <v>321</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="16" t="s">
         <v>322</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="16" t="s">
         <v>323</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="G2" s="17" t="s">
         <v>324</v>
       </c>
-      <c r="H2" s="17" t="s">
+      <c r="H2" s="16" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="3" ht="14.75"/>
     <row r="4" ht="14.75" spans="4:4">
-      <c r="D4" s="19"/>
+      <c r="D4" s="18"/>
     </row>
     <row r="5" ht="14.75" spans="4:4">
-      <c r="D5" s="19"/>
+      <c r="D5" s="18"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7029,7 +7040,7 @@
       <c r="A100" s="13">
         <v>2</v>
       </c>
-      <c r="B100" s="14" t="s">
+      <c r="B100" s="3" t="s">
         <v>422</v>
       </c>
     </row>
@@ -7231,10 +7242,10 @@
       <c r="C137" s="8"/>
     </row>
     <row r="138" spans="1:2">
-      <c r="A138" s="15">
+      <c r="A138" s="14">
         <v>3</v>
       </c>
-      <c r="B138" s="14" t="s">
+      <c r="B138" s="3" t="s">
         <v>445</v>
       </c>
     </row>
@@ -7361,7 +7372,7 @@
       <c r="A161" s="13">
         <v>4</v>
       </c>
-      <c r="B161" s="14" t="s">
+      <c r="B161" s="3" t="s">
         <v>461</v>
       </c>
     </row>
@@ -7458,7 +7469,7 @@
       <c r="A179" s="13">
         <v>5</v>
       </c>
-      <c r="B179" s="14" t="s">
+      <c r="B179" s="3" t="s">
         <v>355</v>
       </c>
     </row>
@@ -7549,7 +7560,7 @@
       <c r="A196" s="13">
         <v>6</v>
       </c>
-      <c r="B196" s="14" t="s">
+      <c r="B196" s="3" t="s">
         <v>481</v>
       </c>
     </row>
@@ -7630,7 +7641,7 @@
       <c r="A211" s="13">
         <v>7</v>
       </c>
-      <c r="B211" s="14" t="s">
+      <c r="B211" s="3" t="s">
         <v>490</v>
       </c>
     </row>
@@ -7743,7 +7754,7 @@
       <c r="A232" s="13">
         <v>8</v>
       </c>
-      <c r="B232" s="14" t="s">
+      <c r="B232" s="3" t="s">
         <v>503</v>
       </c>
     </row>
@@ -7764,7 +7775,7 @@
     </row>
     <row r="236" ht="31" spans="2:3">
       <c r="B236" s="13"/>
-      <c r="C236" s="16" t="s">
+      <c r="C236" s="15" t="s">
         <v>505</v>
       </c>
     </row>

--- a/p/ds_25/apache-spark/topic-list_ap-spk.xlsx
+++ b/p/ds_25/apache-spark/topic-list_ap-spk.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29000" windowHeight="13120" tabRatio="698" activeTab="1"/>
+    <workbookView windowWidth="23040" windowHeight="8960" tabRatio="698" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="what" sheetId="21" r:id="rId1"/>
@@ -2932,7 +2932,7 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
   </numFmts>
-  <fonts count="51">
+  <fonts count="52">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -3030,6 +3030,13 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF161616"/>
+      <name val="Segoe UI"/>
       <charset val="134"/>
     </font>
     <font>
@@ -3216,9 +3223,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <i/>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="10.2"/>
       <color rgb="FF161616"/>
       <name val="Consolas"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color rgb="FF1F2328"/>
+      <name val="Segoe UI"/>
       <charset val="134"/>
     </font>
     <font>
@@ -3228,23 +3249,15 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <i/>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
+      <color rgb="FF161616"/>
+      <name val="Segoe UI"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF4070A0"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="12"/>
-      <color rgb="FF161616"/>
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
@@ -3256,16 +3269,10 @@
       <charset val="134"/>
     </font>
     <font>
-      <i/>
-      <sz val="12"/>
-      <color rgb="FF1F2328"/>
-      <name val="Segoe UI"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <i/>
       <sz val="12"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
@@ -3279,7 +3286,7 @@
       <i/>
       <sz val="12"/>
       <color rgb="FF161616"/>
-      <name val="Segoe UI"/>
+      <name val="Calibri"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -3616,152 +3623,152 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="39" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="40" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="40" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="40" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="40" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="40" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="40" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="40" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="40" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="40" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="40" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="40" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="40" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3830,6 +3837,7 @@
       <alignment readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3842,6 +3850,9 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" indent="1"/>
     </xf>
@@ -3870,29 +3881,30 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
@@ -4117,7 +4129,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="107315" y="19389090"/>
+          <a:off x="107315" y="19370040"/>
           <a:ext cx="8047355" cy="5699125"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4415,334 +4427,334 @@
   <dimension ref="A1:B127"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="15.5" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="1.08461538461538" style="38" customWidth="1"/>
-    <col min="2" max="2" width="93.1307692307692" style="47" customWidth="1"/>
-    <col min="3" max="4" width="3.52307692307692" style="37" customWidth="1"/>
-    <col min="5" max="5" width="30.6153846153846" style="37" customWidth="1"/>
-    <col min="6" max="16384" width="9.23076923076923" style="37"/>
+    <col min="1" max="1" width="1.08461538461538" style="39" customWidth="1"/>
+    <col min="2" max="2" width="93.1307692307692" style="49" customWidth="1"/>
+    <col min="3" max="4" width="3.52307692307692" style="38" customWidth="1"/>
+    <col min="5" max="5" width="30.6153846153846" style="38" customWidth="1"/>
+    <col min="6" max="16384" width="9.23076923076923" style="38"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:2">
-      <c r="B1" s="49" t="s">
+      <c r="B1" s="51" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="2:2">
-      <c r="B2" s="49"/>
+      <c r="B2" s="51"/>
     </row>
     <row r="3" ht="62" spans="2:2">
-      <c r="B3" s="51" t="s">
+      <c r="B3" s="54" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="16" ht="31" spans="2:2">
-      <c r="B16" s="52" t="s">
+      <c r="B16" s="55" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="18" ht="62" spans="2:2">
-      <c r="B18" s="47" t="s">
+      <c r="B18" s="49" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="19" spans="2:2">
-      <c r="B19" s="47" t="s">
+      <c r="B19" s="49" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="20" spans="2:2">
-      <c r="B20" s="47" t="s">
+      <c r="B20" s="49" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="21" ht="46.5" spans="2:2">
-      <c r="B21" s="47" t="s">
+      <c r="B21" s="49" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="46" t="s">
+      <c r="A23" s="48" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="24" spans="2:2">
-      <c r="B24" s="47" t="s">
+      <c r="B24" s="49" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="25" ht="46.5" spans="2:2">
-      <c r="B25" s="47" t="s">
+      <c r="B25" s="49" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="26" spans="2:2">
-      <c r="B26" s="47" t="s">
+      <c r="B26" s="49" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="27" ht="31" spans="2:2">
-      <c r="B27" s="47" t="s">
+      <c r="B27" s="49" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="29" ht="31" spans="2:2">
-      <c r="B29" s="47" t="s">
+      <c r="B29" s="49" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="38" t="s">
+      <c r="A31" s="39" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="32" ht="31" spans="2:2">
-      <c r="B32" s="47" t="s">
+      <c r="B32" s="49" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="33" ht="31" spans="2:2">
-      <c r="B33" s="47" t="s">
+      <c r="B33" s="49" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="36" spans="2:2">
-      <c r="B36" s="49" t="s">
+      <c r="B36" s="51" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="37" spans="2:2">
-      <c r="B37" s="47" t="s">
+      <c r="B37" s="49" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="38" spans="2:2">
-      <c r="B38" s="47" t="s">
+      <c r="B38" s="49" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="40" spans="2:2">
-      <c r="B40" s="53" t="s">
+      <c r="B40" s="56" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="41" ht="77.5" spans="2:2">
-      <c r="B41" s="54" t="s">
+      <c r="B41" s="57" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="43" spans="1:1">
-      <c r="A43" s="38" t="s">
+      <c r="A43" s="39" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="44" spans="2:2">
-      <c r="B44" s="47" t="s">
+      <c r="B44" s="49" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="45" spans="2:2">
-      <c r="B45" s="47" t="s">
+      <c r="B45" s="49" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="46" spans="2:2">
-      <c r="B46" s="47" t="s">
+      <c r="B46" s="49" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="48" spans="1:1">
-      <c r="A48" s="38" t="s">
+      <c r="A48" s="39" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="49" spans="2:2">
-      <c r="B49" s="47" t="s">
+      <c r="B49" s="49" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="50" spans="2:2">
-      <c r="B50" s="47" t="s">
+      <c r="B50" s="49" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="51" spans="2:2">
-      <c r="B51" s="47" t="s">
+      <c r="B51" s="49" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="53" spans="1:1">
-      <c r="A53" s="38" t="s">
+      <c r="A53" s="39" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="54" spans="2:2">
-      <c r="B54" s="47" t="s">
+      <c r="B54" s="49" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="55" spans="2:2">
-      <c r="B55" s="47" t="s">
+      <c r="B55" s="49" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="56" spans="2:2">
-      <c r="B56" s="47" t="s">
+      <c r="B56" s="49" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="57" spans="2:2">
-      <c r="B57" s="47" t="s">
+      <c r="B57" s="49" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="59" spans="1:1">
-      <c r="A59" s="38" t="s">
+      <c r="A59" s="39" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="60" spans="2:2">
-      <c r="B60" s="47" t="s">
+      <c r="B60" s="49" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="61" spans="2:2">
-      <c r="B61" s="47" t="s">
+      <c r="B61" s="49" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="62" spans="2:2">
-      <c r="B62" s="47" t="s">
+      <c r="B62" s="49" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="65" spans="1:1">
-      <c r="A65" s="38" t="s">
+      <c r="A65" s="39" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="66" spans="2:2">
-      <c r="B66" s="47" t="s">
+      <c r="B66" s="49" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="68" spans="1:1">
-      <c r="A68" s="46" t="s">
+      <c r="A68" s="48" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="69" spans="2:2">
-      <c r="B69" s="47" t="s">
+      <c r="B69" s="49" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="70" spans="2:2">
-      <c r="B70" s="47" t="s">
+      <c r="B70" s="49" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="71" spans="2:2">
-      <c r="B71" s="47" t="s">
+      <c r="B71" s="49" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="72" spans="2:2">
-      <c r="B72" s="47" t="s">
+      <c r="B72" s="49" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="73" spans="2:2">
-      <c r="B73" s="47" t="s">
+      <c r="B73" s="49" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="74" spans="2:2">
-      <c r="B74" s="47" t="s">
+      <c r="B74" s="49" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="75" spans="2:2">
-      <c r="B75" s="47" t="s">
+      <c r="B75" s="49" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="106" spans="2:2">
-      <c r="B106" s="49" t="s">
+      <c r="B106" s="51" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="107" spans="2:2">
-      <c r="B107" s="47" t="s">
+      <c r="B107" s="49" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="109" ht="31" spans="2:2">
-      <c r="B109" s="55" t="s">
+      <c r="B109" s="58" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="112" spans="2:2">
-      <c r="B112" s="56" t="s">
+      <c r="B112" s="59" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="113" spans="2:2">
-      <c r="B113" s="47" t="s">
+      <c r="B113" s="49" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="114" ht="31" spans="2:2">
-      <c r="B114" s="57" t="s">
+      <c r="B114" s="60" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="115" spans="2:2">
-      <c r="B115" s="37"/>
+      <c r="B115" s="38"/>
     </row>
     <row r="116" ht="31" spans="2:2">
-      <c r="B116" s="57" t="s">
+      <c r="B116" s="60" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="117" spans="2:2">
-      <c r="B117" s="37"/>
+      <c r="B117" s="38"/>
     </row>
     <row r="118" spans="2:2">
-      <c r="B118" s="57" t="s">
+      <c r="B118" s="60" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="119" spans="2:2">
-      <c r="B119" s="58" t="s">
+      <c r="B119" s="61" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="120" spans="2:2">
-      <c r="B120" s="58" t="s">
+      <c r="B120" s="61" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="121" spans="2:2">
-      <c r="B121" s="58" t="s">
+      <c r="B121" s="61" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="122" ht="31" spans="2:2">
-      <c r="B122" s="58" t="s">
+      <c r="B122" s="61" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="123" spans="2:2">
-      <c r="B123" s="58" t="s">
+      <c r="B123" s="61" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="124" spans="2:2">
-      <c r="B124" s="58" t="s">
+      <c r="B124" s="61" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="125" ht="31" spans="2:2">
-      <c r="B125" s="58" t="s">
+      <c r="B125" s="61" t="s">
         <v>62</v>
       </c>
     </row>
@@ -4763,20 +4775,20 @@
   <dimension ref="A1:D34"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="15.5" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="3.39230769230769" style="44" customWidth="1"/>
-    <col min="2" max="2" width="2.94615384615385" style="45" customWidth="1"/>
-    <col min="3" max="3" width="2.88461538461538" style="45" customWidth="1"/>
-    <col min="4" max="4" width="83.9692307692308" style="45" customWidth="1"/>
-    <col min="5" max="16384" width="9.23076923076923" style="45"/>
+    <col min="1" max="1" width="3.39230769230769" style="46" customWidth="1"/>
+    <col min="2" max="2" width="2.94615384615385" style="47" customWidth="1"/>
+    <col min="3" max="3" width="2.88461538461538" style="47" customWidth="1"/>
+    <col min="4" max="4" width="83.9692307692308" style="47" customWidth="1"/>
+    <col min="5" max="16384" width="9.23076923076923" style="47"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:2">
-      <c r="B1" s="46" t="s">
+      <c r="B1" s="48" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="2" spans="2:2">
-      <c r="B2" s="46" t="s">
+      <c r="B2" s="48" t="s">
         <v>64</v>
       </c>
     </row>
@@ -4784,17 +4796,17 @@
       <c r="B3" s="29"/>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="45" t="s">
+      <c r="A4" s="48" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="45" t="s">
+      <c r="A5" s="47" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="45" t="s">
+      <c r="A6" s="47" t="s">
         <v>67</v>
       </c>
     </row>
@@ -4804,84 +4816,103 @@
       </c>
     </row>
     <row r="8" ht="80" customHeight="1" spans="4:4">
-      <c r="D8" s="47" t="s">
+      <c r="D8" s="49" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="9" ht="46.5" spans="4:4">
-      <c r="D9" s="48" t="s">
+      <c r="D9" s="50" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="10" ht="93" spans="4:4">
-      <c r="D10" s="49" t="s">
+      <c r="D10" s="51" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="11" spans="4:4">
-      <c r="D11" s="47" t="s">
+      <c r="D11" s="49" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="13" spans="4:4">
-      <c r="D13" s="45" t="s">
+      <c r="D13" s="47" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="17" ht="17.5" spans="2:2">
-      <c r="B17" s="50" t="s">
+      <c r="B17" s="52" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="18" ht="35" spans="2:4">
-      <c r="B18" s="50"/>
+      <c r="B18" s="52"/>
       <c r="D18" s="9" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="19" ht="17.5" spans="3:3">
-      <c r="C19" s="50" t="s">
+    <row r="19" ht="17.5" spans="2:3">
+      <c r="B19" s="48"/>
+      <c r="C19" s="53" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="20" ht="17.5" spans="3:4">
-      <c r="C20" s="50"/>
-      <c r="D20" s="47"/>
-    </row>
-    <row r="21" spans="3:3">
-      <c r="C21" s="45" t="s">
+    <row r="20" ht="17.5" spans="2:4">
+      <c r="B20" s="48"/>
+      <c r="C20" s="53"/>
+      <c r="D20" s="49"/>
+    </row>
+    <row r="21" spans="2:3">
+      <c r="B21" s="48"/>
+      <c r="C21" s="47" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="22" spans="3:3">
-      <c r="C22" s="45" t="s">
+    <row r="22" spans="2:3">
+      <c r="B22" s="48"/>
+      <c r="C22" s="47" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="23" spans="3:3">
-      <c r="C23" s="45" t="s">
+    <row r="23" spans="2:3">
+      <c r="B23" s="48"/>
+      <c r="C23" s="47" t="s">
         <v>79</v>
       </c>
     </row>
+    <row r="24" spans="2:2">
+      <c r="B24" s="48"/>
+    </row>
+    <row r="25" spans="2:2">
+      <c r="B25" s="48"/>
+    </row>
     <row r="26" ht="17.5" spans="2:2">
-      <c r="B26" s="50" t="s">
+      <c r="B26" s="52" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="27" ht="106" customHeight="1" spans="4:4">
+    <row r="27" ht="106" customHeight="1" spans="2:4">
+      <c r="B27" s="48"/>
       <c r="D27" s="9" t="s">
         <v>81</v>
       </c>
     </row>
+    <row r="28" spans="2:2">
+      <c r="B28" s="48"/>
+    </row>
+    <row r="29" spans="2:2">
+      <c r="B29" s="48"/>
+    </row>
     <row r="30" ht="35" spans="2:4">
-      <c r="B30" s="45" t="s">
+      <c r="B30" s="48" t="s">
         <v>82</v>
       </c>
       <c r="D30" s="9" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="31" ht="17.5" spans="4:4">
+    <row r="31" ht="17.5" spans="2:4">
+      <c r="B31" s="48"/>
       <c r="D31" s="10" t="s">
         <v>84</v>
       </c>
@@ -4914,30 +4945,30 @@
   <dimension ref="A1:G200"/>
   <sheetFormatPr defaultColWidth="8.66923076923077" defaultRowHeight="15.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="3.07692307692308" style="34" customWidth="1"/>
-    <col min="2" max="4" width="4.15384615384615" style="35" customWidth="1"/>
-    <col min="5" max="5" width="82.6538461538462" style="36" customWidth="1"/>
-    <col min="6" max="6" width="12.1692307692308" style="37" customWidth="1"/>
-    <col min="7" max="8" width="4.5" style="37" customWidth="1"/>
-    <col min="9" max="16384" width="8.66923076923077" style="37"/>
+    <col min="1" max="1" width="3.07692307692308" style="35" customWidth="1"/>
+    <col min="2" max="4" width="4.15384615384615" style="36" customWidth="1"/>
+    <col min="5" max="5" width="82.6538461538462" style="37" customWidth="1"/>
+    <col min="6" max="6" width="12.1692307692308" style="38" customWidth="1"/>
+    <col min="7" max="8" width="4.5" style="38" customWidth="1"/>
+    <col min="9" max="16384" width="8.66923076923077" style="38"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:7">
-      <c r="B1" s="38" t="s">
+      <c r="B1" s="39" t="s">
         <v>88</v>
       </c>
-      <c r="G1" s="39"/>
+      <c r="G1" s="40"/>
     </row>
     <row r="2" spans="2:2">
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="36" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="34">
+      <c r="A5" s="41">
         <v>1</v>
       </c>
-      <c r="B5" s="35" t="s">
+      <c r="B5" s="39" t="s">
         <v>90</v>
       </c>
     </row>
@@ -4945,75 +4976,78 @@
       <c r="B6"/>
     </row>
     <row r="32" ht="52.5" spans="5:5">
-      <c r="E32" s="40" t="s">
+      <c r="E32" s="42" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="33" ht="35" spans="5:5">
-      <c r="E33" s="40" t="s">
+      <c r="E33" s="42" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="34" ht="35" spans="5:5">
-      <c r="E34" s="40" t="s">
+      <c r="E34" s="42" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="35" ht="17.5" spans="5:5">
-      <c r="E35" s="40" t="s">
+      <c r="E35" s="42" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="37" spans="2:2">
-      <c r="B37" s="35" t="s">
+      <c r="B37" s="36" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="38" ht="403" spans="5:5">
-      <c r="E38" s="36" t="s">
+      <c r="E38" s="37" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="40" ht="232.5" spans="5:5">
-      <c r="E40" s="41" t="s">
+      <c r="E40" s="43" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="42" spans="3:3">
-      <c r="C42" s="35" t="s">
+      <c r="C42" s="36" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="43" spans="3:3">
-      <c r="C43" s="35" t="s">
+      <c r="C43" s="36" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="44" spans="3:3">
-      <c r="C44" s="35" t="s">
+      <c r="C44" s="36" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="1:2">
-      <c r="A46" s="34">
+    <row r="46" s="34" customFormat="1" ht="14" customHeight="1" spans="1:5">
+      <c r="A46" s="41">
         <v>2</v>
       </c>
-      <c r="B46" s="35" t="s">
+      <c r="B46" s="39" t="s">
         <v>101</v>
       </c>
+      <c r="C46" s="39"/>
+      <c r="D46" s="39"/>
+      <c r="E46" s="43"/>
     </row>
     <row r="47" ht="31" spans="5:5">
-      <c r="E47" s="36" t="s">
+      <c r="E47" s="37" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="48" ht="17.5" spans="3:3">
-      <c r="C48" s="42" t="s">
+      <c r="C48" s="44" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="49" ht="62" spans="5:5">
-      <c r="E49" s="36" t="s">
+      <c r="E49" s="37" t="s">
         <v>104</v>
       </c>
     </row>
@@ -5021,12 +5055,12 @@
       <c r="B51"/>
     </row>
     <row r="83" spans="2:2">
-      <c r="B83" s="35" t="s">
+      <c r="B83" s="36" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="84" ht="35" spans="5:5">
-      <c r="E84" s="43" t="s">
+      <c r="E84" s="45" t="s">
         <v>106</v>
       </c>
     </row>
@@ -5034,22 +5068,22 @@
       <c r="E85"/>
     </row>
     <row r="86" ht="17.5" spans="5:5">
-      <c r="E86" s="43" t="s">
+      <c r="E86" s="45" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="87" ht="17.5" spans="5:5">
-      <c r="E87" s="40" t="s">
+      <c r="E87" s="42" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="88" ht="17.5" spans="5:5">
-      <c r="E88" s="40" t="s">
+      <c r="E88" s="42" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="90" ht="52.5" spans="5:5">
-      <c r="E90" s="43" t="s">
+      <c r="E90" s="45" t="s">
         <v>110</v>
       </c>
     </row>
@@ -5057,635 +5091,701 @@
       <c r="E91"/>
     </row>
     <row r="92" ht="52.5" spans="5:5">
-      <c r="E92" s="43" t="s">
+      <c r="E92" s="45" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="94" spans="2:2">
-      <c r="B94" s="35" t="s">
+      <c r="B94" s="36" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="95" spans="2:6">
-      <c r="B95" s="38" t="s">
+      <c r="B95" s="39" t="s">
         <v>113</v>
       </c>
-      <c r="C95" s="38"/>
-      <c r="D95" s="38" t="s">
+      <c r="C95" s="39"/>
+      <c r="D95" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="E95" s="38" t="s">
+      <c r="E95" s="39" t="s">
         <v>115</v>
       </c>
-      <c r="F95" s="36"/>
+      <c r="F95" s="37"/>
     </row>
     <row r="96" spans="2:6">
-      <c r="B96" s="35" t="s">
+      <c r="B96" s="36" t="s">
         <v>116</v>
       </c>
-      <c r="D96" s="35" t="s">
+      <c r="D96" s="36" t="s">
         <v>117</v>
       </c>
-      <c r="E96" s="35" t="s">
+      <c r="E96" s="36" t="s">
         <v>118</v>
       </c>
-      <c r="F96" s="36"/>
+      <c r="F96" s="37"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="35" t="s">
+      <c r="B97" s="36" t="s">
         <v>119</v>
       </c>
-      <c r="D97" s="35" t="s">
+      <c r="D97" s="36" t="s">
         <v>120</v>
       </c>
-      <c r="E97" s="35" t="s">
+      <c r="E97" s="36" t="s">
         <v>121</v>
       </c>
-      <c r="F97" s="36"/>
+      <c r="F97" s="37"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="35" t="s">
+      <c r="B98" s="36" t="s">
         <v>122</v>
       </c>
-      <c r="D98" s="35" t="s">
+      <c r="D98" s="36" t="s">
         <v>123</v>
       </c>
-      <c r="E98" s="35" t="s">
+      <c r="E98" s="36" t="s">
         <v>124</v>
       </c>
-      <c r="F98" s="36"/>
+      <c r="F98" s="37"/>
     </row>
     <row r="99" spans="2:6">
-      <c r="B99" s="35" t="s">
+      <c r="B99" s="36" t="s">
         <v>125</v>
       </c>
-      <c r="D99" s="35" t="s">
+      <c r="D99" s="36" t="s">
         <v>126</v>
       </c>
-      <c r="E99" s="35" t="s">
+      <c r="E99" s="36" t="s">
         <v>127</v>
       </c>
-      <c r="F99" s="36"/>
+      <c r="F99" s="37"/>
     </row>
     <row r="100" spans="2:6">
-      <c r="B100" s="35" t="s">
+      <c r="B100" s="36" t="s">
         <v>128</v>
       </c>
-      <c r="D100" s="35" t="s">
+      <c r="D100" s="36" t="s">
         <v>126</v>
       </c>
-      <c r="E100" s="35" t="s">
+      <c r="E100" s="36" t="s">
         <v>129</v>
       </c>
-      <c r="F100" s="36"/>
+      <c r="F100" s="37"/>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="35" t="s">
+      <c r="B101" s="36" t="s">
         <v>130</v>
       </c>
-      <c r="D101" s="35" t="s">
+      <c r="D101" s="36" t="s">
         <v>131</v>
       </c>
-      <c r="E101" s="35" t="s">
+      <c r="E101" s="36" t="s">
         <v>132</v>
       </c>
-      <c r="F101" s="36"/>
+      <c r="F101" s="37"/>
     </row>
     <row r="102" spans="2:6">
-      <c r="B102" s="35" t="s">
+      <c r="B102" s="36" t="s">
         <v>133</v>
       </c>
-      <c r="D102" s="35" t="s">
+      <c r="D102" s="36" t="s">
         <v>134</v>
       </c>
-      <c r="E102" s="35"/>
-      <c r="F102" s="36"/>
+      <c r="E102" s="36"/>
+      <c r="F102" s="37"/>
     </row>
     <row r="103" spans="2:6">
-      <c r="B103" s="35" t="s">
+      <c r="B103" s="36" t="s">
         <v>135</v>
       </c>
-      <c r="E103" s="35"/>
-      <c r="F103" s="36"/>
+      <c r="E103" s="36"/>
+      <c r="F103" s="37"/>
     </row>
     <row r="104" spans="2:6">
-      <c r="B104" s="35" t="s">
+      <c r="B104" s="36" t="s">
         <v>136</v>
       </c>
-      <c r="E104" s="35"/>
-      <c r="F104" s="36"/>
+      <c r="E104" s="36"/>
+      <c r="F104" s="37"/>
     </row>
     <row r="105" spans="2:6">
-      <c r="B105" s="35" t="s">
+      <c r="B105" s="36" t="s">
         <v>137</v>
       </c>
-      <c r="E105" s="35"/>
-      <c r="F105" s="36"/>
+      <c r="E105" s="36"/>
+      <c r="F105" s="37"/>
     </row>
     <row r="106" spans="2:6">
-      <c r="B106" s="35" t="s">
+      <c r="B106" s="36" t="s">
         <v>138</v>
       </c>
-      <c r="E106" s="35"/>
-      <c r="F106" s="36"/>
+      <c r="E106" s="36"/>
+      <c r="F106" s="37"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="35" t="s">
+      <c r="B107" s="36" t="s">
         <v>139</v>
       </c>
-      <c r="E107" s="35"/>
-      <c r="F107" s="36"/>
+      <c r="E107" s="36"/>
+      <c r="F107" s="37"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="35" t="s">
+      <c r="B108" s="36" t="s">
         <v>140</v>
       </c>
-      <c r="E108" s="35"/>
-      <c r="F108" s="36"/>
+      <c r="E108" s="36"/>
+      <c r="F108" s="37"/>
     </row>
     <row r="109" spans="2:6">
-      <c r="B109" s="35" t="s">
+      <c r="B109" s="36" t="s">
         <v>141</v>
       </c>
-      <c r="E109" s="35"/>
-      <c r="F109" s="36"/>
+      <c r="E109" s="36"/>
+      <c r="F109" s="37"/>
     </row>
     <row r="110" spans="2:6">
-      <c r="B110" s="35" t="s">
+      <c r="B110" s="36" t="s">
         <v>142</v>
       </c>
-      <c r="E110" s="35"/>
-      <c r="F110" s="36"/>
+      <c r="E110" s="36"/>
+      <c r="F110" s="37"/>
     </row>
     <row r="111" spans="2:6">
-      <c r="B111" s="35" t="s">
+      <c r="B111" s="36" t="s">
         <v>143</v>
       </c>
-      <c r="E111" s="35"/>
-      <c r="F111" s="36"/>
+      <c r="E111" s="36"/>
+      <c r="F111" s="37"/>
     </row>
     <row r="112" spans="2:6">
-      <c r="B112" s="35" t="s">
+      <c r="B112" s="36" t="s">
         <v>144</v>
       </c>
-      <c r="E112" s="35"/>
-      <c r="F112" s="36"/>
+      <c r="E112" s="36"/>
+      <c r="F112" s="37"/>
     </row>
     <row r="113" spans="2:6">
-      <c r="B113" s="35" t="s">
+      <c r="B113" s="36" t="s">
         <v>145</v>
       </c>
-      <c r="E113" s="35"/>
-      <c r="F113" s="36"/>
+      <c r="E113" s="36"/>
+      <c r="F113" s="37"/>
     </row>
     <row r="115" spans="2:2">
-      <c r="B115" s="38" t="s">
+      <c r="B115" s="39" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="116" ht="263.5" spans="5:5">
-      <c r="E116" s="36" t="s">
+      <c r="E116" s="37" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="117" spans="2:2">
-      <c r="B117" s="35" t="s">
+      <c r="B117" s="36" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="119" spans="1:2">
-      <c r="A119" s="34">
+    <row r="119" s="34" customFormat="1" spans="1:5">
+      <c r="A119" s="41">
         <v>3</v>
       </c>
-      <c r="B119" s="35" t="s">
+      <c r="B119" s="39" t="s">
         <v>148</v>
       </c>
+      <c r="C119" s="39"/>
+      <c r="D119" s="39"/>
+      <c r="E119" s="43"/>
     </row>
     <row r="120" ht="62" spans="5:5">
-      <c r="E120" s="36" t="s">
+      <c r="E120" s="37" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="122" ht="108.5" spans="5:5">
-      <c r="E122" s="36" t="s">
+      <c r="E122" s="37" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="124" spans="3:3">
-      <c r="C124" s="38" t="s">
+      <c r="C124" s="39" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="125" spans="3:3">
-      <c r="C125" s="35" t="s">
+      <c r="C125" s="36" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="126" spans="3:3">
-      <c r="C126" s="38" t="s">
+      <c r="C126" s="39" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="127" spans="2:5">
-      <c r="B127" s="38" t="s">
+      <c r="B127" s="39" t="s">
         <v>153</v>
       </c>
-      <c r="C127" s="38"/>
-      <c r="D127" s="38" t="s">
+      <c r="C127" s="39"/>
+      <c r="D127" s="39" t="s">
         <v>154</v>
       </c>
-      <c r="E127" s="38" t="s">
+      <c r="E127" s="39" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="128" spans="2:5">
-      <c r="B128" s="35" t="s">
+      <c r="B128" s="36" t="s">
         <v>156</v>
       </c>
-      <c r="D128" s="35" t="s">
+      <c r="D128" s="36" t="s">
         <v>157</v>
       </c>
-      <c r="E128" s="35" t="s">
+      <c r="E128" s="36" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="129" spans="2:5">
-      <c r="B129" s="35" t="s">
+      <c r="B129" s="36" t="s">
         <v>159</v>
       </c>
-      <c r="D129" s="35" t="s">
+      <c r="D129" s="36" t="s">
         <v>160</v>
       </c>
-      <c r="E129" s="35" t="s">
+      <c r="E129" s="36" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="130" spans="2:5">
-      <c r="B130" s="35" t="s">
+      <c r="B130" s="36" t="s">
         <v>162</v>
       </c>
-      <c r="D130" s="35" t="s">
+      <c r="D130" s="36" t="s">
         <v>163</v>
       </c>
-      <c r="E130" s="35" t="s">
+      <c r="E130" s="36" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="131" spans="2:5">
-      <c r="B131" s="35" t="s">
+      <c r="B131" s="36" t="s">
         <v>165</v>
       </c>
-      <c r="D131" s="35" t="s">
+      <c r="D131" s="36" t="s">
         <v>166</v>
       </c>
-      <c r="E131" s="35" t="s">
+      <c r="E131" s="36" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="132" spans="2:5">
-      <c r="B132" s="35" t="s">
+      <c r="B132" s="36" t="s">
         <v>167</v>
       </c>
-      <c r="D132" s="35" t="s">
+      <c r="D132" s="36" t="s">
         <v>168</v>
       </c>
-      <c r="E132" s="35" t="s">
+      <c r="E132" s="36" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="133" spans="2:5">
-      <c r="B133" s="35" t="s">
+      <c r="B133" s="36" t="s">
         <v>169</v>
       </c>
-      <c r="D133" s="35" t="s">
+      <c r="D133" s="36" t="s">
         <v>170</v>
       </c>
-      <c r="E133" s="35" t="s">
+      <c r="E133" s="36" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="134" spans="2:5">
-      <c r="B134" s="35" t="s">
+      <c r="B134" s="36" t="s">
         <v>171</v>
       </c>
-      <c r="D134" s="35" t="s">
+      <c r="D134" s="36" t="s">
         <v>172</v>
       </c>
-      <c r="E134" s="35" t="s">
+      <c r="E134" s="36" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="135" spans="2:5">
-      <c r="B135" s="35" t="s">
+      <c r="B135" s="36" t="s">
         <v>173</v>
       </c>
-      <c r="D135" s="35" t="s">
+      <c r="D135" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="E135" s="35" t="s">
+      <c r="E135" s="36" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="136" spans="2:5">
-      <c r="B136" s="35" t="s">
+      <c r="B136" s="36" t="s">
         <v>176</v>
       </c>
-      <c r="D136" s="35" t="s">
+      <c r="D136" s="36" t="s">
         <v>177</v>
       </c>
-      <c r="E136" s="35" t="s">
+      <c r="E136" s="36" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="137" spans="2:5">
-      <c r="B137" s="35" t="s">
+      <c r="B137" s="36" t="s">
         <v>179</v>
       </c>
-      <c r="D137" s="35" t="s">
+      <c r="D137" s="36" t="s">
         <v>180</v>
       </c>
-      <c r="E137" s="35" t="s">
+      <c r="E137" s="36" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="138" ht="46.5" spans="5:5">
-      <c r="E138" s="36" t="s">
+      <c r="E138" s="37" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="140" spans="1:2">
-      <c r="A140" s="34">
+    <row r="140" s="34" customFormat="1" spans="1:5">
+      <c r="A140" s="41">
         <v>4</v>
       </c>
-      <c r="B140" s="35" t="s">
+      <c r="B140" s="39" t="s">
         <v>183</v>
       </c>
+      <c r="C140" s="39"/>
+      <c r="D140" s="39"/>
+      <c r="E140" s="43"/>
     </row>
     <row r="141" spans="2:2">
-      <c r="B141" s="35" t="s">
+      <c r="B141" s="36" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="142" spans="2:2">
-      <c r="B142" s="35" t="s">
+      <c r="B142" s="36" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="143" spans="2:2">
-      <c r="B143" s="35" t="s">
+      <c r="B143" s="36" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="144" ht="46.5" spans="5:5">
-      <c r="E144" s="36" t="s">
+      <c r="E144" s="37" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="145" ht="62" spans="5:5">
-      <c r="E145" s="36" t="s">
+      <c r="E145" s="37" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="146" ht="31" spans="5:5">
-      <c r="E146" s="36" t="s">
+      <c r="E146" s="37" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="147" spans="5:5">
-      <c r="E147" s="36" t="s">
+      <c r="E147" s="37" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="149" spans="1:2">
-      <c r="A149" s="34">
+      <c r="A149" s="41">
         <v>6</v>
       </c>
-      <c r="B149" s="35" t="s">
+      <c r="B149" s="39" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="150" ht="31" spans="5:5">
-      <c r="E150" s="36" t="s">
+      <c r="E150" s="37" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="151" ht="17.5" spans="5:5">
-      <c r="E151" s="42" t="s">
+      <c r="E151" s="44" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="152" spans="3:3">
-      <c r="C152" s="35" t="s">
+      <c r="C152" s="36" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="153" spans="3:3">
-      <c r="C153" s="35" t="s">
+      <c r="C153" s="36" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="155" ht="139.5" spans="5:5">
-      <c r="E155" s="36" t="s">
+      <c r="E155" s="37" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="156" ht="31" spans="5:5">
-      <c r="E156" s="36" t="s">
+      <c r="E156" s="37" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="158" spans="2:5">
-      <c r="B158" s="38" t="s">
+      <c r="B158" s="39" t="s">
         <v>198</v>
       </c>
-      <c r="C158" s="38"/>
-      <c r="D158" s="38"/>
-      <c r="E158" s="41" t="s">
+      <c r="C158" s="39"/>
+      <c r="D158" s="39"/>
+      <c r="E158" s="43" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="159" ht="31" spans="2:5">
-      <c r="B159" s="35" t="s">
+      <c r="B159" s="36" t="s">
         <v>200</v>
       </c>
-      <c r="E159" s="36" t="s">
+      <c r="E159" s="37" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="160" ht="31" spans="2:5">
-      <c r="B160" s="35" t="s">
+      <c r="B160" s="36" t="s">
         <v>202</v>
       </c>
-      <c r="E160" s="36" t="s">
+      <c r="E160" s="37" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="161" ht="31" spans="2:5">
-      <c r="B161" s="35" t="s">
+      <c r="B161" s="36" t="s">
         <v>204</v>
       </c>
-      <c r="E161" s="36" t="s">
+      <c r="E161" s="37" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="162" spans="2:2">
-      <c r="B162" s="35" t="s">
+      <c r="B162" s="36" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="163" ht="31" spans="2:5">
-      <c r="B163" s="35" t="s">
+      <c r="B163" s="36" t="s">
         <v>207</v>
       </c>
-      <c r="E163" s="36" t="s">
+      <c r="E163" s="37" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="164" spans="2:2">
-      <c r="B164" s="35" t="s">
+      <c r="B164" s="36" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="165" spans="2:5">
-      <c r="B165" s="35" t="s">
+      <c r="B165" s="36" t="s">
         <v>209</v>
       </c>
-      <c r="E165" s="36" t="s">
+      <c r="E165" s="37" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="166" spans="2:5">
-      <c r="B166" s="35" t="s">
+      <c r="B166" s="36" t="s">
         <v>211</v>
       </c>
-      <c r="E166" s="36" t="s">
+      <c r="E166" s="37" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="167" ht="31" spans="2:5">
-      <c r="B167" s="35" t="s">
+      <c r="B167" s="36" t="s">
         <v>213</v>
       </c>
-      <c r="E167" s="36" t="s">
+      <c r="E167" s="37" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="169" ht="124" spans="5:5">
-      <c r="E169" s="36" t="s">
+      <c r="E169" s="37" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="171" spans="4:4">
-      <c r="D171" s="38" t="s">
+      <c r="D171" s="39" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="172" ht="232.5" spans="5:5">
-      <c r="E172" s="36" t="s">
+      <c r="E172" s="37" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="174" spans="4:4">
-      <c r="D174" s="38" t="s">
+      <c r="D174" s="39" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="175" ht="62" spans="5:5">
-      <c r="E175" s="36" t="s">
+      <c r="E175" s="37" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="177" spans="2:2">
-      <c r="B177" s="35" t="s">
+      <c r="B177" s="36" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="178" spans="1:2">
-      <c r="A178" s="34">
+      <c r="A178" s="41">
         <v>7</v>
       </c>
-      <c r="B178" s="38" t="s">
+      <c r="B178" s="39" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="179" spans="2:2">
-      <c r="B179" s="35" t="s">
+    <row r="179" spans="2:4">
+      <c r="B179" s="39" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="180" ht="93" spans="5:5">
-      <c r="E180" s="36" t="s">
+      <c r="C179" s="39"/>
+      <c r="D179" s="39"/>
+    </row>
+    <row r="180" ht="93" spans="2:5">
+      <c r="B180" s="39"/>
+      <c r="C180" s="39"/>
+      <c r="D180" s="39"/>
+      <c r="E180" s="37" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="181" spans="3:3">
-      <c r="C181" s="35" t="s">
+    <row r="181" spans="2:4">
+      <c r="B181" s="39"/>
+      <c r="C181" s="39" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="182" ht="310" spans="5:5">
-      <c r="E182" s="36" t="s">
+      <c r="D181" s="39"/>
+    </row>
+    <row r="182" ht="310" spans="2:5">
+      <c r="B182" s="39"/>
+      <c r="C182" s="39"/>
+      <c r="D182" s="39"/>
+      <c r="E182" s="37" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="184" ht="139.5" spans="5:5">
-      <c r="E184" s="36" t="s">
+    <row r="183" spans="2:4">
+      <c r="B183" s="39"/>
+      <c r="C183" s="39"/>
+      <c r="D183" s="39"/>
+    </row>
+    <row r="184" ht="139.5" spans="2:5">
+      <c r="B184" s="39"/>
+      <c r="C184" s="39"/>
+      <c r="D184" s="39"/>
+      <c r="E184" s="37" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="186" spans="3:3">
-      <c r="C186" s="35" t="s">
+    <row r="185" spans="2:4">
+      <c r="B185" s="39"/>
+      <c r="C185" s="39"/>
+      <c r="D185" s="39"/>
+    </row>
+    <row r="186" spans="2:4">
+      <c r="B186" s="39"/>
+      <c r="C186" s="39" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="187" ht="62" spans="5:5">
-      <c r="E187" s="36" t="s">
+      <c r="D186" s="39"/>
+    </row>
+    <row r="187" ht="62" spans="2:5">
+      <c r="B187" s="39"/>
+      <c r="C187" s="39"/>
+      <c r="D187" s="39"/>
+      <c r="E187" s="37" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="189" ht="46.5" spans="5:5">
-      <c r="E189" s="36" t="s">
+    <row r="188" spans="2:4">
+      <c r="B188" s="39"/>
+      <c r="C188" s="39"/>
+      <c r="D188" s="39"/>
+    </row>
+    <row r="189" ht="46.5" spans="2:5">
+      <c r="B189" s="39"/>
+      <c r="C189" s="39"/>
+      <c r="D189" s="39"/>
+      <c r="E189" s="37" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="191" ht="155" spans="5:5">
-      <c r="E191" s="36" t="s">
+    <row r="190" spans="2:4">
+      <c r="B190" s="39"/>
+      <c r="C190" s="39"/>
+      <c r="D190" s="39"/>
+    </row>
+    <row r="191" ht="155" spans="2:5">
+      <c r="B191" s="39"/>
+      <c r="C191" s="39"/>
+      <c r="D191" s="39"/>
+      <c r="E191" s="37" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="193" spans="4:4">
-      <c r="D193" s="35" t="s">
+    <row r="192" spans="2:4">
+      <c r="B192" s="39"/>
+      <c r="C192" s="39"/>
+      <c r="D192" s="39"/>
+    </row>
+    <row r="193" spans="2:4">
+      <c r="B193" s="39"/>
+      <c r="C193" s="39"/>
+      <c r="D193" s="39" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="194" ht="31" spans="5:5">
-      <c r="E194" s="36" t="s">
+    <row r="194" ht="31" spans="2:5">
+      <c r="B194" s="39"/>
+      <c r="C194" s="39"/>
+      <c r="D194" s="39"/>
+      <c r="E194" s="37" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="195" spans="5:5">
-      <c r="E195" s="36" t="s">
+    <row r="195" spans="2:5">
+      <c r="B195" s="39"/>
+      <c r="C195" s="39"/>
+      <c r="D195" s="39"/>
+      <c r="E195" s="37" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="196" spans="5:5">
-      <c r="E196" s="36" t="s">
+    <row r="196" spans="2:5">
+      <c r="B196" s="39"/>
+      <c r="C196" s="39"/>
+      <c r="D196" s="39"/>
+      <c r="E196" s="37" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="198" spans="1:2">
-      <c r="A198" s="34">
+      <c r="A198" s="35">
         <v>8</v>
       </c>
-      <c r="B198" s="35" t="s">
+      <c r="B198" s="36" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="200" spans="1:2">
-      <c r="A200" s="34">
+      <c r="A200" s="35">
         <v>9</v>
       </c>
-      <c r="B200" s="35" t="s">
+      <c r="B200" s="36" t="s">
         <v>236</v>
       </c>
     </row>

--- a/p/ds_25/apache-spark/topic-list_ap-spk.xlsx
+++ b/p/ds_25/apache-spark/topic-list_ap-spk.xlsx
@@ -4,18 +4,20 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8960" tabRatio="698" activeTab="2"/>
+    <workbookView windowWidth="23040" windowHeight="9680" tabRatio="698" activeTab="10"/>
   </bookViews>
   <sheets>
-    <sheet name="what" sheetId="21" r:id="rId1"/>
-    <sheet name="sql" sheetId="23" r:id="rId2"/>
-    <sheet name="architect" sheetId="5" r:id="rId3"/>
-    <sheet name="x1" sheetId="25" r:id="rId4"/>
-    <sheet name="x2" sheetId="2" r:id="rId5"/>
-    <sheet name="x3" sheetId="8" r:id="rId6"/>
-    <sheet name="x4" sheetId="26" r:id="rId7"/>
-    <sheet name="ques" sheetId="6" r:id="rId8"/>
-    <sheet name="how_use-cases" sheetId="22" r:id="rId9"/>
+    <sheet name="core" sheetId="6" r:id="rId1"/>
+    <sheet name="ex" sheetId="29" r:id="rId2"/>
+    <sheet name="adv" sheetId="30" r:id="rId3"/>
+    <sheet name="what" sheetId="21" r:id="rId4"/>
+    <sheet name="sql" sheetId="23" r:id="rId5"/>
+    <sheet name="architect" sheetId="5" r:id="rId6"/>
+    <sheet name="x1" sheetId="25" r:id="rId7"/>
+    <sheet name="x2" sheetId="2" r:id="rId8"/>
+    <sheet name="x3" sheetId="8" r:id="rId9"/>
+    <sheet name="x4" sheetId="26" r:id="rId10"/>
+    <sheet name="how_use-cases" sheetId="22" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +37,1209 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="638">
+  <si>
+    <t>s.no.</t>
+  </si>
+  <si>
+    <t>hints</t>
+  </si>
+  <si>
+    <t>topic</t>
+  </si>
+  <si>
+    <t>sub-topic</t>
+  </si>
+  <si>
+    <t>priority</t>
+  </si>
+  <si>
+    <t>flag</t>
+  </si>
+  <si>
+    <t>https://spark.apache.org/docs/latest/sql-ref-functions.html</t>
+  </si>
+  <si>
+    <t>Start session /  context</t>
+  </si>
+  <si>
+    <r>
+      <t>spark =</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> SparkSession</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>.builder.appName('covid-example').getOrCreate()</t>
+    </r>
+  </si>
+  <si>
+    <t>Import data</t>
+  </si>
+  <si>
+    <t>cases = spark.read.load("./data/Case.csv", format="csv", sep=",", inferSchema="true", header="true")</t>
+  </si>
+  <si>
+    <t>type(cases)</t>
+  </si>
+  <si>
+    <t>pyspark.sql.classic.dataframe.DataFrame</t>
+  </si>
+  <si>
+    <t>equivalent of pd df.info()</t>
+  </si>
+  <si>
+    <r>
+      <t>cases.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>printSchema</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>()</t>
+    </r>
+  </si>
+  <si>
+    <t>data = [ // multi-dimensional array to work as data for spark dataframe</t>
+  </si>
+  <si>
+    <t>[ (("A","B","C"), ["arVal 1", "arVal 2"], "simpleVal 1", "strVal"), ...... ]</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">schema = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>StructType</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">([
+     </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>StructField</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">('n', </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>StructType</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>([
+        StructField('fn', StringType(), True),
+        StructField('mn', StringType(), True),
+         StructField('ln', StringType(), True)
+     ])),
+     StructField('langs', ArrayType(StringType()), True),
+     StructField('st', StringType(), True),
+     StructField('gend', StringType(), True)
+ ])</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>spark.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>createDataFrame</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(data = data, schema = schema)</t>
+    </r>
+  </si>
+  <si>
+    <t>Subset observations / Sliciing</t>
+  </si>
+  <si>
+    <r>
+      <t>cases = cases.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>select</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>('colA','colB','colC')</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>df.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>where</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(col("Age") &gt; 25)</t>
+    </r>
+  </si>
+  <si>
+    <t>register df as temp table, to query</t>
+  </si>
+  <si>
+    <r>
+      <t>cases.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>createOrReplaceTempView</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>('cases_table')</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>newDF =</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> spark.sql(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>'select * from cases_table where confirmed &gt; 100 order by confirmed desc')</t>
+    </r>
+  </si>
+  <si>
+    <t>Replace content</t>
+  </si>
+  <si>
+    <t>PySpark-master\Dataframe Complete.ipynb</t>
+  </si>
+  <si>
+    <t>Columns</t>
+  </si>
+  <si>
+    <t>change one</t>
+  </si>
+  <si>
+    <r>
+      <t>cases = cases.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>withColumnRenamed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>("col_name_a","Col_Name_A")</t>
+    </r>
+  </si>
+  <si>
+    <t>change all</t>
+  </si>
+  <si>
+    <r>
+      <t>cases = cases.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>toDF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(*['A', 'B', 'C', 'D'])</t>
+    </r>
+  </si>
+  <si>
+    <t>Cast column values to other types</t>
+  </si>
+  <si>
+    <t>from pyspark.sql.types import DoubleType, IntegerType, StringType</t>
+  </si>
+  <si>
+    <r>
+      <t>cases = cases.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>withColumn</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>('confirmed', F.col('confirmed').cast(IntegerType()))</t>
+    </r>
+  </si>
+  <si>
+    <t>Reshaping data</t>
+  </si>
+  <si>
+    <r>
+      <t>cases.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>limit</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(10).</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>toPandas</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>()</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>cases.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>sort</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>('confirmed').show()</t>
+    </r>
+  </si>
+  <si>
+    <t>from pyspark.sql import functions as F</t>
+  </si>
+  <si>
+    <r>
+      <t>cases.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>sort</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>F.desc</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>("confirmed")).show()</t>
+    </r>
+  </si>
+  <si>
+    <t>https://sparkbyexamples.com/pyspark/pyspark-where-filter/</t>
+  </si>
+  <si>
+    <r>
+      <t>cases.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>filter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>((cases.confirmed&gt;10) &amp; (cases.province=='Daegu')).show()</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>cases = df1.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>join</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(df2, ['province','city'],how='left')</t>
+    </r>
+  </si>
+  <si>
+    <t>Nan operations</t>
+  </si>
+  <si>
+    <r>
+      <t>df.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>filter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(isnan(col("your_column"))).show()</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>df.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>select</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>([count(when(isnan(c), c)).alias(c) for c in df.columns]).show()</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    df.na.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>drop</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(subset=["your_numeric_column"]).show()</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    df.na.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>fill</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(0.0, subset=["your_numeric_column"]).show()</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>df.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>filter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>~</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(df.state == "OH"))</t>
+    </r>
+  </si>
+  <si>
+    <t>Add new column with calculated values</t>
+  </si>
+  <si>
+    <t>casesWithNewConfirmed = cases.withColumn("NewConfirmed", 100 + F.col("confirmed"))</t>
+  </si>
+  <si>
+    <t>https://community.databricks.com/t5/technical-blog/understanding-pandas-udf-applyinpandas-and-mapinpandas/ba-p/75717</t>
+  </si>
+  <si>
+    <t>Input</t>
+  </si>
+  <si>
+    <t>Output</t>
+  </si>
+  <si>
+    <t>Method</t>
+  </si>
+  <si>
+    <t>One Row</t>
+  </si>
+  <si>
+    <t>One Row for one input row</t>
+  </si>
+  <si>
+    <t>Pandas UDF</t>
+  </si>
+  <si>
+    <t>Many Rows</t>
+  </si>
+  <si>
+    <t>One Row aggregate for many</t>
+  </si>
+  <si>
+    <t>applyInPandas</t>
+  </si>
+  <si>
+    <t>Many Rows for each input row</t>
+  </si>
+  <si>
+    <t>mapInPandas</t>
+  </si>
+  <si>
+    <t>map</t>
+  </si>
+  <si>
+    <t>Primarily used for element-wise transformations on RDDs, where each input element produces exactly one output element.</t>
+  </si>
+  <si>
+    <t>Generally efficient for RDD transformations as it operates on the distributed RDD partitions.</t>
+  </si>
+  <si>
+    <t>Used for grouped aggregations or transformations where a function is applied to each group of data (e.g., after a groupBy operation), and the function returns a Pandas DataFrame for each group.</t>
+  </si>
+  <si>
+    <t>def denormalize(pdf: pd.DataFrame) -&gt; pd.DataFrame:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  aggregated_df = pdf.groupby('device_id', as_index=False).agg(</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      {'trip_id': lambda x: list(x), 'sensor_reading': 'mean', 'sqrt_reading': 'mean'}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  return aggregated_df</t>
+  </si>
+  <si>
+    <r>
+      <t>expected_schema</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = 'device_id int, trip_id array&lt;int&gt;, sensor_reading long, sqrt_reading long'</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>df = df.groupBy('device_id').</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>applyInPandas</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(denormalize, schema=expected_schema)</t>
+    </r>
+  </si>
+  <si>
+    <t>df.display()</t>
+  </si>
+  <si>
+    <t>Used for transformations where a function takes an iterator of Pandas DataFrames and returns an iterator of Pandas DataFrames, allowing for more flexible input/output relationships than a one-to-one mapping.</t>
+  </si>
+  <si>
+    <t>Usecase: Training multiple models per group, complex windowing operations, or when leveraging the rich functionality of the Pandas library on large datasets.</t>
+  </si>
+  <si>
+    <t>Avoid traditional Python UDFs, if performance is a major concern</t>
+  </si>
+  <si>
+    <t>call_udf</t>
+  </si>
+  <si>
+    <t>UDFs are typically used with withColumn to create new columns or transform existing ones based on custom logic.</t>
+  </si>
+  <si>
+    <r>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="var(--pst-font-family-monospace"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF00622F"/>
+        <rFont val="var(--pst-font-family-monospace"/>
+        <charset val="134"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="var(--pst-font-family-monospace"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="var(--pst-font-family-monospace"/>
+        <charset val="134"/>
+      </rPr>
+      <t>spark</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF00622F"/>
+        <rFont val="var(--pst-font-family-monospace"/>
+        <charset val="134"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="var(--pst-font-family-monospace"/>
+        <charset val="134"/>
+      </rPr>
+      <t>udf</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF00622F"/>
+        <rFont val="var(--pst-font-family-monospace"/>
+        <charset val="134"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="var(--pst-font-family-monospace"/>
+        <charset val="134"/>
+      </rPr>
+      <t>register(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF00622F"/>
+        <rFont val="var(--pst-font-family-monospace"/>
+        <charset val="134"/>
+      </rPr>
+      <t>"customFunc1"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="var(--pst-font-family-monospace"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="var(--pst-font-family-monospace"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF6730C5"/>
+        <rFont val="var(--pst-font-family-monospace"/>
+        <charset val="134"/>
+      </rPr>
+      <t>lambda</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="var(--pst-font-family-monospace"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="var(--pst-font-family-monospace"/>
+        <charset val="134"/>
+      </rPr>
+      <t>i:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="var(--pst-font-family-monospace"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="var(--pst-font-family-monospace"/>
+        <charset val="134"/>
+      </rPr>
+      <t>i</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="var(--pst-font-family-monospace"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF00622F"/>
+        <rFont val="var(--pst-font-family-monospace"/>
+        <charset val="134"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="var(--pst-font-family-monospace"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF7F4707"/>
+        <rFont val="var(--pst-font-family-monospace"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="var(--pst-font-family-monospace"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="var(--pst-font-family-monospace"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="var(--pst-font-family-monospace"/>
+        <charset val="134"/>
+      </rPr>
+      <t>IntegerType())</t>
+    </r>
+  </si>
+  <si>
+    <t>UDFs, especially traditional Python UDFs, can incur performance overhead due to serialization and deserialization between the JVM (Spark's core) and the Python interpreter. Pandas UDFs (Vectorized UDFs) mitigate this by leveraging Apache Arrow for efficient data transfer, improving performance for certain operations.</t>
+  </si>
+  <si>
+    <r>
+      <t>df</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF00622F"/>
+        <rFont val="var(--pst-font-family-monospace"/>
+        <charset val="134"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="var(--pst-font-family-monospace"/>
+        <charset val="134"/>
+      </rPr>
+      <t>select(call_udf(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF00622F"/>
+        <rFont val="var(--pst-font-family-monospace"/>
+        <charset val="134"/>
+      </rPr>
+      <t>"customFunc1"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="var(--pst-font-family-monospace"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="var(--pst-font-family-monospace"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF00622F"/>
+        <rFont val="var(--pst-font-family-monospace"/>
+        <charset val="134"/>
+      </rPr>
+      <t>"colA"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="var(--pst-font-family-monospace"/>
+        <charset val="134"/>
+      </rPr>
+      <t>))</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF00622F"/>
+        <rFont val="var(--pst-font-family-monospace"/>
+        <charset val="134"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="var(--pst-font-family-monospace"/>
+        <charset val="134"/>
+      </rPr>
+      <t>show()</t>
+    </r>
+  </si>
+  <si>
+    <t>spark.apache.org/docs/latest/api/python/reference/pyspark.sql/api/pyspark.sql.functions.call_udf.html</t>
+  </si>
+  <si>
+    <t>spark.apache.org/docs/latest/api/python/reference/pyspark.sql/api/pyspark.sql.functions.pandas_udf.html</t>
+  </si>
+  <si>
+    <t>Pandas UDFs, also known as Vectorized UDFs, are a feature in PySpark that allow users to define functions that leverage Pandas for data manipulation within Spark's distributed environment.</t>
+  </si>
+  <si>
+    <t>@pandas_udf('double')</t>
+  </si>
+  <si>
+    <t># pdf is a pandas.DataFrame</t>
+  </si>
+  <si>
+    <t>`</t>
+  </si>
+  <si>
+    <t>def calculate_sqrt(sensor_reading: pd.Series) -&gt; pd.Series:</t>
+  </si>
+  <si>
+    <t>return sensor_reading.apply(lambda x: x**0.5)</t>
+  </si>
+  <si>
+    <t>df.withColumn('sqrt_reading', calculate_sqrt(col('sensor_reading')))</t>
+  </si>
+  <si>
+    <t>https://docs.databricks.com/aws/en/udf/pandas</t>
+  </si>
+  <si>
+    <t>Assign value to new column after more complicated calculation</t>
+  </si>
+  <si>
+    <t>use User-Defined Functions (UDFs)</t>
+  </si>
+  <si>
+    <t>UDF Function by passing in the function and return type of function</t>
+  </si>
+  <si>
+    <t>casesHighLowUDF = F.udf(customFunc, StringType())</t>
+  </si>
+  <si>
+    <t>CasesWithHighLow = cases.withColumn("NewColName", casesHighLowUDF("colA_as-input"))</t>
+  </si>
+  <si>
+    <t>https://spark.apache.org/docs/latest/sql-ref-functions.html#udfs-user-defined-functions</t>
+  </si>
+  <si>
+    <t>UDFs further extends to UDAFs, which are advance topics</t>
+  </si>
+  <si>
+    <t>Summarize Data</t>
+  </si>
+  <si>
+    <t>Group Data</t>
+  </si>
+  <si>
+    <r>
+      <t>cases.groupBy(["a","b"]).</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>agg</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(F.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>sum</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>("c").</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>alias</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>("TotalC") ,F.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>max</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>("c")).show()</t>
+    </r>
+  </si>
+  <si>
+    <t>Combine Data sets</t>
+  </si>
+  <si>
+    <t>Windows</t>
+  </si>
+  <si>
+    <t>Plotting</t>
+  </si>
   <si>
     <t>Apache Spark ? vs Hadoop not pandas</t>
   </si>
@@ -2177,7 +3381,7 @@
     </r>
   </si>
   <si>
-    <t>Examle Spark Programs</t>
+    <t>Example Spark Programs</t>
   </si>
   <si>
     <t>https://spark.apache.org/examples.html</t>
@@ -2186,24 +3390,6 @@
     <t>Most basic things in py</t>
   </si>
   <si>
-    <t>s.no.</t>
-  </si>
-  <si>
-    <t>hints</t>
-  </si>
-  <si>
-    <t>topic</t>
-  </si>
-  <si>
-    <t>sub-topic</t>
-  </si>
-  <si>
-    <t>priority</t>
-  </si>
-  <si>
-    <t>flag</t>
-  </si>
-  <si>
     <t>https://docs.databricks.com/aws/en/pyspark/basics</t>
   </si>
   <si>
@@ -2303,22 +3489,82 @@
     <t>How to better utilize Apache Spark for any use cases</t>
   </si>
   <si>
-    <t>Optimize data partitioning: Partitioning is essential for parallelism, but you should also consider how your data will be read, joined, and queried to avoid data skew and reduce expensive shuffle operations. A well-partitioned dataset balances parallelism and partition size, ensuring efficient data processing. Avoid making users read through large volumes of data unnecessarily by planning partitions based on downstream usage and queries.</t>
-  </si>
-  <si>
-    <t>Use Efficient Data Formats: I highly recommend using Apache Parquet as your go-to data format. Parquet’s columnar storage and excellent compression drastically improve performance, especially for analytical workloads. Its ability to support schema evolution also adds flexibility when working with changing data structures, and the built-in metadata allows Spark to optimize queries without scanning the entire dataset. Overall, I’ve found that Parquet provides the best balance of speed, efficiency, and scalability for Spark-based projects</t>
-  </si>
-  <si>
-    <t>Make use of broadcast variables: For read-only data that needs to be shared across multiple nodes, use broadcast variables. This reduces the overhead of data transfer and improves efficiency in tasks like joins with small lookup tables</t>
-  </si>
-  <si>
-    <t>Utilize accumulator variables: Accumulators are a way to perform a running total or count that can be safely updated across multiple nodes. Use them for counters or sums that need to be aggregated globally.</t>
-  </si>
-  <si>
-    <t>Profile your jobs: Use Spark’s built-in profiling tools, like the Spark UI, to identify bottlenecks and optimize your Spark jobs. Tools like Ganglia or Graphite can also provide deeper insights into your cluster’s performance.</t>
-  </si>
-  <si>
-    <t>Cache strategically: Use caching (cache() or persist()) for intermediate results that are reused multiple times. However, be mindful of memory usage and avoid over-caching, which can lead to memory spills and degrade performance.</t>
+    <r>
+      <t>Optimize data partitioning:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t> Partitioning is essential for parallelism, but you should also consider how your data will be read, joined, and queried to avoid data skew and reduce expensive shuffle operations. A well-partitioned dataset balances parallelism and partition size, ensuring efficient data processing. Avoid making users read through large volumes of data unnecessarily by planning partitions based on downstream usage and queries.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Use Efficient Data Formats:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t> I highly recommend using Apache Parquet as your go-to data format. Parquet’s columnar storage and excellent compression drastically improve performance, especially for analytical workloads. Its ability to support schema evolution also adds flexibility when working with changing data structures, and the built-in metadata allows Spark to optimize queries without scanning the entire dataset. Overall, I’ve found that Parquet provides the best balance of speed, efficiency, and scalability for Spark-based projects</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Make use of broadcast variables</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>: For read-only data that needs to be shared across multiple nodes, use broadcast variables. This reduces the overhead of data transfer and improves efficiency in tasks like joins with small lookup tables</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Utilize accumulator variables</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>: Accumulators are a way to perform a running total or count that can be safely updated across multiple nodes. Use them for counters or sums that need to be aggregated globally.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Profile your jobs:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t> Use Spark’s built-in profiling tools, like the Spark UI, to identify bottlenecks and optimize your Spark jobs. Tools like Ganglia or Graphite can also provide deeper insights into your cluster’s performance.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Cache strategically: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Use caching (cache() or persist()) for intermediate results that are reused multiple times. However, be mindful of memory usage and avoid over-caching, which can lead to memory spills and degrade performance.</t>
+    </r>
   </si>
   <si>
     <t>https://www.instaclustr.com/education/apache-spark/8-amazing-apache-spark-use-cases-with-code-examples/</t>
@@ -2920,6 +4166,129 @@
   </si>
   <si>
     <t>ads.pprint()</t>
+  </si>
+  <si>
+    <t>UDFs vs map vs applyInPandas and mapInPandas</t>
+  </si>
+  <si>
+    <t>Summary of Differences:</t>
+  </si>
+  <si>
+    <t>UDFs: operate on individual column values or rows (with Pandas UDFs operating on batches of Series).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 types: </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">First, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Scalar / Standard python udf</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">   like where we use
+           spark.udf.register('func1', (a,b) =&gt; a+b)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Second, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Vectorized UDF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> where the function need to be annotated by
+           F.pandas_usd(returnType, ..)
+          or     @pandas_udf(....)</t>
+    </r>
+  </si>
+  <si>
+    <t>Vectorize udf are 5 times faster over standard udf. But standard Spark-sql is most faster way</t>
+  </si>
+  <si>
+    <t>to enable Vectorize udf set: spark.sql.execution.arrow.pyspark.enabled = true</t>
+  </si>
+  <si>
+    <t>map: operates on individual elements of RDDs.</t>
+  </si>
+  <si>
+    <t>applyInPandas and mapInPandas: operate on entire Pandas DataFrames or Series, often within a grouped context, and are designed for more complex, potentially multi-row input/output transformations.</t>
+  </si>
+  <si>
+    <t>Choosing the right approach:</t>
+  </si>
+  <si>
+    <t>Prioritize built-in Spark functions and DataFrame/Dataset operations</t>
+  </si>
+  <si>
+    <t>whenever possible for optimal performance due to Spark's Catalyst optimizer.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Use </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Pandas UDFs or applyInPandas/mapInPandas</t>
+    </r>
+  </si>
+  <si>
+    <t>when custom logic or Pandas library functionality is required and performance is critical.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Consider </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>RDD map</t>
+    </r>
+  </si>
+  <si>
+    <t>when working directly with RDDs or for very simple element-wise transformations on unstructured data.</t>
+  </si>
+  <si>
+    <t>Avoid traditional Python UDFs</t>
+  </si>
+  <si>
+    <t>if performance is a major concern, and explore Pandas UDFs as an alternative.</t>
+  </si>
+  <si>
+    <t>https://docs.aws.amazon.com/prescriptive-guidance/latest/tuning-aws-glue-for-apache-spark/optimize-user-defined-functions.html</t>
   </si>
 </sst>
 </file>
@@ -2932,7 +4301,7 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
   </numFmts>
-  <fonts count="52">
+  <fonts count="59">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -2964,15 +4333,17 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Bahnschrift"/>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF161616"/>
+      <name val="Segoe UI"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10.5"/>
-      <color rgb="FF080808"/>
-      <name val="Consolas"/>
+      <b/>
+      <i/>
+      <sz val="12"/>
+      <name val="Calibri"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2990,6 +4361,12 @@
       <i/>
       <sz val="11"/>
       <name val="Bahnschrift"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF080808"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
@@ -3033,13 +4410,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF161616"/>
-      <name val="Segoe UI"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color rgb="FF4183C4"/>
       <name val="Calibri"/>
@@ -3069,6 +4439,31 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Bahnschrift"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Bahnschrift"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Bahnschrift"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF080808"/>
+      <name val="var(--pst-font-family-monospace"/>
       <charset val="134"/>
     </font>
     <font>
@@ -3226,7 +4621,14 @@
       <b/>
       <i/>
       <sz val="12"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.2"/>
+      <color rgb="FF1F2328"/>
+      <name val="var(--fontStack-monospace"/>
       <charset val="134"/>
     </font>
     <font>
@@ -3243,16 +4645,40 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10.2"/>
-      <color rgb="FF1F2328"/>
-      <name val="var(--fontStack-monospace"/>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF333333"/>
+      <name val="Calibri"/>
       <charset val="134"/>
     </font>
     <font>
-      <i/>
+      <sz val="10.5"/>
+      <color theme="1"/>
+      <name val="var(--pst-font-family-monospace"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF00622F"/>
+      <name val="var(--pst-font-family-monospace"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF6730C5"/>
+      <name val="var(--pst-font-family-monospace"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF7F4707"/>
+      <name val="var(--pst-font-family-monospace"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="12"/>
-      <color rgb="FF161616"/>
-      <name val="Segoe UI"/>
+      <color rgb="FF666666"/>
+      <name val="Calibri"/>
       <charset val="134"/>
     </font>
     <font>
@@ -3262,24 +4688,10 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF333333"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
       <i/>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF666666"/>
-      <name val="Calibri"/>
+      <color rgb="FF161616"/>
+      <name val="Segoe UI"/>
       <charset val="134"/>
     </font>
     <font>
@@ -3484,27 +4896,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFD1D5DA"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFD1D5DA"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFD1D5DA"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFD1D5DA"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -3623,152 +5020,152 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3777,6 +5174,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -3793,6 +5193,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" indent="1"/>
     </xf>
@@ -3802,8 +5205,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -3811,11 +5220,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
@@ -3827,66 +5237,67 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3895,7 +5306,7 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3907,6 +5318,24 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4424,2130 +5853,744 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B127"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="15.5" outlineLevelCol="1"/>
+  <dimension ref="A2:H145"/>
+  <sheetFormatPr defaultColWidth="8.66923076923077" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="1.08461538461538" style="39" customWidth="1"/>
-    <col min="2" max="2" width="93.1307692307692" style="49" customWidth="1"/>
-    <col min="3" max="4" width="3.52307692307692" style="38" customWidth="1"/>
-    <col min="5" max="5" width="30.6153846153846" style="38" customWidth="1"/>
-    <col min="6" max="16384" width="9.23076923076923" style="38"/>
+    <col min="1" max="1" width="26.4769230769231" style="69" customWidth="1"/>
+    <col min="2" max="2" width="24.3461538461538" style="69" customWidth="1"/>
+    <col min="3" max="3" width="3.07692307692308" style="70" customWidth="1"/>
+    <col min="4" max="4" width="7.08461538461538" style="69" customWidth="1"/>
+    <col min="5" max="5" width="7.75384615384615" style="69" customWidth="1"/>
+    <col min="6" max="6" width="33.2461538461538" style="69" customWidth="1"/>
+    <col min="7" max="8" width="4.5" style="69" customWidth="1"/>
+    <col min="9" max="16384" width="8.66923076923077" style="69"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:2">
-      <c r="B1" s="51" t="s">
+    <row r="2" spans="1:8">
+      <c r="A2" s="69" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="2:2">
-      <c r="B2" s="51"/>
-    </row>
-    <row r="3" ht="62" spans="2:2">
-      <c r="B3" s="54" t="s">
+      <c r="B2" s="69" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" ht="31" spans="2:2">
-      <c r="B16" s="55" t="s">
+      <c r="C2" s="70" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="18" ht="62" spans="2:2">
-      <c r="B18" s="49" t="s">
+      <c r="E2" s="69" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="2:2">
-      <c r="B19" s="49" t="s">
+      <c r="G2" s="71" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="20" spans="2:2">
-      <c r="B20" s="49" t="s">
+      <c r="H2" s="69" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="21" ht="46.5" spans="2:2">
-      <c r="B21" s="49" t="s">
+    <row r="3" spans="1:6">
+      <c r="A3" s="69" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" s="48" t="s">
+      <c r="C3" s="72"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+    </row>
+    <row r="4" spans="3:6">
+      <c r="C4" s="72"/>
+      <c r="D4" s="74"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+    </row>
+    <row r="5" spans="3:6">
+      <c r="C5" s="72"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="73"/>
+      <c r="F5" s="73"/>
+    </row>
+    <row r="6" spans="3:6">
+      <c r="C6" s="72" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="24" spans="2:2">
-      <c r="B24" s="49" t="s">
+      <c r="D6" s="74"/>
+      <c r="E6" s="73"/>
+      <c r="F6" s="73"/>
+    </row>
+    <row r="7" spans="3:6">
+      <c r="C7" s="72"/>
+      <c r="D7" s="69" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="25" ht="46.5" spans="2:2">
-      <c r="B25" s="49" t="s">
+      <c r="E7" s="73"/>
+      <c r="F7" s="73"/>
+    </row>
+    <row r="8" spans="3:6">
+      <c r="C8" s="72"/>
+      <c r="D8" s="74"/>
+      <c r="E8" s="73"/>
+      <c r="F8" s="73"/>
+    </row>
+    <row r="9" spans="3:6">
+      <c r="C9" s="72"/>
+      <c r="D9" s="74"/>
+      <c r="E9" s="73"/>
+      <c r="F9" s="73"/>
+    </row>
+    <row r="10" spans="3:6">
+      <c r="C10" s="72"/>
+      <c r="D10" s="74"/>
+      <c r="E10" s="73"/>
+      <c r="F10" s="73"/>
+    </row>
+    <row r="11" spans="3:6">
+      <c r="C11" s="72"/>
+      <c r="D11" s="74"/>
+      <c r="E11" s="73"/>
+      <c r="F11" s="73"/>
+    </row>
+    <row r="12" spans="3:6">
+      <c r="C12" s="72"/>
+      <c r="D12" s="74"/>
+      <c r="E12" s="73"/>
+      <c r="F12" s="73"/>
+    </row>
+    <row r="13" spans="3:6">
+      <c r="C13" s="72" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="26" spans="2:2">
-      <c r="B26" s="49" t="s">
+      <c r="D13" s="74"/>
+      <c r="E13" s="73"/>
+      <c r="F13" s="73"/>
+    </row>
+    <row r="14" spans="3:6">
+      <c r="C14" s="72"/>
+      <c r="D14" s="74" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="27" ht="31" spans="2:2">
-      <c r="B27" s="49" t="s">
+      <c r="E14" s="73"/>
+      <c r="F14" s="73"/>
+    </row>
+    <row r="15" spans="3:6">
+      <c r="C15" s="72"/>
+      <c r="D15" s="74" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="29" ht="31" spans="2:2">
-      <c r="B29" s="49" t="s">
+      <c r="E15" s="73"/>
+      <c r="F15" s="73" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
-      <c r="A31" s="39" t="s">
+    <row r="16" spans="3:6">
+      <c r="C16" s="72"/>
+      <c r="D16" s="74"/>
+      <c r="E16" s="73"/>
+      <c r="F16" s="73"/>
+    </row>
+    <row r="17" spans="2:6">
+      <c r="B17" s="69" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="32" ht="31" spans="2:2">
-      <c r="B32" s="49" t="s">
+      <c r="C17" s="72"/>
+      <c r="D17" s="74" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="33" ht="31" spans="2:2">
-      <c r="B33" s="49" t="s">
+      <c r="E17" s="73"/>
+      <c r="F17" s="73"/>
+    </row>
+    <row r="18" spans="3:6">
+      <c r="C18" s="72"/>
+      <c r="D18" s="74"/>
+      <c r="E18" s="73"/>
+      <c r="F18" s="73"/>
+    </row>
+    <row r="19" spans="3:6">
+      <c r="C19" s="72"/>
+      <c r="D19" s="74" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="36" spans="2:2">
-      <c r="B36" s="51" t="s">
+      <c r="E19" s="73"/>
+      <c r="F19" s="73"/>
+    </row>
+    <row r="20" spans="3:6">
+      <c r="C20" s="72"/>
+      <c r="D20" s="74"/>
+      <c r="E20" s="73" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="37" spans="2:2">
-      <c r="B37" s="49" t="s">
+      <c r="F20" s="73"/>
+    </row>
+    <row r="21" ht="157" customHeight="1" spans="3:6">
+      <c r="C21" s="72"/>
+      <c r="D21" s="74"/>
+      <c r="E21" s="73"/>
+      <c r="F21" s="75" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="2:2">
-      <c r="B38" s="49" t="s">
+    <row r="22" spans="3:6">
+      <c r="C22" s="72"/>
+      <c r="D22" s="74" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="40" spans="2:2">
-      <c r="B40" s="56" t="s">
+      <c r="E22" s="73"/>
+      <c r="F22" s="73"/>
+    </row>
+    <row r="23" spans="3:6">
+      <c r="C23" s="72"/>
+      <c r="D23" s="74"/>
+      <c r="E23" s="73"/>
+      <c r="F23" s="73"/>
+    </row>
+    <row r="24" spans="3:6">
+      <c r="C24" s="72"/>
+      <c r="D24" s="74"/>
+      <c r="E24" s="73"/>
+      <c r="F24" s="73"/>
+    </row>
+    <row r="25" spans="3:6">
+      <c r="C25" s="72"/>
+      <c r="D25" s="74"/>
+      <c r="E25" s="73"/>
+      <c r="F25" s="73"/>
+    </row>
+    <row r="26" spans="3:6">
+      <c r="C26" s="72" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="41" ht="77.5" spans="2:2">
-      <c r="B41" s="57" t="s">
+      <c r="D26" s="74"/>
+      <c r="E26" s="73"/>
+      <c r="F26" s="73"/>
+    </row>
+    <row r="27" spans="3:6">
+      <c r="C27" s="72"/>
+      <c r="D27" s="73" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43" s="39" t="s">
+      <c r="E27" s="73"/>
+      <c r="F27" s="73"/>
+    </row>
+    <row r="28" spans="4:4">
+      <c r="D28" s="69" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="44" spans="2:2">
-      <c r="B44" s="49" t="s">
+    <row r="29" spans="2:4">
+      <c r="B29" s="69" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="45" spans="2:2">
-      <c r="B45" s="49" t="s">
+      <c r="C29" s="70"/>
+      <c r="D29" s="69" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="46" spans="2:2">
-      <c r="B46" s="49" t="s">
+    <row r="30" spans="5:5">
+      <c r="E30" s="69" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="48" spans="1:1">
-      <c r="A48" s="39" t="s">
+    <row r="35" spans="3:3">
+      <c r="C35" s="70" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="49" spans="2:2">
-      <c r="B49" s="49" t="s">
+    <row r="36" spans="1:4">
+      <c r="A36" s="69" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="50" spans="2:2">
-      <c r="B50" s="49" t="s">
+      <c r="D36" s="69" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="51" spans="2:2">
-      <c r="B51" s="49" t="s">
+    <row r="37" spans="2:5">
+      <c r="B37" s="69" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="53" spans="1:1">
-      <c r="A53" s="39" t="s">
+      <c r="C37" s="70"/>
+      <c r="E37" s="69" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="54" spans="2:2">
-      <c r="B54" s="49" t="s">
+    <row r="38" spans="2:5">
+      <c r="B38" s="69" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="55" spans="2:2">
-      <c r="B55" s="49" t="s">
+      <c r="C38" s="70"/>
+      <c r="E38" s="69" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="56" spans="2:2">
-      <c r="B56" s="49" t="s">
+    <row r="39" spans="4:4">
+      <c r="D39" s="69" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="57" spans="2:2">
-      <c r="B57" s="49" t="s">
+    <row r="40" spans="5:5">
+      <c r="E40" s="69" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="59" spans="1:1">
-      <c r="A59" s="39" t="s">
+    <row r="41" spans="5:5">
+      <c r="E41" s="69" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="60" spans="2:2">
-      <c r="B60" s="49" t="s">
+    <row r="49" spans="3:3">
+      <c r="C49" s="70" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="61" spans="2:2">
-      <c r="B61" s="49" t="s">
+    <row r="50" spans="4:4">
+      <c r="D50" s="69" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="62" spans="2:2">
-      <c r="B62" s="49" t="s">
+    <row r="51" spans="4:4">
+      <c r="D51" s="69" t="s">
         <v>37</v>
       </c>
     </row>
+    <row r="52" spans="4:4">
+      <c r="D52" s="69" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="53" spans="5:5">
+      <c r="E53" s="69" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" s="69" t="s">
+        <v>40</v>
+      </c>
+      <c r="D54" s="69" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" s="69" t="s">
+        <v>26</v>
+      </c>
+      <c r="D55" s="69" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="56" spans="4:4">
+      <c r="D56" s="70" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="57" spans="5:5">
+      <c r="E57" s="69" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="58" spans="5:5">
+      <c r="E58" s="69" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="59" spans="5:5">
+      <c r="E59" s="69" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="60" spans="5:5">
+      <c r="E60" s="69" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="62" spans="4:4">
+      <c r="D62" s="69" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="63" spans="2:5">
+      <c r="B63" s="69" t="s">
+        <v>49</v>
+      </c>
+      <c r="E63" s="69" t="s">
+        <v>50</v>
+      </c>
+    </row>
     <row r="65" spans="1:1">
-      <c r="A65" s="39" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="66" spans="2:2">
-      <c r="B66" s="49" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1">
-      <c r="A68" s="48" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="69" spans="2:2">
-      <c r="B69" s="49" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="70" spans="2:2">
-      <c r="B70" s="49" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="71" spans="2:2">
-      <c r="B71" s="49" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="72" spans="2:2">
-      <c r="B72" s="49" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="73" spans="2:2">
-      <c r="B73" s="49" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="74" spans="2:2">
-      <c r="B74" s="49" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="75" spans="2:2">
-      <c r="B75" s="49" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="106" spans="2:2">
-      <c r="B106" s="51" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="107" spans="2:2">
-      <c r="B107" s="49" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="109" ht="31" spans="2:2">
-      <c r="B109" s="58" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="112" spans="2:2">
-      <c r="B112" s="59" t="s">
+      <c r="A65" s="69" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="113" spans="2:2">
-      <c r="B113" s="49" t="s">
+    <row r="66" spans="1:3">
+      <c r="A66" s="70" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="114" ht="31" spans="2:2">
-      <c r="B114" s="60" t="s">
+      <c r="B66" s="70" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="115" spans="2:2">
-      <c r="B115" s="38"/>
-    </row>
-    <row r="116" ht="31" spans="2:2">
-      <c r="B116" s="60" t="s">
+      <c r="C66" s="70" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="117" spans="2:2">
-      <c r="B117" s="38"/>
-    </row>
-    <row r="118" spans="2:2">
-      <c r="B118" s="60" t="s">
+    <row r="67" spans="1:3">
+      <c r="A67" s="69" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="119" spans="2:2">
-      <c r="B119" s="61" t="s">
+      <c r="B67" s="69" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="120" spans="2:2">
-      <c r="B120" s="61" t="s">
+      <c r="C67" s="70" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="121" spans="2:2">
-      <c r="B121" s="61" t="s">
+    <row r="68" spans="1:3">
+      <c r="A68" s="69" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="122" ht="31" spans="2:2">
-      <c r="B122" s="61" t="s">
+      <c r="B68" s="69" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="123" spans="2:2">
-      <c r="B123" s="61" t="s">
+      <c r="C68" s="70" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="124" spans="2:2">
-      <c r="B124" s="61" t="s">
+    <row r="69" spans="1:3">
+      <c r="A69" s="69" t="s">
+        <v>55</v>
+      </c>
+      <c r="B69" s="69" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="125" ht="31" spans="2:2">
-      <c r="B125" s="61" t="s">
+      <c r="C69" s="70" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="127" spans="2:2">
-      <c r="B127"/>
+    <row r="73" spans="4:4">
+      <c r="D73" s="70"/>
+    </row>
+    <row r="74" spans="4:4">
+      <c r="D74" s="70"/>
+    </row>
+    <row r="75" spans="4:4">
+      <c r="D75" s="70" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
+      <c r="A76" s="76" t="s">
+        <v>64</v>
+      </c>
+      <c r="D76" s="70"/>
+    </row>
+    <row r="77" spans="1:4">
+      <c r="A77" s="76" t="s">
+        <v>65</v>
+      </c>
+      <c r="D77" s="70"/>
+    </row>
+    <row r="78" spans="1:4">
+      <c r="A78" s="76"/>
+      <c r="D78" s="70"/>
+    </row>
+    <row r="79" spans="1:4">
+      <c r="A79" s="76"/>
+      <c r="D79" s="70"/>
+    </row>
+    <row r="80" spans="1:4">
+      <c r="A80" s="76"/>
+      <c r="D80" s="70"/>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81" s="76"/>
+      <c r="D81" s="70"/>
+    </row>
+    <row r="82" spans="1:4">
+      <c r="A82" s="76"/>
+      <c r="D82" s="70" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4">
+      <c r="A83" s="76" t="s">
+        <v>66</v>
+      </c>
+      <c r="D83" s="70"/>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" s="76"/>
+      <c r="D84" s="70"/>
+      <c r="E84" s="69" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="A85" s="76"/>
+      <c r="D85" s="70"/>
+      <c r="F85" s="69" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="A86" s="76"/>
+      <c r="D86" s="70"/>
+      <c r="F86" s="69" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="A87" s="76" t="s">
+        <v>51</v>
+      </c>
+      <c r="D87" s="70"/>
+      <c r="F87" s="69" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6">
+      <c r="A88" s="76"/>
+      <c r="D88" s="70"/>
+      <c r="F88" s="69" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89" s="76"/>
+      <c r="D89" s="70"/>
+      <c r="E89" s="70" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90" s="76"/>
+      <c r="D90" s="70"/>
+      <c r="E90" s="69" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91" s="76"/>
+      <c r="D91" s="70"/>
+      <c r="E91" s="69" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4">
+      <c r="A92" s="76"/>
+      <c r="D92" s="70"/>
+    </row>
+    <row r="93" spans="1:4">
+      <c r="A93" s="76"/>
+      <c r="D93" s="70" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94" s="76" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95" s="76" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96" s="76"/>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" s="76"/>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" s="76"/>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" s="76"/>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" s="76"/>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101" s="76"/>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" s="76"/>
+    </row>
+    <row r="103" spans="1:4">
+      <c r="A103" s="76" t="s">
+        <v>77</v>
+      </c>
+      <c r="D103" s="70" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5">
+      <c r="A104" s="76" t="s">
+        <v>79</v>
+      </c>
+      <c r="E104" s="77" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5">
+      <c r="A105" s="76" t="s">
+        <v>81</v>
+      </c>
+      <c r="E105" s="77" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5">
+      <c r="A106" s="76" t="s">
+        <v>83</v>
+      </c>
+      <c r="E106" s="77"/>
+    </row>
+    <row r="107" spans="5:5">
+      <c r="E107" s="77"/>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108" s="69" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109" s="76" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110" s="76"/>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111" s="76"/>
+      <c r="D111" s="70" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="112" spans="2:5">
+      <c r="B112" s="69" t="s">
+        <v>87</v>
+      </c>
+      <c r="D112" s="69" t="s">
+        <v>88</v>
+      </c>
+      <c r="E112" s="69" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="113" spans="6:6">
+      <c r="F113" s="69" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="114" spans="5:5">
+      <c r="E114" s="69" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115" s="76" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116" s="69" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4">
+      <c r="A118" s="69" t="s">
+        <v>93</v>
+      </c>
+      <c r="D118" s="70" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5">
+      <c r="A119" s="70" t="s">
+        <v>95</v>
+      </c>
+      <c r="E119" s="69" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5">
+      <c r="A120" s="69" t="s">
+        <v>26</v>
+      </c>
+      <c r="E120" s="69" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121" s="69" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122" s="69" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="129" spans="3:3">
+      <c r="C129" s="70" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="134" spans="4:4">
+      <c r="D134" s="70" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5">
+      <c r="A135" s="69" t="s">
+        <v>26</v>
+      </c>
+      <c r="D135" s="70"/>
+      <c r="E135" s="69" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="136" spans="4:4">
+      <c r="D136" s="70"/>
+    </row>
+    <row r="137" spans="4:4">
+      <c r="D137" s="70"/>
+    </row>
+    <row r="138" spans="4:4">
+      <c r="D138" s="70" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="139" spans="4:4">
+      <c r="D139" s="70"/>
+    </row>
+    <row r="140" spans="4:4">
+      <c r="D140" s="70"/>
+    </row>
+    <row r="141" spans="4:4">
+      <c r="D141" s="70"/>
+    </row>
+    <row r="142" spans="4:4">
+      <c r="D142" s="70"/>
+    </row>
+    <row r="143" spans="4:4">
+      <c r="D143" s="70" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="144" spans="4:4">
+      <c r="D144" s="70"/>
+    </row>
+    <row r="145" spans="4:4">
+      <c r="D145" s="70" t="s">
+        <v>105</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:D34"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="15.5" outlineLevelCol="3"/>
-  <cols>
-    <col min="1" max="1" width="3.39230769230769" style="46" customWidth="1"/>
-    <col min="2" max="2" width="2.94615384615385" style="47" customWidth="1"/>
-    <col min="3" max="3" width="2.88461538461538" style="47" customWidth="1"/>
-    <col min="4" max="4" width="83.9692307692308" style="47" customWidth="1"/>
-    <col min="5" max="16384" width="9.23076923076923" style="47"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:2">
-      <c r="B1" s="48" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="2" spans="2:2">
-      <c r="B2" s="48" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="3" spans="2:2">
-      <c r="B3" s="29"/>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" s="48" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" s="47" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="47" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="7" ht="46.5" spans="4:4">
-      <c r="D7" s="11" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="8" ht="80" customHeight="1" spans="4:4">
-      <c r="D8" s="49" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="9" ht="46.5" spans="4:4">
-      <c r="D9" s="50" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="10" ht="93" spans="4:4">
-      <c r="D10" s="51" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="11" spans="4:4">
-      <c r="D11" s="49" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="13" spans="4:4">
-      <c r="D13" s="47" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="17" ht="17.5" spans="2:2">
-      <c r="B17" s="52" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="18" ht="35" spans="2:4">
-      <c r="B18" s="52"/>
-      <c r="D18" s="9" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="19" ht="17.5" spans="2:3">
-      <c r="B19" s="48"/>
-      <c r="C19" s="53" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="20" ht="17.5" spans="2:4">
-      <c r="B20" s="48"/>
-      <c r="C20" s="53"/>
-      <c r="D20" s="49"/>
-    </row>
-    <row r="21" spans="2:3">
-      <c r="B21" s="48"/>
-      <c r="C21" s="47" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="22" spans="2:3">
-      <c r="B22" s="48"/>
-      <c r="C22" s="47" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="23" spans="2:3">
-      <c r="B23" s="48"/>
-      <c r="C23" s="47" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="24" spans="2:2">
-      <c r="B24" s="48"/>
-    </row>
-    <row r="25" spans="2:2">
-      <c r="B25" s="48"/>
-    </row>
-    <row r="26" ht="17.5" spans="2:2">
-      <c r="B26" s="52" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="27" ht="106" customHeight="1" spans="2:4">
-      <c r="B27" s="48"/>
-      <c r="D27" s="9" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="28" spans="2:2">
-      <c r="B28" s="48"/>
-    </row>
-    <row r="29" spans="2:2">
-      <c r="B29" s="48"/>
-    </row>
-    <row r="30" ht="35" spans="2:4">
-      <c r="B30" s="48" t="s">
-        <v>82</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="31" ht="17.5" spans="2:4">
-      <c r="B31" s="48"/>
-      <c r="D31" s="10" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="32" ht="17.5" spans="4:4">
-      <c r="D32" s="10" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="33" ht="17.5" spans="4:4">
-      <c r="D33" s="10" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="34" ht="17.5" spans="4:4">
-      <c r="D34" s="10" t="s">
-        <v>87</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:G200"/>
-  <sheetFormatPr defaultColWidth="8.66923076923077" defaultRowHeight="15.5" outlineLevelCol="6"/>
-  <cols>
-    <col min="1" max="1" width="3.07692307692308" style="35" customWidth="1"/>
-    <col min="2" max="4" width="4.15384615384615" style="36" customWidth="1"/>
-    <col min="5" max="5" width="82.6538461538462" style="37" customWidth="1"/>
-    <col min="6" max="6" width="12.1692307692308" style="38" customWidth="1"/>
-    <col min="7" max="8" width="4.5" style="38" customWidth="1"/>
-    <col min="9" max="16384" width="8.66923076923077" style="38"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:7">
-      <c r="B1" s="39" t="s">
-        <v>88</v>
-      </c>
-      <c r="G1" s="40"/>
-    </row>
-    <row r="2" spans="2:2">
-      <c r="B2" s="36" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="41">
-        <v>1</v>
-      </c>
-      <c r="B5" s="39" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="6" spans="2:2">
-      <c r="B6"/>
-    </row>
-    <row r="32" ht="52.5" spans="5:5">
-      <c r="E32" s="42" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="33" ht="35" spans="5:5">
-      <c r="E33" s="42" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="34" ht="35" spans="5:5">
-      <c r="E34" s="42" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="35" ht="17.5" spans="5:5">
-      <c r="E35" s="42" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="37" spans="2:2">
-      <c r="B37" s="36" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="38" ht="403" spans="5:5">
-      <c r="E38" s="37" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="40" ht="232.5" spans="5:5">
-      <c r="E40" s="43" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="42" spans="3:3">
-      <c r="C42" s="36" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="43" spans="3:3">
-      <c r="C43" s="36" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="44" spans="3:3">
-      <c r="C44" s="36" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="46" s="34" customFormat="1" ht="14" customHeight="1" spans="1:5">
-      <c r="A46" s="41">
-        <v>2</v>
-      </c>
-      <c r="B46" s="39" t="s">
-        <v>101</v>
-      </c>
-      <c r="C46" s="39"/>
-      <c r="D46" s="39"/>
-      <c r="E46" s="43"/>
-    </row>
-    <row r="47" ht="31" spans="5:5">
-      <c r="E47" s="37" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="48" ht="17.5" spans="3:3">
-      <c r="C48" s="44" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="49" ht="62" spans="5:5">
-      <c r="E49" s="37" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="51" spans="2:2">
-      <c r="B51"/>
-    </row>
-    <row r="83" spans="2:2">
-      <c r="B83" s="36" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="84" ht="35" spans="5:5">
-      <c r="E84" s="45" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="85" spans="5:5">
-      <c r="E85"/>
-    </row>
-    <row r="86" ht="17.5" spans="5:5">
-      <c r="E86" s="45" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="87" ht="17.5" spans="5:5">
-      <c r="E87" s="42" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="88" ht="17.5" spans="5:5">
-      <c r="E88" s="42" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="90" ht="52.5" spans="5:5">
-      <c r="E90" s="45" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="91" spans="5:5">
-      <c r="E91"/>
-    </row>
-    <row r="92" ht="52.5" spans="5:5">
-      <c r="E92" s="45" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="94" spans="2:2">
-      <c r="B94" s="36" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="95" spans="2:6">
-      <c r="B95" s="39" t="s">
-        <v>113</v>
-      </c>
-      <c r="C95" s="39"/>
-      <c r="D95" s="39" t="s">
-        <v>114</v>
-      </c>
-      <c r="E95" s="39" t="s">
-        <v>115</v>
-      </c>
-      <c r="F95" s="37"/>
-    </row>
-    <row r="96" spans="2:6">
-      <c r="B96" s="36" t="s">
-        <v>116</v>
-      </c>
-      <c r="D96" s="36" t="s">
-        <v>117</v>
-      </c>
-      <c r="E96" s="36" t="s">
-        <v>118</v>
-      </c>
-      <c r="F96" s="37"/>
-    </row>
-    <row r="97" spans="2:6">
-      <c r="B97" s="36" t="s">
-        <v>119</v>
-      </c>
-      <c r="D97" s="36" t="s">
-        <v>120</v>
-      </c>
-      <c r="E97" s="36" t="s">
-        <v>121</v>
-      </c>
-      <c r="F97" s="37"/>
-    </row>
-    <row r="98" spans="2:6">
-      <c r="B98" s="36" t="s">
-        <v>122</v>
-      </c>
-      <c r="D98" s="36" t="s">
-        <v>123</v>
-      </c>
-      <c r="E98" s="36" t="s">
-        <v>124</v>
-      </c>
-      <c r="F98" s="37"/>
-    </row>
-    <row r="99" spans="2:6">
-      <c r="B99" s="36" t="s">
-        <v>125</v>
-      </c>
-      <c r="D99" s="36" t="s">
-        <v>126</v>
-      </c>
-      <c r="E99" s="36" t="s">
-        <v>127</v>
-      </c>
-      <c r="F99" s="37"/>
-    </row>
-    <row r="100" spans="2:6">
-      <c r="B100" s="36" t="s">
-        <v>128</v>
-      </c>
-      <c r="D100" s="36" t="s">
-        <v>126</v>
-      </c>
-      <c r="E100" s="36" t="s">
-        <v>129</v>
-      </c>
-      <c r="F100" s="37"/>
-    </row>
-    <row r="101" spans="2:6">
-      <c r="B101" s="36" t="s">
-        <v>130</v>
-      </c>
-      <c r="D101" s="36" t="s">
-        <v>131</v>
-      </c>
-      <c r="E101" s="36" t="s">
-        <v>132</v>
-      </c>
-      <c r="F101" s="37"/>
-    </row>
-    <row r="102" spans="2:6">
-      <c r="B102" s="36" t="s">
-        <v>133</v>
-      </c>
-      <c r="D102" s="36" t="s">
-        <v>134</v>
-      </c>
-      <c r="E102" s="36"/>
-      <c r="F102" s="37"/>
-    </row>
-    <row r="103" spans="2:6">
-      <c r="B103" s="36" t="s">
-        <v>135</v>
-      </c>
-      <c r="E103" s="36"/>
-      <c r="F103" s="37"/>
-    </row>
-    <row r="104" spans="2:6">
-      <c r="B104" s="36" t="s">
-        <v>136</v>
-      </c>
-      <c r="E104" s="36"/>
-      <c r="F104" s="37"/>
-    </row>
-    <row r="105" spans="2:6">
-      <c r="B105" s="36" t="s">
-        <v>137</v>
-      </c>
-      <c r="E105" s="36"/>
-      <c r="F105" s="37"/>
-    </row>
-    <row r="106" spans="2:6">
-      <c r="B106" s="36" t="s">
-        <v>138</v>
-      </c>
-      <c r="E106" s="36"/>
-      <c r="F106" s="37"/>
-    </row>
-    <row r="107" spans="2:6">
-      <c r="B107" s="36" t="s">
-        <v>139</v>
-      </c>
-      <c r="E107" s="36"/>
-      <c r="F107" s="37"/>
-    </row>
-    <row r="108" spans="2:6">
-      <c r="B108" s="36" t="s">
-        <v>140</v>
-      </c>
-      <c r="E108" s="36"/>
-      <c r="F108" s="37"/>
-    </row>
-    <row r="109" spans="2:6">
-      <c r="B109" s="36" t="s">
-        <v>141</v>
-      </c>
-      <c r="E109" s="36"/>
-      <c r="F109" s="37"/>
-    </row>
-    <row r="110" spans="2:6">
-      <c r="B110" s="36" t="s">
-        <v>142</v>
-      </c>
-      <c r="E110" s="36"/>
-      <c r="F110" s="37"/>
-    </row>
-    <row r="111" spans="2:6">
-      <c r="B111" s="36" t="s">
-        <v>143</v>
-      </c>
-      <c r="E111" s="36"/>
-      <c r="F111" s="37"/>
-    </row>
-    <row r="112" spans="2:6">
-      <c r="B112" s="36" t="s">
-        <v>144</v>
-      </c>
-      <c r="E112" s="36"/>
-      <c r="F112" s="37"/>
-    </row>
-    <row r="113" spans="2:6">
-      <c r="B113" s="36" t="s">
-        <v>145</v>
-      </c>
-      <c r="E113" s="36"/>
-      <c r="F113" s="37"/>
-    </row>
-    <row r="115" spans="2:2">
-      <c r="B115" s="39" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="116" ht="263.5" spans="5:5">
-      <c r="E116" s="37" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="117" spans="2:2">
-      <c r="B117" s="36" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="119" s="34" customFormat="1" spans="1:5">
-      <c r="A119" s="41">
-        <v>3</v>
-      </c>
-      <c r="B119" s="39" t="s">
-        <v>148</v>
-      </c>
-      <c r="C119" s="39"/>
-      <c r="D119" s="39"/>
-      <c r="E119" s="43"/>
-    </row>
-    <row r="120" ht="62" spans="5:5">
-      <c r="E120" s="37" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="122" ht="108.5" spans="5:5">
-      <c r="E122" s="37" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="124" spans="3:3">
-      <c r="C124" s="39" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="125" spans="3:3">
-      <c r="C125" s="36" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="126" spans="3:3">
-      <c r="C126" s="39" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="127" spans="2:5">
-      <c r="B127" s="39" t="s">
-        <v>153</v>
-      </c>
-      <c r="C127" s="39"/>
-      <c r="D127" s="39" t="s">
-        <v>154</v>
-      </c>
-      <c r="E127" s="39" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="128" spans="2:5">
-      <c r="B128" s="36" t="s">
-        <v>156</v>
-      </c>
-      <c r="D128" s="36" t="s">
-        <v>157</v>
-      </c>
-      <c r="E128" s="36" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="129" spans="2:5">
-      <c r="B129" s="36" t="s">
-        <v>159</v>
-      </c>
-      <c r="D129" s="36" t="s">
-        <v>160</v>
-      </c>
-      <c r="E129" s="36" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="130" spans="2:5">
-      <c r="B130" s="36" t="s">
-        <v>162</v>
-      </c>
-      <c r="D130" s="36" t="s">
-        <v>163</v>
-      </c>
-      <c r="E130" s="36" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="131" spans="2:5">
-      <c r="B131" s="36" t="s">
-        <v>165</v>
-      </c>
-      <c r="D131" s="36" t="s">
-        <v>166</v>
-      </c>
-      <c r="E131" s="36" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="132" spans="2:5">
-      <c r="B132" s="36" t="s">
-        <v>167</v>
-      </c>
-      <c r="D132" s="36" t="s">
-        <v>168</v>
-      </c>
-      <c r="E132" s="36" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="133" spans="2:5">
-      <c r="B133" s="36" t="s">
-        <v>169</v>
-      </c>
-      <c r="D133" s="36" t="s">
-        <v>170</v>
-      </c>
-      <c r="E133" s="36" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="134" spans="2:5">
-      <c r="B134" s="36" t="s">
-        <v>171</v>
-      </c>
-      <c r="D134" s="36" t="s">
-        <v>172</v>
-      </c>
-      <c r="E134" s="36" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="135" spans="2:5">
-      <c r="B135" s="36" t="s">
-        <v>173</v>
-      </c>
-      <c r="D135" s="36" t="s">
-        <v>174</v>
-      </c>
-      <c r="E135" s="36" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="136" spans="2:5">
-      <c r="B136" s="36" t="s">
-        <v>176</v>
-      </c>
-      <c r="D136" s="36" t="s">
-        <v>177</v>
-      </c>
-      <c r="E136" s="36" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="137" spans="2:5">
-      <c r="B137" s="36" t="s">
-        <v>179</v>
-      </c>
-      <c r="D137" s="36" t="s">
-        <v>180</v>
-      </c>
-      <c r="E137" s="36" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="138" ht="46.5" spans="5:5">
-      <c r="E138" s="37" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="140" s="34" customFormat="1" spans="1:5">
-      <c r="A140" s="41">
-        <v>4</v>
-      </c>
-      <c r="B140" s="39" t="s">
-        <v>183</v>
-      </c>
-      <c r="C140" s="39"/>
-      <c r="D140" s="39"/>
-      <c r="E140" s="43"/>
-    </row>
-    <row r="141" spans="2:2">
-      <c r="B141" s="36" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="142" spans="2:2">
-      <c r="B142" s="36" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="143" spans="2:2">
-      <c r="B143" s="36" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="144" ht="46.5" spans="5:5">
-      <c r="E144" s="37" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="145" ht="62" spans="5:5">
-      <c r="E145" s="37" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="146" ht="31" spans="5:5">
-      <c r="E146" s="37" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="147" spans="5:5">
-      <c r="E147" s="37" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2">
-      <c r="A149" s="41">
-        <v>6</v>
-      </c>
-      <c r="B149" s="39" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="150" ht="31" spans="5:5">
-      <c r="E150" s="37" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="151" ht="17.5" spans="5:5">
-      <c r="E151" s="44" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="152" spans="3:3">
-      <c r="C152" s="36" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="153" spans="3:3">
-      <c r="C153" s="36" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="155" ht="139.5" spans="5:5">
-      <c r="E155" s="37" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="156" ht="31" spans="5:5">
-      <c r="E156" s="37" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="158" spans="2:5">
-      <c r="B158" s="39" t="s">
-        <v>198</v>
-      </c>
-      <c r="C158" s="39"/>
-      <c r="D158" s="39"/>
-      <c r="E158" s="43" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="159" ht="31" spans="2:5">
-      <c r="B159" s="36" t="s">
-        <v>200</v>
-      </c>
-      <c r="E159" s="37" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="160" ht="31" spans="2:5">
-      <c r="B160" s="36" t="s">
-        <v>202</v>
-      </c>
-      <c r="E160" s="37" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="161" ht="31" spans="2:5">
-      <c r="B161" s="36" t="s">
-        <v>204</v>
-      </c>
-      <c r="E161" s="37" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="162" spans="2:2">
-      <c r="B162" s="36" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="163" ht="31" spans="2:5">
-      <c r="B163" s="36" t="s">
-        <v>207</v>
-      </c>
-      <c r="E163" s="37" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="164" spans="2:2">
-      <c r="B164" s="36" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="165" spans="2:5">
-      <c r="B165" s="36" t="s">
-        <v>209</v>
-      </c>
-      <c r="E165" s="37" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="166" spans="2:5">
-      <c r="B166" s="36" t="s">
-        <v>211</v>
-      </c>
-      <c r="E166" s="37" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="167" ht="31" spans="2:5">
-      <c r="B167" s="36" t="s">
-        <v>213</v>
-      </c>
-      <c r="E167" s="37" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="169" ht="124" spans="5:5">
-      <c r="E169" s="37" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="171" spans="4:4">
-      <c r="D171" s="39" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="172" ht="232.5" spans="5:5">
-      <c r="E172" s="37" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="174" spans="4:4">
-      <c r="D174" s="39" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="175" ht="62" spans="5:5">
-      <c r="E175" s="37" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="177" spans="2:2">
-      <c r="B177" s="36" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="178" spans="1:2">
-      <c r="A178" s="41">
-        <v>7</v>
-      </c>
-      <c r="B178" s="39" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="179" spans="2:4">
-      <c r="B179" s="39" t="s">
-        <v>222</v>
-      </c>
-      <c r="C179" s="39"/>
-      <c r="D179" s="39"/>
-    </row>
-    <row r="180" ht="93" spans="2:5">
-      <c r="B180" s="39"/>
-      <c r="C180" s="39"/>
-      <c r="D180" s="39"/>
-      <c r="E180" s="37" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="181" spans="2:4">
-      <c r="B181" s="39"/>
-      <c r="C181" s="39" t="s">
-        <v>224</v>
-      </c>
-      <c r="D181" s="39"/>
-    </row>
-    <row r="182" ht="310" spans="2:5">
-      <c r="B182" s="39"/>
-      <c r="C182" s="39"/>
-      <c r="D182" s="39"/>
-      <c r="E182" s="37" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="183" spans="2:4">
-      <c r="B183" s="39"/>
-      <c r="C183" s="39"/>
-      <c r="D183" s="39"/>
-    </row>
-    <row r="184" ht="139.5" spans="2:5">
-      <c r="B184" s="39"/>
-      <c r="C184" s="39"/>
-      <c r="D184" s="39"/>
-      <c r="E184" s="37" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="185" spans="2:4">
-      <c r="B185" s="39"/>
-      <c r="C185" s="39"/>
-      <c r="D185" s="39"/>
-    </row>
-    <row r="186" spans="2:4">
-      <c r="B186" s="39"/>
-      <c r="C186" s="39" t="s">
-        <v>227</v>
-      </c>
-      <c r="D186" s="39"/>
-    </row>
-    <row r="187" ht="62" spans="2:5">
-      <c r="B187" s="39"/>
-      <c r="C187" s="39"/>
-      <c r="D187" s="39"/>
-      <c r="E187" s="37" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="188" spans="2:4">
-      <c r="B188" s="39"/>
-      <c r="C188" s="39"/>
-      <c r="D188" s="39"/>
-    </row>
-    <row r="189" ht="46.5" spans="2:5">
-      <c r="B189" s="39"/>
-      <c r="C189" s="39"/>
-      <c r="D189" s="39"/>
-      <c r="E189" s="37" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="190" spans="2:4">
-      <c r="B190" s="39"/>
-      <c r="C190" s="39"/>
-      <c r="D190" s="39"/>
-    </row>
-    <row r="191" ht="155" spans="2:5">
-      <c r="B191" s="39"/>
-      <c r="C191" s="39"/>
-      <c r="D191" s="39"/>
-      <c r="E191" s="37" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="192" spans="2:4">
-      <c r="B192" s="39"/>
-      <c r="C192" s="39"/>
-      <c r="D192" s="39"/>
-    </row>
-    <row r="193" spans="2:4">
-      <c r="B193" s="39"/>
-      <c r="C193" s="39"/>
-      <c r="D193" s="39" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="194" ht="31" spans="2:5">
-      <c r="B194" s="39"/>
-      <c r="C194" s="39"/>
-      <c r="D194" s="39"/>
-      <c r="E194" s="37" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="195" spans="2:5">
-      <c r="B195" s="39"/>
-      <c r="C195" s="39"/>
-      <c r="D195" s="39"/>
-      <c r="E195" s="37" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="196" spans="2:5">
-      <c r="B196" s="39"/>
-      <c r="C196" s="39"/>
-      <c r="D196" s="39"/>
-      <c r="E196" s="37" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="198" spans="1:2">
-      <c r="A198" s="35">
-        <v>8</v>
-      </c>
-      <c r="B198" s="36" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="200" spans="1:2">
-      <c r="A200" s="35">
-        <v>9</v>
-      </c>
-      <c r="B200" s="36" t="s">
-        <v>236</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="142" orientation="portrait"/>
-  <headerFooter/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A2:B105"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="15.5" outlineLevelCol="1"/>
-  <cols>
-    <col min="1" max="1" width="3.9" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:1">
-      <c r="A2" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" s="28" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" s="28" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="11" spans="2:2">
-      <c r="B11" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="12" spans="2:2">
-      <c r="B12" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" s="28" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="28" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="20" spans="2:2">
-      <c r="B20" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" s="28" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="25" hidden="1" spans="1:1">
-      <c r="A25" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="26" hidden="1" spans="1:1">
-      <c r="A26" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="27" hidden="1" spans="1:1">
-      <c r="A27" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="28" hidden="1" spans="1:1">
-      <c r="A28" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="29" hidden="1" spans="2:2">
-      <c r="B29" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="30" hidden="1" spans="1:1">
-      <c r="A30" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" s="28" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="34" hidden="1" spans="1:1">
-      <c r="A34" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="35" hidden="1" spans="1:1">
-      <c r="A35" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="36" hidden="1" spans="1:1">
-      <c r="A36" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="37" hidden="1" spans="1:1">
-      <c r="A37" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="38" hidden="1" spans="1:1">
-      <c r="A38" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="39" hidden="1" spans="1:1">
-      <c r="A39" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="40" hidden="1" spans="1:1">
-      <c r="A40" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="41" hidden="1" spans="1:1">
-      <c r="A41" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="42" hidden="1" spans="1:1">
-      <c r="A42" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="43" hidden="1" spans="1:1">
-      <c r="A43" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="44" hidden="1" spans="1:1">
-      <c r="A44" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="45" hidden="1" spans="1:1">
-      <c r="A45" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="46" hidden="1" spans="1:1">
-      <c r="A46" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="47" hidden="1" spans="1:1">
-      <c r="A47" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="48" hidden="1" spans="1:1">
-      <c r="A48" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="49" hidden="1" spans="1:1">
-      <c r="A49" s="29" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="50" hidden="1" spans="1:1">
-      <c r="A50" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="51" hidden="1" spans="1:1">
-      <c r="A51" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="52" hidden="1" spans="1:1">
-      <c r="A52" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="53" hidden="1" spans="1:1">
-      <c r="A53" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1">
-      <c r="A55" s="28" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1">
-      <c r="A56" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="57" hidden="1" spans="1:1">
-      <c r="A57" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="58" hidden="1" spans="1:1">
-      <c r="A58" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="59" hidden="1" spans="1:1">
-      <c r="A59" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="60" hidden="1"/>
-    <row r="61" hidden="1" spans="1:1">
-      <c r="A61" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="62" hidden="1" spans="1:1">
-      <c r="A62" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="63" hidden="1" spans="1:1">
-      <c r="A63" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1">
-      <c r="A65" s="28" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1">
-      <c r="A66" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1">
-      <c r="A67" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="68" hidden="1" spans="1:1">
-      <c r="A68" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="69" hidden="1" spans="1:1">
-      <c r="A69" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="70" hidden="1" spans="1:1">
-      <c r="A70" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="71" hidden="1" spans="1:1">
-      <c r="A71" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="72" hidden="1" spans="1:1">
-      <c r="A72" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="73" hidden="1" spans="1:1">
-      <c r="A73" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="74" hidden="1" spans="1:1">
-      <c r="A74" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="75" hidden="1" spans="1:1">
-      <c r="A75" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="76" hidden="1" spans="1:1">
-      <c r="A76" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1">
-      <c r="A78" s="28" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1">
-      <c r="A79" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1">
-      <c r="A80" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="81" hidden="1" spans="1:1">
-      <c r="A81" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="82" hidden="1" spans="1:1">
-      <c r="A82" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="83" hidden="1" spans="1:1">
-      <c r="A83" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="84" hidden="1" spans="1:1">
-      <c r="A84" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="85" hidden="1" spans="1:1">
-      <c r="A85" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="86" hidden="1" spans="1:1">
-      <c r="A86" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="87" hidden="1" spans="1:1">
-      <c r="A87" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="88" hidden="1" spans="1:1">
-      <c r="A88" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="89" hidden="1" spans="1:1">
-      <c r="A89" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="90" hidden="1" spans="1:1">
-      <c r="A90" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="91" hidden="1" spans="1:1">
-      <c r="A91" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="92" hidden="1" spans="1:1">
-      <c r="A92" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="93" hidden="1" spans="1:1">
-      <c r="A93" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="94" hidden="1"/>
-    <row r="95" hidden="1" spans="1:1">
-      <c r="A95" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="96" hidden="1" spans="1:1">
-      <c r="A96" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2">
-      <c r="A97" s="30"/>
-      <c r="B97" s="30"/>
-    </row>
-    <row r="98" spans="1:2">
-      <c r="A98" s="31" t="s">
-        <v>314</v>
-      </c>
-      <c r="B98" s="30"/>
-    </row>
-    <row r="99" spans="1:2">
-      <c r="A99" s="32" t="s">
-        <v>315</v>
-      </c>
-      <c r="B99" s="30"/>
-    </row>
-    <row r="100" spans="1:2">
-      <c r="A100" s="32" t="s">
-        <v>316</v>
-      </c>
-      <c r="B100" s="30"/>
-    </row>
-    <row r="101" spans="1:2">
-      <c r="A101" s="33"/>
-      <c r="B101" s="30"/>
-    </row>
-    <row r="102" spans="2:2">
-      <c r="B102" s="30"/>
-    </row>
-    <row r="104" spans="1:1">
-      <c r="A104" s="30" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="105" spans="1:1">
-      <c r="A105" t="s">
-        <v>318</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:H88"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14" outlineLevelCol="7"/>
-  <cols>
-    <col min="1" max="1" width="27.3307692307692" style="20" customWidth="1"/>
-    <col min="2" max="2" width="19.8307692307692" style="21" customWidth="1"/>
-    <col min="3" max="3" width="2.41538461538462" style="20" customWidth="1"/>
-    <col min="4" max="4" width="3.33076923076923" style="20" customWidth="1"/>
-    <col min="5" max="5" width="12.6692307692308" style="20" customWidth="1"/>
-    <col min="6" max="6" width="12.1692307692308" style="20" customWidth="1"/>
-    <col min="7" max="8" width="4.5" style="20" customWidth="1"/>
-    <col min="9" max="16384" width="11" style="20"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:2">
-      <c r="B1" s="21" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="20" t="s">
-        <v>320</v>
-      </c>
-      <c r="B2" s="21" t="s">
-        <v>321</v>
-      </c>
-      <c r="C2" s="20" t="s">
-        <v>322</v>
-      </c>
-      <c r="E2" s="20" t="s">
-        <v>323</v>
-      </c>
-      <c r="G2" s="22" t="s">
-        <v>324</v>
-      </c>
-      <c r="H2" s="20" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="4" spans="2:2">
-      <c r="B4" s="21" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="5" ht="15.5" spans="3:3">
-      <c r="C5" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="6" ht="15.5" spans="3:4">
-      <c r="C6" s="21"/>
-      <c r="D6" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="7" ht="15.5" spans="3:3">
-      <c r="C7" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="8" ht="15.5" spans="3:3">
-      <c r="C8" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="9" ht="15.5" spans="1:4">
-      <c r="A9" s="23"/>
-      <c r="C9" s="21"/>
-      <c r="D9" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="10" ht="15.5" spans="3:4">
-      <c r="C10" s="21"/>
-      <c r="D10" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="11" ht="15.5" spans="3:4">
-      <c r="C11" s="21"/>
-      <c r="D11" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="12" ht="15.5" spans="3:4">
-      <c r="C12" s="21"/>
-      <c r="D12" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="13" ht="15.5" spans="3:4">
-      <c r="C13" s="21"/>
-      <c r="D13" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="14" ht="15.5" spans="3:3">
-      <c r="C14" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="15" ht="15.5" spans="3:4">
-      <c r="C15" s="21"/>
-      <c r="D15" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="16" ht="15.5" spans="3:4">
-      <c r="C16" s="21"/>
-      <c r="D16" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="17" ht="15.5" spans="3:4">
-      <c r="C17" s="21"/>
-      <c r="D17" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="18" ht="15.5" spans="3:4">
-      <c r="C18" s="21"/>
-      <c r="D18" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="19" ht="15.5" spans="3:4">
-      <c r="C19" s="21"/>
-      <c r="D19" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="20" ht="15.5" spans="3:3">
-      <c r="C20" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="21" ht="15.5" spans="3:3">
-      <c r="C21" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="22" ht="15.5" spans="3:4">
-      <c r="C22" s="21"/>
-      <c r="D22" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="23" ht="15.5" spans="3:4">
-      <c r="C23" s="21"/>
-      <c r="D23" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="24" ht="15.5" spans="3:3">
-      <c r="C24" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="29" spans="3:3">
-      <c r="C29" s="20" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" s="24"/>
-      <c r="B30" s="25"/>
-      <c r="D30" s="20" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
-      <c r="A31" s="24"/>
-      <c r="B31" s="25"/>
-    </row>
-    <row r="32" spans="1:2">
-      <c r="A32" s="24"/>
-      <c r="B32" s="25"/>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" s="24"/>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34" s="24"/>
-      <c r="B34" s="25"/>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" s="24"/>
-    </row>
-    <row r="40" spans="1:1">
-      <c r="A40" s="24"/>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" s="24"/>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43" s="24"/>
-    </row>
-    <row r="56" spans="4:4">
-      <c r="D56" s="26"/>
-    </row>
-    <row r="57" spans="4:4">
-      <c r="D57" s="26"/>
-    </row>
-    <row r="58" spans="4:4">
-      <c r="D58" s="27"/>
-    </row>
-    <row r="61" spans="3:6">
-      <c r="C61" s="24"/>
-      <c r="D61" s="24"/>
-      <c r="E61" s="24"/>
-      <c r="F61" s="24"/>
-    </row>
-    <row r="62" spans="3:6">
-      <c r="C62" s="24"/>
-      <c r="D62" s="24"/>
-      <c r="E62" s="24"/>
-      <c r="F62" s="24"/>
-    </row>
-    <row r="63" spans="3:6">
-      <c r="C63" s="24"/>
-      <c r="D63" s="24"/>
-      <c r="E63" s="24"/>
-      <c r="F63" s="24"/>
-    </row>
-    <row r="64" spans="3:6">
-      <c r="C64" s="24"/>
-      <c r="D64" s="24"/>
-      <c r="F64" s="24"/>
-    </row>
-    <row r="65" spans="3:6">
-      <c r="C65" s="24"/>
-      <c r="D65" s="24"/>
-      <c r="E65" s="24"/>
-      <c r="F65" s="24"/>
-    </row>
-    <row r="66" spans="3:6">
-      <c r="C66" s="24"/>
-      <c r="D66" s="24"/>
-      <c r="E66" s="24"/>
-      <c r="F66" s="24"/>
-    </row>
-    <row r="88" spans="4:4">
-      <c r="D88" s="26"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="142" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A3"/>
-  <sheetFormatPr defaultColWidth="8.66923076923077" defaultRowHeight="12.5" outlineLevelRow="2"/>
-  <cols>
-    <col min="1" max="16384" width="8.66923076923077" style="19"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="1:1">
-      <c r="A3" s="19" t="s">
-        <v>349</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
@@ -6558,60 +6601,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:H5"/>
-  <sheetFormatPr defaultColWidth="8.66923076923077" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="7"/>
-  <cols>
-    <col min="1" max="1" width="17.2538461538462" style="16" customWidth="1"/>
-    <col min="2" max="2" width="8.66923076923077" style="16"/>
-    <col min="3" max="3" width="5.66923076923077" style="16" customWidth="1"/>
-    <col min="4" max="4" width="7.08461538461538" style="16" customWidth="1"/>
-    <col min="5" max="5" width="7.75384615384615" style="16" customWidth="1"/>
-    <col min="6" max="6" width="23.4692307692308" style="16" customWidth="1"/>
-    <col min="7" max="8" width="4.5" style="16" customWidth="1"/>
-    <col min="9" max="16384" width="8.66923076923077" style="16"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:8">
-      <c r="A2" s="16" t="s">
-        <v>320</v>
-      </c>
-      <c r="B2" s="16" t="s">
-        <v>321</v>
-      </c>
-      <c r="C2" s="16" t="s">
-        <v>322</v>
-      </c>
-      <c r="E2" s="16" t="s">
-        <v>323</v>
-      </c>
-      <c r="G2" s="17" t="s">
-        <v>324</v>
-      </c>
-      <c r="H2" s="16" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="3" ht="14.75"/>
-    <row r="4" ht="14.75" spans="4:4">
-      <c r="D4" s="18"/>
-    </row>
-    <row r="5" ht="14.75" spans="4:4">
-      <c r="D5" s="18"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="142" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:D259"/>
+  <dimension ref="A1:D284"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="15.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="3.43076923076923" style="1" customWidth="1"/>
@@ -6623,7 +6616,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="2" t="s">
-        <v>350</v>
+        <v>450</v>
       </c>
     </row>
     <row r="2" spans="2:3">
@@ -6631,7 +6624,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>351</v>
+        <v>451</v>
       </c>
     </row>
     <row r="3" spans="2:3">
@@ -6639,7 +6632,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>352</v>
+        <v>452</v>
       </c>
     </row>
     <row r="4" spans="2:3">
@@ -6647,7 +6640,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>353</v>
+        <v>453</v>
       </c>
     </row>
     <row r="5" spans="2:3">
@@ -6655,7 +6648,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>354</v>
+        <v>454</v>
       </c>
     </row>
     <row r="6" spans="2:3">
@@ -6663,7 +6656,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>355</v>
+        <v>455</v>
       </c>
     </row>
     <row r="7" spans="2:3">
@@ -6671,7 +6664,7 @@
         <v>6</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>356</v>
+        <v>456</v>
       </c>
     </row>
     <row r="8" spans="2:3">
@@ -6679,12 +6672,12 @@
         <v>7</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="11" spans="2:2">
-      <c r="B11" s="2" t="s">
-        <v>358</v>
+        <v>457</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="2" t="s">
+        <v>458</v>
       </c>
     </row>
     <row r="12" ht="64" customHeight="1" spans="1:4">
@@ -6692,1312 +6685,1484 @@
         <v>1</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>359</v>
-      </c>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
+        <v>459</v>
+      </c>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
     </row>
     <row r="13" ht="79" customHeight="1" spans="1:4">
       <c r="A13" s="4">
         <v>2</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>360</v>
-      </c>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
+        <v>460</v>
+      </c>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
     </row>
     <row r="14" ht="31" customHeight="1" spans="1:4">
       <c r="A14" s="4">
         <v>3</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>361</v>
-      </c>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
+        <v>461</v>
+      </c>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
     </row>
     <row r="15" ht="32" customHeight="1" spans="1:4">
       <c r="A15" s="4">
         <v>4</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>362</v>
-      </c>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
+        <v>462</v>
+      </c>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
     </row>
     <row r="16" ht="33" customHeight="1" spans="1:4">
       <c r="A16" s="4">
         <v>5</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>363</v>
-      </c>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
+        <v>463</v>
+      </c>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
     </row>
     <row r="17" ht="35" customHeight="1" spans="1:4">
       <c r="A17" s="4">
         <v>6</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>364</v>
-      </c>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
+        <v>464</v>
+      </c>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
     </row>
     <row r="18" ht="15" customHeight="1" spans="1:4">
       <c r="A18" s="4"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
     </row>
     <row r="19" ht="16" customHeight="1" spans="1:4">
       <c r="A19" s="4"/>
-      <c r="B19" s="6" t="s">
-        <v>365</v>
-      </c>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
+      <c r="B19" s="7" t="s">
+        <v>465</v>
+      </c>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
     </row>
     <row r="20" spans="2:2">
       <c r="B20" s="1" t="s">
-        <v>366</v>
+        <v>466</v>
       </c>
     </row>
     <row r="21" spans="2:2">
       <c r="B21" s="1" t="s">
-        <v>237</v>
+        <v>343</v>
       </c>
     </row>
     <row r="22" spans="2:2">
-      <c r="B22" s="1" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="23" ht="31" spans="3:3">
-      <c r="C23" s="7" t="s">
-        <v>368</v>
-      </c>
+      <c r="B22" s="2" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="23" ht="31" spans="2:3">
+      <c r="B23" s="2"/>
+      <c r="C23" s="8" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2">
+      <c r="B24" s="2"/>
     </row>
     <row r="25" spans="2:2">
-      <c r="B25" s="1" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="26" spans="3:3">
-      <c r="C26" s="7" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="27" spans="3:3">
-      <c r="C27" s="7"/>
+      <c r="B25" s="2" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3">
+      <c r="B26" s="2"/>
+      <c r="C26" s="8" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3">
+      <c r="B27" s="2"/>
+      <c r="C27" s="8"/>
     </row>
     <row r="28" spans="2:2">
-      <c r="B28" s="1" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="29" spans="3:3">
-      <c r="C29" s="7" t="s">
-        <v>372</v>
-      </c>
+      <c r="B28" s="2" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3">
+      <c r="B29" s="2"/>
+      <c r="C29" s="8" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2">
+      <c r="B30" s="2"/>
     </row>
     <row r="31" spans="2:2">
-      <c r="B31" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="32" spans="3:3">
-      <c r="C32" s="7" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="33" ht="27" customHeight="1" spans="3:3">
-      <c r="C33" s="7" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="34" ht="27" customHeight="1" spans="3:3">
-      <c r="C34" s="7" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="35" ht="16" customHeight="1" spans="3:3">
-      <c r="C35" s="7"/>
+      <c r="B31" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="32" spans="2:3">
+      <c r="B32" s="2"/>
+      <c r="C32" s="8" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="33" ht="27" customHeight="1" spans="2:3">
+      <c r="B33" s="2"/>
+      <c r="C33" s="8" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="34" ht="27" customHeight="1" spans="2:3">
+      <c r="B34" s="2"/>
+      <c r="C34" s="8" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1" spans="2:3">
+      <c r="B35" s="2"/>
+      <c r="C35" s="8"/>
     </row>
     <row r="36" spans="2:2">
-      <c r="B36" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="37" ht="31" spans="3:3">
-      <c r="C37" s="7" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="38" ht="46.5" spans="3:3">
-      <c r="C38" s="7" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="39" ht="31" spans="3:3">
-      <c r="C39" s="7" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="40" spans="3:3">
-      <c r="C40" s="7"/>
+      <c r="B36" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="37" ht="31" spans="2:3">
+      <c r="B37" s="2"/>
+      <c r="C37" s="8" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="38" ht="46.5" spans="2:3">
+      <c r="B38" s="2"/>
+      <c r="C38" s="8" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="39" ht="31" spans="2:3">
+      <c r="B39" s="2"/>
+      <c r="C39" s="8" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="40" spans="2:3">
+      <c r="B40" s="2"/>
+      <c r="C40" s="8"/>
     </row>
     <row r="41" spans="2:2">
-      <c r="B41" s="1" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="42" spans="3:3">
-      <c r="C42" s="7" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="43" ht="31" spans="3:3">
-      <c r="C43" s="7" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="44" ht="62" spans="3:3">
-      <c r="C44" s="7" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="45" spans="3:3">
-      <c r="C45" s="7"/>
+      <c r="B41" s="2" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="42" spans="2:3">
+      <c r="B42" s="2"/>
+      <c r="C42" s="8" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="43" ht="31" spans="2:3">
+      <c r="B43" s="2"/>
+      <c r="C43" s="8" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="44" ht="62" spans="2:3">
+      <c r="B44" s="2"/>
+      <c r="C44" s="8" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="45" spans="2:3">
+      <c r="B45" s="2"/>
+      <c r="C45" s="8"/>
     </row>
     <row r="46" spans="2:2">
-      <c r="B46" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="47" spans="3:3">
-      <c r="C47" s="7" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="48" ht="31" spans="3:3">
-      <c r="C48" s="7" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="49" ht="46.5" spans="3:3">
-      <c r="C49" s="7" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="50" spans="3:3">
-      <c r="C50" s="7"/>
+      <c r="B46" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="47" spans="2:3">
+      <c r="B47" s="2"/>
+      <c r="C47" s="8" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="48" ht="31" spans="2:3">
+      <c r="B48" s="2"/>
+      <c r="C48" s="8" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="49" ht="46.5" spans="2:3">
+      <c r="B49" s="2"/>
+      <c r="C49" s="8" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="50" spans="2:3">
+      <c r="B50" s="2"/>
+      <c r="C50" s="8"/>
     </row>
     <row r="51" spans="2:2">
-      <c r="B51" s="1" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="52" spans="3:3">
-      <c r="C52" s="7" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="53" ht="31" spans="3:3">
-      <c r="C53" s="7" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="54" spans="3:3">
-      <c r="C54" s="7"/>
+      <c r="B51" s="2" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="52" spans="2:3">
+      <c r="B52" s="2"/>
+      <c r="C52" s="8" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="53" ht="31" spans="2:3">
+      <c r="B53" s="2"/>
+      <c r="C53" s="8" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="54" spans="2:3">
+      <c r="B54" s="2"/>
+      <c r="C54" s="8"/>
     </row>
     <row r="55" spans="2:2">
-      <c r="B55" s="1" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="56" spans="3:3">
-      <c r="C56" s="7" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="57" spans="3:3">
-      <c r="C57" s="7"/>
+      <c r="B55" s="2" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="56" spans="2:3">
+      <c r="B56" s="2"/>
+      <c r="C56" s="8" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="57" spans="2:3">
+      <c r="B57" s="2"/>
+      <c r="C57" s="8"/>
     </row>
     <row r="58" spans="2:2">
-      <c r="B58" s="1" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="59" spans="3:3">
-      <c r="C59" s="7" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="60" ht="31" spans="3:3">
-      <c r="C60" s="8" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="61" spans="3:3">
-      <c r="C61" s="8" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="62" ht="87.5" spans="3:3">
-      <c r="C62" s="9" t="s">
-        <v>395</v>
+      <c r="B58" s="2" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="59" spans="2:3">
+      <c r="B59" s="2"/>
+      <c r="C59" s="8" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="60" ht="31" spans="2:3">
+      <c r="B60" s="2"/>
+      <c r="C60" s="9" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="61" spans="2:3">
+      <c r="B61" s="2"/>
+      <c r="C61" s="9" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="62" ht="87.5" spans="2:3">
+      <c r="B62" s="2"/>
+      <c r="C62" s="10" t="s">
+        <v>495</v>
       </c>
     </row>
     <row r="63" spans="3:3">
       <c r="C63"/>
     </row>
     <row r="64" ht="17.5" spans="3:3">
-      <c r="C64" s="9" t="s">
-        <v>396</v>
+      <c r="C64" s="11" t="s">
+        <v>496</v>
       </c>
     </row>
     <row r="65" ht="70" spans="3:3">
-      <c r="C65" s="10" t="s">
-        <v>397</v>
+      <c r="C65" s="12" t="s">
+        <v>497</v>
       </c>
     </row>
     <row r="66" ht="35" spans="3:3">
-      <c r="C66" s="10" t="s">
-        <v>398</v>
+      <c r="C66" s="12" t="s">
+        <v>498</v>
       </c>
     </row>
     <row r="67" ht="87.5" spans="3:3">
-      <c r="C67" s="10" t="s">
-        <v>399</v>
+      <c r="C67" s="12" t="s">
+        <v>499</v>
       </c>
     </row>
     <row r="68" ht="17.5" spans="3:3">
-      <c r="C68" s="9"/>
+      <c r="C68" s="10"/>
     </row>
     <row r="69" spans="2:2">
-      <c r="B69" s="1" t="s">
-        <v>400</v>
+      <c r="B69" s="2" t="s">
+        <v>500</v>
       </c>
     </row>
     <row r="70" spans="3:3">
-      <c r="C70" s="7" t="s">
-        <v>401</v>
+      <c r="C70" s="8" t="s">
+        <v>501</v>
       </c>
     </row>
     <row r="73" spans="1:1">
-      <c r="A73" s="6" t="s">
-        <v>365</v>
+      <c r="A73" s="7" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="1">
         <v>1</v>
       </c>
-      <c r="B74" s="1" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="75" ht="46.5" spans="3:3">
-      <c r="C75" s="11" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="76" spans="3:3">
-      <c r="C76" s="12" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="77" ht="46.5" spans="3:3">
-      <c r="C77" s="11" t="s">
-        <v>405</v>
+      <c r="B74" s="2" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="75" ht="46.5" spans="2:3">
+      <c r="B75" s="2"/>
+      <c r="C75" s="13" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="76" spans="2:3">
+      <c r="B76" s="2"/>
+      <c r="C76" s="14" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="77" ht="46.5" spans="2:3">
+      <c r="B77" s="2"/>
+      <c r="C77" s="13" t="s">
+        <v>505</v>
       </c>
     </row>
     <row r="78" spans="2:3">
-      <c r="B78" s="13"/>
-      <c r="C78" s="8"/>
+      <c r="B78" s="15"/>
+      <c r="C78" s="9"/>
     </row>
     <row r="79" spans="2:3">
-      <c r="B79" s="13"/>
-      <c r="C79" s="8" t="s">
-        <v>406</v>
+      <c r="B79" s="15"/>
+      <c r="C79" s="9" t="s">
+        <v>506</v>
       </c>
     </row>
     <row r="80" spans="2:3">
-      <c r="B80" s="13"/>
-      <c r="C80" s="8"/>
+      <c r="B80" s="15"/>
+      <c r="C80" s="9"/>
     </row>
     <row r="81" hidden="1" spans="2:3">
-      <c r="B81" s="13"/>
-      <c r="C81" s="8" t="s">
-        <v>407</v>
+      <c r="B81" s="15"/>
+      <c r="C81" s="9" t="s">
+        <v>507</v>
       </c>
     </row>
     <row r="82" hidden="1" spans="2:3">
-      <c r="B82" s="13"/>
-      <c r="C82" s="8" t="s">
-        <v>408</v>
+      <c r="B82" s="15"/>
+      <c r="C82" s="9" t="s">
+        <v>508</v>
       </c>
     </row>
     <row r="83" hidden="1" spans="2:3">
-      <c r="B83" s="13"/>
-      <c r="C83" s="8" t="s">
-        <v>409</v>
+      <c r="B83" s="15"/>
+      <c r="C83" s="9" t="s">
+        <v>509</v>
       </c>
     </row>
     <row r="84" hidden="1" spans="2:3">
-      <c r="B84" s="13"/>
-      <c r="C84" s="8" t="s">
-        <v>410</v>
+      <c r="B84" s="15"/>
+      <c r="C84" s="9" t="s">
+        <v>510</v>
       </c>
     </row>
     <row r="85" hidden="1" spans="2:3">
-      <c r="B85" s="13"/>
-      <c r="C85" s="8" t="s">
-        <v>411</v>
+      <c r="B85" s="15"/>
+      <c r="C85" s="9" t="s">
+        <v>511</v>
       </c>
     </row>
     <row r="86" ht="31" hidden="1" spans="2:3">
-      <c r="B86" s="13"/>
-      <c r="C86" s="8" t="s">
-        <v>412</v>
+      <c r="B86" s="15"/>
+      <c r="C86" s="9" t="s">
+        <v>512</v>
       </c>
     </row>
     <row r="87" hidden="1" spans="2:3">
-      <c r="B87" s="13"/>
-      <c r="C87" s="8" t="s">
-        <v>413</v>
+      <c r="B87" s="15"/>
+      <c r="C87" s="9" t="s">
+        <v>513</v>
       </c>
     </row>
     <row r="88" hidden="1" spans="2:3">
-      <c r="B88" s="13"/>
-      <c r="C88" s="8" t="s">
-        <v>414</v>
+      <c r="B88" s="15"/>
+      <c r="C88" s="9" t="s">
+        <v>514</v>
       </c>
     </row>
     <row r="89" hidden="1" spans="2:3">
-      <c r="B89" s="13"/>
-      <c r="C89" s="8" t="s">
-        <v>415</v>
+      <c r="B89" s="15"/>
+      <c r="C89" s="9" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="90" hidden="1" spans="2:3">
-      <c r="B90" s="13"/>
-      <c r="C90" s="8"/>
+      <c r="B90" s="15"/>
+      <c r="C90" s="9"/>
     </row>
     <row r="91" hidden="1" spans="2:3">
-      <c r="B91" s="13"/>
-      <c r="C91" s="8" t="s">
-        <v>416</v>
+      <c r="B91" s="15"/>
+      <c r="C91" s="9" t="s">
+        <v>516</v>
       </c>
     </row>
     <row r="92" hidden="1" spans="2:3">
-      <c r="B92" s="13"/>
-      <c r="C92" s="8" t="s">
-        <v>417</v>
+      <c r="B92" s="15"/>
+      <c r="C92" s="9" t="s">
+        <v>517</v>
       </c>
     </row>
     <row r="93" hidden="1" spans="2:3">
-      <c r="B93" s="13"/>
-      <c r="C93" s="8"/>
+      <c r="B93" s="15"/>
+      <c r="C93" s="9"/>
     </row>
     <row r="94" hidden="1" spans="2:3">
-      <c r="B94" s="13"/>
-      <c r="C94" s="8" t="s">
-        <v>418</v>
+      <c r="B94" s="15"/>
+      <c r="C94" s="9" t="s">
+        <v>518</v>
       </c>
     </row>
     <row r="95" hidden="1" spans="2:3">
-      <c r="B95" s="13"/>
-      <c r="C95" s="8" t="s">
-        <v>419</v>
+      <c r="B95" s="15"/>
+      <c r="C95" s="9" t="s">
+        <v>519</v>
       </c>
     </row>
     <row r="96" hidden="1" spans="2:3">
-      <c r="B96" s="13"/>
-      <c r="C96" s="8"/>
+      <c r="B96" s="15"/>
+      <c r="C96" s="9"/>
     </row>
     <row r="97" hidden="1" spans="2:3">
-      <c r="B97" s="13"/>
-      <c r="C97" s="8" t="s">
-        <v>420</v>
+      <c r="B97" s="15"/>
+      <c r="C97" s="9" t="s">
+        <v>520</v>
       </c>
     </row>
     <row r="98" ht="46.5" hidden="1" spans="2:3">
-      <c r="B98" s="13"/>
-      <c r="C98" s="8" t="s">
-        <v>421</v>
+      <c r="B98" s="15"/>
+      <c r="C98" s="9" t="s">
+        <v>521</v>
       </c>
     </row>
     <row r="99" spans="2:3">
-      <c r="B99" s="13"/>
-      <c r="C99" s="8"/>
+      <c r="B99" s="15"/>
+      <c r="C99" s="9"/>
     </row>
     <row r="100" spans="1:2">
-      <c r="A100" s="13">
+      <c r="A100" s="16">
         <v>2</v>
       </c>
-      <c r="B100" s="3" t="s">
-        <v>422</v>
+      <c r="B100" s="17" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="101" ht="31" spans="2:3">
-      <c r="B101" s="13"/>
-      <c r="C101" s="11" t="s">
-        <v>423</v>
+      <c r="B101" s="15"/>
+      <c r="C101" s="13" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="102" spans="2:2">
-      <c r="B102" s="13"/>
+      <c r="B102" s="15"/>
     </row>
     <row r="103" spans="2:3">
-      <c r="B103" s="13"/>
-      <c r="C103" s="12" t="s">
-        <v>404</v>
+      <c r="B103" s="15"/>
+      <c r="C103" s="14" t="s">
+        <v>504</v>
       </c>
     </row>
     <row r="104" ht="31" spans="2:3">
-      <c r="B104" s="13"/>
-      <c r="C104" s="11" t="s">
-        <v>424</v>
+      <c r="B104" s="15"/>
+      <c r="C104" s="13" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="105" spans="2:3">
-      <c r="B105" s="13"/>
-      <c r="C105" s="8"/>
+      <c r="B105" s="15"/>
+      <c r="C105" s="9"/>
     </row>
     <row r="106" spans="2:3">
-      <c r="B106" s="13"/>
-      <c r="C106" s="8" t="s">
-        <v>406</v>
+      <c r="B106" s="15"/>
+      <c r="C106" s="9" t="s">
+        <v>506</v>
       </c>
     </row>
     <row r="107" spans="2:3">
-      <c r="B107" s="13"/>
-      <c r="C107" s="8" t="s">
-        <v>425</v>
+      <c r="B107" s="15"/>
+      <c r="C107" s="9" t="s">
+        <v>525</v>
       </c>
     </row>
     <row r="108" spans="2:3">
-      <c r="B108" s="13"/>
-      <c r="C108" s="8"/>
+      <c r="B108" s="15"/>
+      <c r="C108" s="9"/>
     </row>
     <row r="109" spans="2:3">
-      <c r="B109" s="13"/>
-      <c r="C109" s="8" t="s">
-        <v>426</v>
+      <c r="B109" s="15"/>
+      <c r="C109" s="9" t="s">
+        <v>526</v>
       </c>
     </row>
     <row r="110" hidden="1" spans="2:3">
-      <c r="B110" s="13"/>
-      <c r="C110" s="8" t="s">
-        <v>407</v>
+      <c r="B110" s="15"/>
+      <c r="C110" s="9" t="s">
+        <v>507</v>
       </c>
     </row>
     <row r="111" hidden="1" spans="2:3">
-      <c r="B111" s="13"/>
-      <c r="C111" s="8" t="s">
-        <v>427</v>
+      <c r="B111" s="15"/>
+      <c r="C111" s="9" t="s">
+        <v>527</v>
       </c>
     </row>
     <row r="112" hidden="1" spans="2:3">
-      <c r="B112" s="13"/>
-      <c r="C112" s="8" t="s">
-        <v>428</v>
+      <c r="B112" s="15"/>
+      <c r="C112" s="9" t="s">
+        <v>528</v>
       </c>
     </row>
     <row r="113" hidden="1" spans="2:3">
-      <c r="B113" s="13"/>
-      <c r="C113" s="8"/>
+      <c r="B113" s="15"/>
+      <c r="C113" s="9"/>
     </row>
     <row r="114" hidden="1" spans="2:3">
-      <c r="B114" s="13"/>
-      <c r="C114" s="8" t="s">
-        <v>429</v>
+      <c r="B114" s="15"/>
+      <c r="C114" s="9" t="s">
+        <v>529</v>
       </c>
     </row>
     <row r="115" hidden="1" spans="2:3">
-      <c r="B115" s="13"/>
-      <c r="C115" s="8" t="s">
-        <v>430</v>
+      <c r="B115" s="15"/>
+      <c r="C115" s="9" t="s">
+        <v>530</v>
       </c>
     </row>
     <row r="116" hidden="1" spans="2:3">
-      <c r="B116" s="13"/>
-      <c r="C116" s="8"/>
+      <c r="B116" s="15"/>
+      <c r="C116" s="9"/>
     </row>
     <row r="117" hidden="1" spans="2:3">
-      <c r="B117" s="13"/>
-      <c r="C117" s="8" t="s">
-        <v>431</v>
+      <c r="B117" s="15"/>
+      <c r="C117" s="9" t="s">
+        <v>531</v>
       </c>
     </row>
     <row r="118" hidden="1" spans="2:3">
-      <c r="B118" s="13"/>
-      <c r="C118" s="8" t="s">
-        <v>432</v>
+      <c r="B118" s="15"/>
+      <c r="C118" s="9" t="s">
+        <v>532</v>
       </c>
     </row>
     <row r="119" hidden="1" spans="2:3">
-      <c r="B119" s="13"/>
-      <c r="C119" s="8"/>
+      <c r="B119" s="15"/>
+      <c r="C119" s="9"/>
     </row>
     <row r="120" hidden="1" spans="2:3">
-      <c r="B120" s="13"/>
-      <c r="C120" s="8" t="s">
-        <v>433</v>
+      <c r="B120" s="15"/>
+      <c r="C120" s="9" t="s">
+        <v>533</v>
       </c>
     </row>
     <row r="121" hidden="1" spans="2:3">
-      <c r="B121" s="13"/>
-      <c r="C121" s="8" t="s">
-        <v>434</v>
+      <c r="B121" s="15"/>
+      <c r="C121" s="9" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="122" hidden="1" spans="2:3">
-      <c r="B122" s="13"/>
-      <c r="C122" s="8"/>
+      <c r="B122" s="15"/>
+      <c r="C122" s="9"/>
     </row>
     <row r="123" hidden="1" spans="2:3">
-      <c r="B123" s="13"/>
-      <c r="C123" s="8" t="s">
-        <v>435</v>
+      <c r="B123" s="15"/>
+      <c r="C123" s="9" t="s">
+        <v>535</v>
       </c>
     </row>
     <row r="124" hidden="1" spans="2:3">
-      <c r="B124" s="13"/>
-      <c r="C124" s="8" t="s">
-        <v>436</v>
+      <c r="B124" s="15"/>
+      <c r="C124" s="9" t="s">
+        <v>536</v>
       </c>
     </row>
     <row r="125" hidden="1" spans="2:3">
-      <c r="B125" s="13"/>
-      <c r="C125" s="8"/>
+      <c r="B125" s="15"/>
+      <c r="C125" s="9"/>
     </row>
     <row r="126" hidden="1" spans="2:3">
-      <c r="B126" s="13"/>
-      <c r="C126" s="8" t="s">
-        <v>437</v>
+      <c r="B126" s="15"/>
+      <c r="C126" s="9" t="s">
+        <v>537</v>
       </c>
     </row>
     <row r="127" hidden="1" spans="2:3">
-      <c r="B127" s="13"/>
-      <c r="C127" s="8" t="s">
-        <v>438</v>
+      <c r="B127" s="15"/>
+      <c r="C127" s="9" t="s">
+        <v>538</v>
       </c>
     </row>
     <row r="128" hidden="1" spans="2:3">
-      <c r="B128" s="13"/>
-      <c r="C128" s="8"/>
+      <c r="B128" s="15"/>
+      <c r="C128" s="9"/>
     </row>
     <row r="129" hidden="1" spans="2:3">
-      <c r="B129" s="13"/>
-      <c r="C129" s="8" t="s">
-        <v>439</v>
+      <c r="B129" s="15"/>
+      <c r="C129" s="9" t="s">
+        <v>539</v>
       </c>
     </row>
     <row r="130" hidden="1" spans="2:3">
-      <c r="B130" s="13"/>
-      <c r="C130" s="8" t="s">
-        <v>440</v>
+      <c r="B130" s="15"/>
+      <c r="C130" s="9" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="131" hidden="1" spans="2:3">
-      <c r="B131" s="13"/>
-      <c r="C131" s="8"/>
+      <c r="B131" s="15"/>
+      <c r="C131" s="9"/>
     </row>
     <row r="132" hidden="1" spans="2:3">
-      <c r="B132" s="13"/>
-      <c r="C132" s="8" t="s">
-        <v>441</v>
+      <c r="B132" s="15"/>
+      <c r="C132" s="9" t="s">
+        <v>541</v>
       </c>
     </row>
     <row r="133" hidden="1" spans="2:3">
-      <c r="B133" s="13"/>
-      <c r="C133" s="8" t="s">
-        <v>442</v>
+      <c r="B133" s="15"/>
+      <c r="C133" s="9" t="s">
+        <v>542</v>
       </c>
     </row>
     <row r="134" hidden="1" spans="2:3">
-      <c r="B134" s="13"/>
-      <c r="C134" s="8"/>
+      <c r="B134" s="15"/>
+      <c r="C134" s="9"/>
     </row>
     <row r="135" hidden="1" spans="2:3">
-      <c r="B135" s="13"/>
-      <c r="C135" s="8" t="s">
-        <v>443</v>
+      <c r="B135" s="15"/>
+      <c r="C135" s="9" t="s">
+        <v>543</v>
       </c>
     </row>
     <row r="136" hidden="1" spans="2:3">
-      <c r="B136" s="13"/>
-      <c r="C136" s="8" t="s">
-        <v>444</v>
+      <c r="B136" s="15"/>
+      <c r="C136" s="9" t="s">
+        <v>544</v>
       </c>
     </row>
     <row r="137" spans="2:3">
-      <c r="B137" s="13"/>
-      <c r="C137" s="8"/>
+      <c r="B137" s="15"/>
+      <c r="C137" s="9"/>
     </row>
     <row r="138" spans="1:2">
-      <c r="A138" s="14">
+      <c r="A138" s="18">
         <v>3</v>
       </c>
-      <c r="B138" s="3" t="s">
-        <v>445</v>
+      <c r="B138" s="17" t="s">
+        <v>545</v>
       </c>
     </row>
     <row r="139" spans="2:3">
-      <c r="B139" s="13"/>
-      <c r="C139" s="11" t="s">
-        <v>446</v>
+      <c r="B139" s="15"/>
+      <c r="C139" s="13" t="s">
+        <v>546</v>
       </c>
     </row>
     <row r="140" spans="2:3">
-      <c r="B140" s="13"/>
-      <c r="C140" s="12" t="s">
-        <v>404</v>
+      <c r="B140" s="15"/>
+      <c r="C140" s="14" t="s">
+        <v>504</v>
       </c>
     </row>
     <row r="141" ht="31" spans="2:3">
-      <c r="B141" s="13"/>
-      <c r="C141" s="11" t="s">
-        <v>447</v>
+      <c r="B141" s="15"/>
+      <c r="C141" s="13" t="s">
+        <v>547</v>
       </c>
     </row>
     <row r="142" spans="2:3">
-      <c r="B142" s="13"/>
-      <c r="C142" s="8"/>
+      <c r="B142" s="15"/>
+      <c r="C142" s="9"/>
     </row>
     <row r="143" spans="2:3">
-      <c r="B143" s="13"/>
-      <c r="C143" s="8" t="s">
-        <v>448</v>
+      <c r="B143" s="15"/>
+      <c r="C143" s="9" t="s">
+        <v>548</v>
       </c>
     </row>
     <row r="144" spans="2:3">
-      <c r="B144" s="13"/>
-      <c r="C144" s="8" t="s">
-        <v>449</v>
+      <c r="B144" s="15"/>
+      <c r="C144" s="9" t="s">
+        <v>549</v>
       </c>
     </row>
     <row r="145" spans="2:3">
-      <c r="B145" s="13"/>
-      <c r="C145" s="8"/>
+      <c r="B145" s="15"/>
+      <c r="C145" s="9"/>
     </row>
     <row r="146" spans="2:3">
-      <c r="B146" s="13"/>
-      <c r="C146" s="8" t="s">
-        <v>450</v>
+      <c r="B146" s="15"/>
+      <c r="C146" s="9" t="s">
+        <v>550</v>
       </c>
     </row>
     <row r="147" hidden="1" spans="2:3">
-      <c r="B147" s="13"/>
-      <c r="C147" s="8" t="s">
-        <v>451</v>
+      <c r="B147" s="15"/>
+      <c r="C147" s="9" t="s">
+        <v>551</v>
       </c>
     </row>
     <row r="148" hidden="1" spans="2:3">
-      <c r="B148" s="13"/>
-      <c r="C148" s="8"/>
+      <c r="B148" s="15"/>
+      <c r="C148" s="9"/>
     </row>
     <row r="149" hidden="1" spans="2:3">
-      <c r="B149" s="13"/>
-      <c r="C149" s="8" t="s">
-        <v>452</v>
+      <c r="B149" s="15"/>
+      <c r="C149" s="9" t="s">
+        <v>552</v>
       </c>
     </row>
     <row r="150" hidden="1" spans="2:3">
-      <c r="B150" s="13"/>
-      <c r="C150" s="8" t="s">
-        <v>453</v>
+      <c r="B150" s="15"/>
+      <c r="C150" s="9" t="s">
+        <v>553</v>
       </c>
     </row>
     <row r="151" hidden="1" spans="2:3">
-      <c r="B151" s="13"/>
-      <c r="C151" s="8" t="s">
-        <v>454</v>
+      <c r="B151" s="15"/>
+      <c r="C151" s="9" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="152" hidden="1" spans="2:3">
-      <c r="B152" s="13"/>
-      <c r="C152" s="8"/>
+      <c r="B152" s="15"/>
+      <c r="C152" s="9"/>
     </row>
     <row r="153" hidden="1" spans="2:3">
-      <c r="B153" s="13"/>
-      <c r="C153" s="8" t="s">
+      <c r="B153" s="15"/>
+      <c r="C153" s="9" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="154" hidden="1" spans="2:3">
+      <c r="B154" s="15"/>
+      <c r="C154" s="9" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="155" hidden="1" spans="2:3">
+      <c r="B155" s="15"/>
+      <c r="C155" s="9" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="156" hidden="1" spans="2:3">
+      <c r="B156" s="15"/>
+      <c r="C156" s="9"/>
+    </row>
+    <row r="157" hidden="1" spans="2:3">
+      <c r="B157" s="15"/>
+      <c r="C157" s="9" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="158" hidden="1" spans="2:3">
+      <c r="B158" s="15"/>
+      <c r="C158" s="9" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="159" hidden="1" spans="2:3">
+      <c r="B159" s="15"/>
+      <c r="C159" s="9" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="160" spans="2:3">
+      <c r="B160" s="2"/>
+      <c r="C160" s="9"/>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161" s="16">
+        <v>4</v>
+      </c>
+      <c r="B161" s="17" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="162" spans="2:3">
+      <c r="B162" s="15"/>
+      <c r="C162" s="13" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="163" spans="2:2">
+      <c r="B163" s="15"/>
+    </row>
+    <row r="164" spans="2:3">
+      <c r="B164" s="15"/>
+      <c r="C164" s="14" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="165" ht="31" spans="2:3">
+      <c r="B165" s="15"/>
+      <c r="C165" s="13" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="166" spans="2:3">
+      <c r="B166" s="15"/>
+      <c r="C166" s="9"/>
+    </row>
+    <row r="167" spans="2:3">
+      <c r="B167" s="15"/>
+      <c r="C167" s="9" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="168" hidden="1" spans="2:3">
+      <c r="B168" s="15"/>
+      <c r="C168" s="9" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="169" hidden="1" spans="2:3">
+      <c r="B169" s="15"/>
+      <c r="C169" s="9"/>
+    </row>
+    <row r="170" hidden="1" spans="2:3">
+      <c r="B170" s="15"/>
+      <c r="C170" s="9" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="171" hidden="1" spans="2:3">
+      <c r="B171" s="15"/>
+      <c r="C171" s="9" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="172" hidden="1" spans="2:3">
+      <c r="B172" s="15"/>
+      <c r="C172" s="9"/>
+    </row>
+    <row r="173" hidden="1" spans="2:3">
+      <c r="B173" s="15"/>
+      <c r="C173" s="9" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="174" hidden="1" spans="2:3">
+      <c r="B174" s="15"/>
+      <c r="C174" s="9" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="175" hidden="1" spans="2:3">
+      <c r="B175" s="15"/>
+      <c r="C175" s="9"/>
+    </row>
+    <row r="176" hidden="1" spans="2:3">
+      <c r="B176" s="15"/>
+      <c r="C176" s="9" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="177" hidden="1" spans="2:3">
+      <c r="B177" s="15"/>
+      <c r="C177" s="9" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="178" spans="2:3">
+      <c r="B178" s="15"/>
+      <c r="C178" s="9"/>
+    </row>
+    <row r="179" spans="1:2">
+      <c r="A179" s="16">
+        <v>5</v>
+      </c>
+      <c r="B179" s="17" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="154" hidden="1" spans="2:3">
-      <c r="B154" s="13"/>
-      <c r="C154" s="8" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="155" hidden="1" spans="2:3">
-      <c r="B155" s="13"/>
-      <c r="C155" s="8" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="156" hidden="1" spans="2:3">
-      <c r="B156" s="13"/>
-      <c r="C156" s="8"/>
-    </row>
-    <row r="157" hidden="1" spans="2:3">
-      <c r="B157" s="13"/>
-      <c r="C157" s="8" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="158" hidden="1" spans="2:3">
-      <c r="B158" s="13"/>
-      <c r="C158" s="8" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="159" hidden="1" spans="2:3">
-      <c r="B159" s="13"/>
-      <c r="C159" s="8" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="160" spans="3:3">
-      <c r="C160" s="8"/>
-    </row>
-    <row r="161" spans="1:2">
-      <c r="A161" s="13">
-        <v>4</v>
-      </c>
-      <c r="B161" s="3" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="162" spans="2:3">
-      <c r="B162" s="13"/>
-      <c r="C162" s="11" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="163" spans="2:2">
-      <c r="B163" s="13"/>
-    </row>
-    <row r="164" spans="2:3">
-      <c r="B164" s="13"/>
-      <c r="C164" s="12" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="165" ht="31" spans="2:3">
-      <c r="B165" s="13"/>
-      <c r="C165" s="11" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="166" spans="2:3">
-      <c r="B166" s="13"/>
-      <c r="C166" s="8"/>
-    </row>
-    <row r="167" spans="2:3">
-      <c r="B167" s="13"/>
-      <c r="C167" s="8" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="168" hidden="1" spans="2:3">
-      <c r="B168" s="13"/>
-      <c r="C168" s="8" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="169" hidden="1" spans="2:3">
-      <c r="B169" s="13"/>
-      <c r="C169" s="8"/>
-    </row>
-    <row r="170" hidden="1" spans="2:3">
-      <c r="B170" s="13"/>
-      <c r="C170" s="8" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="171" hidden="1" spans="2:3">
-      <c r="B171" s="13"/>
-      <c r="C171" s="8" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="172" hidden="1" spans="2:3">
-      <c r="B172" s="13"/>
-      <c r="C172" s="8"/>
-    </row>
-    <row r="173" hidden="1" spans="2:3">
-      <c r="B173" s="13"/>
-      <c r="C173" s="8" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="174" hidden="1" spans="2:3">
-      <c r="B174" s="13"/>
-      <c r="C174" s="8" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="175" hidden="1" spans="2:3">
-      <c r="B175" s="13"/>
-      <c r="C175" s="8"/>
-    </row>
-    <row r="176" hidden="1" spans="2:3">
-      <c r="B176" s="13"/>
-      <c r="C176" s="8" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="177" hidden="1" spans="2:3">
-      <c r="B177" s="13"/>
-      <c r="C177" s="8" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="178" spans="2:3">
-      <c r="B178" s="13"/>
-      <c r="C178" s="8"/>
-    </row>
-    <row r="179" spans="1:2">
-      <c r="A179" s="13">
-        <v>5</v>
-      </c>
-      <c r="B179" s="3" t="s">
-        <v>355</v>
-      </c>
-    </row>
     <row r="180" spans="2:3">
-      <c r="B180" s="13"/>
-      <c r="C180" s="11" t="s">
-        <v>472</v>
+      <c r="B180" s="15"/>
+      <c r="C180" s="13" t="s">
+        <v>572</v>
       </c>
     </row>
     <row r="181" spans="2:2">
-      <c r="B181" s="13"/>
+      <c r="B181" s="15"/>
     </row>
     <row r="182" spans="2:3">
-      <c r="B182" s="13"/>
-      <c r="C182" s="12" t="s">
-        <v>404</v>
+      <c r="B182" s="15"/>
+      <c r="C182" s="14" t="s">
+        <v>504</v>
       </c>
     </row>
     <row r="183" spans="2:3">
-      <c r="B183" s="13"/>
-      <c r="C183" s="11" t="s">
-        <v>473</v>
+      <c r="B183" s="15"/>
+      <c r="C183" s="13" t="s">
+        <v>573</v>
       </c>
     </row>
     <row r="184" spans="2:3">
-      <c r="B184" s="13"/>
-      <c r="C184" s="8"/>
+      <c r="B184" s="15"/>
+      <c r="C184" s="9"/>
     </row>
     <row r="185" spans="2:3">
-      <c r="B185" s="13"/>
-      <c r="C185" s="8" t="s">
-        <v>474</v>
+      <c r="B185" s="15"/>
+      <c r="C185" s="9" t="s">
+        <v>574</v>
       </c>
     </row>
     <row r="186" hidden="1" spans="2:3">
-      <c r="B186" s="13"/>
-      <c r="C186" s="8" t="s">
-        <v>475</v>
+      <c r="B186" s="15"/>
+      <c r="C186" s="9" t="s">
+        <v>575</v>
       </c>
     </row>
     <row r="187" hidden="1" spans="2:3">
-      <c r="B187" s="13"/>
-      <c r="C187" s="8" t="s">
-        <v>476</v>
+      <c r="B187" s="15"/>
+      <c r="C187" s="9" t="s">
+        <v>576</v>
       </c>
     </row>
     <row r="188" hidden="1" spans="2:3">
-      <c r="B188" s="13"/>
-      <c r="C188" s="8" t="s">
-        <v>477</v>
+      <c r="B188" s="15"/>
+      <c r="C188" s="9" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="189" hidden="1" spans="2:3">
-      <c r="B189" s="13"/>
-      <c r="C189" s="8"/>
+      <c r="B189" s="15"/>
+      <c r="C189" s="9"/>
     </row>
     <row r="190" hidden="1" spans="2:3">
-      <c r="B190" s="13"/>
-      <c r="C190" s="8" t="s">
-        <v>478</v>
+      <c r="B190" s="15"/>
+      <c r="C190" s="9" t="s">
+        <v>578</v>
       </c>
     </row>
     <row r="191" hidden="1" spans="2:3">
-      <c r="B191" s="13"/>
-      <c r="C191" s="8"/>
+      <c r="B191" s="15"/>
+      <c r="C191" s="9"/>
     </row>
     <row r="192" hidden="1" spans="2:3">
-      <c r="B192" s="13"/>
-      <c r="C192" s="8" t="s">
-        <v>479</v>
+      <c r="B192" s="15"/>
+      <c r="C192" s="9" t="s">
+        <v>579</v>
       </c>
     </row>
     <row r="193" hidden="1" spans="2:3">
-      <c r="B193" s="13"/>
-      <c r="C193" s="8"/>
+      <c r="B193" s="15"/>
+      <c r="C193" s="9"/>
     </row>
     <row r="194" hidden="1" spans="2:3">
-      <c r="B194" s="13"/>
-      <c r="C194" s="8" t="s">
-        <v>480</v>
+      <c r="B194" s="15"/>
+      <c r="C194" s="9" t="s">
+        <v>580</v>
       </c>
     </row>
     <row r="195" spans="2:3">
-      <c r="B195" s="13"/>
-      <c r="C195" s="8"/>
+      <c r="B195" s="15"/>
+      <c r="C195" s="9"/>
     </row>
     <row r="196" spans="1:2">
-      <c r="A196" s="13">
+      <c r="A196" s="16">
         <v>6</v>
       </c>
-      <c r="B196" s="3" t="s">
-        <v>481</v>
+      <c r="B196" s="17" t="s">
+        <v>581</v>
       </c>
     </row>
     <row r="197" spans="2:3">
-      <c r="B197" s="13"/>
-      <c r="C197" s="11" t="s">
-        <v>482</v>
+      <c r="B197" s="15"/>
+      <c r="C197" s="13" t="s">
+        <v>582</v>
       </c>
     </row>
     <row r="198" spans="2:2">
-      <c r="B198" s="13"/>
+      <c r="B198" s="15"/>
     </row>
     <row r="199" spans="2:3">
-      <c r="B199" s="13"/>
-      <c r="C199" s="12" t="s">
-        <v>404</v>
+      <c r="B199" s="15"/>
+      <c r="C199" s="14" t="s">
+        <v>504</v>
       </c>
     </row>
     <row r="200" ht="31" spans="2:3">
-      <c r="B200" s="13"/>
-      <c r="C200" s="11" t="s">
-        <v>483</v>
+      <c r="B200" s="15"/>
+      <c r="C200" s="13" t="s">
+        <v>583</v>
       </c>
     </row>
     <row r="201" spans="2:3">
-      <c r="B201" s="13"/>
-      <c r="C201" s="8"/>
+      <c r="B201" s="15"/>
+      <c r="C201" s="9"/>
     </row>
     <row r="202" spans="2:3">
-      <c r="B202" s="13"/>
-      <c r="C202" s="8" t="s">
-        <v>484</v>
+      <c r="B202" s="15"/>
+      <c r="C202" s="9" t="s">
+        <v>584</v>
       </c>
     </row>
     <row r="203" hidden="1" spans="2:3">
-      <c r="B203" s="13"/>
-      <c r="C203" s="8" t="s">
-        <v>485</v>
+      <c r="B203" s="15"/>
+      <c r="C203" s="9" t="s">
+        <v>585</v>
       </c>
     </row>
     <row r="204" hidden="1" spans="2:3">
-      <c r="B204" s="13"/>
-      <c r="C204" s="8"/>
+      <c r="B204" s="15"/>
+      <c r="C204" s="9"/>
     </row>
     <row r="205" hidden="1" spans="2:3">
-      <c r="B205" s="13"/>
-      <c r="C205" s="8" t="s">
-        <v>486</v>
+      <c r="B205" s="15"/>
+      <c r="C205" s="9" t="s">
+        <v>586</v>
       </c>
     </row>
     <row r="206" hidden="1" spans="2:3">
-      <c r="B206" s="13"/>
-      <c r="C206" s="8" t="s">
-        <v>487</v>
+      <c r="B206" s="15"/>
+      <c r="C206" s="9" t="s">
+        <v>587</v>
       </c>
     </row>
     <row r="207" hidden="1" spans="2:3">
-      <c r="B207" s="13"/>
-      <c r="C207" s="8"/>
+      <c r="B207" s="15"/>
+      <c r="C207" s="9"/>
     </row>
     <row r="208" hidden="1" spans="2:3">
-      <c r="B208" s="13"/>
-      <c r="C208" s="8" t="s">
-        <v>488</v>
+      <c r="B208" s="15"/>
+      <c r="C208" s="9" t="s">
+        <v>588</v>
       </c>
     </row>
     <row r="209" ht="31" hidden="1" spans="2:3">
-      <c r="B209" s="13"/>
-      <c r="C209" s="8" t="s">
-        <v>489</v>
+      <c r="B209" s="15"/>
+      <c r="C209" s="9" t="s">
+        <v>589</v>
       </c>
     </row>
     <row r="210" spans="2:3">
-      <c r="B210" s="13"/>
-      <c r="C210" s="8"/>
+      <c r="B210" s="15"/>
+      <c r="C210" s="9"/>
     </row>
     <row r="211" spans="1:2">
-      <c r="A211" s="13">
+      <c r="A211" s="16">
         <v>7</v>
       </c>
-      <c r="B211" s="3" t="s">
-        <v>490</v>
+      <c r="B211" s="17" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="212" ht="31" spans="2:3">
-      <c r="B212" s="13"/>
-      <c r="C212" s="11" t="s">
-        <v>491</v>
+      <c r="B212" s="15"/>
+      <c r="C212" s="13" t="s">
+        <v>591</v>
       </c>
     </row>
     <row r="213" spans="2:2">
-      <c r="B213" s="13"/>
+      <c r="B213" s="15"/>
     </row>
     <row r="214" spans="2:3">
-      <c r="B214" s="13"/>
-      <c r="C214" s="12" t="s">
-        <v>404</v>
+      <c r="B214" s="15"/>
+      <c r="C214" s="14" t="s">
+        <v>504</v>
       </c>
     </row>
     <row r="215" ht="31" spans="2:3">
-      <c r="B215" s="13"/>
-      <c r="C215" s="11" t="s">
-        <v>492</v>
+      <c r="B215" s="15"/>
+      <c r="C215" s="13" t="s">
+        <v>592</v>
       </c>
     </row>
     <row r="216" spans="2:3">
-      <c r="B216" s="13"/>
-      <c r="C216" s="8"/>
+      <c r="B216" s="15"/>
+      <c r="C216" s="9"/>
     </row>
     <row r="217" spans="2:3">
-      <c r="B217" s="13"/>
-      <c r="C217" s="8" t="s">
-        <v>493</v>
+      <c r="B217" s="15"/>
+      <c r="C217" s="9" t="s">
+        <v>593</v>
       </c>
     </row>
     <row r="218" spans="2:3">
-      <c r="B218" s="13"/>
-      <c r="C218" s="8"/>
+      <c r="B218" s="15"/>
+      <c r="C218" s="9"/>
     </row>
     <row r="219" hidden="1" spans="2:3">
-      <c r="B219" s="13"/>
-      <c r="C219" s="8" t="s">
-        <v>494</v>
+      <c r="B219" s="15"/>
+      <c r="C219" s="9" t="s">
+        <v>594</v>
       </c>
     </row>
     <row r="220" hidden="1" spans="2:3">
-      <c r="B220" s="13"/>
-      <c r="C220" s="8" t="s">
-        <v>495</v>
+      <c r="B220" s="15"/>
+      <c r="C220" s="9" t="s">
+        <v>595</v>
       </c>
     </row>
     <row r="221" hidden="1" spans="2:3">
-      <c r="B221" s="13"/>
-      <c r="C221" s="8"/>
+      <c r="B221" s="15"/>
+      <c r="C221" s="9"/>
     </row>
     <row r="222" hidden="1" spans="2:3">
-      <c r="B222" s="13"/>
-      <c r="C222" s="8" t="s">
-        <v>496</v>
+      <c r="B222" s="15"/>
+      <c r="C222" s="9" t="s">
+        <v>596</v>
       </c>
     </row>
     <row r="223" hidden="1" spans="2:3">
-      <c r="B223" s="13"/>
-      <c r="C223" s="8" t="s">
-        <v>497</v>
+      <c r="B223" s="15"/>
+      <c r="C223" s="9" t="s">
+        <v>597</v>
       </c>
     </row>
     <row r="224" hidden="1" spans="2:3">
-      <c r="B224" s="13"/>
-      <c r="C224" s="8" t="s">
-        <v>498</v>
+      <c r="B224" s="15"/>
+      <c r="C224" s="9" t="s">
+        <v>598</v>
       </c>
     </row>
     <row r="225" hidden="1" spans="2:3">
-      <c r="B225" s="13"/>
-      <c r="C225" s="8"/>
+      <c r="B225" s="15"/>
+      <c r="C225" s="9"/>
     </row>
     <row r="226" hidden="1" spans="2:3">
-      <c r="B226" s="13"/>
-      <c r="C226" s="8" t="s">
-        <v>499</v>
+      <c r="B226" s="15"/>
+      <c r="C226" s="9" t="s">
+        <v>599</v>
       </c>
     </row>
     <row r="227" hidden="1" spans="2:3">
-      <c r="B227" s="13"/>
-      <c r="C227" s="8" t="s">
-        <v>500</v>
+      <c r="B227" s="15"/>
+      <c r="C227" s="9" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="228" hidden="1" spans="2:3">
-      <c r="B228" s="13"/>
-      <c r="C228" s="8"/>
+      <c r="B228" s="15"/>
+      <c r="C228" s="9"/>
     </row>
     <row r="229" hidden="1" spans="2:3">
-      <c r="B229" s="13"/>
-      <c r="C229" s="8" t="s">
-        <v>501</v>
+      <c r="B229" s="15"/>
+      <c r="C229" s="9" t="s">
+        <v>601</v>
       </c>
     </row>
     <row r="230" hidden="1" spans="2:3">
-      <c r="B230" s="13"/>
-      <c r="C230" s="8" t="s">
-        <v>502</v>
+      <c r="B230" s="15"/>
+      <c r="C230" s="9" t="s">
+        <v>602</v>
       </c>
     </row>
     <row r="231" spans="2:3">
-      <c r="B231" s="13"/>
-      <c r="C231" s="8"/>
+      <c r="B231" s="15"/>
+      <c r="C231" s="9"/>
     </row>
     <row r="232" spans="1:2">
-      <c r="A232" s="13">
+      <c r="A232" s="16">
         <v>8</v>
       </c>
-      <c r="B232" s="3" t="s">
-        <v>503</v>
+      <c r="B232" s="17" t="s">
+        <v>603</v>
       </c>
     </row>
     <row r="233" spans="2:3">
-      <c r="B233" s="13"/>
-      <c r="C233" s="11" t="s">
+      <c r="B233" s="15"/>
+      <c r="C233" s="13" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="234" hidden="1" spans="2:2">
+      <c r="B234" s="16"/>
+    </row>
+    <row r="235" hidden="1" spans="2:3">
+      <c r="B235" s="16"/>
+      <c r="C235" s="14" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="234" spans="2:2">
-      <c r="B234" s="13"/>
-    </row>
-    <row r="235" spans="2:3">
-      <c r="B235" s="13"/>
-      <c r="C235" s="12" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="236" ht="31" spans="2:3">
-      <c r="B236" s="13"/>
-      <c r="C236" s="15" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="237" spans="2:3">
-      <c r="B237" s="13"/>
-      <c r="C237" s="8"/>
-    </row>
-    <row r="238" spans="2:3">
-      <c r="B238" s="13"/>
-      <c r="C238" s="8" t="s">
-        <v>506</v>
+    <row r="236" ht="31" hidden="1" spans="2:3">
+      <c r="B236" s="16"/>
+      <c r="C236" s="19" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="237" hidden="1" spans="2:3">
+      <c r="B237" s="16"/>
+      <c r="C237" s="9"/>
+    </row>
+    <row r="238" hidden="1" spans="2:3">
+      <c r="B238" s="16"/>
+      <c r="C238" s="9" t="s">
+        <v>606</v>
       </c>
     </row>
     <row r="239" hidden="1" spans="2:3">
-      <c r="B239" s="13"/>
-      <c r="C239" s="8" t="s">
-        <v>507</v>
+      <c r="B239" s="16"/>
+      <c r="C239" s="9" t="s">
+        <v>607</v>
       </c>
     </row>
     <row r="240" hidden="1" spans="2:3">
-      <c r="B240" s="13"/>
-      <c r="C240" s="8"/>
+      <c r="B240" s="16"/>
+      <c r="C240" s="9"/>
     </row>
     <row r="241" hidden="1" spans="2:3">
-      <c r="B241" s="13"/>
-      <c r="C241" s="8" t="s">
-        <v>508</v>
+      <c r="B241" s="16"/>
+      <c r="C241" s="9" t="s">
+        <v>608</v>
       </c>
     </row>
     <row r="242" hidden="1" spans="2:3">
-      <c r="B242" s="13"/>
-      <c r="C242" s="8" t="s">
-        <v>509</v>
+      <c r="B242" s="16"/>
+      <c r="C242" s="9" t="s">
+        <v>609</v>
       </c>
     </row>
     <row r="243" hidden="1" spans="2:3">
-      <c r="B243" s="13"/>
-      <c r="C243" s="8"/>
+      <c r="B243" s="16"/>
+      <c r="C243" s="9"/>
     </row>
     <row r="244" hidden="1" spans="2:3">
-      <c r="B244" s="13"/>
-      <c r="C244" s="8" t="s">
-        <v>510</v>
+      <c r="B244" s="16"/>
+      <c r="C244" s="9" t="s">
+        <v>610</v>
       </c>
     </row>
     <row r="245" hidden="1" spans="2:3">
-      <c r="B245" s="13"/>
-      <c r="C245" s="8" t="s">
-        <v>511</v>
+      <c r="B245" s="16"/>
+      <c r="C245" s="9" t="s">
+        <v>611</v>
       </c>
     </row>
     <row r="246" hidden="1" spans="2:3">
-      <c r="B246" s="13"/>
-      <c r="C246" s="8"/>
+      <c r="B246" s="16"/>
+      <c r="C246" s="9"/>
     </row>
     <row r="247" hidden="1" spans="2:3">
-      <c r="B247" s="13"/>
-      <c r="C247" s="8" t="s">
-        <v>512</v>
+      <c r="B247" s="16"/>
+      <c r="C247" s="9" t="s">
+        <v>612</v>
       </c>
     </row>
     <row r="248" hidden="1" spans="2:3">
-      <c r="B248" s="13"/>
-      <c r="C248" s="8" t="s">
-        <v>513</v>
+      <c r="B248" s="16"/>
+      <c r="C248" s="9" t="s">
+        <v>613</v>
       </c>
     </row>
     <row r="249" hidden="1" spans="2:3">
-      <c r="B249" s="13"/>
-      <c r="C249" s="8"/>
+      <c r="B249" s="16"/>
+      <c r="C249" s="9"/>
     </row>
     <row r="250" hidden="1" spans="2:3">
-      <c r="B250" s="13"/>
-      <c r="C250" s="8" t="s">
-        <v>514</v>
+      <c r="B250" s="16"/>
+      <c r="C250" s="9" t="s">
+        <v>614</v>
       </c>
     </row>
     <row r="251" hidden="1" spans="2:3">
-      <c r="B251" s="13"/>
-      <c r="C251" s="8" t="s">
-        <v>515</v>
+      <c r="B251" s="16"/>
+      <c r="C251" s="9" t="s">
+        <v>615</v>
       </c>
     </row>
     <row r="252" hidden="1" spans="2:3">
-      <c r="B252" s="13"/>
-      <c r="C252" s="8"/>
+      <c r="B252" s="16"/>
+      <c r="C252" s="9"/>
     </row>
     <row r="253" hidden="1" spans="2:3">
-      <c r="B253" s="13"/>
-      <c r="C253" s="8" t="s">
-        <v>516</v>
+      <c r="B253" s="16"/>
+      <c r="C253" s="9" t="s">
+        <v>616</v>
       </c>
     </row>
     <row r="254" hidden="1" spans="2:3">
-      <c r="B254" s="13"/>
-      <c r="C254" s="8" t="s">
-        <v>517</v>
+      <c r="B254" s="16"/>
+      <c r="C254" s="9" t="s">
+        <v>617</v>
       </c>
     </row>
     <row r="255" hidden="1" spans="2:3">
-      <c r="B255" s="13"/>
-      <c r="C255" s="8"/>
+      <c r="B255" s="16"/>
+      <c r="C255" s="9"/>
     </row>
     <row r="256" hidden="1" spans="2:3">
-      <c r="B256" s="13"/>
-      <c r="C256" s="8" t="s">
-        <v>442</v>
+      <c r="B256" s="16"/>
+      <c r="C256" s="9" t="s">
+        <v>542</v>
       </c>
     </row>
     <row r="257" hidden="1" spans="2:3">
-      <c r="B257" s="13"/>
-      <c r="C257" s="8" t="s">
-        <v>444</v>
+      <c r="B257" s="16"/>
+      <c r="C257" s="9" t="s">
+        <v>544</v>
       </c>
     </row>
     <row r="258" spans="2:3">
-      <c r="B258" s="13"/>
-      <c r="C258" s="8"/>
-    </row>
-    <row r="259" spans="2:3">
-      <c r="B259" s="13"/>
-      <c r="C259" s="8"/>
+      <c r="B258" s="16"/>
+      <c r="C258" s="9"/>
+    </row>
+    <row r="259" spans="1:3">
+      <c r="A259" s="2"/>
+      <c r="B259" s="16"/>
+      <c r="C259" s="9"/>
+    </row>
+    <row r="260" spans="1:3">
+      <c r="A260" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="B260" s="16"/>
+      <c r="C260" s="9"/>
+    </row>
+    <row r="261" spans="1:1">
+      <c r="A261" s="2" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2">
+      <c r="A262" s="2"/>
+      <c r="B262" s="2" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3">
+      <c r="A263" s="2"/>
+      <c r="B263" s="2"/>
+      <c r="C263" s="2" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="264" ht="31" spans="1:3">
+      <c r="A264" s="2"/>
+      <c r="B264" s="2"/>
+      <c r="C264" s="20" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="265" ht="46.5" spans="1:3">
+      <c r="A265" s="2"/>
+      <c r="B265" s="2"/>
+      <c r="C265" s="20" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3">
+      <c r="A266" s="2"/>
+      <c r="B266" s="2"/>
+      <c r="C266" s="21" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3">
+      <c r="A267" s="2"/>
+      <c r="B267" s="2"/>
+      <c r="C267" s="21" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2">
+      <c r="A268" s="2"/>
+      <c r="B268" s="2" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2">
+      <c r="A269" s="2"/>
+      <c r="B269" s="2" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="270" spans="1:1">
+      <c r="A270" s="2"/>
+    </row>
+    <row r="271" spans="1:1">
+      <c r="A271" s="2" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="272" spans="2:2">
+      <c r="B272" s="2" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2">
+      <c r="A273" s="2"/>
+      <c r="B273" s="1" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="274" spans="1:1">
+      <c r="A274" s="2"/>
+    </row>
+    <row r="275" spans="1:2">
+      <c r="A275" s="2"/>
+      <c r="B275" s="1" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2">
+      <c r="A276" s="2"/>
+      <c r="B276" s="1" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="277" spans="1:1">
+      <c r="A277" s="2"/>
+    </row>
+    <row r="278" spans="1:2">
+      <c r="A278" s="2"/>
+      <c r="B278" s="1" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2">
+      <c r="A279" s="2"/>
+      <c r="B279" s="1" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="280" spans="1:1">
+      <c r="A280" s="2"/>
+    </row>
+    <row r="281" spans="1:1">
+      <c r="A281" s="2" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="282" spans="2:2">
+      <c r="B282" s="1" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="284" spans="1:1">
+      <c r="A284" s="1" t="s">
+        <v>637</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -8015,4 +8180,2216 @@
   <pageSetup paperSize="1" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A2:H2"/>
+  <sheetFormatPr defaultColWidth="8.66923076923077" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="28.3538461538462" style="66" customWidth="1"/>
+    <col min="2" max="2" width="28.8923076923077" style="66" customWidth="1"/>
+    <col min="3" max="3" width="5.66923076923077" style="67" customWidth="1"/>
+    <col min="4" max="4" width="7.08461538461538" style="66" customWidth="1"/>
+    <col min="5" max="5" width="7.75384615384615" style="66" customWidth="1"/>
+    <col min="6" max="6" width="23.4692307692308" style="66" customWidth="1"/>
+    <col min="7" max="8" width="4.5" style="66" customWidth="1"/>
+    <col min="9" max="16384" width="8.66923076923077" style="66"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:8">
+      <c r="A2" s="66" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="67" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="66" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" s="66" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="142" orientation="portrait"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A2:H2"/>
+  <sheetFormatPr defaultColWidth="8.66923076923077" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="28.3538461538462" style="66" customWidth="1"/>
+    <col min="2" max="2" width="28.8923076923077" style="66" customWidth="1"/>
+    <col min="3" max="3" width="5.66923076923077" style="67" customWidth="1"/>
+    <col min="4" max="4" width="7.08461538461538" style="66" customWidth="1"/>
+    <col min="5" max="5" width="7.75384615384615" style="66" customWidth="1"/>
+    <col min="6" max="6" width="23.4692307692308" style="66" customWidth="1"/>
+    <col min="7" max="8" width="4.5" style="66" customWidth="1"/>
+    <col min="9" max="16384" width="8.66923076923077" style="66"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:8">
+      <c r="A2" s="66" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="67" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="66" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" s="66" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="142" orientation="portrait"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:B127"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="15.5" outlineLevelCol="1"/>
+  <cols>
+    <col min="1" max="1" width="1.08461538461538" style="43" customWidth="1"/>
+    <col min="2" max="2" width="93.1307692307692" style="53" customWidth="1"/>
+    <col min="3" max="4" width="3.52307692307692" style="42" customWidth="1"/>
+    <col min="5" max="5" width="30.6153846153846" style="42" customWidth="1"/>
+    <col min="6" max="16384" width="9.23076923076923" style="42"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:2">
+      <c r="B1" s="55" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="2" spans="2:2">
+      <c r="B2" s="55"/>
+    </row>
+    <row r="3" ht="62" spans="2:2">
+      <c r="B3" s="58" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="16" ht="31" spans="2:2">
+      <c r="B16" s="59" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="18" ht="62" spans="2:2">
+      <c r="B18" s="53" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2">
+      <c r="B19" s="53" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2">
+      <c r="B20" s="53" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="21" ht="46.5" spans="2:2">
+      <c r="B21" s="53" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="52" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2">
+      <c r="B24" s="53" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="25" ht="46.5" spans="2:2">
+      <c r="B25" s="53" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2">
+      <c r="B26" s="53" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="27" ht="31" spans="2:2">
+      <c r="B27" s="53" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="29" ht="31" spans="2:2">
+      <c r="B29" s="53" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="43" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="32" ht="31" spans="2:2">
+      <c r="B32" s="53" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="33" ht="31" spans="2:2">
+      <c r="B33" s="53" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2">
+      <c r="B36" s="55" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2">
+      <c r="B37" s="53" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="38" spans="2:2">
+      <c r="B38" s="53" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2">
+      <c r="B40" s="60" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="41" ht="77.5" spans="2:2">
+      <c r="B41" s="61" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="43" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="44" spans="2:2">
+      <c r="B44" s="53" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="45" spans="2:2">
+      <c r="B45" s="53" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="46" spans="2:2">
+      <c r="B46" s="53" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="43" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2">
+      <c r="B49" s="53" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2">
+      <c r="B50" s="53" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2">
+      <c r="B51" s="53" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" s="43" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="54" spans="2:2">
+      <c r="B54" s="53" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="55" spans="2:2">
+      <c r="B55" s="53" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="56" spans="2:2">
+      <c r="B56" s="53" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="57" spans="2:2">
+      <c r="B57" s="53" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" s="43" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="60" spans="2:2">
+      <c r="B60" s="53" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="61" spans="2:2">
+      <c r="B61" s="53" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="62" spans="2:2">
+      <c r="B62" s="53" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" s="43" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="66" spans="2:2">
+      <c r="B66" s="53" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" s="52" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="69" spans="2:2">
+      <c r="B69" s="53" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="70" spans="2:2">
+      <c r="B70" s="53" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="71" spans="2:2">
+      <c r="B71" s="53" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="72" spans="2:2">
+      <c r="B72" s="53" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="73" spans="2:2">
+      <c r="B73" s="53" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="74" spans="2:2">
+      <c r="B74" s="53" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="75" spans="2:2">
+      <c r="B75" s="53" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="106" spans="2:2">
+      <c r="B106" s="55" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="107" spans="2:2">
+      <c r="B107" s="53" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="109" ht="31" spans="2:2">
+      <c r="B109" s="62" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="112" spans="2:2">
+      <c r="B112" s="63" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="113" spans="2:2">
+      <c r="B113" s="53" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="114" ht="31" spans="2:2">
+      <c r="B114" s="64" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="115" spans="2:2">
+      <c r="B115" s="42"/>
+    </row>
+    <row r="116" ht="31" spans="2:2">
+      <c r="B116" s="64" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="117" spans="2:2">
+      <c r="B117" s="42"/>
+    </row>
+    <row r="118" spans="2:2">
+      <c r="B118" s="64" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="119" spans="2:2">
+      <c r="B119" s="65" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="120" spans="2:2">
+      <c r="B120" s="65" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="121" spans="2:2">
+      <c r="B121" s="65" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="122" ht="31" spans="2:2">
+      <c r="B122" s="65" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="123" spans="2:2">
+      <c r="B123" s="65" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="124" spans="2:2">
+      <c r="B124" s="65" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="125" ht="31" spans="2:2">
+      <c r="B125" s="65" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="127" spans="2:2">
+      <c r="B127"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D34"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="15.5" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="3.39230769230769" style="50" customWidth="1"/>
+    <col min="2" max="2" width="2.94615384615385" style="51" customWidth="1"/>
+    <col min="3" max="3" width="2.88461538461538" style="51" customWidth="1"/>
+    <col min="4" max="4" width="83.9692307692308" style="51" customWidth="1"/>
+    <col min="5" max="16384" width="9.23076923076923" style="51"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:2">
+      <c r="B1" s="52" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="2" spans="2:2">
+      <c r="B2" s="52" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2">
+      <c r="B3" s="32"/>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="52" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="51" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="51" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="7" ht="46.5" spans="4:4">
+      <c r="D7" s="13" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="8" ht="80" customHeight="1" spans="4:4">
+      <c r="D8" s="53" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="9" ht="46.5" spans="4:4">
+      <c r="D9" s="54" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="10" ht="93" spans="4:4">
+      <c r="D10" s="55" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="11" spans="4:4">
+      <c r="D11" s="53" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="13" spans="4:4">
+      <c r="D13" s="51" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="17" ht="17.5" spans="2:2">
+      <c r="B17" s="56" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="18" ht="35" spans="2:4">
+      <c r="B18" s="56"/>
+      <c r="D18" s="10" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="19" ht="17.5" spans="2:3">
+      <c r="B19" s="52"/>
+      <c r="C19" s="57" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="20" ht="17.5" spans="2:4">
+      <c r="B20" s="52"/>
+      <c r="C20" s="57"/>
+      <c r="D20" s="53"/>
+    </row>
+    <row r="21" spans="2:3">
+      <c r="B21" s="52"/>
+      <c r="C21" s="51" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3">
+      <c r="B22" s="52"/>
+      <c r="C22" s="51" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3">
+      <c r="B23" s="52"/>
+      <c r="C23" s="51" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2">
+      <c r="B24" s="52"/>
+    </row>
+    <row r="25" spans="2:2">
+      <c r="B25" s="52"/>
+    </row>
+    <row r="26" ht="17.5" spans="2:2">
+      <c r="B26" s="56" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="27" ht="106" customHeight="1" spans="2:4">
+      <c r="B27" s="52"/>
+      <c r="D27" s="10" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2">
+      <c r="B28" s="52"/>
+    </row>
+    <row r="29" spans="2:2">
+      <c r="B29" s="52"/>
+    </row>
+    <row r="30" ht="35" spans="2:4">
+      <c r="B30" s="52" t="s">
+        <v>188</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="31" ht="17.5" spans="2:4">
+      <c r="B31" s="52"/>
+      <c r="D31" s="12" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="32" ht="17.5" spans="4:4">
+      <c r="D32" s="12" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="33" ht="17.5" spans="4:4">
+      <c r="D33" s="12" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="34" ht="17.5" spans="4:4">
+      <c r="D34" s="12" t="s">
+        <v>193</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G200"/>
+  <sheetFormatPr defaultColWidth="8.66923076923077" defaultRowHeight="15.5" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="1" width="3.07692307692308" style="39" customWidth="1"/>
+    <col min="2" max="4" width="4.15384615384615" style="40" customWidth="1"/>
+    <col min="5" max="5" width="82.6538461538462" style="41" customWidth="1"/>
+    <col min="6" max="6" width="12.1692307692308" style="42" customWidth="1"/>
+    <col min="7" max="8" width="4.5" style="42" customWidth="1"/>
+    <col min="9" max="16384" width="8.66923076923077" style="42"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:7">
+      <c r="B1" s="43" t="s">
+        <v>194</v>
+      </c>
+      <c r="G1" s="44"/>
+    </row>
+    <row r="2" spans="2:2">
+      <c r="B2" s="40" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="45">
+        <v>1</v>
+      </c>
+      <c r="B5" s="43" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2">
+      <c r="B6"/>
+    </row>
+    <row r="32" ht="52.5" spans="5:5">
+      <c r="E32" s="46" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="33" ht="35" spans="5:5">
+      <c r="E33" s="46" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="34" ht="35" spans="5:5">
+      <c r="E34" s="46" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="35" ht="17.5" spans="5:5">
+      <c r="E35" s="46" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2">
+      <c r="B37" s="40" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="38" ht="403" spans="5:5">
+      <c r="E38" s="41" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="40" ht="232.5" spans="5:5">
+      <c r="E40" s="47" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="42" spans="3:3">
+      <c r="C42" s="40" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="43" spans="3:3">
+      <c r="C43" s="40" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="44" spans="3:3">
+      <c r="C44" s="40" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="46" s="38" customFormat="1" ht="14" customHeight="1" spans="1:5">
+      <c r="A46" s="45">
+        <v>2</v>
+      </c>
+      <c r="B46" s="43" t="s">
+        <v>207</v>
+      </c>
+      <c r="C46" s="43"/>
+      <c r="D46" s="43"/>
+      <c r="E46" s="47"/>
+    </row>
+    <row r="47" ht="31" spans="5:5">
+      <c r="E47" s="41" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="48" ht="17.5" spans="3:3">
+      <c r="C48" s="48" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="49" ht="62" spans="5:5">
+      <c r="E49" s="41" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2">
+      <c r="B51"/>
+    </row>
+    <row r="83" spans="2:2">
+      <c r="B83" s="40" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="84" ht="35" spans="5:5">
+      <c r="E84" s="49" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="85" spans="5:5">
+      <c r="E85"/>
+    </row>
+    <row r="86" ht="17.5" spans="5:5">
+      <c r="E86" s="49" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="87" ht="17.5" spans="5:5">
+      <c r="E87" s="46" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="88" ht="17.5" spans="5:5">
+      <c r="E88" s="46" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="90" ht="52.5" spans="5:5">
+      <c r="E90" s="49" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="91" spans="5:5">
+      <c r="E91"/>
+    </row>
+    <row r="92" ht="52.5" spans="5:5">
+      <c r="E92" s="49" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="94" spans="2:2">
+      <c r="B94" s="40" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="95" spans="2:6">
+      <c r="B95" s="43" t="s">
+        <v>219</v>
+      </c>
+      <c r="C95" s="43"/>
+      <c r="D95" s="43" t="s">
+        <v>220</v>
+      </c>
+      <c r="E95" s="43" t="s">
+        <v>221</v>
+      </c>
+      <c r="F95" s="41"/>
+    </row>
+    <row r="96" spans="2:6">
+      <c r="B96" s="40" t="s">
+        <v>222</v>
+      </c>
+      <c r="D96" s="40" t="s">
+        <v>223</v>
+      </c>
+      <c r="E96" s="40" t="s">
+        <v>224</v>
+      </c>
+      <c r="F96" s="41"/>
+    </row>
+    <row r="97" spans="2:6">
+      <c r="B97" s="40" t="s">
+        <v>225</v>
+      </c>
+      <c r="D97" s="40" t="s">
+        <v>226</v>
+      </c>
+      <c r="E97" s="40" t="s">
+        <v>227</v>
+      </c>
+      <c r="F97" s="41"/>
+    </row>
+    <row r="98" spans="2:6">
+      <c r="B98" s="40" t="s">
+        <v>228</v>
+      </c>
+      <c r="D98" s="40" t="s">
+        <v>229</v>
+      </c>
+      <c r="E98" s="40" t="s">
+        <v>230</v>
+      </c>
+      <c r="F98" s="41"/>
+    </row>
+    <row r="99" spans="2:6">
+      <c r="B99" s="40" t="s">
+        <v>231</v>
+      </c>
+      <c r="D99" s="40" t="s">
+        <v>232</v>
+      </c>
+      <c r="E99" s="40" t="s">
+        <v>233</v>
+      </c>
+      <c r="F99" s="41"/>
+    </row>
+    <row r="100" spans="2:6">
+      <c r="B100" s="40" t="s">
+        <v>234</v>
+      </c>
+      <c r="D100" s="40" t="s">
+        <v>232</v>
+      </c>
+      <c r="E100" s="40" t="s">
+        <v>235</v>
+      </c>
+      <c r="F100" s="41"/>
+    </row>
+    <row r="101" spans="2:6">
+      <c r="B101" s="40" t="s">
+        <v>236</v>
+      </c>
+      <c r="D101" s="40" t="s">
+        <v>237</v>
+      </c>
+      <c r="E101" s="40" t="s">
+        <v>238</v>
+      </c>
+      <c r="F101" s="41"/>
+    </row>
+    <row r="102" spans="2:6">
+      <c r="B102" s="40" t="s">
+        <v>239</v>
+      </c>
+      <c r="D102" s="40" t="s">
+        <v>240</v>
+      </c>
+      <c r="E102" s="40"/>
+      <c r="F102" s="41"/>
+    </row>
+    <row r="103" spans="2:6">
+      <c r="B103" s="40" t="s">
+        <v>241</v>
+      </c>
+      <c r="E103" s="40"/>
+      <c r="F103" s="41"/>
+    </row>
+    <row r="104" spans="2:6">
+      <c r="B104" s="40" t="s">
+        <v>242</v>
+      </c>
+      <c r="E104" s="40"/>
+      <c r="F104" s="41"/>
+    </row>
+    <row r="105" spans="2:6">
+      <c r="B105" s="40" t="s">
+        <v>243</v>
+      </c>
+      <c r="E105" s="40"/>
+      <c r="F105" s="41"/>
+    </row>
+    <row r="106" spans="2:6">
+      <c r="B106" s="40" t="s">
+        <v>244</v>
+      </c>
+      <c r="E106" s="40"/>
+      <c r="F106" s="41"/>
+    </row>
+    <row r="107" spans="2:6">
+      <c r="B107" s="40" t="s">
+        <v>245</v>
+      </c>
+      <c r="E107" s="40"/>
+      <c r="F107" s="41"/>
+    </row>
+    <row r="108" spans="2:6">
+      <c r="B108" s="40" t="s">
+        <v>246</v>
+      </c>
+      <c r="E108" s="40"/>
+      <c r="F108" s="41"/>
+    </row>
+    <row r="109" spans="2:6">
+      <c r="B109" s="40" t="s">
+        <v>247</v>
+      </c>
+      <c r="E109" s="40"/>
+      <c r="F109" s="41"/>
+    </row>
+    <row r="110" spans="2:6">
+      <c r="B110" s="40" t="s">
+        <v>248</v>
+      </c>
+      <c r="E110" s="40"/>
+      <c r="F110" s="41"/>
+    </row>
+    <row r="111" spans="2:6">
+      <c r="B111" s="40" t="s">
+        <v>249</v>
+      </c>
+      <c r="E111" s="40"/>
+      <c r="F111" s="41"/>
+    </row>
+    <row r="112" spans="2:6">
+      <c r="B112" s="40" t="s">
+        <v>250</v>
+      </c>
+      <c r="E112" s="40"/>
+      <c r="F112" s="41"/>
+    </row>
+    <row r="113" spans="2:6">
+      <c r="B113" s="40" t="s">
+        <v>251</v>
+      </c>
+      <c r="E113" s="40"/>
+      <c r="F113" s="41"/>
+    </row>
+    <row r="115" spans="2:2">
+      <c r="B115" s="43" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="116" ht="263.5" spans="5:5">
+      <c r="E116" s="41" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="117" spans="2:2">
+      <c r="B117" s="40" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="119" s="38" customFormat="1" spans="1:5">
+      <c r="A119" s="45">
+        <v>3</v>
+      </c>
+      <c r="B119" s="43" t="s">
+        <v>254</v>
+      </c>
+      <c r="C119" s="43"/>
+      <c r="D119" s="43"/>
+      <c r="E119" s="47"/>
+    </row>
+    <row r="120" ht="62" spans="5:5">
+      <c r="E120" s="41" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="122" ht="108.5" spans="5:5">
+      <c r="E122" s="41" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="124" spans="3:3">
+      <c r="C124" s="43" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="125" spans="3:3">
+      <c r="C125" s="40" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="126" spans="3:3">
+      <c r="C126" s="43" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="127" spans="2:5">
+      <c r="B127" s="43" t="s">
+        <v>259</v>
+      </c>
+      <c r="C127" s="43"/>
+      <c r="D127" s="43" t="s">
+        <v>260</v>
+      </c>
+      <c r="E127" s="43" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="128" spans="2:5">
+      <c r="B128" s="40" t="s">
+        <v>262</v>
+      </c>
+      <c r="D128" s="40" t="s">
+        <v>263</v>
+      </c>
+      <c r="E128" s="40" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="129" spans="2:5">
+      <c r="B129" s="40" t="s">
+        <v>265</v>
+      </c>
+      <c r="D129" s="40" t="s">
+        <v>266</v>
+      </c>
+      <c r="E129" s="40" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="130" spans="2:5">
+      <c r="B130" s="40" t="s">
+        <v>268</v>
+      </c>
+      <c r="D130" s="40" t="s">
+        <v>269</v>
+      </c>
+      <c r="E130" s="40" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="131" spans="2:5">
+      <c r="B131" s="40" t="s">
+        <v>271</v>
+      </c>
+      <c r="D131" s="40" t="s">
+        <v>272</v>
+      </c>
+      <c r="E131" s="40" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="132" spans="2:5">
+      <c r="B132" s="40" t="s">
+        <v>273</v>
+      </c>
+      <c r="D132" s="40" t="s">
+        <v>274</v>
+      </c>
+      <c r="E132" s="40" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="133" spans="2:5">
+      <c r="B133" s="40" t="s">
+        <v>275</v>
+      </c>
+      <c r="D133" s="40" t="s">
+        <v>276</v>
+      </c>
+      <c r="E133" s="40" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="134" spans="2:5">
+      <c r="B134" s="40" t="s">
+        <v>277</v>
+      </c>
+      <c r="D134" s="40" t="s">
+        <v>278</v>
+      </c>
+      <c r="E134" s="40" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="135" spans="2:5">
+      <c r="B135" s="40" t="s">
+        <v>279</v>
+      </c>
+      <c r="D135" s="40" t="s">
+        <v>280</v>
+      </c>
+      <c r="E135" s="40" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="136" spans="2:5">
+      <c r="B136" s="40" t="s">
+        <v>282</v>
+      </c>
+      <c r="D136" s="40" t="s">
+        <v>283</v>
+      </c>
+      <c r="E136" s="40" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="137" spans="2:5">
+      <c r="B137" s="40" t="s">
+        <v>285</v>
+      </c>
+      <c r="D137" s="40" t="s">
+        <v>286</v>
+      </c>
+      <c r="E137" s="40" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="138" ht="46.5" spans="5:5">
+      <c r="E138" s="41" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="140" s="38" customFormat="1" spans="1:5">
+      <c r="A140" s="45">
+        <v>4</v>
+      </c>
+      <c r="B140" s="43" t="s">
+        <v>289</v>
+      </c>
+      <c r="C140" s="43"/>
+      <c r="D140" s="43"/>
+      <c r="E140" s="47"/>
+    </row>
+    <row r="141" spans="2:2">
+      <c r="B141" s="40" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="142" spans="2:2">
+      <c r="B142" s="40" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="143" spans="2:2">
+      <c r="B143" s="40" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="144" ht="46.5" spans="5:5">
+      <c r="E144" s="41" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="145" ht="62" spans="5:5">
+      <c r="E145" s="41" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="146" ht="31" spans="5:5">
+      <c r="E146" s="41" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="147" spans="5:5">
+      <c r="E147" s="41" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149" s="45">
+        <v>6</v>
+      </c>
+      <c r="B149" s="43" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="150" ht="31" spans="5:5">
+      <c r="E150" s="41" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="151" ht="17.5" spans="5:5">
+      <c r="E151" s="48" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="152" spans="3:3">
+      <c r="C152" s="40" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="153" spans="3:3">
+      <c r="C153" s="40" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="155" ht="139.5" spans="5:5">
+      <c r="E155" s="41" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="156" ht="31" spans="5:5">
+      <c r="E156" s="41" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="158" spans="2:5">
+      <c r="B158" s="43" t="s">
+        <v>304</v>
+      </c>
+      <c r="C158" s="43"/>
+      <c r="D158" s="43"/>
+      <c r="E158" s="47" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="159" ht="31" spans="2:5">
+      <c r="B159" s="40" t="s">
+        <v>306</v>
+      </c>
+      <c r="E159" s="41" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="160" ht="31" spans="2:5">
+      <c r="B160" s="40" t="s">
+        <v>308</v>
+      </c>
+      <c r="E160" s="41" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="161" ht="31" spans="2:5">
+      <c r="B161" s="40" t="s">
+        <v>310</v>
+      </c>
+      <c r="E161" s="41" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="162" spans="2:2">
+      <c r="B162" s="40" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="163" ht="31" spans="2:5">
+      <c r="B163" s="40" t="s">
+        <v>313</v>
+      </c>
+      <c r="E163" s="41" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="164" spans="2:2">
+      <c r="B164" s="40" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="165" spans="2:5">
+      <c r="B165" s="40" t="s">
+        <v>315</v>
+      </c>
+      <c r="E165" s="41" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="166" spans="2:5">
+      <c r="B166" s="40" t="s">
+        <v>317</v>
+      </c>
+      <c r="E166" s="41" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="167" ht="31" spans="2:5">
+      <c r="B167" s="40" t="s">
+        <v>319</v>
+      </c>
+      <c r="E167" s="41" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="169" ht="124" spans="5:5">
+      <c r="E169" s="41" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="171" spans="4:4">
+      <c r="D171" s="43" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="172" ht="232.5" spans="5:5">
+      <c r="E172" s="41" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="174" spans="4:4">
+      <c r="D174" s="43" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="175" ht="62" spans="5:5">
+      <c r="E175" s="41" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="177" spans="2:2">
+      <c r="B177" s="40" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2">
+      <c r="A178" s="45">
+        <v>7</v>
+      </c>
+      <c r="B178" s="43" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="179" spans="2:4">
+      <c r="B179" s="43" t="s">
+        <v>328</v>
+      </c>
+      <c r="C179" s="43"/>
+      <c r="D179" s="43"/>
+    </row>
+    <row r="180" ht="93" spans="2:5">
+      <c r="B180" s="43"/>
+      <c r="C180" s="43"/>
+      <c r="D180" s="43"/>
+      <c r="E180" s="41" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="181" spans="2:4">
+      <c r="B181" s="43"/>
+      <c r="C181" s="43" t="s">
+        <v>330</v>
+      </c>
+      <c r="D181" s="43"/>
+    </row>
+    <row r="182" ht="310" spans="2:5">
+      <c r="B182" s="43"/>
+      <c r="C182" s="43"/>
+      <c r="D182" s="43"/>
+      <c r="E182" s="41" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="183" spans="2:4">
+      <c r="B183" s="43"/>
+      <c r="C183" s="43"/>
+      <c r="D183" s="43"/>
+    </row>
+    <row r="184" ht="139.5" spans="2:5">
+      <c r="B184" s="43"/>
+      <c r="C184" s="43"/>
+      <c r="D184" s="43"/>
+      <c r="E184" s="41" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="185" spans="2:4">
+      <c r="B185" s="43"/>
+      <c r="C185" s="43"/>
+      <c r="D185" s="43"/>
+    </row>
+    <row r="186" spans="2:4">
+      <c r="B186" s="43"/>
+      <c r="C186" s="43" t="s">
+        <v>333</v>
+      </c>
+      <c r="D186" s="43"/>
+    </row>
+    <row r="187" ht="62" spans="2:5">
+      <c r="B187" s="43"/>
+      <c r="C187" s="43"/>
+      <c r="D187" s="43"/>
+      <c r="E187" s="41" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="188" spans="2:4">
+      <c r="B188" s="43"/>
+      <c r="C188" s="43"/>
+      <c r="D188" s="43"/>
+    </row>
+    <row r="189" ht="46.5" spans="2:5">
+      <c r="B189" s="43"/>
+      <c r="C189" s="43"/>
+      <c r="D189" s="43"/>
+      <c r="E189" s="41" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="190" spans="2:4">
+      <c r="B190" s="43"/>
+      <c r="C190" s="43"/>
+      <c r="D190" s="43"/>
+    </row>
+    <row r="191" ht="155" spans="2:5">
+      <c r="B191" s="43"/>
+      <c r="C191" s="43"/>
+      <c r="D191" s="43"/>
+      <c r="E191" s="41" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="192" spans="2:4">
+      <c r="B192" s="43"/>
+      <c r="C192" s="43"/>
+      <c r="D192" s="43"/>
+    </row>
+    <row r="193" spans="2:4">
+      <c r="B193" s="43"/>
+      <c r="C193" s="43"/>
+      <c r="D193" s="43" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="194" ht="31" spans="2:5">
+      <c r="B194" s="43"/>
+      <c r="C194" s="43"/>
+      <c r="D194" s="43"/>
+      <c r="E194" s="41" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="195" spans="2:5">
+      <c r="B195" s="43"/>
+      <c r="C195" s="43"/>
+      <c r="D195" s="43"/>
+      <c r="E195" s="41" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="196" spans="2:5">
+      <c r="B196" s="43"/>
+      <c r="C196" s="43"/>
+      <c r="D196" s="43"/>
+      <c r="E196" s="41" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2">
+      <c r="A198" s="39">
+        <v>8</v>
+      </c>
+      <c r="B198" s="40" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2">
+      <c r="A200" s="39">
+        <v>9</v>
+      </c>
+      <c r="B200" s="40" t="s">
+        <v>342</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="142" orientation="portrait"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A2:B105"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="15.5" outlineLevelCol="1"/>
+  <cols>
+    <col min="1" max="1" width="3.9" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="31" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="31" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2">
+      <c r="B11" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2">
+      <c r="B12" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="31" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="31" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2">
+      <c r="B20" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="31" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="25" hidden="1" spans="1:1">
+      <c r="A25" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="26" hidden="1" spans="1:1">
+      <c r="A26" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="27" hidden="1" spans="1:1">
+      <c r="A27" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="28" hidden="1" spans="1:1">
+      <c r="A28" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="29" hidden="1" spans="2:2">
+      <c r="B29" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="30" hidden="1" spans="1:1">
+      <c r="A30" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="31" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="34" hidden="1" spans="1:1">
+      <c r="A34" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="35" hidden="1" spans="1:1">
+      <c r="A35" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="36" hidden="1" spans="1:1">
+      <c r="A36" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="37" hidden="1" spans="1:1">
+      <c r="A37" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="38" hidden="1" spans="1:1">
+      <c r="A38" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="39" hidden="1" spans="1:1">
+      <c r="A39" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="40" hidden="1" spans="1:1">
+      <c r="A40" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="41" hidden="1" spans="1:1">
+      <c r="A41" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="42" hidden="1" spans="1:1">
+      <c r="A42" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="43" hidden="1" spans="1:1">
+      <c r="A43" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="44" hidden="1" spans="1:1">
+      <c r="A44" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="45" hidden="1" spans="1:1">
+      <c r="A45" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="46" hidden="1" spans="1:1">
+      <c r="A46" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="47" hidden="1" spans="1:1">
+      <c r="A47" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="48" hidden="1" spans="1:1">
+      <c r="A48" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="49" hidden="1" spans="1:1">
+      <c r="A49" s="32" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="50" hidden="1" spans="1:1">
+      <c r="A50" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="51" hidden="1" spans="1:1">
+      <c r="A51" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="52" hidden="1" spans="1:1">
+      <c r="A52" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="53" hidden="1" spans="1:1">
+      <c r="A53" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="31" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="57" hidden="1" spans="1:1">
+      <c r="A57" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="58" hidden="1" spans="1:1">
+      <c r="A58" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="59" hidden="1" spans="1:1">
+      <c r="A59" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="60" hidden="1"/>
+    <row r="61" hidden="1" spans="1:1">
+      <c r="A61" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="62" hidden="1" spans="1:1">
+      <c r="A62" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="63" hidden="1" spans="1:1">
+      <c r="A63" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" s="31" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="68" hidden="1" spans="1:1">
+      <c r="A68" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="69" hidden="1" spans="1:1">
+      <c r="A69" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="70" hidden="1" spans="1:1">
+      <c r="A70" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="71" hidden="1" spans="1:1">
+      <c r="A71" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="72" hidden="1" spans="1:1">
+      <c r="A72" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="73" hidden="1" spans="1:1">
+      <c r="A73" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="74" hidden="1" spans="1:1">
+      <c r="A74" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="75" hidden="1" spans="1:1">
+      <c r="A75" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="76" hidden="1" spans="1:1">
+      <c r="A76" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" s="31" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="81" hidden="1" spans="1:1">
+      <c r="A81" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="82" hidden="1" spans="1:1">
+      <c r="A82" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="83" hidden="1" spans="1:1">
+      <c r="A83" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="84" hidden="1" spans="1:1">
+      <c r="A84" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="85" hidden="1" spans="1:1">
+      <c r="A85" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="86" hidden="1" spans="1:1">
+      <c r="A86" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="87" hidden="1" spans="1:1">
+      <c r="A87" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="88" hidden="1" spans="1:1">
+      <c r="A88" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="89" hidden="1" spans="1:1">
+      <c r="A89" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="90" hidden="1" spans="1:1">
+      <c r="A90" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="91" hidden="1" spans="1:1">
+      <c r="A91" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="92" hidden="1" spans="1:1">
+      <c r="A92" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="93" hidden="1" spans="1:1">
+      <c r="A93" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="94" hidden="1"/>
+    <row r="95" hidden="1" spans="1:1">
+      <c r="A95" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="96" hidden="1" spans="1:1">
+      <c r="A96" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97" s="33"/>
+      <c r="B97" s="33"/>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98" s="34" t="s">
+        <v>420</v>
+      </c>
+      <c r="B98" s="33"/>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99" s="35" t="s">
+        <v>421</v>
+      </c>
+      <c r="B99" s="33"/>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" s="35" t="s">
+        <v>422</v>
+      </c>
+      <c r="B100" s="33"/>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" s="36"/>
+      <c r="B101" s="33"/>
+    </row>
+    <row r="102" spans="2:2">
+      <c r="B102" s="33"/>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104" s="37" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105" t="s">
+        <v>424</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H88"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="27.3307692307692" style="23" customWidth="1"/>
+    <col min="2" max="2" width="19.8307692307692" style="24" customWidth="1"/>
+    <col min="3" max="3" width="2.41538461538462" style="23" customWidth="1"/>
+    <col min="4" max="4" width="3.33076923076923" style="23" customWidth="1"/>
+    <col min="5" max="5" width="12.6692307692308" style="23" customWidth="1"/>
+    <col min="6" max="6" width="12.1692307692308" style="23" customWidth="1"/>
+    <col min="7" max="8" width="4.5" style="23" customWidth="1"/>
+    <col min="9" max="16384" width="11" style="23"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:2">
+      <c r="B1" s="24" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" s="23" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2">
+      <c r="B4" s="24" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="5" ht="15.5" spans="3:3">
+      <c r="C5" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="6" ht="15.5" spans="3:4">
+      <c r="C6" s="24"/>
+      <c r="D6" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="7" ht="15.5" spans="3:3">
+      <c r="C7" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="8" ht="15.5" spans="3:3">
+      <c r="C8" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="9" ht="15.5" spans="1:4">
+      <c r="A9" s="26"/>
+      <c r="C9" s="24"/>
+      <c r="D9" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="10" ht="15.5" spans="3:4">
+      <c r="C10" s="24"/>
+      <c r="D10" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="11" ht="15.5" spans="3:4">
+      <c r="C11" s="24"/>
+      <c r="D11" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="12" ht="15.5" spans="3:4">
+      <c r="C12" s="24"/>
+      <c r="D12" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="13" ht="15.5" spans="3:4">
+      <c r="C13" s="24"/>
+      <c r="D13" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="14" ht="15.5" spans="3:3">
+      <c r="C14" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="15" ht="15.5" spans="3:4">
+      <c r="C15" s="24"/>
+      <c r="D15" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="16" ht="15.5" spans="3:4">
+      <c r="C16" s="24"/>
+      <c r="D16" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="17" ht="15.5" spans="3:4">
+      <c r="C17" s="24"/>
+      <c r="D17" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="18" ht="15.5" spans="3:4">
+      <c r="C18" s="24"/>
+      <c r="D18" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="19" ht="15.5" spans="3:4">
+      <c r="C19" s="24"/>
+      <c r="D19" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="20" ht="15.5" spans="3:3">
+      <c r="C20" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="21" ht="15.5" spans="3:3">
+      <c r="C21" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="22" ht="15.5" spans="3:4">
+      <c r="C22" s="24"/>
+      <c r="D22" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="23" ht="15.5" spans="3:4">
+      <c r="C23" s="24"/>
+      <c r="D23" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="24" ht="15.5" spans="3:3">
+      <c r="C24" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="29" spans="3:3">
+      <c r="C29" s="23" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="27"/>
+      <c r="B30" s="28"/>
+      <c r="D30" s="23" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="27"/>
+      <c r="B31" s="28"/>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="27"/>
+      <c r="B32" s="28"/>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="27"/>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="27"/>
+      <c r="B34" s="28"/>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="27"/>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="27"/>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="27"/>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="27"/>
+    </row>
+    <row r="56" spans="4:4">
+      <c r="D56" s="29"/>
+    </row>
+    <row r="57" spans="4:4">
+      <c r="D57" s="29"/>
+    </row>
+    <row r="58" spans="4:4">
+      <c r="D58" s="30"/>
+    </row>
+    <row r="61" spans="3:6">
+      <c r="C61" s="27"/>
+      <c r="D61" s="27"/>
+      <c r="E61" s="27"/>
+      <c r="F61" s="27"/>
+    </row>
+    <row r="62" spans="3:6">
+      <c r="C62" s="27"/>
+      <c r="D62" s="27"/>
+      <c r="E62" s="27"/>
+      <c r="F62" s="27"/>
+    </row>
+    <row r="63" spans="3:6">
+      <c r="C63" s="27"/>
+      <c r="D63" s="27"/>
+      <c r="E63" s="27"/>
+      <c r="F63" s="27"/>
+    </row>
+    <row r="64" spans="3:6">
+      <c r="C64" s="27"/>
+      <c r="D64" s="27"/>
+      <c r="F64" s="27"/>
+    </row>
+    <row r="65" spans="3:6">
+      <c r="C65" s="27"/>
+      <c r="D65" s="27"/>
+      <c r="E65" s="27"/>
+      <c r="F65" s="27"/>
+    </row>
+    <row r="66" spans="3:6">
+      <c r="C66" s="27"/>
+      <c r="D66" s="27"/>
+      <c r="E66" s="27"/>
+      <c r="F66" s="27"/>
+    </row>
+    <row r="88" spans="4:4">
+      <c r="D88" s="29"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="142" orientation="portrait"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A3"/>
+  <sheetFormatPr defaultColWidth="8.66923076923077" defaultRowHeight="12.5" outlineLevelRow="2"/>
+  <cols>
+    <col min="1" max="16384" width="8.66923076923077" style="22"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:1">
+      <c r="A3" s="22" t="s">
+        <v>449</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/p/ds_25/apache-spark/topic-list_ap-spk.xlsx
+++ b/p/ds_25/apache-spark/topic-list_ap-spk.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9680" tabRatio="698" activeTab="4"/>
+    <workbookView windowWidth="21010" windowHeight="11150" tabRatio="698" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="core" sheetId="6" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1416" uniqueCount="1081">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1417" uniqueCount="1082">
   <si>
     <t>s.no.</t>
   </si>
@@ -173,6 +173,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
       <t>df.withColumn('new_column',</t>
     </r>
     <r>
@@ -201,6 +206,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
       <t>df.groupBy("author").</t>
     </r>
     <r>
@@ -923,6 +933,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">select("colA", </t>
     </r>
     <r>
@@ -962,6 +977,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
       <t>df [df.colA.</t>
     </r>
     <r>
@@ -984,6 +1004,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
       <t>dg.select("colA", "colB", df.colC.</t>
     </r>
     <r>
@@ -1015,6 +1040,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
       <t>df.select(df.colA.substr(1, 3).</t>
     </r>
     <r>
@@ -1217,6 +1247,9 @@
   </si>
   <si>
     <t>registerTempTable, repartition,</t>
+  </si>
+  <si>
+    <t>display(df.select("First_Name", "Count").orderBy(desc("Count")))</t>
   </si>
   <si>
     <t>&amp; many mores.</t>
@@ -6354,14 +6387,20 @@
     </font>
     <font>
       <sz val="10.2"/>
-      <color rgb="FF161616"/>
-      <name val="Consolas"/>
+      <color rgb="FF1F2328"/>
+      <name val="var(--fontStack-monospace"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10.2"/>
-      <color rgb="FF1F2328"/>
-      <name val="var(--fontStack-monospace"/>
+      <sz val="12"/>
+      <color rgb="FF666666"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF4070A0"/>
+      <name val="Calibri"/>
       <charset val="134"/>
     </font>
     <font>
@@ -6369,6 +6408,24 @@
       <sz val="12"/>
       <color rgb="FF333333"/>
       <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color rgb="FF1F2328"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.2"/>
+      <color rgb="FF161616"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
@@ -6399,31 +6456,14 @@
       <i/>
       <sz val="12"/>
       <color rgb="FF161616"/>
-      <name val="Segoe UI"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF666666"/>
       <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF4070A0"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
       <i/>
       <sz val="12"/>
       <color rgb="FF161616"/>
-      <name val="Calibri"/>
+      <name val="Segoe UI"/>
       <charset val="134"/>
     </font>
     <font>
@@ -6432,13 +6472,6 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="12"/>
-      <color rgb="FF1F2328"/>
-      <name val="Segoe UI"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -6905,7 +6938,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -7097,7 +7130,6 @@
     <xf numFmtId="180" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -7646,7 +7678,7 @@
       <c r="E2" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="88" t="s">
+      <c r="G2" s="87" t="s">
         <v>4</v>
       </c>
       <c r="H2" s="79" t="s">
@@ -8014,7 +8046,7 @@
   <sheetData>
     <row r="1" spans="2:2">
       <c r="B1" s="54" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="2" spans="2:2">
@@ -8022,267 +8054,267 @@
     </row>
     <row r="3" ht="62" spans="2:2">
       <c r="B3" s="57" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="16" ht="31" spans="2:2">
       <c r="B16" s="58" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="18" ht="62" spans="2:2">
       <c r="B18" s="52" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="19" spans="2:2">
       <c r="B19" s="52" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="20" spans="2:2">
       <c r="B20" s="52" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="21" ht="46.5" spans="2:2">
       <c r="B21" s="52" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="51" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="24" spans="2:2">
       <c r="B24" s="52" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="25" ht="46.5" spans="2:2">
       <c r="B25" s="52" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="26" spans="2:2">
       <c r="B26" s="52" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="27" ht="31" spans="2:2">
       <c r="B27" s="52" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="29" ht="31" spans="2:2">
       <c r="B29" s="52" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="42" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="32" ht="31" spans="2:2">
       <c r="B32" s="52" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="33" ht="31" spans="2:2">
       <c r="B33" s="52" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="36" spans="2:2">
       <c r="B36" s="54" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="37" spans="2:2">
       <c r="B37" s="52" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="38" spans="2:2">
       <c r="B38" s="52" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="40" spans="2:2">
       <c r="B40" s="59" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="41" ht="77.5" spans="2:2">
       <c r="B41" s="60" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="42" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="44" spans="2:2">
       <c r="B44" s="52" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="45" spans="2:2">
       <c r="B45" s="52" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="46" spans="2:2">
       <c r="B46" s="52" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="42" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="49" spans="2:2">
       <c r="B49" s="52" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="50" spans="2:2">
       <c r="B50" s="52" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="51" spans="2:2">
       <c r="B51" s="52" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="42" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="54" spans="2:2">
       <c r="B54" s="52" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="55" spans="2:2">
       <c r="B55" s="52" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="56" spans="2:2">
       <c r="B56" s="52" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="57" spans="2:2">
       <c r="B57" s="52" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="42" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="60" spans="2:2">
       <c r="B60" s="52" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="61" spans="2:2">
       <c r="B61" s="52" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="62" spans="2:2">
       <c r="B62" s="52" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="42" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="66" spans="2:2">
       <c r="B66" s="52" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="51" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="69" spans="2:2">
       <c r="B69" s="52" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="70" spans="2:2">
       <c r="B70" s="52" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="71" spans="2:2">
       <c r="B71" s="52" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="72" spans="2:2">
       <c r="B72" s="52" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="73" spans="2:2">
       <c r="B73" s="52" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="74" spans="2:2">
       <c r="B74" s="52" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="75" spans="2:2">
       <c r="B75" s="52" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="106" spans="2:2">
       <c r="B106" s="54" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="107" spans="2:2">
       <c r="B107" s="52" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="109" ht="31" spans="2:2">
       <c r="B109" s="61" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="112" spans="2:2">
       <c r="B112" s="62" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="113" spans="2:2">
       <c r="B113" s="52" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="114" ht="31" spans="2:2">
       <c r="B114" s="63" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="115" spans="2:2">
@@ -8290,7 +8322,7 @@
     </row>
     <row r="116" ht="31" spans="2:2">
       <c r="B116" s="63" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="117" spans="2:2">
@@ -8298,42 +8330,42 @@
     </row>
     <row r="118" spans="2:2">
       <c r="B118" s="63" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="119" spans="2:2">
       <c r="B119" s="64" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="120" spans="2:2">
       <c r="B120" s="64" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="121" spans="2:2">
       <c r="B121" s="64" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="122" ht="31" spans="2:2">
       <c r="B122" s="64" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="123" spans="2:2">
       <c r="B123" s="64" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="124" spans="2:2">
       <c r="B124" s="64" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="125" ht="31" spans="2:2">
       <c r="B125" s="64" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="127" spans="2:2">
@@ -8362,12 +8394,12 @@
   <sheetData>
     <row r="1" spans="2:2">
       <c r="B1" s="51" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="2" spans="2:2">
       <c r="B2" s="51" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="3" spans="2:2">
@@ -8375,64 +8407,64 @@
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="51" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="50" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="50" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="7" ht="46.5" spans="4:4">
       <c r="D7" s="13" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="8" ht="80" customHeight="1" spans="4:4">
       <c r="D8" s="52" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="9" ht="46.5" spans="4:4">
       <c r="D9" s="53" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="10" ht="93" spans="4:4">
       <c r="D10" s="54" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" s="52" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" s="50" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="17" ht="17.5" spans="2:2">
       <c r="B17" s="55" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="18" ht="35" spans="2:4">
       <c r="B18" s="55"/>
       <c r="D18" s="10" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="19" ht="17.5" spans="2:3">
       <c r="B19" s="51"/>
       <c r="C19" s="56" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="20" ht="17.5" spans="2:4">
@@ -8443,19 +8475,19 @@
     <row r="21" spans="2:3">
       <c r="B21" s="51"/>
       <c r="C21" s="50" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="22" spans="2:3">
       <c r="B22" s="51"/>
       <c r="C22" s="50" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="23" spans="2:3">
       <c r="B23" s="51"/>
       <c r="C23" s="50" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="24" spans="2:2">
@@ -8466,13 +8498,13 @@
     </row>
     <row r="26" ht="17.5" spans="2:2">
       <c r="B26" s="55" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="27" ht="106" customHeight="1" spans="2:4">
       <c r="B27" s="51"/>
       <c r="D27" s="10" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="28" spans="2:2">
@@ -8483,31 +8515,31 @@
     </row>
     <row r="30" ht="35" spans="2:4">
       <c r="B30" s="51" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="31" ht="17.5" spans="2:4">
       <c r="B31" s="51"/>
       <c r="D31" s="12" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="32" ht="17.5" spans="4:4">
       <c r="D32" s="12" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="33" ht="17.5" spans="4:4">
       <c r="D33" s="12" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="34" ht="17.5" spans="4:4">
       <c r="D34" s="12" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
   </sheetData>
@@ -8533,13 +8565,13 @@
   <sheetData>
     <row r="1" spans="2:7">
       <c r="B1" s="42" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="G1" s="43"/>
     </row>
     <row r="2" spans="2:2">
       <c r="B2" s="39" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -8547,7 +8579,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="6" spans="2:2">
@@ -8555,52 +8587,52 @@
     </row>
     <row r="32" ht="52.5" spans="5:5">
       <c r="E32" s="45" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="33" ht="35" spans="5:5">
       <c r="E33" s="45" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="34" ht="35" spans="5:5">
       <c r="E34" s="45" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="35" ht="17.5" spans="5:5">
       <c r="E35" s="45" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="37" spans="2:2">
       <c r="B37" s="39" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="38" ht="403" spans="5:5">
       <c r="E38" s="40" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="40" ht="232.5" spans="5:5">
       <c r="E40" s="46" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="42" spans="3:3">
       <c r="C42" s="39" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="43" spans="3:3">
       <c r="C43" s="39" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="44" spans="3:3">
       <c r="C44" s="39" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="46" s="37" customFormat="1" ht="14" customHeight="1" spans="1:5">
@@ -8608,7 +8640,7 @@
         <v>2</v>
       </c>
       <c r="B46" s="42" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C46" s="42"/>
       <c r="D46" s="42"/>
@@ -8616,17 +8648,17 @@
     </row>
     <row r="47" ht="31" spans="5:5">
       <c r="E47" s="40" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="48" ht="17.5" spans="3:3">
       <c r="C48" s="47" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="49" ht="62" spans="5:5">
       <c r="E49" s="40" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="51" spans="2:2">
@@ -8634,12 +8666,12 @@
     </row>
     <row r="83" spans="2:2">
       <c r="B83" s="39" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="84" ht="35" spans="5:5">
       <c r="E84" s="48" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="85" spans="5:5">
@@ -8647,22 +8679,22 @@
     </row>
     <row r="86" ht="17.5" spans="5:5">
       <c r="E86" s="48" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="87" ht="17.5" spans="5:5">
       <c r="E87" s="45" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="88" ht="17.5" spans="5:5">
       <c r="E88" s="45" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="90" ht="52.5" spans="5:5">
       <c r="E90" s="48" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="91" spans="5:5">
@@ -8670,204 +8702,204 @@
     </row>
     <row r="92" ht="52.5" spans="5:5">
       <c r="E92" s="48" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="95" spans="2:2">
       <c r="B95" s="39" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="96" spans="2:6">
       <c r="B96" s="42" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C96" s="42"/>
       <c r="D96" s="42" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E96" s="42" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="F96" s="40"/>
     </row>
     <row r="97" spans="2:6">
       <c r="B97" s="39" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="D97" s="39" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="E97" s="39" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="F97" s="40"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="39" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="D98" s="39" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="E98" s="39" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="F98" s="40"/>
     </row>
     <row r="99" spans="2:6">
       <c r="B99" s="39" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="D99" s="39" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="E99" s="39" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="F99" s="40"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="39" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="D100" s="39" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E100" s="39" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="F100" s="40"/>
     </row>
     <row r="101" spans="2:6">
       <c r="B101" s="39" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="D101" s="39" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E101" s="39" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="F101" s="40"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="39" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="D102" s="39" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E102" s="39" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="F102" s="40"/>
     </row>
     <row r="103" spans="2:6">
       <c r="B103" s="39" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D103" s="39" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="E103" s="39"/>
       <c r="F103" s="40"/>
     </row>
     <row r="104" spans="2:6">
       <c r="B104" s="39" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="E104" s="39"/>
       <c r="F104" s="40"/>
     </row>
     <row r="105" spans="2:6">
       <c r="B105" s="39" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="E105" s="39"/>
       <c r="F105" s="40"/>
     </row>
     <row r="106" spans="2:6">
       <c r="B106" s="39" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="E106" s="39"/>
       <c r="F106" s="40"/>
     </row>
     <row r="107" spans="2:6">
       <c r="B107" s="39" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="E107" s="39"/>
       <c r="F107" s="40"/>
     </row>
     <row r="108" spans="2:6">
       <c r="B108" s="39" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="E108" s="39"/>
       <c r="F108" s="40"/>
     </row>
     <row r="109" spans="2:6">
       <c r="B109" s="39" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="E109" s="39"/>
       <c r="F109" s="40"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="39" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="E110" s="39"/>
       <c r="F110" s="40"/>
     </row>
     <row r="111" spans="2:6">
       <c r="B111" s="39" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="E111" s="39"/>
       <c r="F111" s="40"/>
     </row>
     <row r="112" spans="2:6">
       <c r="B112" s="39" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="E112" s="39"/>
       <c r="F112" s="40"/>
     </row>
     <row r="113" spans="2:6">
       <c r="B113" s="39" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="E113" s="39"/>
       <c r="F113" s="40"/>
     </row>
     <row r="114" spans="2:6">
       <c r="B114" s="39" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="E114" s="39"/>
       <c r="F114" s="40"/>
     </row>
     <row r="115" spans="2:2">
       <c r="B115" s="39" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="120" spans="2:2">
       <c r="B120" s="42" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="121" ht="263.5" spans="5:5">
       <c r="E121" s="40" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="122" spans="2:2">
       <c r="B122" s="39" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="124" s="37" customFormat="1" spans="1:5">
@@ -8875,7 +8907,7 @@
         <v>3</v>
       </c>
       <c r="B124" s="42" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C124" s="42"/>
       <c r="D124" s="42"/>
@@ -8883,174 +8915,174 @@
     </row>
     <row r="125" ht="62" spans="5:5">
       <c r="E125" s="40" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="127" ht="108.5" spans="5:5">
       <c r="E127" s="40" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="129" spans="3:3">
       <c r="C129" s="42" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="130" spans="3:3">
       <c r="C130" s="39" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
     <row r="131" spans="3:3">
       <c r="C131" s="42" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="132" spans="2:5">
       <c r="B132" s="42" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C132" s="42"/>
       <c r="D132" s="42" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="E132" s="42" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="133" spans="2:5">
       <c r="B133" s="39" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="D133" s="39" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="E133" s="39" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
     <row r="134" spans="2:5">
       <c r="B134" s="39" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="D134" s="39" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="E134" s="39" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="135" spans="2:5">
       <c r="B135" s="39" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="D135" s="39" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="E135" s="39" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="136" spans="2:5">
       <c r="B136" s="39" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="D136" s="39" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="E136" s="39" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="137" spans="2:5">
       <c r="B137" s="39" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="D137" s="39" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="E137" s="39" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="138" spans="2:5">
       <c r="B138" s="39" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="D138" s="39" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="E138" s="39" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="139" spans="2:5">
       <c r="B139" s="39" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="D139" s="39" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="E139" s="39" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="140" spans="2:5">
       <c r="B140" s="39" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="D140" s="39" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="E140" s="39" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
     </row>
     <row r="141" spans="2:5">
       <c r="B141" s="39" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="D141" s="39" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="E141" s="39" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
     </row>
     <row r="142" spans="2:5">
       <c r="B142" s="39" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="D142" s="39" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="E142" s="39" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="143" ht="46.5" spans="5:5">
       <c r="E143" s="40" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
     </row>
     <row r="144" spans="2:2">
       <c r="B144" s="39" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="145" spans="2:2">
       <c r="B145" s="39" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
     </row>
     <row r="146" spans="2:2">
       <c r="B146" s="39" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
     </row>
     <row r="147" spans="2:2">
       <c r="B147" s="39" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
     </row>
     <row r="148" customFormat="1" spans="1:5">
@@ -9079,7 +9111,7 @@
         <v>4</v>
       </c>
       <c r="B151" s="42" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C151" s="42"/>
       <c r="D151" s="42"/>
@@ -9087,37 +9119,37 @@
     </row>
     <row r="152" spans="2:2">
       <c r="B152" s="39" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
     </row>
     <row r="153" spans="2:2">
       <c r="B153" s="39" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
     </row>
     <row r="154" spans="2:2">
       <c r="B154" s="39" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
     </row>
     <row r="155" ht="46.5" spans="5:5">
       <c r="E155" s="40" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="156" ht="62" spans="5:5">
       <c r="E156" s="40" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
     </row>
     <row r="157" ht="31" spans="5:5">
       <c r="E157" s="40" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
     </row>
     <row r="158" spans="5:5">
       <c r="E158" s="40" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -9125,143 +9157,143 @@
         <v>6</v>
       </c>
       <c r="B160" s="42" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
     </row>
     <row r="161" ht="31" spans="5:5">
       <c r="E161" s="40" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
     </row>
     <row r="162" ht="17.5" spans="5:5">
       <c r="E162" s="47" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
     </row>
     <row r="163" spans="3:3">
       <c r="C163" s="39" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
     </row>
     <row r="164" spans="3:3">
       <c r="C164" s="39" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
     </row>
     <row r="166" ht="139.5" spans="5:5">
       <c r="E166" s="40" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
     </row>
     <row r="167" ht="31" spans="5:5">
       <c r="E167" s="40" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
     </row>
     <row r="169" spans="2:5">
       <c r="B169" s="42" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C169" s="42"/>
       <c r="D169" s="42"/>
       <c r="E169" s="46" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="170" ht="31" spans="2:5">
       <c r="B170" s="39" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="E170" s="40" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="171" ht="31" spans="2:5">
       <c r="B171" s="39" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="E171" s="40" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="172" ht="31" spans="2:5">
       <c r="B172" s="39" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="E172" s="40" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="173" spans="2:2">
       <c r="B173" s="39" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="174" ht="31" spans="2:5">
       <c r="B174" s="39" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="E174" s="40" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="175" spans="2:2">
       <c r="B175" s="39" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="176" spans="2:5">
       <c r="B176" s="39" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="E176" s="40" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
     <row r="177" spans="2:5">
       <c r="B177" s="39" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="E177" s="40" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
     </row>
     <row r="178" ht="31" spans="2:5">
       <c r="B178" s="39" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="E178" s="40" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
     </row>
     <row r="180" ht="124" spans="5:5">
       <c r="E180" s="40" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
     </row>
     <row r="182" spans="4:4">
       <c r="D182" s="42" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
     </row>
     <row r="183" ht="232.5" spans="5:5">
       <c r="E183" s="40" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
     </row>
     <row r="185" spans="4:4">
       <c r="D185" s="42" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
     </row>
     <row r="186" ht="62" spans="5:5">
       <c r="E186" s="40" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
     </row>
     <row r="188" spans="2:2">
       <c r="B188" s="39" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
     </row>
     <row r="189" spans="1:2">
@@ -9269,12 +9301,12 @@
         <v>7</v>
       </c>
       <c r="B189" s="42" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
     </row>
     <row r="190" spans="2:4">
       <c r="B190" s="42" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C190" s="42"/>
       <c r="D190" s="42"/>
@@ -9284,13 +9316,13 @@
       <c r="C191" s="42"/>
       <c r="D191" s="42"/>
       <c r="E191" s="40" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
     </row>
     <row r="192" spans="2:4">
       <c r="B192" s="42"/>
       <c r="C192" s="42" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="D192" s="42"/>
     </row>
@@ -9299,7 +9331,7 @@
       <c r="C193" s="42"/>
       <c r="D193" s="42"/>
       <c r="E193" s="40" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
     </row>
     <row r="194" spans="2:4">
@@ -9312,7 +9344,7 @@
       <c r="C195" s="42"/>
       <c r="D195" s="42"/>
       <c r="E195" s="40" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
     </row>
     <row r="196" spans="2:4">
@@ -9323,7 +9355,7 @@
     <row r="197" spans="2:4">
       <c r="B197" s="42"/>
       <c r="C197" s="42" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="D197" s="42"/>
     </row>
@@ -9332,7 +9364,7 @@
       <c r="C198" s="42"/>
       <c r="D198" s="42"/>
       <c r="E198" s="40" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
     </row>
     <row r="199" spans="2:4">
@@ -9345,7 +9377,7 @@
       <c r="C200" s="42"/>
       <c r="D200" s="42"/>
       <c r="E200" s="40" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
     </row>
     <row r="201" spans="2:4">
@@ -9358,7 +9390,7 @@
       <c r="C202" s="42"/>
       <c r="D202" s="42"/>
       <c r="E202" s="40" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
     </row>
     <row r="203" spans="2:4">
@@ -9370,7 +9402,7 @@
       <c r="B204" s="42"/>
       <c r="C204" s="42"/>
       <c r="D204" s="42" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
     </row>
     <row r="205" ht="31" spans="2:5">
@@ -9378,7 +9410,7 @@
       <c r="C205" s="42"/>
       <c r="D205" s="42"/>
       <c r="E205" s="40" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
     </row>
     <row r="206" spans="2:5">
@@ -9386,7 +9418,7 @@
       <c r="C206" s="42"/>
       <c r="D206" s="42"/>
       <c r="E206" s="40" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
     </row>
     <row r="207" spans="2:5">
@@ -9394,7 +9426,7 @@
       <c r="C207" s="42"/>
       <c r="D207" s="42"/>
       <c r="E207" s="40" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
     </row>
     <row r="209" spans="1:2">
@@ -9402,7 +9434,7 @@
         <v>8</v>
       </c>
       <c r="B209" s="39" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
     </row>
     <row r="211" spans="1:2">
@@ -9410,7 +9442,7 @@
         <v>9</v>
       </c>
       <c r="B211" s="39" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
     </row>
   </sheetData>
@@ -9432,424 +9464,424 @@
   <sheetData>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="30" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="30" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
     </row>
     <row r="11" spans="2:2">
       <c r="B11" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
     </row>
     <row r="12" spans="2:2">
       <c r="B12" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="30" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="30" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
     </row>
     <row r="20" spans="2:2">
       <c r="B20" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="30" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
     </row>
     <row r="25" hidden="1" spans="1:1">
       <c r="A25" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
     </row>
     <row r="26" hidden="1" spans="1:1">
       <c r="A26" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
     </row>
     <row r="27" hidden="1" spans="1:1">
       <c r="A27" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
     </row>
     <row r="28" hidden="1" spans="1:1">
       <c r="A28" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
     </row>
     <row r="29" hidden="1" spans="2:2">
       <c r="B29" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
     </row>
     <row r="30" hidden="1" spans="1:1">
       <c r="A30" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="30" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
     </row>
     <row r="34" hidden="1" spans="1:1">
       <c r="A34" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="35" hidden="1" spans="1:1">
       <c r="A35" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
     </row>
     <row r="36" hidden="1" spans="1:1">
       <c r="A36" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="37" hidden="1" spans="1:1">
       <c r="A37" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
     </row>
     <row r="38" hidden="1" spans="1:1">
       <c r="A38" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
     </row>
     <row r="39" hidden="1" spans="1:1">
       <c r="A39" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
     </row>
     <row r="40" hidden="1" spans="1:1">
       <c r="A40" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
     </row>
     <row r="41" hidden="1" spans="1:1">
       <c r="A41" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
     </row>
     <row r="42" hidden="1" spans="1:1">
       <c r="A42" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
     </row>
     <row r="43" hidden="1" spans="1:1">
       <c r="A43" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
     </row>
     <row r="44" hidden="1" spans="1:1">
       <c r="A44" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
     </row>
     <row r="45" hidden="1" spans="1:1">
       <c r="A45" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
     </row>
     <row r="46" hidden="1" spans="1:1">
       <c r="A46" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
     </row>
     <row r="47" hidden="1" spans="1:1">
       <c r="A47" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
     </row>
     <row r="48" hidden="1" spans="1:1">
       <c r="A48" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
     </row>
     <row r="49" hidden="1" spans="1:1">
       <c r="A49" s="31" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
     </row>
     <row r="50" hidden="1" spans="1:1">
       <c r="A50" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
     </row>
     <row r="51" hidden="1" spans="1:1">
       <c r="A51" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
     </row>
     <row r="52" hidden="1" spans="1:1">
       <c r="A52" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
     </row>
     <row r="53" hidden="1" spans="1:1">
       <c r="A53" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="30" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
     </row>
     <row r="57" hidden="1" spans="1:1">
       <c r="A57" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
     </row>
     <row r="58" hidden="1" spans="1:1">
       <c r="A58" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
     </row>
     <row r="59" hidden="1" spans="1:1">
       <c r="A59" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
     </row>
     <row r="60" hidden="1"/>
     <row r="61" hidden="1" spans="1:1">
       <c r="A61" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
     </row>
     <row r="62" hidden="1" spans="1:1">
       <c r="A62" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
     </row>
     <row r="63" hidden="1" spans="1:1">
       <c r="A63" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="30" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
     </row>
     <row r="68" hidden="1" spans="1:1">
       <c r="A68" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
     </row>
     <row r="69" hidden="1" spans="1:1">
       <c r="A69" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
     </row>
     <row r="70" hidden="1" spans="1:1">
       <c r="A70" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
     </row>
     <row r="71" hidden="1" spans="1:1">
       <c r="A71" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
     </row>
     <row r="72" hidden="1" spans="1:1">
       <c r="A72" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
     </row>
     <row r="73" hidden="1" spans="1:1">
       <c r="A73" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
     </row>
     <row r="74" hidden="1" spans="1:1">
       <c r="A74" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="75" hidden="1" spans="1:1">
       <c r="A75" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
     </row>
     <row r="76" hidden="1" spans="1:1">
       <c r="A76" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="30" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
     </row>
     <row r="81" hidden="1" spans="1:1">
       <c r="A81" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
     </row>
     <row r="82" hidden="1" spans="1:1">
       <c r="A82" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
     </row>
     <row r="83" hidden="1" spans="1:1">
       <c r="A83" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
     </row>
     <row r="84" hidden="1" spans="1:1">
       <c r="A84" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
     </row>
     <row r="85" hidden="1" spans="1:1">
       <c r="A85" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
     </row>
     <row r="86" hidden="1" spans="1:1">
       <c r="A86" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
     </row>
     <row r="87" hidden="1" spans="1:1">
       <c r="A87" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
     </row>
     <row r="88" hidden="1" spans="1:1">
       <c r="A88" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
     </row>
     <row r="89" hidden="1" spans="1:1">
       <c r="A89" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
     </row>
     <row r="90" hidden="1" spans="1:1">
       <c r="A90" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
     </row>
     <row r="91" hidden="1" spans="1:1">
       <c r="A91" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
     </row>
     <row r="92" hidden="1" spans="1:1">
       <c r="A92" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
     </row>
     <row r="93" hidden="1" spans="1:1">
       <c r="A93" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
     </row>
     <row r="94" hidden="1"/>
     <row r="95" hidden="1" spans="1:1">
       <c r="A95" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
     </row>
     <row r="96" hidden="1" spans="1:1">
       <c r="A96" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -9858,19 +9890,19 @@
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="33" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B98" s="32"/>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="34" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B99" s="32"/>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="34" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B100" s="32"/>
     </row>
@@ -9883,12 +9915,12 @@
     </row>
     <row r="104" spans="1:1">
       <c r="A104" s="36" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
     </row>
     <row r="105" spans="1:1">
       <c r="A105" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
     </row>
   </sheetData>
@@ -9916,7 +9948,7 @@
   <sheetData>
     <row r="1" spans="2:2">
       <c r="B1" s="23" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -9941,133 +9973,133 @@
     </row>
     <row r="4" spans="2:2">
       <c r="B4" s="23" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="5" ht="15.5" spans="3:3">
       <c r="C5" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
     </row>
     <row r="6" ht="15.5" spans="3:4">
       <c r="C6" s="23"/>
       <c r="D6" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
     </row>
     <row r="7" ht="15.5" spans="3:3">
       <c r="C7" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
     </row>
     <row r="8" ht="15.5" spans="3:3">
       <c r="C8" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
     </row>
     <row r="9" ht="15.5" spans="1:4">
       <c r="A9" s="25"/>
       <c r="C9" s="23"/>
       <c r="D9" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="10" ht="15.5" spans="3:4">
       <c r="C10" s="23"/>
       <c r="D10" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
     </row>
     <row r="11" ht="15.5" spans="3:4">
       <c r="C11" s="23"/>
       <c r="D11" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
     </row>
     <row r="12" ht="15.5" spans="3:4">
       <c r="C12" s="23"/>
       <c r="D12" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
     </row>
     <row r="13" ht="15.5" spans="3:4">
       <c r="C13" s="23"/>
       <c r="D13" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
     </row>
     <row r="14" ht="15.5" spans="3:3">
       <c r="C14" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
     </row>
     <row r="15" ht="15.5" spans="3:4">
       <c r="C15" s="23"/>
       <c r="D15" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
     </row>
     <row r="16" ht="15.5" spans="3:4">
       <c r="C16" s="23"/>
       <c r="D16" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
     </row>
     <row r="17" ht="15.5" spans="3:4">
       <c r="C17" s="23"/>
       <c r="D17" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
     </row>
     <row r="18" ht="15.5" spans="3:4">
       <c r="C18" s="23"/>
       <c r="D18" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
     </row>
     <row r="19" ht="15.5" spans="3:4">
       <c r="C19" s="23"/>
       <c r="D19" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
     </row>
     <row r="20" ht="15.5" spans="3:3">
       <c r="C20" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
     </row>
     <row r="21" ht="15.5" spans="3:3">
       <c r="C21" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
     </row>
     <row r="22" ht="15.5" spans="3:4">
       <c r="C22" s="23"/>
       <c r="D22" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
     </row>
     <row r="23" ht="15.5" spans="3:4">
       <c r="C23" s="23"/>
       <c r="D23" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
     </row>
     <row r="24" ht="15.5" spans="3:3">
       <c r="C24" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
     </row>
     <row r="29" spans="3:3">
       <c r="C29" s="22" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="26"/>
       <c r="B30" s="27"/>
       <c r="D30" s="22" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -10162,7 +10194,7 @@
   <sheetData>
     <row r="3" spans="1:1">
       <c r="A3" s="21" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
     </row>
   </sheetData>
@@ -10179,902 +10211,902 @@
   <sheetData>
     <row r="2" spans="2:3">
       <c r="B2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="3" spans="2:3">
       <c r="B3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4" spans="2:3">
       <c r="B4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5" spans="2:3">
       <c r="B5" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="C5" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="6" spans="2:2">
       <c r="B6" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
     </row>
     <row r="8" spans="2:3">
       <c r="B8" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="9" spans="2:2">
       <c r="B9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="11" spans="2:3">
       <c r="B11" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C11" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="12" spans="2:3">
       <c r="B12" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C12" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="13" spans="2:3">
       <c r="B13" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C13" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="14" spans="2:2">
       <c r="B14" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="16" spans="2:3">
       <c r="B16" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C16" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="17" spans="2:2">
       <c r="B17" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="19" spans="2:3">
       <c r="B19" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C19" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="20" spans="2:3">
       <c r="B20" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C20" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="21" spans="2:3">
       <c r="B21" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C21" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="22" spans="2:3">
       <c r="B22" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C22" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="23" spans="2:3">
       <c r="B23" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C23" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="24" spans="2:3">
       <c r="B24" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C24" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="25" spans="2:3">
       <c r="B25" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C25" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="26" spans="2:3">
       <c r="B26" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C26" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="27" spans="2:3">
       <c r="B27" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C27" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="28" spans="2:3">
       <c r="B28" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C28" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="29" spans="2:3">
       <c r="B29" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C29" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="30" spans="2:3">
       <c r="B30" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C30" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="31" spans="2:3">
       <c r="B31" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C31" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="32" spans="2:3">
       <c r="B32" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C32" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="33" spans="2:3">
       <c r="B33" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C33" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="34" spans="2:3">
       <c r="B34" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C34" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="35" spans="2:3">
       <c r="B35" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C35" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="36" spans="2:3">
       <c r="B36" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C36" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="37" spans="2:3">
       <c r="B37" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C37" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="38" spans="2:3">
       <c r="B38" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C38" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="39" spans="2:2">
       <c r="B39" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="41" spans="2:3">
       <c r="B41" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C41" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="42" spans="2:3">
       <c r="B42" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C42" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="43" spans="2:3">
       <c r="B43" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C43" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="44" spans="2:3">
       <c r="B44" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C44" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="45" spans="2:3">
       <c r="B45" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C45" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="46" spans="2:3">
       <c r="B46" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C46" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="47" spans="2:3">
       <c r="B47" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C47" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="48" spans="2:3">
       <c r="B48" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C48" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="49" spans="2:3">
       <c r="B49" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C49" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="50" spans="2:3">
       <c r="B50" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C50" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="51" spans="2:3">
       <c r="B51" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C51" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="52" spans="2:3">
       <c r="B52" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C52" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="53" spans="2:3">
       <c r="B53" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C53" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="54" spans="2:3">
       <c r="B54" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C54" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="55" spans="2:3">
       <c r="B55" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C55" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="56" spans="2:2">
       <c r="B56" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="58" spans="2:3">
       <c r="B58" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C58" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="59" spans="2:2">
       <c r="B59" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="61" spans="2:3">
       <c r="B61" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C61" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="62" spans="2:3">
       <c r="B62" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C62" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="63" spans="2:2">
       <c r="B63" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="65" spans="2:3">
       <c r="B65" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C65" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="66" spans="2:3">
       <c r="B66" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C66" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="67" spans="2:2">
       <c r="B67" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="69" spans="2:3">
       <c r="B69" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C69" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="70" spans="2:3">
       <c r="B70" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C70" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="71" spans="2:3">
       <c r="B71" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C71" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="72" spans="2:3">
       <c r="B72" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C72" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="73" spans="2:3">
       <c r="B73" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C73" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="74" spans="2:3">
       <c r="B74" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C74" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="75" spans="2:3">
       <c r="B75" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C75" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="76" spans="2:3">
       <c r="B76" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C76" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="77" spans="2:3">
       <c r="B77" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C77" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="78" spans="2:3">
       <c r="B78" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C78" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="79" spans="2:3">
       <c r="B79" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C79" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="80" spans="2:3">
       <c r="B80" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C80" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="81" spans="2:3">
       <c r="B81" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C81" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="82" spans="2:3">
       <c r="B82" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C82" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="83" spans="2:3">
       <c r="B83" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C83" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="84" spans="2:3">
       <c r="B84" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C84" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="85" spans="2:3">
       <c r="B85" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C85" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="86" spans="2:3">
       <c r="B86" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C86" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="87" spans="2:3">
       <c r="B87" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C87" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="88" spans="2:3">
       <c r="B88" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C88" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="89" spans="2:2">
       <c r="B89" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="91" spans="2:3">
       <c r="B91" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C91" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="92" spans="2:3">
       <c r="B92" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C92" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="93" spans="2:3">
       <c r="B93" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C93" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="94" spans="2:3">
       <c r="B94" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C94" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="95" spans="2:3">
       <c r="B95" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C95" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="96" spans="2:3">
       <c r="B96" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C96" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="97" spans="2:3">
       <c r="B97" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C97" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="98" spans="2:3">
       <c r="B98" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C98" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="99" spans="2:3">
       <c r="B99" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C99" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="100" spans="2:3">
       <c r="B100" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C100" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="101" spans="2:3">
       <c r="B101" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C101" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="102" spans="2:3">
       <c r="B102" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C102" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="103" spans="2:3">
       <c r="B103" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C103" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="104" spans="2:3">
       <c r="B104" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C104" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="105" spans="2:3">
       <c r="B105" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C105" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="106" spans="2:3">
       <c r="B106" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C106" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="107" spans="2:3">
       <c r="B107" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C107" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="108" spans="2:2">
       <c r="B108" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="110" spans="2:3">
       <c r="B110" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C110" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="111" spans="2:2">
       <c r="B111" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="113" spans="2:3">
       <c r="B113" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C113" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="114" spans="2:3">
       <c r="B114" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C114" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="115" spans="2:3">
       <c r="B115" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C115" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="116" spans="2:3">
       <c r="B116" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C116" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="117" spans="2:3">
       <c r="B117" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C117" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="118" spans="2:3">
       <c r="B118" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C118" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="119" spans="2:3">
       <c r="B119" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C119" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="120" spans="2:3">
       <c r="B120" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C120" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="121" spans="2:3">
       <c r="B121" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C121" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="122" spans="2:3">
       <c r="B122" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C122" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="123" spans="2:3">
       <c r="B123" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C123" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="124" spans="2:3">
       <c r="B124" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C124" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="125" spans="2:3">
       <c r="B125" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C125" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="126" spans="2:3">
       <c r="B126" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C126" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="127" spans="2:3">
       <c r="B127" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C127" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="128" spans="2:3">
       <c r="B128" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C128" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="129" spans="2:3">
       <c r="B129" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C129" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="130" spans="2:3">
       <c r="B130" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C130" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
   </sheetData>
@@ -11097,7 +11129,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="2" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
     </row>
     <row r="2" hidden="1" spans="2:4">
@@ -11105,7 +11137,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
     </row>
     <row r="3" hidden="1" spans="2:4">
@@ -11113,7 +11145,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
     </row>
     <row r="4" hidden="1" spans="2:4">
@@ -11121,7 +11153,7 @@
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
     </row>
     <row r="5" hidden="1" spans="2:4">
@@ -11129,7 +11161,7 @@
         <v>4</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
     </row>
     <row r="6" hidden="1" spans="2:4">
@@ -11137,7 +11169,7 @@
         <v>5</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
     </row>
     <row r="7" hidden="1" spans="2:4">
@@ -11145,7 +11177,7 @@
         <v>6</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
     </row>
     <row r="8" hidden="1" spans="2:4">
@@ -11153,12 +11185,12 @@
         <v>7</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="2" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
     </row>
     <row r="12" ht="64" hidden="1" customHeight="1" spans="1:5">
@@ -11166,7 +11198,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
@@ -11177,7 +11209,7 @@
         <v>2</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
@@ -11188,7 +11220,7 @@
         <v>3</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
@@ -11199,7 +11231,7 @@
         <v>4</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
@@ -11210,7 +11242,7 @@
         <v>5</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
@@ -11221,7 +11253,7 @@
         <v>6</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
@@ -11237,7 +11269,7 @@
     <row r="19" ht="16" customHeight="1" spans="1:5">
       <c r="A19" s="4"/>
       <c r="B19" s="7" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
@@ -11245,24 +11277,24 @@
     </row>
     <row r="20" spans="2:2">
       <c r="B20" s="1" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
     </row>
     <row r="21" spans="2:2">
       <c r="B21" s="1" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
     </row>
     <row r="22" spans="2:2">
       <c r="B22" s="2" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
     </row>
     <row r="23" ht="31" spans="2:4">
       <c r="B23" s="2"/>
       <c r="C23" s="8"/>
       <c r="D23" s="8" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
     </row>
     <row r="24" spans="2:2">
@@ -11270,14 +11302,14 @@
     </row>
     <row r="25" spans="2:2">
       <c r="B25" s="2" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
     </row>
     <row r="26" spans="2:4">
       <c r="B26" s="2"/>
       <c r="C26" s="8"/>
       <c r="D26" s="8" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
     </row>
     <row r="27" spans="2:4">
@@ -11287,14 +11319,14 @@
     </row>
     <row r="28" spans="2:2">
       <c r="B28" s="2" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
     </row>
     <row r="29" spans="2:4">
       <c r="B29" s="2"/>
       <c r="C29" s="8"/>
       <c r="D29" s="8" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
     </row>
     <row r="30" spans="2:2">
@@ -11302,28 +11334,28 @@
     </row>
     <row r="31" spans="2:2">
       <c r="B31" s="2" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="32" hidden="1" spans="2:4">
       <c r="B32" s="2"/>
       <c r="C32" s="8"/>
       <c r="D32" s="8" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
     </row>
     <row r="33" ht="27" hidden="1" customHeight="1" spans="2:4">
       <c r="B33" s="2"/>
       <c r="C33" s="8"/>
       <c r="D33" s="8" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
     </row>
     <row r="34" ht="27" hidden="1" customHeight="1" spans="2:4">
       <c r="B34" s="2"/>
       <c r="C34" s="8"/>
       <c r="D34" s="8" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
     </row>
     <row r="35" ht="16" hidden="1" customHeight="1" spans="2:4">
@@ -11333,28 +11365,28 @@
     </row>
     <row r="36" hidden="1" spans="2:2">
       <c r="B36" s="2" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="37" ht="31" hidden="1" spans="2:4">
       <c r="B37" s="2"/>
       <c r="C37" s="8"/>
       <c r="D37" s="8" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
     </row>
     <row r="38" ht="46.5" hidden="1" spans="2:4">
       <c r="B38" s="2"/>
       <c r="C38" s="8"/>
       <c r="D38" s="8" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
     </row>
     <row r="39" ht="31" hidden="1" spans="2:4">
       <c r="B39" s="2"/>
       <c r="C39" s="8"/>
       <c r="D39" s="8" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
     </row>
     <row r="40" hidden="1" spans="2:4">
@@ -11364,28 +11396,28 @@
     </row>
     <row r="41" hidden="1" spans="2:2">
       <c r="B41" s="2" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
     </row>
     <row r="42" hidden="1" spans="2:4">
       <c r="B42" s="2"/>
       <c r="C42" s="8"/>
       <c r="D42" s="8" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
     </row>
     <row r="43" ht="31" hidden="1" spans="2:4">
       <c r="B43" s="2"/>
       <c r="C43" s="8"/>
       <c r="D43" s="8" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
     </row>
     <row r="44" ht="62" hidden="1" spans="2:4">
       <c r="B44" s="2"/>
       <c r="C44" s="8"/>
       <c r="D44" s="8" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
     </row>
     <row r="45" hidden="1" spans="2:4">
@@ -11395,28 +11427,28 @@
     </row>
     <row r="46" hidden="1" spans="2:2">
       <c r="B46" s="2" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="47" hidden="1" spans="2:4">
       <c r="B47" s="2"/>
       <c r="C47" s="8"/>
       <c r="D47" s="8" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
     </row>
     <row r="48" ht="31" hidden="1" spans="2:4">
       <c r="B48" s="2"/>
       <c r="C48" s="8"/>
       <c r="D48" s="8" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
     </row>
     <row r="49" ht="46.5" hidden="1" spans="2:4">
       <c r="B49" s="2"/>
       <c r="C49" s="8"/>
       <c r="D49" s="8" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
     </row>
     <row r="50" hidden="1" spans="2:4">
@@ -11426,21 +11458,21 @@
     </row>
     <row r="51" hidden="1" spans="2:2">
       <c r="B51" s="2" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
     </row>
     <row r="52" hidden="1" spans="2:4">
       <c r="B52" s="2"/>
       <c r="C52" s="8"/>
       <c r="D52" s="8" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
     </row>
     <row r="53" ht="31" hidden="1" spans="2:4">
       <c r="B53" s="2"/>
       <c r="C53" s="8"/>
       <c r="D53" s="8" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
     </row>
     <row r="54" hidden="1" spans="2:4">
@@ -11450,14 +11482,14 @@
     </row>
     <row r="55" hidden="1" spans="2:2">
       <c r="B55" s="2" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
     </row>
     <row r="56" hidden="1" spans="2:4">
       <c r="B56" s="2"/>
       <c r="C56" s="8"/>
       <c r="D56" s="8" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
     </row>
     <row r="57" hidden="1" spans="2:4">
@@ -11467,35 +11499,35 @@
     </row>
     <row r="58" hidden="1" spans="2:2">
       <c r="B58" s="2" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
     </row>
     <row r="59" hidden="1" spans="2:4">
       <c r="B59" s="2"/>
       <c r="C59" s="8"/>
       <c r="D59" s="8" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
     </row>
     <row r="60" ht="31" hidden="1" spans="2:4">
       <c r="B60" s="2"/>
       <c r="C60" s="9"/>
       <c r="D60" s="9" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
     </row>
     <row r="61" hidden="1" spans="2:4">
       <c r="B61" s="2"/>
       <c r="C61" s="9"/>
       <c r="D61" s="9" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
     </row>
     <row r="62" ht="87.5" hidden="1" spans="2:4">
       <c r="B62" s="2"/>
       <c r="C62" s="10"/>
       <c r="D62" s="10" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
     </row>
     <row r="63" hidden="1" spans="3:4">
@@ -11505,25 +11537,25 @@
     <row r="64" ht="17.5" hidden="1" spans="3:4">
       <c r="C64" s="11"/>
       <c r="D64" s="11" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
     </row>
     <row r="65" ht="70" hidden="1" spans="3:4">
       <c r="C65" s="12"/>
       <c r="D65" s="12" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
     </row>
     <row r="66" ht="35" hidden="1" spans="3:4">
       <c r="C66" s="12"/>
       <c r="D66" s="12" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
     </row>
     <row r="67" ht="87.5" hidden="1" spans="3:4">
       <c r="C67" s="12"/>
       <c r="D67" s="12" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
     </row>
     <row r="68" ht="17.5" hidden="1" spans="3:4">
@@ -11532,18 +11564,18 @@
     </row>
     <row r="69" hidden="1" spans="2:2">
       <c r="B69" s="2" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
     </row>
     <row r="70" hidden="1" spans="3:4">
       <c r="C70" s="8"/>
       <c r="D70" s="8" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="7" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -11551,28 +11583,28 @@
         <v>1</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
     </row>
     <row r="75" ht="46.5" hidden="1" spans="2:4">
       <c r="B75" s="2"/>
       <c r="C75" s="13"/>
       <c r="D75" s="13" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
     </row>
     <row r="76" hidden="1" spans="2:4">
       <c r="B76" s="2"/>
       <c r="C76" s="14"/>
       <c r="D76" s="14" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
     </row>
     <row r="77" ht="46.5" hidden="1" spans="2:4">
       <c r="B77" s="2"/>
       <c r="C77" s="13"/>
       <c r="D77" s="13" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
     </row>
     <row r="78" hidden="1" spans="2:4">
@@ -11584,7 +11616,7 @@
       <c r="B79" s="15"/>
       <c r="C79" s="9"/>
       <c r="D79" s="9" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
     </row>
     <row r="80" hidden="1" spans="2:4">
@@ -11596,63 +11628,63 @@
       <c r="B81" s="15"/>
       <c r="C81" s="9"/>
       <c r="D81" s="9" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
     </row>
     <row r="82" hidden="1" spans="2:4">
       <c r="B82" s="15"/>
       <c r="C82" s="9"/>
       <c r="D82" s="9" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
     </row>
     <row r="83" hidden="1" spans="2:4">
       <c r="B83" s="15"/>
       <c r="C83" s="9"/>
       <c r="D83" s="9" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
     </row>
     <row r="84" hidden="1" spans="2:4">
       <c r="B84" s="15"/>
       <c r="C84" s="9"/>
       <c r="D84" s="9" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
     </row>
     <row r="85" hidden="1" spans="2:4">
       <c r="B85" s="15"/>
       <c r="C85" s="9"/>
       <c r="D85" s="9" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
     </row>
     <row r="86" ht="31" hidden="1" spans="2:4">
       <c r="B86" s="15"/>
       <c r="C86" s="9"/>
       <c r="D86" s="9" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
     </row>
     <row r="87" hidden="1" spans="2:4">
       <c r="B87" s="15"/>
       <c r="C87" s="9"/>
       <c r="D87" s="9" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
     </row>
     <row r="88" hidden="1" spans="2:4">
       <c r="B88" s="15"/>
       <c r="C88" s="9"/>
       <c r="D88" s="9" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
     </row>
     <row r="89" hidden="1" spans="2:4">
       <c r="B89" s="15"/>
       <c r="C89" s="9"/>
       <c r="D89" s="9" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
     </row>
     <row r="90" hidden="1" spans="2:4">
@@ -11664,14 +11696,14 @@
       <c r="B91" s="15"/>
       <c r="C91" s="9"/>
       <c r="D91" s="9" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
     </row>
     <row r="92" hidden="1" spans="2:4">
       <c r="B92" s="15"/>
       <c r="C92" s="9"/>
       <c r="D92" s="9" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
     </row>
     <row r="93" hidden="1" spans="2:4">
@@ -11683,14 +11715,14 @@
       <c r="B94" s="15"/>
       <c r="C94" s="9"/>
       <c r="D94" s="9" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
     </row>
     <row r="95" hidden="1" spans="2:4">
       <c r="B95" s="15"/>
       <c r="C95" s="9"/>
       <c r="D95" s="9" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
     </row>
     <row r="96" hidden="1" spans="2:4">
@@ -11702,14 +11734,14 @@
       <c r="B97" s="15"/>
       <c r="C97" s="9"/>
       <c r="D97" s="9" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
     </row>
     <row r="98" ht="46.5" hidden="1" spans="2:4">
       <c r="B98" s="15"/>
       <c r="C98" s="9"/>
       <c r="D98" s="9" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
     </row>
     <row r="99" hidden="1" spans="2:4">
@@ -11722,14 +11754,14 @@
         <v>2</v>
       </c>
       <c r="B100" s="17" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
     </row>
     <row r="101" ht="31" hidden="1" spans="2:4">
       <c r="B101" s="15"/>
       <c r="C101" s="13"/>
       <c r="D101" s="13" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
     </row>
     <row r="102" hidden="1" spans="2:2">
@@ -11739,14 +11771,14 @@
       <c r="B103" s="15"/>
       <c r="C103" s="14"/>
       <c r="D103" s="14" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
     </row>
     <row r="104" ht="31" hidden="1" spans="2:4">
       <c r="B104" s="15"/>
       <c r="C104" s="13"/>
       <c r="D104" s="13" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
     </row>
     <row r="105" hidden="1" spans="2:4">
@@ -11758,14 +11790,14 @@
       <c r="B106" s="15"/>
       <c r="C106" s="9"/>
       <c r="D106" s="9" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
     </row>
     <row r="107" hidden="1" spans="2:4">
       <c r="B107" s="15"/>
       <c r="C107" s="9"/>
       <c r="D107" s="9" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
     </row>
     <row r="108" hidden="1" spans="2:4">
@@ -11777,28 +11809,28 @@
       <c r="B109" s="15"/>
       <c r="C109" s="9"/>
       <c r="D109" s="9" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
     </row>
     <row r="110" hidden="1" spans="2:4">
       <c r="B110" s="15"/>
       <c r="C110" s="9"/>
       <c r="D110" s="9" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
     </row>
     <row r="111" hidden="1" spans="2:4">
       <c r="B111" s="15"/>
       <c r="C111" s="9"/>
       <c r="D111" s="9" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
     </row>
     <row r="112" hidden="1" spans="2:4">
       <c r="B112" s="15"/>
       <c r="C112" s="9"/>
       <c r="D112" s="9" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
     </row>
     <row r="113" hidden="1" spans="2:4">
@@ -11810,14 +11842,14 @@
       <c r="B114" s="15"/>
       <c r="C114" s="9"/>
       <c r="D114" s="9" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
     </row>
     <row r="115" hidden="1" spans="2:4">
       <c r="B115" s="15"/>
       <c r="C115" s="9"/>
       <c r="D115" s="9" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
     </row>
     <row r="116" hidden="1" spans="2:4">
@@ -11829,14 +11861,14 @@
       <c r="B117" s="15"/>
       <c r="C117" s="9"/>
       <c r="D117" s="9" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
     </row>
     <row r="118" hidden="1" spans="2:4">
       <c r="B118" s="15"/>
       <c r="C118" s="9"/>
       <c r="D118" s="9" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
     </row>
     <row r="119" hidden="1" spans="2:4">
@@ -11848,14 +11880,14 @@
       <c r="B120" s="15"/>
       <c r="C120" s="9"/>
       <c r="D120" s="9" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
     </row>
     <row r="121" hidden="1" spans="2:4">
       <c r="B121" s="15"/>
       <c r="C121" s="9"/>
       <c r="D121" s="9" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="122" hidden="1" spans="2:4">
@@ -11867,14 +11899,14 @@
       <c r="B123" s="15"/>
       <c r="C123" s="9"/>
       <c r="D123" s="9" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
     </row>
     <row r="124" hidden="1" spans="2:4">
       <c r="B124" s="15"/>
       <c r="C124" s="9"/>
       <c r="D124" s="9" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
     </row>
     <row r="125" hidden="1" spans="2:4">
@@ -11886,14 +11918,14 @@
       <c r="B126" s="15"/>
       <c r="C126" s="9"/>
       <c r="D126" s="9" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
     </row>
     <row r="127" hidden="1" spans="2:4">
       <c r="B127" s="15"/>
       <c r="C127" s="9"/>
       <c r="D127" s="9" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
     </row>
     <row r="128" hidden="1" spans="2:4">
@@ -11905,14 +11937,14 @@
       <c r="B129" s="15"/>
       <c r="C129" s="9"/>
       <c r="D129" s="9" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
     </row>
     <row r="130" hidden="1" spans="2:4">
       <c r="B130" s="15"/>
       <c r="C130" s="9"/>
       <c r="D130" s="9" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="131" hidden="1" spans="2:4">
@@ -11924,14 +11956,14 @@
       <c r="B132" s="15"/>
       <c r="C132" s="9"/>
       <c r="D132" s="9" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
     </row>
     <row r="133" hidden="1" spans="2:4">
       <c r="B133" s="15"/>
       <c r="C133" s="9"/>
       <c r="D133" s="9" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
     </row>
     <row r="134" hidden="1" spans="2:4">
@@ -11943,14 +11975,14 @@
       <c r="B135" s="15"/>
       <c r="C135" s="9"/>
       <c r="D135" s="9" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
     </row>
     <row r="136" hidden="1" spans="2:4">
       <c r="B136" s="15"/>
       <c r="C136" s="9"/>
       <c r="D136" s="9" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
     </row>
     <row r="137" hidden="1" spans="2:4">
@@ -11963,28 +11995,28 @@
         <v>3</v>
       </c>
       <c r="B138" s="17" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
     </row>
     <row r="139" hidden="1" spans="2:4">
       <c r="B139" s="15"/>
       <c r="C139" s="13"/>
       <c r="D139" s="13" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
     </row>
     <row r="140" hidden="1" spans="2:4">
       <c r="B140" s="15"/>
       <c r="C140" s="14"/>
       <c r="D140" s="14" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
     </row>
     <row r="141" ht="31" hidden="1" spans="2:4">
       <c r="B141" s="15"/>
       <c r="C141" s="13"/>
       <c r="D141" s="13" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
     </row>
     <row r="142" hidden="1" spans="2:4">
@@ -11996,14 +12028,14 @@
       <c r="B143" s="15"/>
       <c r="C143" s="9"/>
       <c r="D143" s="9" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
     </row>
     <row r="144" hidden="1" spans="2:4">
       <c r="B144" s="15"/>
       <c r="C144" s="9"/>
       <c r="D144" s="9" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
     </row>
     <row r="145" hidden="1" spans="2:4">
@@ -12015,14 +12047,14 @@
       <c r="B146" s="15"/>
       <c r="C146" s="9"/>
       <c r="D146" s="9" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
     </row>
     <row r="147" hidden="1" spans="2:4">
       <c r="B147" s="15"/>
       <c r="C147" s="9"/>
       <c r="D147" s="9" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
     </row>
     <row r="148" hidden="1" spans="2:4">
@@ -12034,21 +12066,21 @@
       <c r="B149" s="15"/>
       <c r="C149" s="9"/>
       <c r="D149" s="9" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
     </row>
     <row r="150" hidden="1" spans="2:4">
       <c r="B150" s="15"/>
       <c r="C150" s="9"/>
       <c r="D150" s="9" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
     </row>
     <row r="151" hidden="1" spans="2:4">
       <c r="B151" s="15"/>
       <c r="C151" s="9"/>
       <c r="D151" s="9" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
     </row>
     <row r="152" hidden="1" spans="2:4">
@@ -12060,21 +12092,21 @@
       <c r="B153" s="15"/>
       <c r="C153" s="9"/>
       <c r="D153" s="9" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
     </row>
     <row r="154" hidden="1" spans="2:4">
       <c r="B154" s="15"/>
       <c r="C154" s="9"/>
       <c r="D154" s="9" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="155" hidden="1" spans="2:4">
       <c r="B155" s="15"/>
       <c r="C155" s="9"/>
       <c r="D155" s="9" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
     </row>
     <row r="156" hidden="1" spans="2:4">
@@ -12086,21 +12118,21 @@
       <c r="B157" s="15"/>
       <c r="C157" s="9"/>
       <c r="D157" s="9" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
     </row>
     <row r="158" hidden="1" spans="2:4">
       <c r="B158" s="15"/>
       <c r="C158" s="9"/>
       <c r="D158" s="9" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
     </row>
     <row r="159" hidden="1" spans="2:4">
       <c r="B159" s="15"/>
       <c r="C159" s="9"/>
       <c r="D159" s="9" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
     </row>
     <row r="160" hidden="1" spans="2:4">
@@ -12113,14 +12145,14 @@
         <v>4</v>
       </c>
       <c r="B161" s="17" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="162" hidden="1" spans="2:4">
       <c r="B162" s="15"/>
       <c r="C162" s="13"/>
       <c r="D162" s="13" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="163" hidden="1" spans="2:2">
@@ -12130,14 +12162,14 @@
       <c r="B164" s="15"/>
       <c r="C164" s="14"/>
       <c r="D164" s="14" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
     </row>
     <row r="165" ht="31" hidden="1" spans="2:4">
       <c r="B165" s="15"/>
       <c r="C165" s="13"/>
       <c r="D165" s="13" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="166" hidden="1" spans="2:4">
@@ -12149,14 +12181,14 @@
       <c r="B167" s="15"/>
       <c r="C167" s="9"/>
       <c r="D167" s="9" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="168" hidden="1" spans="2:4">
       <c r="B168" s="15"/>
       <c r="C168" s="9"/>
       <c r="D168" s="9" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="169" hidden="1" spans="2:4">
@@ -12168,14 +12200,14 @@
       <c r="B170" s="15"/>
       <c r="C170" s="9"/>
       <c r="D170" s="9" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="171" hidden="1" spans="2:4">
       <c r="B171" s="15"/>
       <c r="C171" s="9"/>
       <c r="D171" s="9" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="172" hidden="1" spans="2:4">
@@ -12187,14 +12219,14 @@
       <c r="B173" s="15"/>
       <c r="C173" s="9"/>
       <c r="D173" s="9" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="174" hidden="1" spans="2:4">
       <c r="B174" s="15"/>
       <c r="C174" s="9"/>
       <c r="D174" s="9" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="175" hidden="1" spans="2:4">
@@ -12206,14 +12238,14 @@
       <c r="B176" s="15"/>
       <c r="C176" s="9"/>
       <c r="D176" s="9" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="177" hidden="1" spans="2:4">
       <c r="B177" s="15"/>
       <c r="C177" s="9"/>
       <c r="D177" s="9" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="178" hidden="1" spans="2:4">
@@ -12226,14 +12258,14 @@
         <v>5</v>
       </c>
       <c r="B179" s="17" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
     </row>
     <row r="180" hidden="1" spans="2:4">
       <c r="B180" s="15"/>
       <c r="C180" s="13"/>
       <c r="D180" s="13" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="181" hidden="1" spans="2:2">
@@ -12243,14 +12275,14 @@
       <c r="B182" s="15"/>
       <c r="C182" s="14"/>
       <c r="D182" s="14" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
     </row>
     <row r="183" hidden="1" spans="2:4">
       <c r="B183" s="15"/>
       <c r="C183" s="13"/>
       <c r="D183" s="13" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="184" hidden="1" spans="2:4">
@@ -12262,28 +12294,28 @@
       <c r="B185" s="15"/>
       <c r="C185" s="9"/>
       <c r="D185" s="9" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="186" hidden="1" spans="2:4">
       <c r="B186" s="15"/>
       <c r="C186" s="9"/>
       <c r="D186" s="9" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="187" hidden="1" spans="2:4">
       <c r="B187" s="15"/>
       <c r="C187" s="9"/>
       <c r="D187" s="9" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="188" hidden="1" spans="2:4">
       <c r="B188" s="15"/>
       <c r="C188" s="9"/>
       <c r="D188" s="9" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="189" hidden="1" spans="2:4">
@@ -12295,7 +12327,7 @@
       <c r="B190" s="15"/>
       <c r="C190" s="9"/>
       <c r="D190" s="9" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="191" hidden="1" spans="2:4">
@@ -12307,7 +12339,7 @@
       <c r="B192" s="15"/>
       <c r="C192" s="9"/>
       <c r="D192" s="9" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="193" hidden="1" spans="2:4">
@@ -12319,7 +12351,7 @@
       <c r="B194" s="15"/>
       <c r="C194" s="9"/>
       <c r="D194" s="9" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="195" hidden="1" spans="2:4">
@@ -12332,14 +12364,14 @@
         <v>6</v>
       </c>
       <c r="B196" s="17" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="197" hidden="1" spans="2:4">
       <c r="B197" s="15"/>
       <c r="C197" s="13"/>
       <c r="D197" s="13" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="198" hidden="1" spans="2:2">
@@ -12349,14 +12381,14 @@
       <c r="B199" s="15"/>
       <c r="C199" s="14"/>
       <c r="D199" s="14" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
     </row>
     <row r="200" ht="31" hidden="1" spans="2:4">
       <c r="B200" s="15"/>
       <c r="C200" s="13"/>
       <c r="D200" s="13" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="201" hidden="1" spans="2:4">
@@ -12368,14 +12400,14 @@
       <c r="B202" s="15"/>
       <c r="C202" s="9"/>
       <c r="D202" s="9" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="203" hidden="1" spans="2:4">
       <c r="B203" s="15"/>
       <c r="C203" s="9"/>
       <c r="D203" s="9" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="204" hidden="1" spans="2:4">
@@ -12387,14 +12419,14 @@
       <c r="B205" s="15"/>
       <c r="C205" s="9"/>
       <c r="D205" s="9" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="206" hidden="1" spans="2:4">
       <c r="B206" s="15"/>
       <c r="C206" s="9"/>
       <c r="D206" s="9" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="207" hidden="1" spans="2:4">
@@ -12406,14 +12438,14 @@
       <c r="B208" s="15"/>
       <c r="C208" s="9"/>
       <c r="D208" s="9" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="209" ht="31" hidden="1" spans="2:4">
       <c r="B209" s="15"/>
       <c r="C209" s="9"/>
       <c r="D209" s="9" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="210" hidden="1" spans="2:4">
@@ -12426,14 +12458,14 @@
         <v>7</v>
       </c>
       <c r="B211" s="17" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="212" ht="31" hidden="1" spans="2:4">
       <c r="B212" s="15"/>
       <c r="C212" s="13"/>
       <c r="D212" s="13" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="213" hidden="1" spans="2:2">
@@ -12443,14 +12475,14 @@
       <c r="B214" s="15"/>
       <c r="C214" s="14"/>
       <c r="D214" s="14" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
     </row>
     <row r="215" ht="31" hidden="1" spans="2:4">
       <c r="B215" s="15"/>
       <c r="C215" s="13"/>
       <c r="D215" s="13" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="216" hidden="1" spans="2:4">
@@ -12462,7 +12494,7 @@
       <c r="B217" s="15"/>
       <c r="C217" s="9"/>
       <c r="D217" s="9" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="218" hidden="1" spans="2:4">
@@ -12474,14 +12506,14 @@
       <c r="B219" s="15"/>
       <c r="C219" s="9"/>
       <c r="D219" s="9" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="220" hidden="1" spans="2:4">
       <c r="B220" s="15"/>
       <c r="C220" s="9"/>
       <c r="D220" s="9" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="221" hidden="1" spans="2:4">
@@ -12493,21 +12525,21 @@
       <c r="B222" s="15"/>
       <c r="C222" s="9"/>
       <c r="D222" s="9" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="223" hidden="1" spans="2:4">
       <c r="B223" s="15"/>
       <c r="C223" s="9"/>
       <c r="D223" s="9" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="224" hidden="1" spans="2:4">
       <c r="B224" s="15"/>
       <c r="C224" s="9"/>
       <c r="D224" s="9" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="225" hidden="1" spans="2:4">
@@ -12519,14 +12551,14 @@
       <c r="B226" s="15"/>
       <c r="C226" s="9"/>
       <c r="D226" s="9" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="227" hidden="1" spans="2:4">
       <c r="B227" s="15"/>
       <c r="C227" s="9"/>
       <c r="D227" s="9" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="228" hidden="1" spans="2:4">
@@ -12538,14 +12570,14 @@
       <c r="B229" s="15"/>
       <c r="C229" s="9"/>
       <c r="D229" s="9" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="230" hidden="1" spans="2:4">
       <c r="B230" s="15"/>
       <c r="C230" s="9"/>
       <c r="D230" s="9" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="231" hidden="1" spans="2:4">
@@ -12558,14 +12590,14 @@
         <v>8</v>
       </c>
       <c r="B232" s="17" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="233" hidden="1" spans="2:4">
       <c r="B233" s="15"/>
       <c r="C233" s="13"/>
       <c r="D233" s="13" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="234" hidden="1" spans="2:2">
@@ -12575,14 +12607,14 @@
       <c r="B235" s="16"/>
       <c r="C235" s="14"/>
       <c r="D235" s="14" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
     </row>
     <row r="236" ht="31" hidden="1" spans="2:4">
       <c r="B236" s="16"/>
       <c r="C236" s="19"/>
       <c r="D236" s="19" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="237" hidden="1" spans="2:4">
@@ -12594,14 +12626,14 @@
       <c r="B238" s="16"/>
       <c r="C238" s="9"/>
       <c r="D238" s="9" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="239" hidden="1" spans="2:4">
       <c r="B239" s="16"/>
       <c r="C239" s="9"/>
       <c r="D239" s="9" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="240" hidden="1" spans="2:4">
@@ -12613,14 +12645,14 @@
       <c r="B241" s="16"/>
       <c r="C241" s="9"/>
       <c r="D241" s="9" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="242" hidden="1" spans="2:4">
       <c r="B242" s="16"/>
       <c r="C242" s="9"/>
       <c r="D242" s="9" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="243" hidden="1" spans="2:4">
@@ -12632,14 +12664,14 @@
       <c r="B244" s="16"/>
       <c r="C244" s="9"/>
       <c r="D244" s="9" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="245" hidden="1" spans="2:4">
       <c r="B245" s="16"/>
       <c r="C245" s="9"/>
       <c r="D245" s="9" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="246" hidden="1" spans="2:4">
@@ -12651,14 +12683,14 @@
       <c r="B247" s="16"/>
       <c r="C247" s="9"/>
       <c r="D247" s="9" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="248" hidden="1" spans="2:4">
       <c r="B248" s="16"/>
       <c r="C248" s="9"/>
       <c r="D248" s="9" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="249" hidden="1" spans="2:4">
@@ -12670,14 +12702,14 @@
       <c r="B250" s="16"/>
       <c r="C250" s="9"/>
       <c r="D250" s="9" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="251" hidden="1" spans="2:4">
       <c r="B251" s="16"/>
       <c r="C251" s="9"/>
       <c r="D251" s="9" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="252" hidden="1" spans="2:4">
@@ -12689,14 +12721,14 @@
       <c r="B253" s="16"/>
       <c r="C253" s="9"/>
       <c r="D253" s="9" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="254" hidden="1" spans="2:4">
       <c r="B254" s="16"/>
       <c r="C254" s="9"/>
       <c r="D254" s="9" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="255" hidden="1" spans="2:4">
@@ -12708,14 +12740,14 @@
       <c r="B256" s="16"/>
       <c r="C256" s="9"/>
       <c r="D256" s="9" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
     </row>
     <row r="257" hidden="1" spans="2:4">
       <c r="B257" s="16"/>
       <c r="C257" s="9"/>
       <c r="D257" s="9" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
     </row>
     <row r="258" spans="2:4">
@@ -12731,7 +12763,7 @@
     </row>
     <row r="260" spans="1:4">
       <c r="A260" s="2" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="B260" s="16"/>
       <c r="C260" s="9"/>
@@ -12739,20 +12771,20 @@
     </row>
     <row r="261" spans="1:1">
       <c r="A261" s="2" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="262" spans="1:2">
       <c r="A262" s="2"/>
       <c r="B262" s="2" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="263" spans="1:3">
       <c r="A263" s="2"/>
       <c r="B263" s="2"/>
       <c r="C263" s="2" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="264" ht="31" spans="1:4">
@@ -12760,7 +12792,7 @@
       <c r="B264" s="2"/>
       <c r="C264" s="8"/>
       <c r="D264" s="8" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="265" spans="1:4">
@@ -12768,7 +12800,7 @@
       <c r="B265" s="2"/>
       <c r="C265" s="8"/>
       <c r="D265" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="266" spans="1:4">
@@ -12776,7 +12808,7 @@
       <c r="B266" s="2"/>
       <c r="C266" s="8"/>
       <c r="D266" s="8" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="267" spans="1:4">
@@ -12784,7 +12816,7 @@
       <c r="B267" s="2"/>
       <c r="C267" s="8"/>
       <c r="D267" s="8" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -12792,7 +12824,7 @@
       <c r="B268" s="2"/>
       <c r="C268" s="8"/>
       <c r="D268" s="8" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="269" spans="1:4">
@@ -12800,7 +12832,7 @@
       <c r="B269" s="2"/>
       <c r="C269" s="8"/>
       <c r="D269" s="8" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="270" spans="1:4">
@@ -12808,7 +12840,7 @@
       <c r="B270" s="2"/>
       <c r="C270" s="8"/>
       <c r="D270" s="1" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="271" spans="1:4">
@@ -12828,7 +12860,7 @@
       <c r="B273" s="2"/>
       <c r="C273" s="8"/>
       <c r="D273" s="8" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="274" spans="1:4">
@@ -12836,7 +12868,7 @@
       <c r="B274" s="2"/>
       <c r="C274" s="20"/>
       <c r="D274" s="20" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="275" spans="1:4">
@@ -12844,19 +12876,19 @@
       <c r="B275" s="2"/>
       <c r="C275" s="20"/>
       <c r="D275" s="20" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="276" spans="1:2">
       <c r="A276" s="2"/>
       <c r="B276" s="2" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="277" spans="1:2">
       <c r="A277" s="2"/>
       <c r="B277" s="2" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="278" spans="1:1">
@@ -12864,18 +12896,18 @@
     </row>
     <row r="279" spans="1:1">
       <c r="A279" s="2" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="280" spans="2:2">
       <c r="B280" s="2" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="281" spans="1:2">
       <c r="A281" s="2"/>
       <c r="B281" s="1" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="282" spans="1:1">
@@ -12884,13 +12916,13 @@
     <row r="283" spans="1:2">
       <c r="A283" s="2"/>
       <c r="B283" s="1" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="284" spans="1:2">
       <c r="A284" s="2"/>
       <c r="B284" s="1" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="285" spans="1:1">
@@ -12899,13 +12931,13 @@
     <row r="286" spans="1:2">
       <c r="A286" s="2"/>
       <c r="B286" s="1" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="287" spans="1:2">
       <c r="A287" s="2"/>
       <c r="B287" s="1" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="288" spans="1:1">
@@ -12913,17 +12945,17 @@
     </row>
     <row r="289" spans="1:1">
       <c r="A289" s="2" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="290" spans="2:2">
       <c r="B290" s="1" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="292" spans="1:1">
       <c r="A292" s="1" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
     </row>
   </sheetData>
@@ -12985,7 +13017,7 @@
         <v>59</v>
       </c>
       <c r="B3" s="79"/>
-      <c r="C3" s="86"/>
+      <c r="C3" s="85"/>
       <c r="D3" s="22"/>
       <c r="E3" s="22"/>
       <c r="F3" s="22"/>
@@ -12996,7 +13028,7 @@
     <row r="4" spans="1:9">
       <c r="A4" s="79"/>
       <c r="B4" s="79"/>
-      <c r="C4" s="86"/>
+      <c r="C4" s="85"/>
       <c r="D4" s="22"/>
       <c r="E4" s="22"/>
       <c r="F4" s="22"/>
@@ -13007,7 +13039,7 @@
     <row r="5" spans="1:9">
       <c r="A5" s="79"/>
       <c r="B5" s="79"/>
-      <c r="C5" s="86" t="s">
+      <c r="C5" s="85" t="s">
         <v>60</v>
       </c>
       <c r="D5" s="22"/>
@@ -13020,7 +13052,7 @@
     <row r="6" spans="1:9">
       <c r="A6" s="79"/>
       <c r="B6" s="79"/>
-      <c r="C6" s="86"/>
+      <c r="C6" s="85"/>
       <c r="D6" s="79" t="s">
         <v>61</v>
       </c>
@@ -13033,7 +13065,7 @@
     <row r="7" spans="1:9">
       <c r="A7" s="79"/>
       <c r="B7" s="79"/>
-      <c r="C7" s="86"/>
+      <c r="C7" s="85"/>
       <c r="D7" s="22"/>
       <c r="E7" s="22"/>
       <c r="F7" s="22"/>
@@ -13044,7 +13076,7 @@
     <row r="8" spans="1:9">
       <c r="A8" s="79"/>
       <c r="B8" s="79"/>
-      <c r="C8" s="86"/>
+      <c r="C8" s="85"/>
       <c r="D8" s="22"/>
       <c r="E8" s="22"/>
       <c r="F8" s="22"/>
@@ -13055,7 +13087,7 @@
     <row r="9" spans="1:9">
       <c r="A9" s="79"/>
       <c r="B9" s="79"/>
-      <c r="C9" s="86" t="s">
+      <c r="C9" s="85" t="s">
         <v>62</v>
       </c>
       <c r="D9" s="22"/>
@@ -13068,7 +13100,7 @@
     <row r="10" spans="1:9">
       <c r="A10" s="79"/>
       <c r="B10" s="79"/>
-      <c r="C10" s="86"/>
+      <c r="C10" s="85"/>
       <c r="D10" s="22" t="s">
         <v>63</v>
       </c>
@@ -13081,7 +13113,7 @@
     <row r="11" spans="1:9">
       <c r="A11" s="79"/>
       <c r="B11" s="79"/>
-      <c r="C11" s="86"/>
+      <c r="C11" s="85"/>
       <c r="D11" s="22" t="s">
         <v>64</v>
       </c>
@@ -13097,7 +13129,7 @@
       <c r="A12" s="81" t="s">
         <v>66</v>
       </c>
-      <c r="C12" s="86"/>
+      <c r="C12" s="85"/>
       <c r="D12" s="22" t="s">
         <v>67</v>
       </c>
@@ -13110,7 +13142,7 @@
     <row r="13" spans="1:9">
       <c r="A13" s="79"/>
       <c r="B13" s="79"/>
-      <c r="C13" s="86"/>
+      <c r="C13" s="85"/>
       <c r="D13" s="22"/>
       <c r="E13" s="22"/>
       <c r="F13" s="22"/>
@@ -13121,7 +13153,7 @@
     <row r="14" spans="1:9">
       <c r="A14" s="79"/>
       <c r="B14" s="79"/>
-      <c r="C14" s="86"/>
+      <c r="C14" s="85"/>
       <c r="D14" s="22"/>
       <c r="E14" s="22"/>
       <c r="F14" s="22"/>
@@ -13134,7 +13166,7 @@
       <c r="B15" s="79" t="s">
         <v>68</v>
       </c>
-      <c r="C15" s="86"/>
+      <c r="C15" s="85"/>
       <c r="D15" s="22" t="s">
         <v>69</v>
       </c>
@@ -13147,7 +13179,7 @@
     <row r="16" spans="1:9">
       <c r="A16" s="79"/>
       <c r="B16" s="79"/>
-      <c r="C16" s="86"/>
+      <c r="C16" s="85"/>
       <c r="D16" s="22"/>
       <c r="E16" s="22"/>
       <c r="F16" s="22"/>
@@ -13158,7 +13190,7 @@
     <row r="17" spans="1:9">
       <c r="A17" s="79"/>
       <c r="B17" s="79"/>
-      <c r="C17" s="86"/>
+      <c r="C17" s="85"/>
       <c r="D17" s="22" t="s">
         <v>70</v>
       </c>
@@ -13171,7 +13203,7 @@
     <row r="18" spans="1:9">
       <c r="A18" s="79"/>
       <c r="B18" s="79"/>
-      <c r="C18" s="86"/>
+      <c r="C18" s="85"/>
       <c r="D18" s="22"/>
       <c r="E18" s="22" t="s">
         <v>71</v>
@@ -13184,7 +13216,7 @@
     <row r="19" ht="238" spans="1:9">
       <c r="A19" s="79"/>
       <c r="B19" s="79"/>
-      <c r="C19" s="86"/>
+      <c r="C19" s="85"/>
       <c r="D19" s="22"/>
       <c r="E19" s="22"/>
       <c r="F19" s="25" t="s">
@@ -13197,7 +13229,7 @@
     <row r="20" spans="1:9">
       <c r="A20" s="79"/>
       <c r="B20" s="79"/>
-      <c r="C20" s="86"/>
+      <c r="C20" s="85"/>
       <c r="D20" s="22" t="s">
         <v>73</v>
       </c>
@@ -13210,7 +13242,7 @@
     <row r="21" spans="1:9">
       <c r="A21" s="79"/>
       <c r="B21" s="79"/>
-      <c r="C21" s="86"/>
+      <c r="C21" s="85"/>
       <c r="D21" s="22"/>
       <c r="E21" s="22"/>
       <c r="F21" s="22"/>
@@ -13221,7 +13253,7 @@
     <row r="22" spans="1:9">
       <c r="A22" s="79"/>
       <c r="B22" s="79"/>
-      <c r="C22" s="86"/>
+      <c r="C22" s="85"/>
       <c r="D22" s="22" t="s">
         <v>74</v>
       </c>
@@ -13236,7 +13268,7 @@
     <row r="23" spans="1:9">
       <c r="A23" s="79"/>
       <c r="B23" s="79"/>
-      <c r="C23" s="86"/>
+      <c r="C23" s="85"/>
       <c r="D23" s="22"/>
       <c r="E23" s="22"/>
       <c r="F23" s="22" t="s">
@@ -13249,7 +13281,7 @@
     <row r="24" spans="1:9">
       <c r="A24" s="79"/>
       <c r="B24" s="79"/>
-      <c r="C24" s="86"/>
+      <c r="C24" s="85"/>
       <c r="D24" s="22"/>
       <c r="E24" s="22"/>
       <c r="F24" s="22"/>
@@ -13260,7 +13292,7 @@
     <row r="25" spans="1:9">
       <c r="A25" s="79"/>
       <c r="B25" s="79"/>
-      <c r="C25" s="86"/>
+      <c r="C25" s="85"/>
       <c r="D25" s="22"/>
       <c r="E25" s="22"/>
       <c r="F25" s="22"/>
@@ -13271,7 +13303,7 @@
     <row r="26" spans="1:9">
       <c r="A26" s="79"/>
       <c r="B26" s="79"/>
-      <c r="C26" s="86"/>
+      <c r="C26" s="85"/>
       <c r="D26" s="22"/>
       <c r="E26" s="22"/>
       <c r="F26" s="22"/>
@@ -13282,7 +13314,7 @@
     <row r="27" spans="1:9">
       <c r="A27" s="79"/>
       <c r="B27" s="79"/>
-      <c r="C27" s="86" t="s">
+      <c r="C27" s="85" t="s">
         <v>77</v>
       </c>
       <c r="D27" s="22"/>
@@ -13295,7 +13327,7 @@
     <row r="28" spans="1:9">
       <c r="A28" s="79"/>
       <c r="B28" s="79"/>
-      <c r="C28" s="86"/>
+      <c r="C28" s="85"/>
       <c r="D28" s="22" t="s">
         <v>78</v>
       </c>
@@ -13499,7 +13531,7 @@
       </c>
     </row>
     <row r="50" spans="3:3">
-      <c r="C50" s="87" t="s">
+      <c r="C50" s="86" t="s">
         <v>95</v>
       </c>
     </row>
@@ -13790,9 +13822,14 @@
         <v>122</v>
       </c>
     </row>
+    <row r="36" spans="6:6">
+      <c r="F36" s="65" t="s">
+        <v>123</v>
+      </c>
+    </row>
     <row r="37" spans="6:6">
       <c r="F37" s="65" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="39" spans="4:4">
@@ -13808,7 +13845,7 @@
     </row>
     <row r="42" spans="4:4">
       <c r="D42" s="66" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="43" spans="4:4">
@@ -13816,7 +13853,7 @@
     </row>
     <row r="44" spans="4:4">
       <c r="D44" s="66" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="45" spans="4:4">
@@ -13824,91 +13861,91 @@
     </row>
     <row r="46" spans="4:4">
       <c r="D46" s="66" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="47" spans="5:5">
       <c r="E47" s="65" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="48" spans="6:6">
       <c r="F48" s="65" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="49" spans="5:5">
       <c r="E49" s="65" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="50" spans="6:6">
       <c r="F50" s="65" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="65" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F51" s="65" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="65" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F52" s="65" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="65" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F53" s="65" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="55" spans="5:5">
       <c r="E55" s="65" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="56" spans="6:6">
       <c r="F56" s="65" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="58" spans="5:5">
       <c r="E58" s="65" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="60" spans="5:5">
       <c r="E60" s="65" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="61" spans="6:6">
       <c r="F61" s="65" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="63" spans="5:5">
       <c r="E63" s="65" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="64" spans="6:6">
       <c r="F64" s="65" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="65" spans="5:5">
       <c r="E65" s="65" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="66" ht="15.5" spans="4:4">
@@ -13916,1131 +13953,1076 @@
     </row>
     <row r="67" spans="5:5">
       <c r="E67" s="65" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="68" spans="6:6">
       <c r="F68" s="65" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="69" spans="6:6">
       <c r="F69" s="65" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="71" spans="5:5">
       <c r="E71" s="65" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="72" spans="6:6">
       <c r="F72" s="65" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="73" spans="5:5">
       <c r="E73" s="65" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="75" spans="5:5">
       <c r="E75" s="65" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="76" spans="6:6">
       <c r="F76" s="65" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="79" spans="5:5">
       <c r="E79" s="65" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="65" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F80" s="65" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="81" spans="6:6">
       <c r="F81" s="65" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="82" spans="6:6">
       <c r="F82" s="65" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="83" spans="6:6">
       <c r="F83" s="65" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="65" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F84" s="65" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="85" spans="6:6">
       <c r="F85" s="65" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="86" spans="6:6">
       <c r="F86" s="65" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="87" spans="6:6">
       <c r="F87" s="65" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="90" spans="5:5">
       <c r="E90" s="65" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="91" spans="6:6">
       <c r="F91" s="65" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="93" spans="5:5">
       <c r="E93" s="65" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="94" spans="6:6">
       <c r="F94" s="65" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="96" spans="5:5">
       <c r="E96" s="65" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="97" spans="6:6">
       <c r="F97" s="65" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="98" spans="5:5">
       <c r="E98" s="65" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="100" spans="5:5">
       <c r="E100" s="65" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="103" spans="4:4">
       <c r="D103" s="65" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="104" spans="6:6">
       <c r="F104" s="65" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="105" spans="6:6">
       <c r="F105" s="65" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="107" spans="4:4">
       <c r="D107" s="65" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="108" spans="6:6">
       <c r="F108" s="65" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="110" spans="4:4">
       <c r="D110" s="65" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="111" spans="6:6">
       <c r="F111" s="65" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="112" spans="6:6">
       <c r="F112" s="65" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114" s="65" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C114" s="66" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="65" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D115" s="65" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="65" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D116" s="65" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="65" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D117" s="65" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="65" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D118" s="65" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="65" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D120" s="65" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
       <c r="A121" s="65" t="s">
-        <v>191</v>
-      </c>
-      <c r="D121" s="85"/>
-    </row>
-    <row r="122" spans="1:4">
-      <c r="A122" s="85"/>
-      <c r="D122" s="85"/>
+        <v>192</v>
+      </c>
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="65" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D123" s="65" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="65" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D124" s="65" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="65" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D125" s="65" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
       <c r="A126" s="65" t="s">
-        <v>198</v>
-      </c>
-      <c r="D126" s="85"/>
-    </row>
-    <row r="127" spans="1:4">
-      <c r="A127" s="85"/>
-      <c r="D127" s="85"/>
+        <v>199</v>
+      </c>
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="65" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D128" s="65" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1">
       <c r="A129" s="65" t="s">
-        <v>201</v>
-      </c>
-      <c r="D129" s="85"/>
-    </row>
-    <row r="130" spans="1:4">
-      <c r="A130" s="85"/>
-      <c r="D130" s="85"/>
+        <v>202</v>
+      </c>
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="65" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D131" s="65" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="65" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D132" s="65" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="65" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D133" s="65" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="65" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D134" s="65" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="65" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D135" s="65" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="65" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D136" s="65" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="65" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D137" s="65" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="65" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D138" s="65" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="65" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D139" s="65" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="65" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D140" s="65" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="65" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D141" s="65" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="65" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D142" s="65" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="143" spans="1:4">
       <c r="A143" s="65" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D143" s="65" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="65" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D144" s="65" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="65" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D145" s="65" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="65" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D146" s="65" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="65" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D147" s="65" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="65" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D148" s="65" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="65" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D149" s="65" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="65" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D150" s="65" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="151" spans="1:4">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1">
       <c r="A151" s="65" t="s">
-        <v>242</v>
-      </c>
-      <c r="D151" s="85"/>
-    </row>
-    <row r="152" spans="1:4">
-      <c r="A152" s="85"/>
-      <c r="D152" s="85"/>
+        <v>243</v>
+      </c>
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="65" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D153" s="65" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="154" spans="1:4">
       <c r="A154" s="65" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D154" s="65" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="155" spans="1:4">
       <c r="A155" s="65" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D155" s="65" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="156" spans="1:4">
       <c r="A156" s="65" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D156" s="65" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="157" spans="1:4">
       <c r="A157" s="65" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D157" s="65" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="158" spans="1:4">
       <c r="A158" s="65" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D158" s="65" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="65" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D159" s="65" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="160" spans="1:4">
       <c r="A160" s="65" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D160" s="65" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="161" spans="1:4">
       <c r="A161" s="65" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D161" s="65" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="162" spans="1:4">
       <c r="A162" s="65" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D162" s="65" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="163" spans="1:4">
       <c r="A163" s="65" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D163" s="65" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="65" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D164" s="65" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="165" spans="1:4">
       <c r="A165" s="65" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D165" s="65" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="166" spans="1:4">
       <c r="A166" s="65" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D166" s="65" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="167" spans="1:4">
       <c r="A167" s="65" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D167" s="65" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="168" spans="1:4">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1">
       <c r="A168" s="65" t="s">
-        <v>242</v>
-      </c>
-      <c r="D168" s="85"/>
-    </row>
-    <row r="169" spans="1:4">
-      <c r="A169" s="85"/>
-      <c r="D169" s="85"/>
+        <v>243</v>
+      </c>
     </row>
     <row r="170" spans="1:4">
       <c r="A170" s="65" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D170" s="65" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="171" spans="1:4">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1">
       <c r="A171" s="65" t="s">
-        <v>275</v>
-      </c>
-      <c r="D171" s="85"/>
-    </row>
-    <row r="172" spans="1:4">
-      <c r="A172" s="85"/>
-      <c r="D172" s="85"/>
+        <v>276</v>
+      </c>
     </row>
     <row r="173" spans="1:4">
       <c r="A173" s="65" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D173" s="65" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="174" spans="1:4">
       <c r="A174" s="65" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D174" s="65" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="175" spans="1:4">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1">
       <c r="A175" s="65" t="s">
-        <v>242</v>
-      </c>
-      <c r="D175" s="85"/>
-    </row>
-    <row r="176" spans="1:4">
-      <c r="A176" s="85"/>
-      <c r="D176" s="85"/>
+        <v>243</v>
+      </c>
     </row>
     <row r="177" spans="1:4">
       <c r="A177" s="65" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D177" s="65" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="178" spans="1:4">
       <c r="A178" s="65" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D178" s="65" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="179" spans="1:4">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1">
       <c r="A179" s="65" t="s">
-        <v>284</v>
-      </c>
-      <c r="D179" s="85"/>
-    </row>
-    <row r="180" spans="1:4">
-      <c r="A180" s="85"/>
-      <c r="D180" s="85"/>
+        <v>285</v>
+      </c>
     </row>
     <row r="181" spans="1:4">
       <c r="A181" s="65" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D181" s="65" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="182" spans="1:4">
       <c r="A182" s="65" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D182" s="65" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="183" spans="1:4">
       <c r="A183" s="65" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D183" s="65" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="184" spans="1:4">
       <c r="A184" s="65" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D184" s="65" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="185" spans="1:4">
       <c r="A185" s="65" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D185" s="65" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="186" spans="1:4">
       <c r="A186" s="65" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D186" s="65" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="187" spans="1:4">
       <c r="A187" s="65" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D187" s="65" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="188" spans="1:4">
       <c r="A188" s="65" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D188" s="65" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="189" spans="1:4">
       <c r="A189" s="65" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D189" s="65" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="190" spans="1:4">
       <c r="A190" s="65" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D190" s="65" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="191" spans="1:4">
       <c r="A191" s="65" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D191" s="65" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="192" spans="1:4">
       <c r="A192" s="65" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D192" s="65" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="193" spans="1:4">
       <c r="A193" s="65" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D193" s="65" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="194" spans="1:4">
       <c r="A194" s="65" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D194" s="65" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="195" spans="1:4">
       <c r="A195" s="65" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D195" s="65" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="196" spans="1:4">
       <c r="A196" s="65" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D196" s="65" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="197" spans="1:4">
       <c r="A197" s="65" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D197" s="65" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="198" spans="1:4">
       <c r="A198" s="65" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D198" s="65" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="199" spans="1:4">
       <c r="A199" s="65" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D199" s="65" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="200" spans="1:4">
       <c r="A200" s="65" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D200" s="65" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="201" spans="1:4">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1">
       <c r="A201" s="65" t="s">
-        <v>242</v>
-      </c>
-      <c r="D201" s="85"/>
-    </row>
-    <row r="202" spans="1:4">
-      <c r="A202" s="85"/>
-      <c r="D202" s="85"/>
+        <v>243</v>
+      </c>
     </row>
     <row r="203" spans="1:4">
       <c r="A203" s="65" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D203" s="65" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="204" spans="1:4">
       <c r="A204" s="65" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D204" s="65" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="205" spans="1:4">
       <c r="A205" s="65" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D205" s="65" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="206" spans="1:4">
       <c r="A206" s="65" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D206" s="65" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="207" spans="1:4">
       <c r="A207" s="65" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D207" s="65" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="208" spans="1:4">
       <c r="A208" s="65" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D208" s="65" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="209" spans="1:4">
       <c r="A209" s="65" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D209" s="65" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="210" spans="1:4">
       <c r="A210" s="65" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D210" s="65" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="211" spans="1:4">
       <c r="A211" s="65" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D211" s="65" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="212" spans="1:4">
       <c r="A212" s="65" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D212" s="65" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="213" spans="1:4">
       <c r="A213" s="65" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D213" s="65" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="214" spans="1:4">
       <c r="A214" s="65" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D214" s="65" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="215" spans="1:4">
       <c r="A215" s="65" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D215" s="65" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="216" spans="1:4">
       <c r="A216" s="65" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D216" s="65" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="217" spans="1:4">
       <c r="A217" s="65" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D217" s="65" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="218" spans="1:4">
       <c r="A218" s="65" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D218" s="65" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="219" spans="1:4">
       <c r="A219" s="65" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D219" s="65" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="220" spans="1:4">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1">
       <c r="A220" s="65" t="s">
-        <v>355</v>
-      </c>
-      <c r="D220" s="85"/>
-    </row>
-    <row r="221" spans="1:4">
-      <c r="A221" s="85"/>
-      <c r="D221" s="85"/>
+        <v>356</v>
+      </c>
     </row>
     <row r="222" spans="1:4">
       <c r="A222" s="65" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D222" s="65" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="223" spans="1:4">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1">
       <c r="A223" s="65" t="s">
-        <v>358</v>
-      </c>
-      <c r="D223" s="85"/>
-    </row>
-    <row r="224" spans="1:4">
-      <c r="A224" s="85"/>
-      <c r="D224" s="85"/>
+        <v>359</v>
+      </c>
     </row>
     <row r="225" spans="1:4">
       <c r="A225" s="65" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D225" s="65" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="226" spans="1:4">
       <c r="A226" s="65" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D226" s="65" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="227" spans="1:4">
       <c r="A227" s="65" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D227" s="65" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="228" spans="1:4">
       <c r="A228" s="65" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D228" s="65" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="229" spans="1:4">
       <c r="A229" s="65" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D229" s="65" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="230" spans="1:4">
       <c r="A230" s="65" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D230" s="65" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="231" spans="1:4">
       <c r="A231" s="65" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D231" s="65" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="232" spans="1:4">
       <c r="A232" s="65" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D232" s="65" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="233" spans="1:4">
       <c r="A233" s="65" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D233" s="65" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="234" spans="1:4">
       <c r="A234" s="65" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D234" s="65" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="235" spans="1:4">
       <c r="A235" s="65" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D235" s="65" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="236" spans="1:4">
       <c r="A236" s="65" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D236" s="65" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="237" spans="1:4">
       <c r="A237" s="65" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D237" s="65" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="238" spans="1:4">
       <c r="A238" s="65" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D238" s="65" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="239" spans="1:4">
       <c r="A239" s="65" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D239" s="65" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="240" spans="1:4">
       <c r="A240" s="65" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D240" s="65" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="241" spans="1:4">
       <c r="A241" s="65" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D241" s="65" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="242" spans="1:4">
       <c r="A242" s="65" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D242" s="65" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="243" spans="1:1">
@@ -15048,42 +15030,42 @@
     </row>
     <row r="260" spans="1:3">
       <c r="A260" s="65" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C260" s="66" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="262" spans="1:3">
       <c r="A262" s="65" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C262" s="66" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="264" spans="1:3">
       <c r="A264" s="65" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C264" s="66" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="266" spans="1:3">
       <c r="A266" s="65" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C266" s="66" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="268" spans="1:3">
       <c r="A268" s="65" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C268" s="66" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
   </sheetData>
@@ -15157,132 +15139,132 @@
   <sheetData>
     <row r="2" ht="37" customHeight="1" spans="1:6">
       <c r="A2" s="70" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B2" s="70" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C2" s="70" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D2" s="70" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E2" s="70" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F2" s="70" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="3" ht="28" spans="1:6">
       <c r="A3" s="71" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B3" s="71" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C3" s="71" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D3" s="71" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E3" s="71" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F3" s="71" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="4" ht="28" spans="1:6">
       <c r="A4" s="71" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B4" s="71" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C4" s="71" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D4" s="71" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E4" s="71" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F4" s="71" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="5" ht="28" spans="1:6">
       <c r="A5" s="71" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B5" s="71" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C5" s="71" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D5" s="71" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E5" s="71" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F5" s="71" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="6" ht="28" spans="1:6">
       <c r="A6" s="71" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B6" s="71" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C6" s="71" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D6" s="71" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E6" s="71" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F6" s="71" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="7" ht="28" spans="1:6">
       <c r="A7" s="71" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B7" s="71" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C7" s="71" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D7" s="71" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E7" s="71" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F7" s="71" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="72" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:6">
       <c r="A10" s="73" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B10" s="73"/>
       <c r="C10" s="73"/>
@@ -15292,7 +15274,7 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="74" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B11" s="74"/>
       <c r="C11" s="74"/>
@@ -15302,7 +15284,7 @@
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:6">
       <c r="A12" s="75" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B12" s="75"/>
       <c r="C12" s="75"/>
@@ -15312,7 +15294,7 @@
     </row>
     <row r="13" ht="28" customHeight="1" spans="1:6">
       <c r="A13" s="75" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B13" s="75"/>
       <c r="C13" s="75"/>
@@ -15322,12 +15304,12 @@
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="72" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="16" ht="43" customHeight="1" spans="1:6">
       <c r="A16" s="76" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B16" s="76"/>
       <c r="C16" s="76"/>
@@ -15337,27 +15319,27 @@
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="69" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="77" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="69" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="69" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="23" ht="32" customHeight="1" spans="1:6">
       <c r="A23" s="78" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B23" s="78"/>
       <c r="C23" s="78"/>
@@ -15378,7 +15360,7 @@
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="79" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B26" s="79"/>
       <c r="C26" s="80"/>
@@ -15391,7 +15373,7 @@
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="79" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B27" s="79"/>
       <c r="C27" s="80"/>
@@ -15404,13 +15386,13 @@
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="80" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B28" s="80" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C28" s="80" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D28" s="79"/>
       <c r="E28" s="79"/>
@@ -15423,12 +15405,12 @@
       <c r="A29" s="80"/>
       <c r="B29" s="80"/>
       <c r="C29" s="80" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D29" s="79"/>
       <c r="E29" s="79"/>
       <c r="F29" s="79" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="G29" s="79"/>
       <c r="H29" s="79"/>
@@ -15436,32 +15418,32 @@
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="79" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B30" s="79" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C30" s="80" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D30" s="79"/>
       <c r="E30" s="79"/>
       <c r="F30" s="79"/>
       <c r="G30" s="79" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H30" s="79"/>
       <c r="I30" s="79"/>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="81" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B31" s="79"/>
       <c r="C31" s="80"/>
       <c r="D31" s="79"/>
       <c r="E31" s="80" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="F31" s="79"/>
       <c r="G31" s="79"/>
@@ -15470,40 +15452,40 @@
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="79" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B32" s="79" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C32" s="80" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D32" s="79"/>
       <c r="E32" s="79"/>
       <c r="F32" s="79"/>
       <c r="G32" s="82" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H32" s="79"/>
       <c r="I32" s="79"/>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="79" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B33" s="79" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C33" s="80" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D33" s="79"/>
       <c r="E33" s="79"/>
       <c r="F33" s="79" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="G33" s="79" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H33" s="79"/>
       <c r="I33" s="79"/>
@@ -15512,7 +15494,7 @@
       <c r="A34" s="79"/>
       <c r="B34" s="79"/>
       <c r="C34" s="80" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D34" s="79"/>
       <c r="E34" s="79"/>
@@ -15525,7 +15507,7 @@
       <c r="A35" s="79"/>
       <c r="B35" s="79"/>
       <c r="C35" s="80" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D35" s="79"/>
       <c r="E35" s="79"/>
@@ -15547,21 +15529,21 @@
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="79" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B37" s="79" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C37" s="80" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D37" s="79"/>
       <c r="E37" s="79"/>
       <c r="F37" s="79" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="G37" s="79" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H37" s="79"/>
       <c r="I37" s="79"/>
@@ -15570,7 +15552,7 @@
       <c r="A38" s="79"/>
       <c r="B38" s="79"/>
       <c r="C38" s="80" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D38" s="79"/>
       <c r="E38" s="79"/>
@@ -15581,7 +15563,7 @@
     </row>
     <row r="39" spans="1:9">
       <c r="A39" s="79" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B39" s="79"/>
       <c r="C39" s="80"/>
@@ -15594,7 +15576,7 @@
     </row>
     <row r="40" spans="1:9">
       <c r="A40" s="79" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B40" s="79"/>
       <c r="C40" s="80"/>
@@ -15632,7 +15614,7 @@
       <c r="B43" s="79"/>
       <c r="C43" s="80"/>
       <c r="D43" s="80" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E43" s="79"/>
       <c r="F43" s="79"/>
@@ -15642,7 +15624,7 @@
     </row>
     <row r="44" spans="1:9">
       <c r="A44" s="81" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B44" s="79"/>
       <c r="C44" s="80"/>
@@ -15655,7 +15637,7 @@
     </row>
     <row r="45" spans="1:9">
       <c r="A45" s="81" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B45" s="79"/>
       <c r="C45" s="80"/>
@@ -15703,7 +15685,7 @@
       <c r="A49" s="81"/>
       <c r="B49" s="79"/>
       <c r="C49" s="83" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D49" s="79"/>
       <c r="E49" s="79"/>
@@ -15717,7 +15699,7 @@
       <c r="B50" s="79"/>
       <c r="C50" s="80"/>
       <c r="D50" s="80" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E50" s="79"/>
       <c r="F50" s="79"/>
@@ -15727,7 +15709,7 @@
     </row>
     <row r="51" spans="1:9">
       <c r="A51" s="81" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B51" s="79"/>
       <c r="C51" s="80"/>
@@ -15744,7 +15726,7 @@
       <c r="C52" s="80"/>
       <c r="D52" s="80"/>
       <c r="E52" s="79" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="F52" s="79"/>
       <c r="G52" s="79"/>
@@ -15758,7 +15740,7 @@
       <c r="D53" s="80"/>
       <c r="E53" s="79"/>
       <c r="F53" s="79" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="G53" s="79"/>
       <c r="H53" s="79"/>
@@ -15771,7 +15753,7 @@
       <c r="D54" s="80"/>
       <c r="E54" s="79"/>
       <c r="F54" s="79" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="G54" s="79"/>
       <c r="H54" s="79"/>
@@ -15779,14 +15761,14 @@
     </row>
     <row r="55" spans="1:9">
       <c r="A55" s="81" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B55" s="79"/>
       <c r="C55" s="80"/>
       <c r="D55" s="80"/>
       <c r="E55" s="79"/>
       <c r="F55" s="79" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="G55" s="79"/>
       <c r="H55" s="79"/>
@@ -15799,7 +15781,7 @@
       <c r="D56" s="80"/>
       <c r="E56" s="79"/>
       <c r="F56" s="79" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="G56" s="79"/>
       <c r="H56" s="79"/>
@@ -15808,12 +15790,12 @@
     <row r="57" spans="1:9">
       <c r="A57" s="81"/>
       <c r="B57" s="79" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C57" s="80"/>
       <c r="D57" s="80"/>
       <c r="E57" s="80" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F57" s="79"/>
       <c r="G57" s="79"/>
@@ -15826,7 +15808,7 @@
       <c r="C58" s="80"/>
       <c r="D58" s="80"/>
       <c r="E58" s="79" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="F58" s="79"/>
       <c r="G58" s="79"/>
@@ -15839,7 +15821,7 @@
       <c r="C59" s="80"/>
       <c r="D59" s="80"/>
       <c r="E59" s="79" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="F59" s="79"/>
       <c r="G59" s="79"/>
@@ -15862,7 +15844,7 @@
       <c r="B61" s="79"/>
       <c r="C61" s="80"/>
       <c r="D61" s="80" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E61" s="79"/>
       <c r="F61" s="79"/>
@@ -15872,7 +15854,7 @@
     </row>
     <row r="62" spans="1:9">
       <c r="A62" s="81" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B62" s="79"/>
       <c r="C62" s="80"/>
@@ -15885,7 +15867,7 @@
     </row>
     <row r="63" spans="1:9">
       <c r="A63" s="81" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B63" s="79"/>
       <c r="C63" s="80"/>
@@ -15975,12 +15957,12 @@
     </row>
     <row r="71" spans="1:9">
       <c r="A71" s="81" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B71" s="79"/>
       <c r="C71" s="80"/>
       <c r="D71" s="80" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E71" s="79"/>
       <c r="F71" s="79"/>
@@ -15990,13 +15972,13 @@
     </row>
     <row r="72" spans="1:9">
       <c r="A72" s="81" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B72" s="79"/>
       <c r="C72" s="80"/>
       <c r="D72" s="79"/>
       <c r="E72" s="84" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="F72" s="79"/>
       <c r="G72" s="79"/>
@@ -16005,13 +15987,13 @@
     </row>
     <row r="73" spans="1:9">
       <c r="A73" s="81" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B73" s="79"/>
       <c r="C73" s="80"/>
       <c r="D73" s="79"/>
       <c r="E73" s="84" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="F73" s="79"/>
       <c r="G73" s="79"/>
@@ -16020,7 +16002,7 @@
     </row>
     <row r="74" spans="1:9">
       <c r="A74" s="81" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B74" s="79"/>
       <c r="C74" s="80"/>
@@ -16044,7 +16026,7 @@
     </row>
     <row r="76" spans="1:9">
       <c r="A76" s="79" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B76" s="79"/>
       <c r="C76" s="80"/>
@@ -16057,7 +16039,7 @@
     </row>
     <row r="77" spans="1:9">
       <c r="A77" s="81" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B77" s="79"/>
       <c r="C77" s="80"/>
@@ -16084,7 +16066,7 @@
       <c r="B79" s="79"/>
       <c r="C79" s="80"/>
       <c r="D79" s="80" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="E79" s="79"/>
       <c r="F79" s="79"/>
@@ -16095,12 +16077,12 @@
     <row r="80" spans="1:9">
       <c r="A80" s="79"/>
       <c r="B80" s="79" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C80" s="80"/>
       <c r="D80" s="79"/>
       <c r="E80" s="79" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="F80" s="79"/>
       <c r="G80" s="79"/>
@@ -16114,7 +16096,7 @@
       <c r="D81" s="79"/>
       <c r="E81" s="79"/>
       <c r="F81" s="79" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="G81" s="79"/>
       <c r="H81" s="79"/>
@@ -16126,7 +16108,7 @@
       <c r="C82" s="80"/>
       <c r="D82" s="79"/>
       <c r="E82" s="79" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F82" s="79"/>
       <c r="G82" s="79"/>
@@ -16139,7 +16121,7 @@
       <c r="C83" s="80"/>
       <c r="D83" s="79"/>
       <c r="E83" s="79" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="F83" s="79"/>
       <c r="G83" s="79"/>
@@ -16159,7 +16141,7 @@
     </row>
     <row r="85" spans="1:9">
       <c r="A85" s="81" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B85" s="79"/>
       <c r="C85" s="80"/>
@@ -16172,7 +16154,7 @@
     </row>
     <row r="86" spans="1:9">
       <c r="A86" s="79" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B86" s="79"/>
       <c r="C86" s="80"/>
@@ -16196,12 +16178,12 @@
     </row>
     <row r="88" spans="1:9">
       <c r="A88" s="79" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B88" s="79"/>
       <c r="C88" s="80"/>
       <c r="D88" s="80" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="E88" s="79"/>
       <c r="F88" s="79"/>
@@ -16211,13 +16193,13 @@
     </row>
     <row r="89" spans="1:9">
       <c r="A89" s="80" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B89" s="79"/>
       <c r="C89" s="80"/>
       <c r="D89" s="79"/>
       <c r="E89" s="79" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F89" s="79"/>
       <c r="G89" s="79"/>
@@ -16232,7 +16214,7 @@
       <c r="C90" s="80"/>
       <c r="D90" s="79"/>
       <c r="E90" s="79" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F90" s="79"/>
       <c r="G90" s="79"/>
@@ -16241,7 +16223,7 @@
     </row>
     <row r="91" spans="1:9">
       <c r="A91" s="79" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B91" s="79"/>
       <c r="C91" s="80"/>
@@ -16254,13 +16236,13 @@
     </row>
     <row r="92" spans="1:9">
       <c r="A92" s="79" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B92" s="79"/>
       <c r="C92" s="80"/>
       <c r="D92" s="79"/>
       <c r="E92" s="79" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F92" s="79"/>
       <c r="G92" s="79"/>
@@ -16274,7 +16256,7 @@
       <c r="D93" s="79"/>
       <c r="E93" s="79"/>
       <c r="F93" s="79" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="G93" s="79"/>
       <c r="H93" s="79"/>
@@ -16296,7 +16278,7 @@
       <c r="B95" s="79"/>
       <c r="C95" s="80"/>
       <c r="D95" s="80" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="E95" s="79"/>
       <c r="F95" s="79"/>
@@ -16310,7 +16292,7 @@
       <c r="C96" s="80"/>
       <c r="D96" s="79"/>
       <c r="E96" s="79" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F96" s="79"/>
       <c r="G96" s="79"/>
@@ -16323,7 +16305,7 @@
       <c r="C97" s="80"/>
       <c r="D97" s="79"/>
       <c r="E97" s="79" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F97" s="79"/>
       <c r="G97" s="79"/>
@@ -16337,7 +16319,7 @@
       <c r="D98" s="79"/>
       <c r="E98" s="79"/>
       <c r="F98" s="79" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="G98" s="79"/>
       <c r="H98" s="79"/>
@@ -16356,7 +16338,7 @@
     </row>
     <row r="100" spans="1:9">
       <c r="A100" s="79" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B100" s="79"/>
       <c r="C100" s="80"/>
@@ -16369,7 +16351,7 @@
     </row>
     <row r="101" spans="1:9">
       <c r="A101" s="79" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B101" s="79"/>
       <c r="C101" s="80"/>
@@ -16382,7 +16364,7 @@
     </row>
     <row r="102" spans="1:9">
       <c r="A102" s="79" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B102" s="79"/>
       <c r="C102" s="80"/>
@@ -16398,7 +16380,7 @@
       <c r="B103" s="79"/>
       <c r="C103" s="80"/>
       <c r="D103" s="80" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E103" s="79"/>
       <c r="F103" s="79"/>
@@ -16419,7 +16401,7 @@
     </row>
     <row r="105" spans="1:9">
       <c r="A105" s="83" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B105" s="79"/>
       <c r="C105" s="80"/>
@@ -16433,11 +16415,11 @@
     <row r="106" spans="1:9">
       <c r="A106" s="79"/>
       <c r="B106" s="79" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C106" s="80"/>
       <c r="D106" s="80" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E106" s="79"/>
       <c r="F106" s="79"/>
@@ -16497,17 +16479,17 @@
     </row>
     <row r="4" spans="3:3">
       <c r="C4" s="66" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" s="65" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" s="65" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -16515,33 +16497,33 @@
         <v>48</v>
       </c>
       <c r="C10" s="66" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="65" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D11" s="65" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" s="65" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" s="65" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="68" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D15" s="65" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
   </sheetData>
